--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F297DB51-1EB0-4F03-8BE2-D3431FD8453F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45DFD0D-6A1B-4685-8622-4A79FB65D1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="49">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -159,6 +159,33 @@
   </si>
   <si>
     <t xml:space="preserve"> Nico AI Robot Dog </t>
+  </si>
+  <si>
+    <t>Gifts</t>
+  </si>
+  <si>
+    <t>Premium</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>Ropet</t>
+  </si>
+  <si>
+    <t>KAMOMO</t>
+  </si>
+  <si>
+    <t>Camera</t>
+  </si>
+  <si>
+    <t>Internet Access</t>
+  </si>
+  <si>
+    <t>Affiliate Agreement</t>
   </si>
 </sst>
 </file>
@@ -548,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -556,9 +583,12 @@
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
@@ -574,8 +604,23 @@
       <c r="E1" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -591,8 +636,17 @@
       <c r="E2" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -608,8 +662,17 @@
       <c r="E3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -625,8 +688,17 @@
       <c r="E4" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" t="s">
+        <v>43</v>
+      </c>
+      <c r="J4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -642,8 +714,17 @@
       <c r="E5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -659,8 +740,17 @@
       <c r="E6" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -676,8 +766,17 @@
       <c r="E7" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="J7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -693,8 +792,17 @@
       <c r="E8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -710,8 +818,17 @@
       <c r="E9" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -727,8 +844,17 @@
       <c r="E10" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -744,8 +870,17 @@
       <c r="E11" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" t="s">
+        <v>43</v>
+      </c>
+      <c r="J11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -761,8 +896,17 @@
       <c r="E12" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -778,8 +922,17 @@
       <c r="E13" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -795,8 +948,17 @@
       <c r="E14" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -812,8 +974,17 @@
       <c r="E15" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" t="s">
+        <v>43</v>
+      </c>
+      <c r="J15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -829,8 +1000,17 @@
       <c r="E16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" t="s">
+        <v>43</v>
+      </c>
+      <c r="J16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -846,8 +1026,17 @@
       <c r="E17" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -863,8 +1052,17 @@
       <c r="E18" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -880,8 +1078,17 @@
       <c r="E19" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -897,8 +1104,17 @@
       <c r="E20" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" t="s">
+        <v>43</v>
+      </c>
+      <c r="J20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -914,8 +1130,17 @@
       <c r="E21" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" t="s">
+        <v>43</v>
+      </c>
+      <c r="J21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -931,8 +1156,17 @@
       <c r="E22" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" t="s">
+        <v>43</v>
+      </c>
+      <c r="J22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -948,8 +1182,17 @@
       <c r="E23" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" t="s">
+        <v>43</v>
+      </c>
+      <c r="J23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -964,6 +1207,44 @@
       </c>
       <c r="E24" t="s">
         <v>37</v>
+      </c>
+      <c r="F24" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" t="s">
+        <v>43</v>
+      </c>
+      <c r="J24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" t="s">
+        <v>37</v>
+      </c>
+      <c r="F25" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" t="s">
+        <v>42</v>
+      </c>
+      <c r="I25" t="s">
+        <v>42</v>
+      </c>
+      <c r="J25" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F45DFD0D-6A1B-4685-8622-4A79FB65D1D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BE80A6F-E453-4235-A80D-FE01DAEF0E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="51">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -186,6 +186,12 @@
   </si>
   <si>
     <t>Affiliate Agreement</t>
+  </si>
+  <si>
+    <t>Product URL</t>
+  </si>
+  <si>
+    <t>Image URL</t>
   </si>
 </sst>
 </file>
@@ -575,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
@@ -583,12 +589,14 @@
     <col min="3" max="3" width="17.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.140625" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
@@ -611,16 +619,22 @@
         <v>41</v>
       </c>
       <c r="H1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -642,11 +656,11 @@
       <c r="G2" t="s">
         <v>43</v>
       </c>
-      <c r="J2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -668,11 +682,11 @@
       <c r="G3" t="s">
         <v>42</v>
       </c>
-      <c r="J3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -694,11 +708,11 @@
       <c r="G4" t="s">
         <v>43</v>
       </c>
-      <c r="J4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -720,11 +734,11 @@
       <c r="G5" t="s">
         <v>43</v>
       </c>
-      <c r="J5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -746,11 +760,11 @@
       <c r="G6" t="s">
         <v>43</v>
       </c>
-      <c r="J6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -772,11 +786,11 @@
       <c r="G7" t="s">
         <v>43</v>
       </c>
-      <c r="J7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1</v>
       </c>
@@ -798,11 +812,11 @@
       <c r="G8" t="s">
         <v>43</v>
       </c>
-      <c r="J8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -824,11 +838,11 @@
       <c r="G9" t="s">
         <v>43</v>
       </c>
-      <c r="J9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L9" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -850,11 +864,11 @@
       <c r="G10" t="s">
         <v>43</v>
       </c>
-      <c r="J10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -876,11 +890,11 @@
       <c r="G11" t="s">
         <v>43</v>
       </c>
-      <c r="J11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -902,11 +916,11 @@
       <c r="G12" t="s">
         <v>43</v>
       </c>
-      <c r="J12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L12" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -928,11 +942,11 @@
       <c r="G13" t="s">
         <v>43</v>
       </c>
-      <c r="J13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>23</v>
       </c>
@@ -954,11 +968,11 @@
       <c r="G14" t="s">
         <v>43</v>
       </c>
-      <c r="J14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -980,11 +994,11 @@
       <c r="G15" t="s">
         <v>43</v>
       </c>
-      <c r="J15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1006,11 +1020,11 @@
       <c r="G16" t="s">
         <v>43</v>
       </c>
-      <c r="J16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L16" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -1032,11 +1046,11 @@
       <c r="G17" t="s">
         <v>43</v>
       </c>
-      <c r="J17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1058,11 +1072,11 @@
       <c r="G18" t="s">
         <v>43</v>
       </c>
-      <c r="J18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>15</v>
       </c>
@@ -1084,11 +1098,11 @@
       <c r="G19" t="s">
         <v>43</v>
       </c>
-      <c r="J19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L19" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>15</v>
       </c>
@@ -1110,11 +1124,11 @@
       <c r="G20" t="s">
         <v>43</v>
       </c>
-      <c r="J20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L20" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>15</v>
       </c>
@@ -1136,11 +1150,11 @@
       <c r="G21" t="s">
         <v>43</v>
       </c>
-      <c r="J21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L21" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -1162,11 +1176,11 @@
       <c r="G22" t="s">
         <v>43</v>
       </c>
-      <c r="J22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>27</v>
       </c>
@@ -1188,11 +1202,11 @@
       <c r="G23" t="s">
         <v>43</v>
       </c>
-      <c r="J23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L23" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>39</v>
       </c>
@@ -1214,11 +1228,11 @@
       <c r="G24" t="s">
         <v>43</v>
       </c>
-      <c r="J24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -1237,13 +1251,13 @@
       <c r="G25" t="s">
         <v>42</v>
       </c>
-      <c r="H25" t="s">
-        <v>42</v>
-      </c>
-      <c r="I25" t="s">
-        <v>42</v>
-      </c>
       <c r="J25" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" t="s">
         <v>43</v>
       </c>
     </row>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1BE80A6F-E453-4235-A80D-FE01DAEF0E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FAC1D58-8ACB-49BE-BD67-A25D861A3B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="58">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -192,13 +192,34 @@
   </si>
   <si>
     <t>Image URL</t>
+  </si>
+  <si>
+    <t>https://joyforall.com/products/companion-pet-pup</t>
+  </si>
+  <si>
+    <t>https://joyforall.com/products/companion-cats</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/matecat-pro-hyper-realistic-bionic-cat</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/ELEPHANT-ROBOTICS-Companion-Animation-Interaction/dp/B0BY2H7W1C</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/products/ebo-air-2-plus-familybot</t>
+  </si>
+  <si>
+    <t>/images/products/Mr-Dog.png</t>
+  </si>
+  <si>
+    <t>/images/products/Sweetie-Cat.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -219,6 +240,32 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF14181F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -241,12 +288,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -262,6 +332,72 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Open file on desktop">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0742E7B-9613-530A-2FD7-41DFFB3BC4E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7991475" y="15459075"/>
+          <a:ext cx="190500" cy="190500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -581,688 +717,760 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L59"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" customWidth="1"/>
-    <col min="4" max="4" width="18.140625" customWidth="1"/>
-    <col min="5" max="5" width="15.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="2" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="8" max="8" width="52.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="32.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:12" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="E2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="E3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E4" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>42</v>
-      </c>
-      <c r="G5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="E5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" t="s">
-        <v>43</v>
-      </c>
-      <c r="L6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" t="s">
-        <v>43</v>
-      </c>
-      <c r="L7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E8" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+      <c r="E8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E9" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" t="s">
-        <v>42</v>
-      </c>
-      <c r="G9" t="s">
-        <v>43</v>
-      </c>
-      <c r="L9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="E9" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="C10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="E10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="25.5">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="C11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E11" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" t="s">
-        <v>42</v>
-      </c>
-      <c r="G11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="E11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E12" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" t="s">
-        <v>43</v>
-      </c>
-      <c r="L12" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="E12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="4"/>
+      <c r="L12" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="C13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E13" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" t="s">
-        <v>42</v>
-      </c>
-      <c r="G13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="E13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C14" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="C14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E14" t="s">
-        <v>36</v>
-      </c>
-      <c r="F14" t="s">
-        <v>42</v>
-      </c>
-      <c r="G14" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="E14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="C15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E15" t="s">
-        <v>36</v>
-      </c>
-      <c r="F15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G15" t="s">
-        <v>43</v>
-      </c>
-      <c r="L15" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
+      <c r="E15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C16" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="C16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F16" t="s">
-        <v>42</v>
-      </c>
-      <c r="G16" t="s">
-        <v>43</v>
-      </c>
-      <c r="L16" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
+      <c r="E16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="I16" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E17" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" t="s">
-        <v>43</v>
-      </c>
-      <c r="L17" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
+      <c r="E17" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="C18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" t="s">
-        <v>42</v>
-      </c>
-      <c r="G18" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="E18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H18" s="5"/>
+      <c r="I18" s="4"/>
+      <c r="L18" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="C19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" t="s">
-        <v>42</v>
-      </c>
-      <c r="G19" t="s">
-        <v>43</v>
-      </c>
-      <c r="L19" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="E19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="5"/>
+      <c r="I19" s="4"/>
+      <c r="L19" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C20" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="C20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E20" t="s">
-        <v>36</v>
-      </c>
-      <c r="F20" t="s">
-        <v>42</v>
-      </c>
-      <c r="G20" t="s">
-        <v>43</v>
-      </c>
-      <c r="L20" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="E20" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H20" s="5"/>
+      <c r="I20" s="4"/>
+      <c r="L20" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" t="s">
+      <c r="C21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" t="s">
-        <v>43</v>
-      </c>
-      <c r="L21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="E21" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="6"/>
+      <c r="L21" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C22" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="C22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F22" t="s">
-        <v>42</v>
-      </c>
-      <c r="G22" t="s">
-        <v>43</v>
-      </c>
-      <c r="L22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="F22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="C23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F23" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" t="s">
-        <v>43</v>
-      </c>
-      <c r="L23" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="F23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="L23" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="C24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F24" t="s">
-        <v>42</v>
-      </c>
-      <c r="G24" t="s">
-        <v>43</v>
-      </c>
-      <c r="L24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="F24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C25" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="C25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F25" t="s">
-        <v>42</v>
-      </c>
-      <c r="G25" t="s">
-        <v>42</v>
-      </c>
-      <c r="J25" t="s">
-        <v>42</v>
-      </c>
-      <c r="K25" t="s">
-        <v>42</v>
-      </c>
-      <c r="L25" t="s">
-        <v>43</v>
-      </c>
+      <c r="F25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="J25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="H26" s="7"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="H27" s="7"/>
+    </row>
+    <row r="38" spans="8:8">
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="8:8">
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" spans="8:8">
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="8:8">
+      <c r="H41" s="8"/>
+    </row>
+    <row r="43" spans="8:8">
+      <c r="H43" s="1"/>
+    </row>
+    <row r="49" spans="8:8">
+      <c r="H49" s="7"/>
+    </row>
+    <row r="53" spans="8:8">
+      <c r="H53" s="7"/>
+    </row>
+    <row r="59" spans="8:8">
+      <c r="H59" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A411BD-7B96-4715-8FF2-DDC38D57A7E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C888E0F-4CA0-44E4-B8DD-F673D39F6552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -326,18 +326,6 @@
     <t>Frequently Returned</t>
   </si>
   <si>
-    <t>/images/products/Chongker Percy Robot Cat.jpg</t>
-  </si>
-  <si>
-    <t>/images/products/Joy for All Companion Cat Orange Tabby</t>
-  </si>
-  <si>
-    <t>/images/products/Joy for All Companion Pet Cat Tuxedo.jpg</t>
-  </si>
-  <si>
-    <t>/images/products/Joy for All Companion Cat Silver</t>
-  </si>
-  <si>
     <t>/images/products/interactive_pet_toys.png</t>
   </si>
   <si>
@@ -423,6 +411,18 @@
   </si>
   <si>
     <t>https://www.amazon.com/s?k=furby&amp;i=toys-and-games&amp;crid=30VFFMN70W1XS&amp;sprefix=furby%2Ctoys-and-games%2C158&amp;ref=nb_sb_ss_p13n-expert-pd-ops-ranker_ci_hl-bn-left_1_5</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-for-All Companion-Cat-Silver</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-for-All-Companion-Cat-Orange-Tabby</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-for-All-Companion-Pet-Cat-Tuxedo.jpg</t>
+  </si>
+  <si>
+    <t>/images/products/Chongker-Percy-Robot-Cat.jpg</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1048,7 @@
         <v>61</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>36</v>
@@ -1080,7 +1080,7 @@
         <v>62</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>36</v>
@@ -1112,7 +1112,7 @@
         <v>63</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>36</v>
@@ -1144,7 +1144,7 @@
         <v>64</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>36</v>
@@ -1176,7 +1176,7 @@
         <v>69</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>36</v>
@@ -1208,7 +1208,7 @@
         <v>70</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>36</v>
@@ -1240,7 +1240,7 @@
         <v>65</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>36</v>
@@ -1272,7 +1272,7 @@
         <v>66</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>36</v>
@@ -1301,10 +1301,10 @@
         <v>36</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>36</v>
@@ -1333,10 +1333,10 @@
         <v>36</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>36</v>
@@ -1365,11 +1365,11 @@
         <v>36</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>36</v>
@@ -1398,10 +1398,10 @@
         <v>36</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>36</v>
@@ -1499,7 +1499,7 @@
         <v>56</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>98</v>
+        <v>124</v>
       </c>
       <c r="J16" s="4"/>
       <c r="M16" s="3" t="s">
@@ -1532,7 +1532,7 @@
         <v>60</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>96</v>
+        <v>125</v>
       </c>
       <c r="J17" s="4"/>
       <c r="M17" s="3" t="s">
@@ -1565,7 +1565,7 @@
         <v>58</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="J18" s="4"/>
       <c r="M18" s="3" t="s">
@@ -1630,7 +1630,7 @@
         <v>47</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="J20" s="4"/>
       <c r="M20" s="3" t="s">
@@ -1696,7 +1696,7 @@
         <v>49</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="J22" s="4"/>
       <c r="M22" s="3" t="s">
@@ -1729,7 +1729,7 @@
         <v>50</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="J23" s="5"/>
       <c r="M23" s="3" t="s">
@@ -1762,7 +1762,7 @@
         <v>72</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>36</v>
@@ -1788,10 +1788,10 @@
         <v>35</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>35</v>
@@ -1829,7 +1829,7 @@
         <v>75</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="30">
@@ -1858,7 +1858,7 @@
         <v>77</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="30">
@@ -1887,7 +1887,7 @@
         <v>79</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="30">
@@ -1916,7 +1916,7 @@
         <v>81</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="14.25" customHeight="1">
@@ -1945,7 +1945,7 @@
         <v>92</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="14.25" customHeight="1">
@@ -2029,7 +2029,7 @@
         <v>87</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="14.25" customHeight="1">
@@ -2058,7 +2058,7 @@
         <v>91</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="30">
@@ -2084,7 +2084,7 @@
         <v>36</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>45</v>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="36" spans="1:13" ht="30">
       <c r="A36" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>25</v>
@@ -2116,18 +2116,18 @@
         <v>36</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="30">
       <c r="A37" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>25</v>
@@ -2145,24 +2145,24 @@
         <v>35</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="30">
       <c r="A38" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>31</v>
@@ -2174,15 +2174,15 @@
         <v>35</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="30">
       <c r="B39" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>25</v>
@@ -2200,15 +2200,15 @@
         <v>36</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="30">
       <c r="A40" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="41" spans="1:13" s="9" customFormat="1" ht="150">
@@ -2242,13 +2242,13 @@
     </row>
     <row r="42" spans="1:13" s="9" customFormat="1">
       <c r="B42" s="9" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F42" s="9" t="s">
         <v>35</v>
@@ -2257,7 +2257,7 @@
         <v>35</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:13">

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C888E0F-4CA0-44E4-B8DD-F673D39F6552}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0086B07D-5CFC-404A-AA93-C508C8AC282B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -203,9 +203,6 @@
     <t>https://joyforall.com/products/companion-pet-pup?variant=37624426102967</t>
   </si>
   <si>
-    <t>ttps://joyforall.com/products/companion-pet-pup?variant=37624426070199</t>
-  </si>
-  <si>
     <t>Companion Pet Cat Silver</t>
   </si>
   <si>
@@ -413,16 +410,19 @@
     <t>https://www.amazon.com/s?k=furby&amp;i=toys-and-games&amp;crid=30VFFMN70W1XS&amp;sprefix=furby%2Ctoys-and-games%2C158&amp;ref=nb_sb_ss_p13n-expert-pd-ops-ranker_ci_hl-bn-left_1_5</t>
   </si>
   <si>
-    <t>/images/products/Joy-for-All Companion-Cat-Silver</t>
-  </si>
-  <si>
     <t>/images/products/Joy-for-All-Companion-Cat-Orange-Tabby</t>
   </si>
   <si>
-    <t>/images/products/Joy-for-All-Companion-Pet-Cat-Tuxedo.jpg</t>
-  </si>
-  <si>
     <t>/images/products/Chongker-Percy-Robot-Cat.jpg</t>
+  </si>
+  <si>
+    <t>https://joyforall.com/products/companion-pet-pup?variant=37624426070199</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-for-All-Companion-Cat-Silver</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-for-All-Companion-Cat-Tuxedo.jpg</t>
   </si>
 </sst>
 </file>
@@ -1010,7 +1010,7 @@
         <v>43</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K1" s="6" t="s">
         <v>39</v>
@@ -1045,10 +1045,10 @@
         <v>36</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>36</v>
@@ -1077,10 +1077,10 @@
         <v>35</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>36</v>
@@ -1109,10 +1109,10 @@
         <v>36</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>36</v>
@@ -1141,10 +1141,10 @@
         <v>36</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>36</v>
@@ -1155,7 +1155,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
@@ -1173,10 +1173,10 @@
         <v>36</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>36</v>
@@ -1187,7 +1187,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>25</v>
@@ -1205,10 +1205,10 @@
         <v>36</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>36</v>
@@ -1237,10 +1237,10 @@
         <v>36</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>36</v>
@@ -1269,10 +1269,10 @@
         <v>36</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>36</v>
@@ -1301,10 +1301,10 @@
         <v>36</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>36</v>
@@ -1333,10 +1333,10 @@
         <v>36</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>36</v>
@@ -1365,11 +1365,11 @@
         <v>36</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>36</v>
@@ -1398,10 +1398,10 @@
         <v>36</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>36</v>
@@ -1429,8 +1429,8 @@
       <c r="G14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>54</v>
+      <c r="H14" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>45</v>
@@ -1478,7 +1478,7 @@
         <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>26</v>
@@ -1496,10 +1496,10 @@
         <v>36</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" s="4"/>
       <c r="M16" s="3" t="s">
@@ -1511,7 +1511,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>26</v>
@@ -1529,10 +1529,10 @@
         <v>36</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="J17" s="4"/>
       <c r="M17" s="3" t="s">
@@ -1544,7 +1544,7 @@
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>26</v>
@@ -1562,10 +1562,10 @@
         <v>36</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J18" s="4"/>
       <c r="M18" s="3" t="s">
@@ -1630,7 +1630,7 @@
         <v>47</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J20" s="4"/>
       <c r="M20" s="3" t="s">
@@ -1696,7 +1696,7 @@
         <v>49</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J22" s="4"/>
       <c r="M22" s="3" t="s">
@@ -1729,7 +1729,7 @@
         <v>50</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J23" s="5"/>
       <c r="M23" s="3" t="s">
@@ -1759,10 +1759,10 @@
         <v>36</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>36</v>
@@ -1788,10 +1788,10 @@
         <v>35</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>35</v>
@@ -1805,10 +1805,10 @@
     </row>
     <row r="26" spans="1:13" ht="30">
       <c r="A26" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>26</v>
@@ -1826,18 +1826,18 @@
         <v>36</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="30">
       <c r="A27" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>26</v>
@@ -1855,18 +1855,18 @@
         <v>36</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="30">
       <c r="A28" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>26</v>
@@ -1884,18 +1884,18 @@
         <v>36</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="30">
       <c r="A29" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>26</v>
@@ -1913,18 +1913,18 @@
         <v>36</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="14.25" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>26</v>
@@ -1942,18 +1942,18 @@
         <v>36</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="14.25" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>26</v>
@@ -1971,15 +1971,15 @@
         <v>36</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>26</v>
@@ -1997,7 +1997,7 @@
         <v>36</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>46</v>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="33" spans="1:13" ht="14.25" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>26</v>
@@ -2026,18 +2026,18 @@
         <v>36</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="14.25" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>26</v>
@@ -2055,10 +2055,10 @@
         <v>36</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="30">
@@ -2084,7 +2084,7 @@
         <v>36</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>45</v>
@@ -2095,10 +2095,10 @@
     </row>
     <row r="36" spans="1:13" ht="30">
       <c r="A36" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>109</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>25</v>
@@ -2116,18 +2116,18 @@
         <v>36</v>
       </c>
       <c r="H36" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="I36" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="30">
       <c r="A37" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B37" s="10" t="s">
         <v>112</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>113</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>25</v>
@@ -2145,24 +2145,24 @@
         <v>35</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="30">
       <c r="A38" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>31</v>
@@ -2174,15 +2174,15 @@
         <v>35</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="30">
       <c r="B39" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>25</v>
@@ -2200,23 +2200,23 @@
         <v>36</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="30">
       <c r="A40" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:13" s="9" customFormat="1" ht="150">
       <c r="A41" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C41" s="9" t="s">
         <v>26</v>
@@ -2234,30 +2234,30 @@
         <v>36</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="42" spans="1:13" s="9" customFormat="1">
       <c r="B42" s="9" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C42" s="9" t="s">
+      <c r="D42" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="F42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="G42" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H42" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>116</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2318,9 +2318,10 @@
     <hyperlink ref="H38" r:id="rId30" display="https://www.amazon.com/EMOPET-Desk-Robot-Companion-Interactive/dp/B0DDT2MT9K/ref=sr_1_21?crid=2O5HMBCMPZSCM&amp;dib=eyJ2IjoiMSJ9.tBPkvanml9eOr0jCsfrK3VkgBNveY9G09eBULXTgAJV7bjEY2Hj-IJNQpEKRA7TKPSMtXw8BST0SGzoLoNo4Oj6XaW93ezKXzKP2bpkxhFazfuqf5bcmpjLqtIVqZDb_r1kzyZ3zwqZYDq6f9Asg-Rhq_lB6kZ1exnNbn_ujAMpmNN8RymnrltXuFQPJdqIi0R8rSCt12bvf_aOwVbJlgADdMcJ-ziQh9c0Pw1aZBQRB53IXKJgh3MtIMeEz4i0Arwv7UAXZML42MrR2mrHvuRBnBjvnCkaVLIybi2r8-as.Ct2NuHfWrC-dOFAgBR1gJErliZzv32ERIpSeMowSokg&amp;dib_tag=se&amp;keywords=robot+pets&amp;qid=1777583022&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot+pets%2Ctoys-and-games%2C180&amp;sr=1-21" xr:uid="{971B5E96-FF15-4688-9704-1BDA0E592A7B}"/>
     <hyperlink ref="H42" r:id="rId31" display="https://www.amazon.com/EMOPET-Aibi-Pocket-Pet-Magnetically/dp/B0F1TH7D65/ref=sr_1_24?crid=2O5HMBCMPZSCM&amp;dib=eyJ2IjoiMSJ9.tBPkvanml9eOr0jCsfrK3VkgBNveY9G09eBULXTgAJV7bjEY2Hj-IJNQpEKRA7TKPSMtXw8BST0SGzoLoNo4Oj6XaW93ezKXzKP2bpkxhFazfuqf5bcmpjLqtIVqZDb_r1kzyZ3zwqZYDq6f9Asg-Rhq_lB6kZ1exnNbn_ujAMpmNN8RymnrltXuFQPJdqIi0R8rSCt12bvf_aOwVbJlgADdMcJ-ziQh9c0Pw1aZBQRB53IXKJgh3MtIMeEz4i0Arwv7UAXZML42MrR2mrHvuRBnBjvnCkaVLIybi2r8-as.Ct2NuHfWrC-dOFAgBR1gJErliZzv32ERIpSeMowSokg&amp;dib_tag=se&amp;keywords=robot+pets&amp;qid=1777583022&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot+pets%2Ctoys-and-games%2C180&amp;sr=1-24" xr:uid="{060CEC9A-E326-4B9D-8850-0EA5D77DC3C7}"/>
     <hyperlink ref="H39" r:id="rId32" xr:uid="{A3108714-65E7-4B89-BD81-DD27A31D4994}"/>
+    <hyperlink ref="H14" r:id="rId33" xr:uid="{84BECE61-5789-45D2-9870-323428A767C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId33"/>
-  <drawing r:id="rId34"/>
+  <pageSetup orientation="portrait" r:id="rId34"/>
+  <drawing r:id="rId35"/>
 </worksheet>
 </file>
--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0086B07D-5CFC-404A-AA93-C508C8AC282B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388790DA-5CE8-4DFB-B141-8299E3403DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -410,19 +410,19 @@
     <t>https://www.amazon.com/s?k=furby&amp;i=toys-and-games&amp;crid=30VFFMN70W1XS&amp;sprefix=furby%2Ctoys-and-games%2C158&amp;ref=nb_sb_ss_p13n-expert-pd-ops-ranker_ci_hl-bn-left_1_5</t>
   </si>
   <si>
-    <t>/images/products/Joy-for-All-Companion-Cat-Orange-Tabby</t>
-  </si>
-  <si>
     <t>/images/products/Chongker-Percy-Robot-Cat.jpg</t>
   </si>
   <si>
     <t>https://joyforall.com/products/companion-pet-pup?variant=37624426070199</t>
   </si>
   <si>
-    <t>/images/products/Joy-for-All-Companion-Cat-Silver</t>
-  </si>
-  <si>
     <t>/images/products/Joy-for-All-Companion-Cat-Tuxedo.jpg</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-for-All-Companion-Cat-Silver.png</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-for-All-Companion-Cat-Orange-Tabby.png</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1430,7 @@
         <v>36</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>45</v>
@@ -1506,7 +1506,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="17" spans="1:13">
+    <row r="17" spans="1:13" ht="25.5">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>59</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J17" s="4"/>
       <c r="M17" s="3" t="s">
@@ -1565,7 +1565,7 @@
         <v>57</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J18" s="4"/>
       <c r="M18" s="3" t="s">
@@ -1630,7 +1630,7 @@
         <v>47</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J20" s="4"/>
       <c r="M20" s="3" t="s">
@@ -1696,7 +1696,7 @@
         <v>49</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J22" s="4"/>
       <c r="M22" s="3" t="s">

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{388790DA-5CE8-4DFB-B141-8299E3403DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D89B544-690E-487C-9F08-2F96EDE84F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -392,9 +392,6 @@
     <t>Amazon.com: EMOPET AI Desk Robot Companion - ChatGPT Enabled with Voice Commands &amp; Dancing, Interactive AI Robot Pet with Personality, for Adults and Kids : Toys &amp; Games</t>
   </si>
   <si>
-    <t>AI Desk Robpt Companion</t>
-  </si>
-  <si>
     <t>Aibi</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>/images/products/Joy-for-All-Companion-Cat-Orange-Tabby.png</t>
+  </si>
+  <si>
+    <t>AI Desk Robot Companion</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1430,7 @@
         <v>36</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>45</v>
@@ -1499,7 +1499,7 @@
         <v>55</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="J16" s="4"/>
       <c r="M16" s="3" t="s">
@@ -1532,7 +1532,7 @@
         <v>59</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="J17" s="4"/>
       <c r="M17" s="3" t="s">
@@ -1565,7 +1565,7 @@
         <v>57</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J18" s="4"/>
       <c r="M18" s="3" t="s">
@@ -1630,7 +1630,7 @@
         <v>47</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J20" s="4"/>
       <c r="M20" s="3" t="s">
@@ -1696,7 +1696,7 @@
         <v>49</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="J22" s="4"/>
       <c r="M22" s="3" t="s">
@@ -2156,7 +2156,7 @@
         <v>114</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>25</v>
@@ -2182,7 +2182,7 @@
     </row>
     <row r="39" spans="1:13" ht="30">
       <c r="B39" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>25</v>
@@ -2200,7 +2200,7 @@
         <v>36</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>94</v>
@@ -2242,10 +2242,10 @@
     </row>
     <row r="42" spans="1:13" s="9" customFormat="1">
       <c r="B42" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C42" s="9" t="s">
         <v>118</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>119</v>
       </c>
       <c r="D42" s="9" t="s">
         <v>115</v>
@@ -2257,7 +2257,7 @@
         <v>35</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="46" spans="1:13">

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D89B544-690E-487C-9F08-2F96EDE84F43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5310C9C4-8866-43B3-B03C-CEC09E2A18A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="122">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -302,12 +302,6 @@
     <t>https://www.amazon.com/dp/B003XSJ4YE/ref=sspa_dk_hqp_detail_aax_0?psc=1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9ocXBfc2hhcmVk</t>
   </si>
   <si>
-    <t>Huggable Pug</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Realistic-Battery-Operated-Companion-Interactive-Synthetic/dp/B000N9EE8C/ref=sr_1_1_sspa?crid=3UDJCT8VT358V&amp;dib=eyJ2IjoiMSJ9.h-XYOsGcHfqztS8iEKqApORMOEWdzWYZoJ7_5bV_MgLnKGqG1B-rgf5GL8FwagSdV-_puqUDBfzCky0nt1yWs59UtQo3HURoZCBbK_fzD9_9aAcGyz_CgYPhBT-2YETzzZbIdiS_FrzVAbsoZB4NeEvj7kPBta4GGp27Rf3KCW-pEbmT0K6yV6gSDTyRkcH8MCIowVLXRPx2OQZFUzy7oX3ui0nvi1Me1fZikibtAvIDkwpHoAgtOVG_OD-uztSuoXtO6U0XYT4XPxuwIEXnQNP4sZWkLSAt6Y8gNNSNvRs.8IxOpm0OpwE53R6f2zLlDN8_03EM0nnJhmOTjrakC24&amp;dib_tag=se&amp;keywords=huggable%2Bpug&amp;qid=1777496322&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=huggable%2Bpug%2Ctoys-and-games%2C156&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
     <t>Siamese Cat</t>
   </si>
   <si>
@@ -317,21 +311,12 @@
     <t>https://www.amazon.com/dp/B004M42ER2/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B004M42ER2&amp;pd_rd_w=AjABt&amp;content-id=amzn1.sym.386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_p=386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_r=7VNR97CX8AWABRX62554&amp;pd_rd_wg=zOSGV&amp;pd_rd_r=20ddc17d-c84f-4870-9b91-0bc9f9332ef1&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM</t>
   </si>
   <si>
-    <t>https://www.amazon.com/Perfect-Petzzz-4934-Peluche-Blanc/dp/B00CZC87Y2/ref=sr_1_1?crid=14YL8V2AVTHVU&amp;dib=eyJ2IjoiMSJ9.syNMjb00PcieFuHWZ14dNpX10fhBwfzVgDq48Mbsqy3wt6r7yAuiizQ-gJqO3gutmd-usuS-1jPuSSDuiE8F7KrUYEf7VW63FZMnBQXJ1yXijFD75YrnwKFHPSfpDZYB1rHfEdMxpplUGz5YsxdxlmKzk7P_kQ2hvnnoz4lFOOuC_rnNYtHWW2OqKG2kQ6QEh60SfaZB2WUehvtMMK64w-yWAgQNZs6EU_Yb2xeKjmM-5Khfk68ma90TLCkycwBQGqOe_EP8B2SiQb0HED-g_vVNrlQePali6C5BDgOyMAI.mLk5dZzie9i8qjd0wveehxGN82-UShHPDyYkBPSCokQ&amp;dib_tag=se&amp;keywords=perfect+petzzz+plush+white+cat&amp;qid=1777496864&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+ptezz+plush+white+ca%2Ctoys-and-games%2C140&amp;sr=1-1</t>
-  </si>
-  <si>
-    <t>Frequently Returned</t>
-  </si>
-  <si>
     <t>/images/products/interactive_pet_toys.png</t>
   </si>
   <si>
     <t>Not Currently Available in the US</t>
   </si>
   <si>
-    <t>FREQUENTLY RETURNED</t>
-  </si>
-  <si>
     <t>/images/products/red_panda.png</t>
   </si>
   <si>
@@ -392,15 +377,6 @@
     <t>Amazon.com: EMOPET AI Desk Robot Companion - ChatGPT Enabled with Voice Commands &amp; Dancing, Interactive AI Robot Pet with Personality, for Adults and Kids : Toys &amp; Games</t>
   </si>
   <si>
-    <t>Aibi</t>
-  </si>
-  <si>
-    <t>Pocket Pet</t>
-  </si>
-  <si>
-    <t>Amazon.com: Aibi Pocket Pet - Wearable Robot | ChatGPT Powered AI Companion with Voice Commands, Emotional Interaction, Singing &amp; Dancing | Magnetically Attaches to Anywhere | Ultra Portable : Toys &amp; Games</t>
-  </si>
-  <si>
     <t>Furby</t>
   </si>
   <si>
@@ -423,13 +399,19 @@
   </si>
   <si>
     <t>AI Desk Robot Companion</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Petzzz-4934-Peluche-Blanc/dp/B00CZC87Y2/ref=sr_1_6?crid=2DSSQ9S1E17NT&amp;dib=eyJ2IjoiMSJ9._xaIiZ3a8J-2z_JxV4X0R1nw7RT5-CCIJzohURKRauFh_1RApvGWEwFyxaTPIRG0fd7JLrjcVFTscPNGqZPcCHaT3y_Gjbz2NESJ1A5vooYH9_NY5d5S3HCLV8e5X2cnjrlKwhEeBEl7YMYEpQpLISegcsFM1M2ERHH5rtaX5Ar8LIk5u-ZNupL7J6nKsknSkgg6PL09UNdCy6kOqBj_PGAQdMw9DYc5-lTxiudpdaLjCbSIKtjflEL9Ps7HVqUoTYgae4nqiuP7LDa_KVVQroDijVCYDcu-ZgVXOKtI2lA.V0rWULiC_BM4S_mny5HR3o4lGLc9nu_QZU0sazj6Toc&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1777734273&amp;s=toys-and-games&amp;sprefix=per%2Ctoys-and-games%2C185&amp;sr=1-6</t>
+  </si>
+  <si>
+    <t>/images/products/Sweetie-White-Cat.png</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -470,13 +452,6 @@
       <name val="Arial Unicode MS"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -500,17 +475,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -522,12 +492,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -541,29 +510,24 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Bad" xfId="1" builtinId="27"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1048,7 +1012,7 @@
         <v>60</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>36</v>
@@ -1080,7 +1044,7 @@
         <v>61</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>36</v>
@@ -1112,7 +1076,7 @@
         <v>62</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>36</v>
@@ -1144,7 +1108,7 @@
         <v>63</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>36</v>
@@ -1176,7 +1140,7 @@
         <v>68</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>36</v>
@@ -1208,7 +1172,7 @@
         <v>69</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>36</v>
@@ -1240,7 +1204,7 @@
         <v>64</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>36</v>
@@ -1272,7 +1236,7 @@
         <v>65</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>36</v>
@@ -1301,10 +1265,10 @@
         <v>36</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>36</v>
@@ -1333,10 +1297,10 @@
         <v>36</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>36</v>
@@ -1365,11 +1329,11 @@
         <v>36</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>36</v>
@@ -1398,10 +1362,10 @@
         <v>36</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>36</v>
@@ -1430,7 +1394,7 @@
         <v>36</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>45</v>
@@ -1499,7 +1463,7 @@
         <v>55</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="J16" s="4"/>
       <c r="M16" s="3" t="s">
@@ -1532,7 +1496,7 @@
         <v>59</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J17" s="4"/>
       <c r="M17" s="3" t="s">
@@ -1565,7 +1529,7 @@
         <v>57</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="J18" s="4"/>
       <c r="M18" s="3" t="s">
@@ -1630,7 +1594,7 @@
         <v>47</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J20" s="4"/>
       <c r="M20" s="3" t="s">
@@ -1696,7 +1660,7 @@
         <v>49</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J22" s="4"/>
       <c r="M22" s="3" t="s">
@@ -1729,7 +1693,7 @@
         <v>50</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="J23" s="5"/>
       <c r="M23" s="3" t="s">
@@ -1762,7 +1726,7 @@
         <v>71</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>36</v>
@@ -1788,10 +1752,10 @@
         <v>35</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>35</v>
@@ -1829,7 +1793,7 @@
         <v>74</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="30">
@@ -1858,7 +1822,7 @@
         <v>76</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="30">
@@ -1887,7 +1851,7 @@
         <v>78</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="30">
@@ -1916,7 +1880,7 @@
         <v>80</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="14.25" customHeight="1">
@@ -1942,10 +1906,10 @@
         <v>36</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="14.25" customHeight="1">
@@ -1971,7 +1935,10 @@
         <v>36</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>92</v>
+        <v>120</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="14.25" customHeight="1">
@@ -2029,7 +1996,7 @@
         <v>86</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="14.25" customHeight="1">
@@ -2037,7 +2004,7 @@
         <v>72</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>26</v>
@@ -2055,10 +2022,10 @@
         <v>36</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="I34" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="30">
@@ -2084,7 +2051,7 @@
         <v>36</v>
       </c>
       <c r="H35" s="7" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>45</v>
@@ -2095,10 +2062,10 @@
     </row>
     <row r="36" spans="1:13" ht="30">
       <c r="A36" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>108</v>
+        <v>102</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>103</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>25</v>
@@ -2116,18 +2083,18 @@
         <v>36</v>
       </c>
       <c r="H36" s="7" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="30">
       <c r="A37" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>112</v>
+        <v>106</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>107</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>25</v>
@@ -2145,24 +2112,24 @@
         <v>35</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="30">
       <c r="A38" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>127</v>
+        <v>109</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>119</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E38" s="3" t="s">
         <v>31</v>
@@ -2174,15 +2141,15 @@
         <v>35</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I38" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="30">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="27.75" customHeight="1">
       <c r="B39" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>25</v>
@@ -2200,64 +2167,10 @@
         <v>36</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="30">
-      <c r="A40" s="6" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" s="9" customFormat="1" ht="150">
-      <c r="A41" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="D41" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E41" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G41" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" s="9" customFormat="1">
-      <c r="B42" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C42" s="9" t="s">
-        <v>118</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>115</v>
-      </c>
-      <c r="F42" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G42" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="H42" s="11" t="s">
-        <v>119</v>
+        <v>90</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -2316,12 +2229,11 @@
     <hyperlink ref="H36" r:id="rId28" display="https://www.amazon.com/Ruko-18011-Interactive-Expressions-Programmable/dp/B0FLXCXPHD/ref=sr_1_3_sspa?crid=1SVOVUI4YUECO&amp;dib=eyJ2IjoiMSJ9.3hF_MQV4B-IHq5j4jAivqbkOHRO5zitzXHgCaYvxePjfLUaF8FzF13Y5z96sut9I4qI5NacM67aJmQh2fSG_rHl06dBM8XRt-KQiTrQqsdg_DRAMAF6O2o8lA5jxdXD__uSV2k8ElSHQjEhlGuuQU4HNMy8zX_b59y97EMoH341qgn5DLZswbGe9aX94vwYL1Kof4VsrUXg5ppj37Pn6qy_mDKyJRehzAk_7sH96IM1FzhzruTNqKQi1NhP6B6QfJITWm4p1DIKJ-Ocoq5LFohCkcuulJ2yTLS8bprH7tio.qCkDoDZhqdLp3BeSDLRcSP4eqtKCXiY08ZhypI70hPU&amp;dib_tag=se&amp;keywords=robot%2Bdog&amp;qid=1777581735&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot%2Bdog%2Caps%2C227&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{21A8C767-EC55-4D08-AE65-5476028865EE}"/>
     <hyperlink ref="H37" r:id="rId29" display="https://www.amazon.com/dp/B0DCF53PCH/ref=sspa_dk_detail_right_aax_0?sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfcmlnaHRfc2hhcmVk&amp;th=1" xr:uid="{C1CD4974-517B-4A12-B980-BE333F29C866}"/>
     <hyperlink ref="H38" r:id="rId30" display="https://www.amazon.com/EMOPET-Desk-Robot-Companion-Interactive/dp/B0DDT2MT9K/ref=sr_1_21?crid=2O5HMBCMPZSCM&amp;dib=eyJ2IjoiMSJ9.tBPkvanml9eOr0jCsfrK3VkgBNveY9G09eBULXTgAJV7bjEY2Hj-IJNQpEKRA7TKPSMtXw8BST0SGzoLoNo4Oj6XaW93ezKXzKP2bpkxhFazfuqf5bcmpjLqtIVqZDb_r1kzyZ3zwqZYDq6f9Asg-Rhq_lB6kZ1exnNbn_ujAMpmNN8RymnrltXuFQPJdqIi0R8rSCt12bvf_aOwVbJlgADdMcJ-ziQh9c0Pw1aZBQRB53IXKJgh3MtIMeEz4i0Arwv7UAXZML42MrR2mrHvuRBnBjvnCkaVLIybi2r8-as.Ct2NuHfWrC-dOFAgBR1gJErliZzv32ERIpSeMowSokg&amp;dib_tag=se&amp;keywords=robot+pets&amp;qid=1777583022&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot+pets%2Ctoys-and-games%2C180&amp;sr=1-21" xr:uid="{971B5E96-FF15-4688-9704-1BDA0E592A7B}"/>
-    <hyperlink ref="H42" r:id="rId31" display="https://www.amazon.com/EMOPET-Aibi-Pocket-Pet-Magnetically/dp/B0F1TH7D65/ref=sr_1_24?crid=2O5HMBCMPZSCM&amp;dib=eyJ2IjoiMSJ9.tBPkvanml9eOr0jCsfrK3VkgBNveY9G09eBULXTgAJV7bjEY2Hj-IJNQpEKRA7TKPSMtXw8BST0SGzoLoNo4Oj6XaW93ezKXzKP2bpkxhFazfuqf5bcmpjLqtIVqZDb_r1kzyZ3zwqZYDq6f9Asg-Rhq_lB6kZ1exnNbn_ujAMpmNN8RymnrltXuFQPJdqIi0R8rSCt12bvf_aOwVbJlgADdMcJ-ziQh9c0Pw1aZBQRB53IXKJgh3MtIMeEz4i0Arwv7UAXZML42MrR2mrHvuRBnBjvnCkaVLIybi2r8-as.Ct2NuHfWrC-dOFAgBR1gJErliZzv32ERIpSeMowSokg&amp;dib_tag=se&amp;keywords=robot+pets&amp;qid=1777583022&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot+pets%2Ctoys-and-games%2C180&amp;sr=1-24" xr:uid="{060CEC9A-E326-4B9D-8850-0EA5D77DC3C7}"/>
-    <hyperlink ref="H39" r:id="rId32" xr:uid="{A3108714-65E7-4B89-BD81-DD27A31D4994}"/>
-    <hyperlink ref="H14" r:id="rId33" xr:uid="{84BECE61-5789-45D2-9870-323428A767C6}"/>
+    <hyperlink ref="H39" r:id="rId31" xr:uid="{A3108714-65E7-4B89-BD81-DD27A31D4994}"/>
+    <hyperlink ref="H14" r:id="rId32" xr:uid="{84BECE61-5789-45D2-9870-323428A767C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId34"/>
-  <drawing r:id="rId35"/>
+  <pageSetup orientation="portrait" r:id="rId33"/>
+  <drawing r:id="rId34"/>
 </worksheet>
 </file>
--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5310C9C4-8866-43B3-B03C-CEC09E2A18A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8BBB6C-C6B4-4792-A6F3-C1CD7DA137DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="123">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>/images/products/Sweetie-White-Cat.png</t>
+  </si>
+  <si>
+    <t>Top Pick</t>
   </si>
 </sst>
 </file>
@@ -547,13 +550,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -926,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:M67"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" style="3" bestFit="1" customWidth="1"/>
@@ -935,17 +938,17 @@
     <col min="4" max="4" width="10.28515625" style="3" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="6.140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="98" style="3" customWidth="1"/>
-    <col min="9" max="9" width="54.140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="32.140625" style="6" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="3"/>
+    <col min="7" max="8" width="9.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="98" style="3" customWidth="1"/>
+    <col min="10" max="10" width="54.140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="32.140625" style="6" customWidth="1"/>
+    <col min="12" max="12" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="6" customFormat="1">
+    <row r="1" spans="1:14" s="6" customFormat="1">
       <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
@@ -968,25 +971,28 @@
         <v>34</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1008,17 +1014,20 @@
       <c r="G2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
+      <c r="N2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1040,17 +1049,20 @@
       <c r="G3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+      <c r="N3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -1072,17 +1084,20 @@
       <c r="G4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+      <c r="N4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
@@ -1104,17 +1119,20 @@
       <c r="G5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M5" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+      <c r="N5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
@@ -1136,17 +1154,20 @@
       <c r="G6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M6" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="N6" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="3" t="s">
         <v>1</v>
       </c>
@@ -1168,17 +1189,20 @@
       <c r="G7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M7" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="N7" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" s="3" t="s">
         <v>1</v>
       </c>
@@ -1200,17 +1224,20 @@
       <c r="G8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M8" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="N8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
@@ -1232,17 +1259,20 @@
       <c r="G9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="I9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="N9" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -1264,17 +1294,20 @@
       <c r="G10" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="K10" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="N10" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1296,17 +1329,20 @@
       <c r="G11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="K11" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -1328,18 +1364,21 @@
       <c r="G12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="I12" s="2"/>
-      <c r="J12" s="6" t="s">
+      <c r="J12" s="2"/>
+      <c r="K12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M12" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="N12" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
@@ -1361,17 +1400,20 @@
       <c r="G13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I13" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="6" t="s">
+      <c r="K13" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
@@ -1393,18 +1435,21 @@
       <c r="G14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I14" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="I14" s="2" t="s">
+      <c r="J14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J14" s="4"/>
-      <c r="M14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="K14" s="4"/>
+      <c r="N14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
@@ -1426,18 +1471,21 @@
       <c r="G15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="7" t="s">
+      <c r="H15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="I15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J15" s="4"/>
-      <c r="M15" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="K15" s="4"/>
+      <c r="N15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="3" t="s">
         <v>20</v>
       </c>
@@ -1459,18 +1507,21 @@
       <c r="G16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H16" s="7" t="s">
+      <c r="H16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I16" s="2" t="s">
+      <c r="J16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="J16" s="4"/>
-      <c r="M16" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" ht="25.5">
+      <c r="K16" s="4"/>
+      <c r="N16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" ht="25.5">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
@@ -1492,18 +1543,21 @@
       <c r="G17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="7" t="s">
+      <c r="H17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I17" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="I17" s="2" t="s">
+      <c r="J17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="J17" s="4"/>
-      <c r="M17" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" ht="15" customHeight="1">
+      <c r="K17" s="4"/>
+      <c r="N17" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
@@ -1525,18 +1579,21 @@
       <c r="G18" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J18" s="4"/>
-      <c r="M18" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="K18" s="4"/>
+      <c r="N18" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
@@ -1559,16 +1616,19 @@
         <v>36</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="M19" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="N19" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="3" t="s">
         <v>13</v>
       </c>
@@ -1590,18 +1650,21 @@
       <c r="G20" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I20" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J20" s="4"/>
-      <c r="M20" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="K20" s="4"/>
+      <c r="N20" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
@@ -1623,18 +1686,21 @@
       <c r="G21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H21" s="7" t="s">
+      <c r="H21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="I21" s="2" t="s">
+      <c r="J21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="J21" s="4"/>
-      <c r="M21" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="15" customHeight="1">
+      <c r="K21" s="4"/>
+      <c r="N21" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" ht="15" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
@@ -1656,18 +1722,21 @@
       <c r="G22" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H22" s="7" t="s">
+      <c r="H22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J22" s="4"/>
-      <c r="M22" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="K22" s="4"/>
+      <c r="N22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
@@ -1689,18 +1758,21 @@
       <c r="G23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H23" s="7" t="s">
+      <c r="H23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I23" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="J23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J23" s="5"/>
-      <c r="M23" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="30">
+      <c r="K23" s="5"/>
+      <c r="N23" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" ht="30">
       <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
@@ -1722,17 +1794,20 @@
       <c r="G24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H24" s="7" t="s">
+      <c r="H24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="I24" s="2" t="s">
+      <c r="J24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="N24" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
@@ -1751,23 +1826,26 @@
       <c r="G25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H25" s="7" t="s">
+      <c r="H25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="I25" s="2" t="s">
+      <c r="J25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="L25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="30">
+        <v>35</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" ht="30">
       <c r="A26" s="3" t="s">
         <v>72</v>
       </c>
@@ -1789,14 +1867,17 @@
       <c r="G26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H26" s="7" t="s">
+      <c r="H26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I26" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I26" s="2" t="s">
+      <c r="J26" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="30">
+    <row r="27" spans="1:14" ht="30">
       <c r="A27" s="3" t="s">
         <v>72</v>
       </c>
@@ -1818,14 +1899,17 @@
       <c r="G27" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H27" s="7" t="s">
+      <c r="H27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="I27" s="2" t="s">
+      <c r="J27" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="30">
+    <row r="28" spans="1:14" ht="30">
       <c r="A28" s="3" t="s">
         <v>72</v>
       </c>
@@ -1847,14 +1931,17 @@
       <c r="G28" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H28" s="7" t="s">
+      <c r="H28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I28" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="I28" s="2" t="s">
+      <c r="J28" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="30">
+    <row r="29" spans="1:14" ht="30">
       <c r="A29" s="3" t="s">
         <v>72</v>
       </c>
@@ -1876,14 +1963,17 @@
       <c r="G29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="7" t="s">
+      <c r="H29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="I29" s="2" t="s">
+      <c r="J29" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="14.25" customHeight="1">
+    <row r="30" spans="1:14" ht="14.25" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
@@ -1905,14 +1995,17 @@
       <c r="G30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="7" t="s">
+      <c r="H30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="2" t="s">
+      <c r="J30" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="14.25" customHeight="1">
+    <row r="31" spans="1:14" ht="14.25" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>72</v>
       </c>
@@ -1934,14 +2027,17 @@
       <c r="G31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H31" s="8" t="s">
+      <c r="H31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I31" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="I31" s="2" t="s">
+      <c r="J31" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="14.25" customHeight="1">
+    <row r="32" spans="1:14" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>72</v>
       </c>
@@ -1963,14 +2059,17 @@
       <c r="G32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H32" s="7" t="s">
+      <c r="H32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I32" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="14.25" customHeight="1">
+    <row r="33" spans="1:14" ht="14.25" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>72</v>
       </c>
@@ -1992,14 +2091,17 @@
       <c r="G33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H33" s="7" t="s">
+      <c r="H33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I33" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="I33" s="2" t="s">
+      <c r="J33" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="14.25" customHeight="1">
+    <row r="34" spans="1:14" ht="14.25" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>72</v>
       </c>
@@ -2021,14 +2123,17 @@
       <c r="G34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H34" s="7" t="s">
+      <c r="H34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="I34" s="2" t="s">
+      <c r="J34" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="30">
+    <row r="35" spans="1:14" ht="30">
       <c r="A35" s="3" t="s">
         <v>22</v>
       </c>
@@ -2050,17 +2155,20 @@
       <c r="G35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H35" s="7" t="s">
+      <c r="H35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="I35" s="2" t="s">
+      <c r="J35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" ht="30">
+      <c r="N35" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" ht="30">
       <c r="A36" s="3" t="s">
         <v>102</v>
       </c>
@@ -2082,14 +2190,17 @@
       <c r="G36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H36" s="7" t="s">
+      <c r="H36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I36" s="2" t="s">
+      <c r="J36" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="30">
+    <row r="37" spans="1:14" ht="30">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
@@ -2111,14 +2222,17 @@
       <c r="G37" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H37" s="7" t="s">
+      <c r="H37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I37" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="I37" s="2" t="s">
+      <c r="J37" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="30">
+    <row r="38" spans="1:14" ht="30">
       <c r="A38" s="3" t="s">
         <v>109</v>
       </c>
@@ -2140,14 +2254,17 @@
       <c r="G38" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H38" s="7" t="s">
+      <c r="H38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I38" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="I38" s="2" t="s">
+      <c r="J38" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="27.75" customHeight="1">
+    <row r="39" spans="1:14" ht="27.75" customHeight="1">
       <c r="B39" s="3" t="s">
         <v>112</v>
       </c>
@@ -2166,71 +2283,74 @@
       <c r="G39" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H39" s="7" t="s">
+      <c r="H39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I39" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="I39" s="2" t="s">
+      <c r="J39" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:13">
-      <c r="H46" s="4"/>
-    </row>
-    <row r="47" spans="1:13">
-      <c r="H47" s="4"/>
-    </row>
-    <row r="48" spans="1:13">
-      <c r="H48" s="4"/>
-    </row>
-    <row r="49" spans="8:8">
-      <c r="H49" s="4"/>
-    </row>
-    <row r="51" spans="8:8">
-      <c r="H51" s="6"/>
-    </row>
-    <row r="57" spans="8:8">
-      <c r="H57" s="8"/>
-    </row>
-    <row r="61" spans="8:8">
-      <c r="H61" s="8"/>
-    </row>
-    <row r="67" spans="8:8">
-      <c r="H67" s="6"/>
+    <row r="46" spans="1:14">
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="1:14">
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="1:14">
+      <c r="I48" s="4"/>
+    </row>
+    <row r="49" spans="9:9">
+      <c r="I49" s="4"/>
+    </row>
+    <row r="51" spans="9:9">
+      <c r="I51" s="6"/>
+    </row>
+    <row r="57" spans="9:9">
+      <c r="I57" s="8"/>
+    </row>
+    <row r="61" spans="9:9">
+      <c r="I61" s="8"/>
+    </row>
+    <row r="67" spans="9:9">
+      <c r="I67" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="H20" r:id="rId1" display="https://chongker.com/products/matecat10-interactive-cat" xr:uid="{6A6B66E7-EFA9-4C01-A8EA-9FC28D138092}"/>
-    <hyperlink ref="H21" r:id="rId2" display="https://chongker.com/products/percy-robotic-dog-companion-designed-for-comfort" xr:uid="{33B7E068-D39E-4359-A980-4956C64F28BD}"/>
-    <hyperlink ref="H22" r:id="rId3" display="https://chongker.com/products/ragdoll-percy-interactive-cat-1-1" xr:uid="{56A80108-DC52-4F38-B5B7-E6F38E8F3ECC}"/>
-    <hyperlink ref="H23" r:id="rId4" display="https://chongker.com/products/breathing-red-panda" xr:uid="{213BB2E5-5459-4A38-992E-7E2658523271}"/>
-    <hyperlink ref="H15" r:id="rId5" xr:uid="{D237B42D-17AA-460F-B784-E8F07972476C}"/>
-    <hyperlink ref="H16" r:id="rId6" xr:uid="{4FB1BAAD-1B59-459D-B076-BEC8534C5468}"/>
-    <hyperlink ref="H18" r:id="rId7" xr:uid="{12CB9543-D99E-401B-A92D-8A43D39066E9}"/>
-    <hyperlink ref="H17" r:id="rId8" xr:uid="{01AA717A-8251-4D9A-981C-C86F4068EC19}"/>
-    <hyperlink ref="H2" r:id="rId9" xr:uid="{61986D39-AC73-4733-851F-E4D8DA4135B4}"/>
-    <hyperlink ref="H3" r:id="rId10" display="https://www.enabot.com/home-robot/ebo-air-2-plus" xr:uid="{4E06DA7A-7CAD-4054-BBE6-70F8B6093B84}"/>
-    <hyperlink ref="H4" r:id="rId11" display="https://www.enabot.com/home-robot/ebo-x" xr:uid="{ADA71D89-8C1B-4B93-A048-545BC5C00388}"/>
-    <hyperlink ref="H5" r:id="rId12" xr:uid="{CB14D57D-F38C-4C0B-8515-8FA7E1CD6C43}"/>
-    <hyperlink ref="H8" r:id="rId13" display="https://www.enabot.com/home-robot/ebo-se" xr:uid="{FA8B4958-90B9-45F8-8B56-98CFC90D7C48}"/>
-    <hyperlink ref="H9" r:id="rId14" display="https://www.enabot.com/pet-robot/rola-mini" xr:uid="{27A699FA-EF41-449B-A688-367BB2D2FF9B}"/>
-    <hyperlink ref="H6" r:id="rId15" display="https://www.enabot.com/home-robot/ebo-air-2" xr:uid="{647575FE-3C8A-4A98-B07B-48ECD59D1F50}"/>
-    <hyperlink ref="H7" r:id="rId16" display="https://www.enabot.com/home-robot/ebo-air-2s" xr:uid="{9101E83F-ACD4-4CDE-9DCD-76DA195E0ADF}"/>
-    <hyperlink ref="H24" r:id="rId17" display="https://www.amazon.com/chinatera-Wuffy-Robot-Dog-Lifelike/dp/B0GBVGT2TT/ref=sr_1_11?crid=2ZSJTOWRVH3MM&amp;dib=eyJ2IjoiMSJ9.VS90R1zgFrlwmdQJILWsx8m56kTkq9RI8It8FjE6_EsPGshcuFzUHkYPqgtgO3b94hrRhUCeyIZ5TnmhSVHMRIPO2MaXyv8QFBSllfa10huT9VK2WYjvmngpudJWd1rnHAu1bkPiUKRv-UOO-4Gc7oJnLIe5BJhTJsHsp-U4N_E81XPcHef9US6-JWA2YsvOGXw69ZtKIRlYFj3lkLKDUVuERCcbVo8DpKDkFb-Vp2yktqw7RhsPrf1nD1SLe8pHpfqHkeo8Hbp8kDoUiEu4TF2zRnLlNliNXwzhHL1u2zE.GyQtPiCSX6a8bzQBO82HXb9lsAlnDFyQzSpsnNErlKQ&amp;dib_tag=se&amp;keywords=wuffy%2Brobot%2Bdog&amp;qid=1777493502&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=wuffy%2Caps%2C189&amp;sr=8-11&amp;th=1" xr:uid="{D87F9739-8EB7-4B96-8724-048ECAD6590B}"/>
-    <hyperlink ref="H26" r:id="rId18" display="https://www.amazon.com/Perfect-Petzzz-Realistic-Battery-Operated-Interactive/dp/B002PJ37XG/ref=sr_1_1?crid=1LZYEDXW3RV5I&amp;dib=eyJ2IjoiMSJ9.pUlBEkNhfUa4eyzR6zknHIS2YWFT7NFoBnBzNTSb084ARoJgJUsPbq3F1yeWbgPAiE_SE0xe5MWy0y9QLchfwXhi3ceqCN6rD-jmDSXrA0yQxSruxDzk95BxVnqmBIsTTpjw91BYEiV5liGGpZmCKBd2pxsvNWTRk0Eh62VlUb-_5wpaIanBhKn9HwwtQ64CN-ZaeyHPy2Ru0e32vtz84euLzKlZrkooYg9Ao9xkjKNL2Ai-O6H1Dt6MugojLSq5BgQFnsModHhuLtdPaS2IV-Mh2oojRPCRBTC1Rpk4cXQ.RQwNtdUMob0iyv9kxlQ0L7Xmavug8bJnsjamlMM7t7E&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1777495169&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+petzzz%2Caps%2C194&amp;sr=8-1" xr:uid="{5C86EB84-F893-43DE-A55B-125E1B73C946}"/>
-    <hyperlink ref="H27" r:id="rId19" display="https://www.amazon.com/dp/B008Y0QTV2/ref=sspa_dk_hqp_detail_aax_0?psc=1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9ocXBfc2hhcmVk" xr:uid="{5EA03AE2-75D8-46FF-A323-6F9E13327F5E}"/>
-    <hyperlink ref="H28" r:id="rId20" display="https://www.amazon.com/Perfect-Petzzz-Realistic-Interactive-Handcrafted/dp/B0040127N8?pd_rd_w=jx9sh&amp;content-id=amzn1.sym.ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_p=ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_r=6W8C01JJ3VNPS3GPTM6E&amp;pd_rd_wg=EScz2&amp;pd_rd_r=8b92b89c-acde-4bab-8c85-f00ac605c149&amp;ref_=sspa_dk_detail_sbt_1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1" xr:uid="{8D9599B6-7DF6-44AD-B20E-1ABC37923A89}"/>
-    <hyperlink ref="H29" r:id="rId21" display="https://www.amazon.com/Perfect-Pets-International-Sleeping-Beagle/dp/B00279NUFY?psc=1&amp;pd_rd_w=mNONg&amp;content-id=amzn1.sym.ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_p=ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_r=W199027EDH8MX7GDECC3&amp;pd_rd_wg=Kn80z&amp;pd_rd_r=46bdf95b-223f-4163-be9a-8a1d241d6683&amp;ref_=sspa_dk_detail_sbt_1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM=" xr:uid="{0F7C88EE-BD60-40FB-9C03-C5276E99C4ED}"/>
-    <hyperlink ref="H32" r:id="rId22" display="https://www.amazon.com/dp/B0039Y3YOI/ref=sspa_dk_detail_2?psc=1&amp;pd_rd_i=B0039Y3YOI&amp;pd_rd_w=jV6FN&amp;content-id=amzn1.sym.7dc70186-c171-4ad3-b982-b0b7c53e2f49&amp;pf_rd_p=7dc70186-c171-4ad3-b982-b0b7c53e2f49&amp;pf_rd_r=3DRP3XZZ66P886VD0ZFC&amp;pd_rd_wg=uugqL&amp;pd_rd_r=8a18b43f-7351-4cbb-b6ef-1a274737daec&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw" xr:uid="{46700710-23E6-43AA-8971-BF6A11239C4A}"/>
-    <hyperlink ref="H33" r:id="rId23" xr:uid="{4687C11F-7031-4058-A6D5-B94251851D80}"/>
-    <hyperlink ref="H34" r:id="rId24" display="https://www.amazon.com/Perfect-Petzzz-Siamese-Breathing-Puppy/dp/B06ZY3CYX4/ref=sr_1_8?crid=1XJLXJYXVYQ0N&amp;dib=eyJ2IjoiMSJ9.6FAL5yqb0pMjyqjFtFff8rapxTJu7wMCuvWT1oB0FoiCW57t5bub7u1NfN0AA5zBFsU4gc4ytAnzqJApDDdbP0hHkEStYFQ35EFnDZxNAK5TFJM69-45Y77dUTPoYIG8__C0urwPJwptiB9FoReL8Ecf6rveMLte519ejCIqK2WBEkxV_yMxUnuPVSl6wowjx0nWJI1nn61k61TTjBmGiLTxc7Ngd3-geAWUShdDsOGxPjweoq0vBlaSg9orzCV7ZWaOF5itfJDmYObEAQpFHhhK9QkKYlqQnBxC6WSpo6k.qI5Tpy3lpOA4p4BdnoGUTgnQI-eAcDsYtY4VBBLoyVA&amp;dib_tag=se&amp;keywords=perfect+petzzz+cats&amp;qid=1777496385&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+petzzz+cats%2Ctoys-and-games%2C203&amp;sr=1-8" xr:uid="{10510C29-E591-47CB-A65E-91A9694F53AC}"/>
-    <hyperlink ref="H30" r:id="rId25" display="https://www.amazon.com/dp/B004M42ER2/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B004M42ER2&amp;pd_rd_w=AjABt&amp;content-id=amzn1.sym.386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_p=386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_r=7VNR97CX8AWABRX62554&amp;pd_rd_wg=zOSGV&amp;pd_rd_r=20ddc17d-c84f-4870-9b91-0bc9f9332ef1&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM" xr:uid="{D9F8D30D-E2C0-40A9-8471-6903B21AA511}"/>
-    <hyperlink ref="H25" r:id="rId26" xr:uid="{F81372EB-9409-45C8-8BCF-85AC4DD003A3}"/>
-    <hyperlink ref="H35" r:id="rId27" display="https://www.amazon.com/Electronic-Walking-Pomeranian-Realistic-Interactive/dp/B0B7MR3CFP/ref=sr_1_3?crid=YWYC6W0LFAXU&amp;dib=eyJ2IjoiMSJ9.wy5-rpjLPrH786btWTET4c25tGgrSfmH7yKUeHBPqnNkmrB2oigYxDkAS7pVsRNkle8aIk3XYMn2h6clGEEQcDaTE8t8aymZDBt05FYlJ-GH4eGGxBbf7Ig1s82GEwRBiKKOV3G2irleHtBP4F_hv6NMJyknPUtqTpJNj65pspZ7KCByQF56t6QJoxu1YZszw0l8o5_aanUuqTVumwrAlGR2tYS2v5PkCErJz2hiJqJqxLkwsmxHJ9oNRquwCySespKIiJE5o0e8RvyR4sO2Eq00KFSOsAqh0ajB3kjC0xI.NEkZKEQBsFNiMNN-4QrmamwZ0fcTnwcKi8CtPmlcjkQ&amp;dib_tag=se&amp;keywords=milo%2Brobot%2Bpuppy&amp;qid=1777581403&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=milo%2Briobot%2Bpuppy%2Ctoys-and-games%2C181&amp;sr=1-3&amp;th=1" xr:uid="{5EBB9AF1-324C-41A3-9FB0-558087967E28}"/>
-    <hyperlink ref="H36" r:id="rId28" display="https://www.amazon.com/Ruko-18011-Interactive-Expressions-Programmable/dp/B0FLXCXPHD/ref=sr_1_3_sspa?crid=1SVOVUI4YUECO&amp;dib=eyJ2IjoiMSJ9.3hF_MQV4B-IHq5j4jAivqbkOHRO5zitzXHgCaYvxePjfLUaF8FzF13Y5z96sut9I4qI5NacM67aJmQh2fSG_rHl06dBM8XRt-KQiTrQqsdg_DRAMAF6O2o8lA5jxdXD__uSV2k8ElSHQjEhlGuuQU4HNMy8zX_b59y97EMoH341qgn5DLZswbGe9aX94vwYL1Kof4VsrUXg5ppj37Pn6qy_mDKyJRehzAk_7sH96IM1FzhzruTNqKQi1NhP6B6QfJITWm4p1DIKJ-Ocoq5LFohCkcuulJ2yTLS8bprH7tio.qCkDoDZhqdLp3BeSDLRcSP4eqtKCXiY08ZhypI70hPU&amp;dib_tag=se&amp;keywords=robot%2Bdog&amp;qid=1777581735&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot%2Bdog%2Caps%2C227&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{21A8C767-EC55-4D08-AE65-5476028865EE}"/>
-    <hyperlink ref="H37" r:id="rId29" display="https://www.amazon.com/dp/B0DCF53PCH/ref=sspa_dk_detail_right_aax_0?sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfcmlnaHRfc2hhcmVk&amp;th=1" xr:uid="{C1CD4974-517B-4A12-B980-BE333F29C866}"/>
-    <hyperlink ref="H38" r:id="rId30" display="https://www.amazon.com/EMOPET-Desk-Robot-Companion-Interactive/dp/B0DDT2MT9K/ref=sr_1_21?crid=2O5HMBCMPZSCM&amp;dib=eyJ2IjoiMSJ9.tBPkvanml9eOr0jCsfrK3VkgBNveY9G09eBULXTgAJV7bjEY2Hj-IJNQpEKRA7TKPSMtXw8BST0SGzoLoNo4Oj6XaW93ezKXzKP2bpkxhFazfuqf5bcmpjLqtIVqZDb_r1kzyZ3zwqZYDq6f9Asg-Rhq_lB6kZ1exnNbn_ujAMpmNN8RymnrltXuFQPJdqIi0R8rSCt12bvf_aOwVbJlgADdMcJ-ziQh9c0Pw1aZBQRB53IXKJgh3MtIMeEz4i0Arwv7UAXZML42MrR2mrHvuRBnBjvnCkaVLIybi2r8-as.Ct2NuHfWrC-dOFAgBR1gJErliZzv32ERIpSeMowSokg&amp;dib_tag=se&amp;keywords=robot+pets&amp;qid=1777583022&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot+pets%2Ctoys-and-games%2C180&amp;sr=1-21" xr:uid="{971B5E96-FF15-4688-9704-1BDA0E592A7B}"/>
-    <hyperlink ref="H39" r:id="rId31" xr:uid="{A3108714-65E7-4B89-BD81-DD27A31D4994}"/>
-    <hyperlink ref="H14" r:id="rId32" xr:uid="{84BECE61-5789-45D2-9870-323428A767C6}"/>
+    <hyperlink ref="I20" r:id="rId1" display="https://chongker.com/products/matecat10-interactive-cat" xr:uid="{6A6B66E7-EFA9-4C01-A8EA-9FC28D138092}"/>
+    <hyperlink ref="I21" r:id="rId2" display="https://chongker.com/products/percy-robotic-dog-companion-designed-for-comfort" xr:uid="{33B7E068-D39E-4359-A980-4956C64F28BD}"/>
+    <hyperlink ref="I22" r:id="rId3" display="https://chongker.com/products/ragdoll-percy-interactive-cat-1-1" xr:uid="{56A80108-DC52-4F38-B5B7-E6F38E8F3ECC}"/>
+    <hyperlink ref="I23" r:id="rId4" display="https://chongker.com/products/breathing-red-panda" xr:uid="{213BB2E5-5459-4A38-992E-7E2658523271}"/>
+    <hyperlink ref="I15" r:id="rId5" xr:uid="{D237B42D-17AA-460F-B784-E8F07972476C}"/>
+    <hyperlink ref="I16" r:id="rId6" xr:uid="{4FB1BAAD-1B59-459D-B076-BEC8534C5468}"/>
+    <hyperlink ref="I18" r:id="rId7" xr:uid="{12CB9543-D99E-401B-A92D-8A43D39066E9}"/>
+    <hyperlink ref="I17" r:id="rId8" xr:uid="{01AA717A-8251-4D9A-981C-C86F4068EC19}"/>
+    <hyperlink ref="I2" r:id="rId9" xr:uid="{61986D39-AC73-4733-851F-E4D8DA4135B4}"/>
+    <hyperlink ref="I3" r:id="rId10" display="https://www.enabot.com/home-robot/ebo-air-2-plus" xr:uid="{4E06DA7A-7CAD-4054-BBE6-70F8B6093B84}"/>
+    <hyperlink ref="I4" r:id="rId11" display="https://www.enabot.com/home-robot/ebo-x" xr:uid="{ADA71D89-8C1B-4B93-A048-545BC5C00388}"/>
+    <hyperlink ref="I5" r:id="rId12" xr:uid="{CB14D57D-F38C-4C0B-8515-8FA7E1CD6C43}"/>
+    <hyperlink ref="I8" r:id="rId13" display="https://www.enabot.com/home-robot/ebo-se" xr:uid="{FA8B4958-90B9-45F8-8B56-98CFC90D7C48}"/>
+    <hyperlink ref="I9" r:id="rId14" display="https://www.enabot.com/pet-robot/rola-mini" xr:uid="{27A699FA-EF41-449B-A688-367BB2D2FF9B}"/>
+    <hyperlink ref="I6" r:id="rId15" display="https://www.enabot.com/home-robot/ebo-air-2" xr:uid="{647575FE-3C8A-4A98-B07B-48ECD59D1F50}"/>
+    <hyperlink ref="I7" r:id="rId16" display="https://www.enabot.com/home-robot/ebo-air-2s" xr:uid="{9101E83F-ACD4-4CDE-9DCD-76DA195E0ADF}"/>
+    <hyperlink ref="I24" r:id="rId17" display="https://www.amazon.com/chinatera-Wuffy-Robot-Dog-Lifelike/dp/B0GBVGT2TT/ref=sr_1_11?crid=2ZSJTOWRVH3MM&amp;dib=eyJ2IjoiMSJ9.VS90R1zgFrlwmdQJILWsx8m56kTkq9RI8It8FjE6_EsPGshcuFzUHkYPqgtgO3b94hrRhUCeyIZ5TnmhSVHMRIPO2MaXyv8QFBSllfa10huT9VK2WYjvmngpudJWd1rnHAu1bkPiUKRv-UOO-4Gc7oJnLIe5BJhTJsHsp-U4N_E81XPcHef9US6-JWA2YsvOGXw69ZtKIRlYFj3lkLKDUVuERCcbVo8DpKDkFb-Vp2yktqw7RhsPrf1nD1SLe8pHpfqHkeo8Hbp8kDoUiEu4TF2zRnLlNliNXwzhHL1u2zE.GyQtPiCSX6a8bzQBO82HXb9lsAlnDFyQzSpsnNErlKQ&amp;dib_tag=se&amp;keywords=wuffy%2Brobot%2Bdog&amp;qid=1777493502&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=wuffy%2Caps%2C189&amp;sr=8-11&amp;th=1" xr:uid="{D87F9739-8EB7-4B96-8724-048ECAD6590B}"/>
+    <hyperlink ref="I26" r:id="rId18" display="https://www.amazon.com/Perfect-Petzzz-Realistic-Battery-Operated-Interactive/dp/B002PJ37XG/ref=sr_1_1?crid=1LZYEDXW3RV5I&amp;dib=eyJ2IjoiMSJ9.pUlBEkNhfUa4eyzR6zknHIS2YWFT7NFoBnBzNTSb084ARoJgJUsPbq3F1yeWbgPAiE_SE0xe5MWy0y9QLchfwXhi3ceqCN6rD-jmDSXrA0yQxSruxDzk95BxVnqmBIsTTpjw91BYEiV5liGGpZmCKBd2pxsvNWTRk0Eh62VlUb-_5wpaIanBhKn9HwwtQ64CN-ZaeyHPy2Ru0e32vtz84euLzKlZrkooYg9Ao9xkjKNL2Ai-O6H1Dt6MugojLSq5BgQFnsModHhuLtdPaS2IV-Mh2oojRPCRBTC1Rpk4cXQ.RQwNtdUMob0iyv9kxlQ0L7Xmavug8bJnsjamlMM7t7E&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1777495169&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+petzzz%2Caps%2C194&amp;sr=8-1" xr:uid="{5C86EB84-F893-43DE-A55B-125E1B73C946}"/>
+    <hyperlink ref="I27" r:id="rId19" display="https://www.amazon.com/dp/B008Y0QTV2/ref=sspa_dk_hqp_detail_aax_0?psc=1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9ocXBfc2hhcmVk" xr:uid="{5EA03AE2-75D8-46FF-A323-6F9E13327F5E}"/>
+    <hyperlink ref="I28" r:id="rId20" display="https://www.amazon.com/Perfect-Petzzz-Realistic-Interactive-Handcrafted/dp/B0040127N8?pd_rd_w=jx9sh&amp;content-id=amzn1.sym.ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_p=ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_r=6W8C01JJ3VNPS3GPTM6E&amp;pd_rd_wg=EScz2&amp;pd_rd_r=8b92b89c-acde-4bab-8c85-f00ac605c149&amp;ref_=sspa_dk_detail_sbt_1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1" xr:uid="{8D9599B6-7DF6-44AD-B20E-1ABC37923A89}"/>
+    <hyperlink ref="I29" r:id="rId21" display="https://www.amazon.com/Perfect-Pets-International-Sleeping-Beagle/dp/B00279NUFY?psc=1&amp;pd_rd_w=mNONg&amp;content-id=amzn1.sym.ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_p=ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_r=W199027EDH8MX7GDECC3&amp;pd_rd_wg=Kn80z&amp;pd_rd_r=46bdf95b-223f-4163-be9a-8a1d241d6683&amp;ref_=sspa_dk_detail_sbt_1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM=" xr:uid="{0F7C88EE-BD60-40FB-9C03-C5276E99C4ED}"/>
+    <hyperlink ref="I32" r:id="rId22" display="https://www.amazon.com/dp/B0039Y3YOI/ref=sspa_dk_detail_2?psc=1&amp;pd_rd_i=B0039Y3YOI&amp;pd_rd_w=jV6FN&amp;content-id=amzn1.sym.7dc70186-c171-4ad3-b982-b0b7c53e2f49&amp;pf_rd_p=7dc70186-c171-4ad3-b982-b0b7c53e2f49&amp;pf_rd_r=3DRP3XZZ66P886VD0ZFC&amp;pd_rd_wg=uugqL&amp;pd_rd_r=8a18b43f-7351-4cbb-b6ef-1a274737daec&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw" xr:uid="{46700710-23E6-43AA-8971-BF6A11239C4A}"/>
+    <hyperlink ref="I33" r:id="rId23" xr:uid="{4687C11F-7031-4058-A6D5-B94251851D80}"/>
+    <hyperlink ref="I34" r:id="rId24" display="https://www.amazon.com/Perfect-Petzzz-Siamese-Breathing-Puppy/dp/B06ZY3CYX4/ref=sr_1_8?crid=1XJLXJYXVYQ0N&amp;dib=eyJ2IjoiMSJ9.6FAL5yqb0pMjyqjFtFff8rapxTJu7wMCuvWT1oB0FoiCW57t5bub7u1NfN0AA5zBFsU4gc4ytAnzqJApDDdbP0hHkEStYFQ35EFnDZxNAK5TFJM69-45Y77dUTPoYIG8__C0urwPJwptiB9FoReL8Ecf6rveMLte519ejCIqK2WBEkxV_yMxUnuPVSl6wowjx0nWJI1nn61k61TTjBmGiLTxc7Ngd3-geAWUShdDsOGxPjweoq0vBlaSg9orzCV7ZWaOF5itfJDmYObEAQpFHhhK9QkKYlqQnBxC6WSpo6k.qI5Tpy3lpOA4p4BdnoGUTgnQI-eAcDsYtY4VBBLoyVA&amp;dib_tag=se&amp;keywords=perfect+petzzz+cats&amp;qid=1777496385&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+petzzz+cats%2Ctoys-and-games%2C203&amp;sr=1-8" xr:uid="{10510C29-E591-47CB-A65E-91A9694F53AC}"/>
+    <hyperlink ref="I30" r:id="rId25" display="https://www.amazon.com/dp/B004M42ER2/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B004M42ER2&amp;pd_rd_w=AjABt&amp;content-id=amzn1.sym.386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_p=386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_r=7VNR97CX8AWABRX62554&amp;pd_rd_wg=zOSGV&amp;pd_rd_r=20ddc17d-c84f-4870-9b91-0bc9f9332ef1&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM" xr:uid="{D9F8D30D-E2C0-40A9-8471-6903B21AA511}"/>
+    <hyperlink ref="I25" r:id="rId26" xr:uid="{F81372EB-9409-45C8-8BCF-85AC4DD003A3}"/>
+    <hyperlink ref="I35" r:id="rId27" display="https://www.amazon.com/Electronic-Walking-Pomeranian-Realistic-Interactive/dp/B0B7MR3CFP/ref=sr_1_3?crid=YWYC6W0LFAXU&amp;dib=eyJ2IjoiMSJ9.wy5-rpjLPrH786btWTET4c25tGgrSfmH7yKUeHBPqnNkmrB2oigYxDkAS7pVsRNkle8aIk3XYMn2h6clGEEQcDaTE8t8aymZDBt05FYlJ-GH4eGGxBbf7Ig1s82GEwRBiKKOV3G2irleHtBP4F_hv6NMJyknPUtqTpJNj65pspZ7KCByQF56t6QJoxu1YZszw0l8o5_aanUuqTVumwrAlGR2tYS2v5PkCErJz2hiJqJqxLkwsmxHJ9oNRquwCySespKIiJE5o0e8RvyR4sO2Eq00KFSOsAqh0ajB3kjC0xI.NEkZKEQBsFNiMNN-4QrmamwZ0fcTnwcKi8CtPmlcjkQ&amp;dib_tag=se&amp;keywords=milo%2Brobot%2Bpuppy&amp;qid=1777581403&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=milo%2Briobot%2Bpuppy%2Ctoys-and-games%2C181&amp;sr=1-3&amp;th=1" xr:uid="{5EBB9AF1-324C-41A3-9FB0-558087967E28}"/>
+    <hyperlink ref="I36" r:id="rId28" display="https://www.amazon.com/Ruko-18011-Interactive-Expressions-Programmable/dp/B0FLXCXPHD/ref=sr_1_3_sspa?crid=1SVOVUI4YUECO&amp;dib=eyJ2IjoiMSJ9.3hF_MQV4B-IHq5j4jAivqbkOHRO5zitzXHgCaYvxePjfLUaF8FzF13Y5z96sut9I4qI5NacM67aJmQh2fSG_rHl06dBM8XRt-KQiTrQqsdg_DRAMAF6O2o8lA5jxdXD__uSV2k8ElSHQjEhlGuuQU4HNMy8zX_b59y97EMoH341qgn5DLZswbGe9aX94vwYL1Kof4VsrUXg5ppj37Pn6qy_mDKyJRehzAk_7sH96IM1FzhzruTNqKQi1NhP6B6QfJITWm4p1DIKJ-Ocoq5LFohCkcuulJ2yTLS8bprH7tio.qCkDoDZhqdLp3BeSDLRcSP4eqtKCXiY08ZhypI70hPU&amp;dib_tag=se&amp;keywords=robot%2Bdog&amp;qid=1777581735&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot%2Bdog%2Caps%2C227&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{21A8C767-EC55-4D08-AE65-5476028865EE}"/>
+    <hyperlink ref="I37" r:id="rId29" display="https://www.amazon.com/dp/B0DCF53PCH/ref=sspa_dk_detail_right_aax_0?sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfcmlnaHRfc2hhcmVk&amp;th=1" xr:uid="{C1CD4974-517B-4A12-B980-BE333F29C866}"/>
+    <hyperlink ref="I38" r:id="rId30" display="https://www.amazon.com/EMOPET-Desk-Robot-Companion-Interactive/dp/B0DDT2MT9K/ref=sr_1_21?crid=2O5HMBCMPZSCM&amp;dib=eyJ2IjoiMSJ9.tBPkvanml9eOr0jCsfrK3VkgBNveY9G09eBULXTgAJV7bjEY2Hj-IJNQpEKRA7TKPSMtXw8BST0SGzoLoNo4Oj6XaW93ezKXzKP2bpkxhFazfuqf5bcmpjLqtIVqZDb_r1kzyZ3zwqZYDq6f9Asg-Rhq_lB6kZ1exnNbn_ujAMpmNN8RymnrltXuFQPJdqIi0R8rSCt12bvf_aOwVbJlgADdMcJ-ziQh9c0Pw1aZBQRB53IXKJgh3MtIMeEz4i0Arwv7UAXZML42MrR2mrHvuRBnBjvnCkaVLIybi2r8-as.Ct2NuHfWrC-dOFAgBR1gJErliZzv32ERIpSeMowSokg&amp;dib_tag=se&amp;keywords=robot+pets&amp;qid=1777583022&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot+pets%2Ctoys-and-games%2C180&amp;sr=1-21" xr:uid="{971B5E96-FF15-4688-9704-1BDA0E592A7B}"/>
+    <hyperlink ref="I39" r:id="rId31" xr:uid="{A3108714-65E7-4B89-BD81-DD27A31D4994}"/>
+    <hyperlink ref="I14" r:id="rId32" xr:uid="{84BECE61-5789-45D2-9870-323428A767C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId33"/>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8BBB6C-C6B4-4792-A6F3-C1CD7DA137DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486A89E2-B78F-422F-ADF0-CACF61AB432B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -938,7 +938,8 @@
     <col min="4" max="4" width="10.28515625" style="3" customWidth="1"/>
     <col min="5" max="5" width="9.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="6.140625" style="3" customWidth="1"/>
-    <col min="7" max="8" width="9.140625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" style="3" customWidth="1"/>
     <col min="9" max="9" width="98" style="3" customWidth="1"/>
     <col min="10" max="10" width="54.140625" style="3" customWidth="1"/>
     <col min="11" max="11" width="32.140625" style="6" customWidth="1"/>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{486A89E2-B78F-422F-ADF0-CACF61AB432B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DA655E-B545-4397-8AC0-8FC07A536F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="125">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -408,6 +408,12 @@
   </si>
   <si>
     <t>Top Pick</t>
+  </si>
+  <si>
+    <t>/images/products/Mr-Siberian-Husky.png</t>
+  </si>
+  <si>
+    <t>/images/products/Skinny-AI-Cat.png</t>
   </si>
 </sst>
 </file>
@@ -1301,6 +1307,9 @@
       <c r="I10" s="6" t="s">
         <v>91</v>
       </c>
+      <c r="J10" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="K10" s="6" t="s">
         <v>91</v>
       </c>
@@ -1308,7 +1317,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -1335,6 +1344,9 @@
       </c>
       <c r="I11" s="6" t="s">
         <v>91</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>91</v>
@@ -1371,7 +1383,9 @@
       <c r="I12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="2"/>
+      <c r="J12" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="K12" s="6" t="s">
         <v>91</v>
       </c>
@@ -1406,6 +1420,9 @@
       </c>
       <c r="I13" s="6" t="s">
         <v>91</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>92</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>91</v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1DA655E-B545-4397-8AC0-8FC07A536F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A0296D-6993-4DEE-A305-CDA5A5424871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="29430" yWindow="3450" windowWidth="21600" windowHeight="11295" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1299,7 +1299,7 @@
         <v>35</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>36</v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A0296D-6993-4DEE-A305-CDA5A5424871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337CD2C0-261F-493D-85B3-DB117B1FAB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29430" yWindow="3450" windowWidth="21600" windowHeight="11295" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2238,7 +2238,7 @@
         <v>35</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>36</v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{337CD2C0-261F-493D-85B3-DB117B1FAB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDF5101-C602-40CD-9AB8-85E3D3DBE1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="130">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -414,6 +414,21 @@
   </si>
   <si>
     <t>/images/products/Skinny-AI-Cat.png</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Cat</t>
+  </si>
+  <si>
+    <t>Robot</t>
+  </si>
+  <si>
+    <t>Panda</t>
+  </si>
+  <si>
+    <t>Dog</t>
   </si>
 </sst>
 </file>
@@ -556,13 +571,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>75</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
       <xdr:row>76</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -935,27 +950,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:O67"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="31.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="17.85546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" style="3" customWidth="1"/>
-    <col min="6" max="6" width="6.140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="98" style="3" customWidth="1"/>
-    <col min="10" max="10" width="54.140625" style="3" customWidth="1"/>
-    <col min="11" max="11" width="32.140625" style="6" customWidth="1"/>
-    <col min="12" max="12" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="3"/>
+    <col min="3" max="3" width="17.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="17.85546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" style="3" customWidth="1"/>
+    <col min="6" max="6" width="9.7109375" style="3" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="98" style="3" customWidth="1"/>
+    <col min="11" max="11" width="54.140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="32.140625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="6" customFormat="1">
+    <row r="1" spans="1:15" s="6" customFormat="1">
       <c r="A1" s="6" t="s">
         <v>24</v>
       </c>
@@ -963,95 +979,97 @@
         <v>23</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1"/>
+      <c r="D2" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F2" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="O2" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>35</v>
@@ -1059,811 +1077,850 @@
       <c r="H3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N3" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N4" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N5" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="O5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1"/>
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N6" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="O6" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="1"/>
+      <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N7" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="1"/>
+      <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F8" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="1"/>
+      <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C10" s="1"/>
       <c r="D10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I10" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J10" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="K10" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="L10" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15" customHeight="1">
+      <c r="O10" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="15" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C11" s="1"/>
       <c r="D11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F11" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J11" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="K11" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="L11" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="N11" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="O11" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C12" s="1"/>
       <c r="D12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F12" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="K12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="L12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="O12" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C13" s="1"/>
       <c r="D13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J13" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="K13" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="L13" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="N13" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C14" s="1"/>
       <c r="D14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I14" s="7" t="s">
+      <c r="I14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="K14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="N14" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="L14" s="4"/>
+      <c r="O14" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C15" s="1"/>
       <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I15" s="7" t="s">
+      <c r="I15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="K15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="N15" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+      <c r="L15" s="4"/>
+      <c r="O15" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C16" s="1"/>
       <c r="D16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I16" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="2" t="s">
+      <c r="K16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K16" s="4"/>
-      <c r="N16" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" ht="25.5">
+      <c r="L16" s="4"/>
+      <c r="O16" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="25.5">
       <c r="A17" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C17" s="1"/>
       <c r="D17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="K17" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="N17" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" ht="15" customHeight="1">
+      <c r="L17" s="4"/>
+      <c r="O17" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" ht="15" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="C18" s="1"/>
       <c r="D18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I18" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="N18" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+      <c r="L18" s="4"/>
+      <c r="O18" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>26</v>
+      <c r="C19" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O19" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>26</v>
+      <c r="C20" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F20" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I20" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J20" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K20" s="4"/>
-      <c r="N20" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="L20" s="4"/>
+      <c r="O20" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>26</v>
+      <c r="C21" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="D21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I21" s="7" t="s">
+      <c r="I21" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J21" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="J21" s="2" t="s">
+      <c r="K21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="K21" s="4"/>
-      <c r="N21" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" ht="15" customHeight="1">
+      <c r="L21" s="4"/>
+      <c r="O21" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" ht="15" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>26</v>
+      <c r="C22" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="D22" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I22" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K22" s="4"/>
-      <c r="N22" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="L22" s="4"/>
+      <c r="O22" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>26</v>
+      <c r="C23" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I23" s="7" t="s">
+      <c r="I23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J23" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="J23" s="2" t="s">
+      <c r="K23" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="K23" s="5"/>
-      <c r="N23" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" ht="30">
+      <c r="L23" s="5"/>
+      <c r="O23" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" ht="30">
       <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>26</v>
+      <c r="C24" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G24" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I24" s="7" t="s">
+      <c r="I24" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J24" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="J24" s="2" t="s">
+      <c r="K24" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="O24" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>26</v>
+      <c r="C25" s="1" t="s">
+        <v>127</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I25" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="J25" s="2" t="s">
+      <c r="K25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="L25" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="M25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="N25" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" ht="30">
+        <v>35</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" ht="30">
       <c r="A26" s="3" t="s">
         <v>72</v>
       </c>
@@ -1871,31 +1928,34 @@
         <v>73</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G26" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I26" s="7" t="s">
+      <c r="I26" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J26" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J26" s="2" t="s">
+      <c r="K26" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:14" ht="30">
+    <row r="27" spans="1:15" ht="30">
       <c r="A27" s="3" t="s">
         <v>72</v>
       </c>
@@ -1903,31 +1963,34 @@
         <v>75</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G27" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I27" s="7" t="s">
+      <c r="I27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J27" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="J27" s="2" t="s">
+      <c r="K27" s="2" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="28" spans="1:14" ht="30">
+    <row r="28" spans="1:15" ht="30">
       <c r="A28" s="3" t="s">
         <v>72</v>
       </c>
@@ -1935,31 +1998,34 @@
         <v>77</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E28" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F28" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G28" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I28" s="7" t="s">
+      <c r="I28" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J28" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="J28" s="2" t="s">
+      <c r="K28" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="30">
+    <row r="29" spans="1:15" ht="30">
       <c r="A29" s="3" t="s">
         <v>72</v>
       </c>
@@ -1967,63 +2033,66 @@
         <v>79</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>26</v>
+        <v>129</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E29" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F29" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G29" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I29" s="7" t="s">
+      <c r="I29" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J29" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="J29" s="2" t="s">
+      <c r="K29" s="2" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:14" ht="14.25" customHeight="1">
+    <row r="30" spans="1:15" ht="14.25" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>72</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="D30" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G30" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I30" s="7" t="s">
+      <c r="I30" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J30" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="J30" s="2" t="s">
+      <c r="K30" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="31" spans="1:14" ht="14.25" customHeight="1">
+    <row r="31" spans="1:15" ht="14.25" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>72</v>
       </c>
@@ -2031,31 +2100,34 @@
         <v>82</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F31" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G31" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I31" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J31" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="J31" s="2" t="s">
+      <c r="K31" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="32" spans="1:14" ht="14.25" customHeight="1">
+    <row r="32" spans="1:15" ht="14.25" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>72</v>
       </c>
@@ -2063,31 +2135,34 @@
         <v>83</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G32" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I32" s="7" t="s">
+      <c r="I32" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J32" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="1:14" ht="14.25" customHeight="1">
+    <row r="33" spans="1:15" ht="14.25" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>72</v>
       </c>
@@ -2095,31 +2170,34 @@
         <v>85</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G33" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I33" s="7" t="s">
+      <c r="I33" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J33" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="J33" s="2" t="s">
+      <c r="K33" s="2" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="34" spans="1:14" ht="14.25" customHeight="1">
+    <row r="34" spans="1:15" ht="14.25" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>72</v>
       </c>
@@ -2127,248 +2205,269 @@
         <v>87</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>26</v>
+        <v>126</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G34" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I34" s="7" t="s">
+      <c r="I34" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J34" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="J34" s="2" t="s">
+      <c r="K34" s="2" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:14" ht="30">
+    <row r="35" spans="1:15" ht="30">
       <c r="A35" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>26</v>
+      <c r="C35" s="1" t="s">
+        <v>129</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G35" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I35" s="7" t="s">
+      <c r="I35" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J35" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="J35" s="2" t="s">
+      <c r="K35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" ht="30">
+      <c r="O35" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="30">
       <c r="A36" s="3" t="s">
         <v>102</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C36" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="E36" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G36" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I36" s="7" t="s">
+      <c r="I36" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J36" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="J36" s="2" t="s">
+      <c r="K36" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="37" spans="1:14" ht="30">
+    <row r="37" spans="1:15" ht="30">
       <c r="A37" s="3" t="s">
         <v>106</v>
       </c>
       <c r="B37" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C37" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="E37" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G37" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I37" s="7" t="s">
+      <c r="I37" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J37" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J37" s="2" t="s">
+      <c r="K37" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="30">
+    <row r="38" spans="1:15" ht="30">
       <c r="A38" s="3" t="s">
         <v>109</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C38" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="F38" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F38" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G38" s="3" t="s">
         <v>35</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I38" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J38" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="J38" s="2" t="s">
+      <c r="K38" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="27.75" customHeight="1">
+    <row r="39" spans="1:15" ht="27.75" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>112</v>
+      </c>
       <c r="B39" s="3" t="s">
         <v>112</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="E39" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F39" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="G39" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="I39" s="7" t="s">
+      <c r="I39" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J39" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="J39" s="2" t="s">
+      <c r="K39" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="9:9">
-      <c r="I49" s="4"/>
-    </row>
-    <row r="51" spans="9:9">
-      <c r="I51" s="6"/>
-    </row>
-    <row r="57" spans="9:9">
-      <c r="I57" s="8"/>
-    </row>
-    <row r="61" spans="9:9">
-      <c r="I61" s="8"/>
-    </row>
-    <row r="67" spans="9:9">
-      <c r="I67" s="6"/>
+    <row r="46" spans="1:15">
+      <c r="J46" s="4"/>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="J47" s="4"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="J48" s="4"/>
+    </row>
+    <row r="49" spans="10:10">
+      <c r="J49" s="4"/>
+    </row>
+    <row r="51" spans="10:10">
+      <c r="J51" s="6"/>
+    </row>
+    <row r="57" spans="10:10">
+      <c r="J57" s="8"/>
+    </row>
+    <row r="61" spans="10:10">
+      <c r="J61" s="8"/>
+    </row>
+    <row r="67" spans="10:10">
+      <c r="J67" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="I20" r:id="rId1" display="https://chongker.com/products/matecat10-interactive-cat" xr:uid="{6A6B66E7-EFA9-4C01-A8EA-9FC28D138092}"/>
-    <hyperlink ref="I21" r:id="rId2" display="https://chongker.com/products/percy-robotic-dog-companion-designed-for-comfort" xr:uid="{33B7E068-D39E-4359-A980-4956C64F28BD}"/>
-    <hyperlink ref="I22" r:id="rId3" display="https://chongker.com/products/ragdoll-percy-interactive-cat-1-1" xr:uid="{56A80108-DC52-4F38-B5B7-E6F38E8F3ECC}"/>
-    <hyperlink ref="I23" r:id="rId4" display="https://chongker.com/products/breathing-red-panda" xr:uid="{213BB2E5-5459-4A38-992E-7E2658523271}"/>
-    <hyperlink ref="I15" r:id="rId5" xr:uid="{D237B42D-17AA-460F-B784-E8F07972476C}"/>
-    <hyperlink ref="I16" r:id="rId6" xr:uid="{4FB1BAAD-1B59-459D-B076-BEC8534C5468}"/>
-    <hyperlink ref="I18" r:id="rId7" xr:uid="{12CB9543-D99E-401B-A92D-8A43D39066E9}"/>
-    <hyperlink ref="I17" r:id="rId8" xr:uid="{01AA717A-8251-4D9A-981C-C86F4068EC19}"/>
-    <hyperlink ref="I2" r:id="rId9" xr:uid="{61986D39-AC73-4733-851F-E4D8DA4135B4}"/>
-    <hyperlink ref="I3" r:id="rId10" display="https://www.enabot.com/home-robot/ebo-air-2-plus" xr:uid="{4E06DA7A-7CAD-4054-BBE6-70F8B6093B84}"/>
-    <hyperlink ref="I4" r:id="rId11" display="https://www.enabot.com/home-robot/ebo-x" xr:uid="{ADA71D89-8C1B-4B93-A048-545BC5C00388}"/>
-    <hyperlink ref="I5" r:id="rId12" xr:uid="{CB14D57D-F38C-4C0B-8515-8FA7E1CD6C43}"/>
-    <hyperlink ref="I8" r:id="rId13" display="https://www.enabot.com/home-robot/ebo-se" xr:uid="{FA8B4958-90B9-45F8-8B56-98CFC90D7C48}"/>
-    <hyperlink ref="I9" r:id="rId14" display="https://www.enabot.com/pet-robot/rola-mini" xr:uid="{27A699FA-EF41-449B-A688-367BB2D2FF9B}"/>
-    <hyperlink ref="I6" r:id="rId15" display="https://www.enabot.com/home-robot/ebo-air-2" xr:uid="{647575FE-3C8A-4A98-B07B-48ECD59D1F50}"/>
-    <hyperlink ref="I7" r:id="rId16" display="https://www.enabot.com/home-robot/ebo-air-2s" xr:uid="{9101E83F-ACD4-4CDE-9DCD-76DA195E0ADF}"/>
-    <hyperlink ref="I24" r:id="rId17" display="https://www.amazon.com/chinatera-Wuffy-Robot-Dog-Lifelike/dp/B0GBVGT2TT/ref=sr_1_11?crid=2ZSJTOWRVH3MM&amp;dib=eyJ2IjoiMSJ9.VS90R1zgFrlwmdQJILWsx8m56kTkq9RI8It8FjE6_EsPGshcuFzUHkYPqgtgO3b94hrRhUCeyIZ5TnmhSVHMRIPO2MaXyv8QFBSllfa10huT9VK2WYjvmngpudJWd1rnHAu1bkPiUKRv-UOO-4Gc7oJnLIe5BJhTJsHsp-U4N_E81XPcHef9US6-JWA2YsvOGXw69ZtKIRlYFj3lkLKDUVuERCcbVo8DpKDkFb-Vp2yktqw7RhsPrf1nD1SLe8pHpfqHkeo8Hbp8kDoUiEu4TF2zRnLlNliNXwzhHL1u2zE.GyQtPiCSX6a8bzQBO82HXb9lsAlnDFyQzSpsnNErlKQ&amp;dib_tag=se&amp;keywords=wuffy%2Brobot%2Bdog&amp;qid=1777493502&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=wuffy%2Caps%2C189&amp;sr=8-11&amp;th=1" xr:uid="{D87F9739-8EB7-4B96-8724-048ECAD6590B}"/>
-    <hyperlink ref="I26" r:id="rId18" display="https://www.amazon.com/Perfect-Petzzz-Realistic-Battery-Operated-Interactive/dp/B002PJ37XG/ref=sr_1_1?crid=1LZYEDXW3RV5I&amp;dib=eyJ2IjoiMSJ9.pUlBEkNhfUa4eyzR6zknHIS2YWFT7NFoBnBzNTSb084ARoJgJUsPbq3F1yeWbgPAiE_SE0xe5MWy0y9QLchfwXhi3ceqCN6rD-jmDSXrA0yQxSruxDzk95BxVnqmBIsTTpjw91BYEiV5liGGpZmCKBd2pxsvNWTRk0Eh62VlUb-_5wpaIanBhKn9HwwtQ64CN-ZaeyHPy2Ru0e32vtz84euLzKlZrkooYg9Ao9xkjKNL2Ai-O6H1Dt6MugojLSq5BgQFnsModHhuLtdPaS2IV-Mh2oojRPCRBTC1Rpk4cXQ.RQwNtdUMob0iyv9kxlQ0L7Xmavug8bJnsjamlMM7t7E&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1777495169&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+petzzz%2Caps%2C194&amp;sr=8-1" xr:uid="{5C86EB84-F893-43DE-A55B-125E1B73C946}"/>
-    <hyperlink ref="I27" r:id="rId19" display="https://www.amazon.com/dp/B008Y0QTV2/ref=sspa_dk_hqp_detail_aax_0?psc=1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9ocXBfc2hhcmVk" xr:uid="{5EA03AE2-75D8-46FF-A323-6F9E13327F5E}"/>
-    <hyperlink ref="I28" r:id="rId20" display="https://www.amazon.com/Perfect-Petzzz-Realistic-Interactive-Handcrafted/dp/B0040127N8?pd_rd_w=jx9sh&amp;content-id=amzn1.sym.ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_p=ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_r=6W8C01JJ3VNPS3GPTM6E&amp;pd_rd_wg=EScz2&amp;pd_rd_r=8b92b89c-acde-4bab-8c85-f00ac605c149&amp;ref_=sspa_dk_detail_sbt_1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1" xr:uid="{8D9599B6-7DF6-44AD-B20E-1ABC37923A89}"/>
-    <hyperlink ref="I29" r:id="rId21" display="https://www.amazon.com/Perfect-Pets-International-Sleeping-Beagle/dp/B00279NUFY?psc=1&amp;pd_rd_w=mNONg&amp;content-id=amzn1.sym.ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_p=ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_r=W199027EDH8MX7GDECC3&amp;pd_rd_wg=Kn80z&amp;pd_rd_r=46bdf95b-223f-4163-be9a-8a1d241d6683&amp;ref_=sspa_dk_detail_sbt_1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM=" xr:uid="{0F7C88EE-BD60-40FB-9C03-C5276E99C4ED}"/>
-    <hyperlink ref="I32" r:id="rId22" display="https://www.amazon.com/dp/B0039Y3YOI/ref=sspa_dk_detail_2?psc=1&amp;pd_rd_i=B0039Y3YOI&amp;pd_rd_w=jV6FN&amp;content-id=amzn1.sym.7dc70186-c171-4ad3-b982-b0b7c53e2f49&amp;pf_rd_p=7dc70186-c171-4ad3-b982-b0b7c53e2f49&amp;pf_rd_r=3DRP3XZZ66P886VD0ZFC&amp;pd_rd_wg=uugqL&amp;pd_rd_r=8a18b43f-7351-4cbb-b6ef-1a274737daec&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw" xr:uid="{46700710-23E6-43AA-8971-BF6A11239C4A}"/>
-    <hyperlink ref="I33" r:id="rId23" xr:uid="{4687C11F-7031-4058-A6D5-B94251851D80}"/>
-    <hyperlink ref="I34" r:id="rId24" display="https://www.amazon.com/Perfect-Petzzz-Siamese-Breathing-Puppy/dp/B06ZY3CYX4/ref=sr_1_8?crid=1XJLXJYXVYQ0N&amp;dib=eyJ2IjoiMSJ9.6FAL5yqb0pMjyqjFtFff8rapxTJu7wMCuvWT1oB0FoiCW57t5bub7u1NfN0AA5zBFsU4gc4ytAnzqJApDDdbP0hHkEStYFQ35EFnDZxNAK5TFJM69-45Y77dUTPoYIG8__C0urwPJwptiB9FoReL8Ecf6rveMLte519ejCIqK2WBEkxV_yMxUnuPVSl6wowjx0nWJI1nn61k61TTjBmGiLTxc7Ngd3-geAWUShdDsOGxPjweoq0vBlaSg9orzCV7ZWaOF5itfJDmYObEAQpFHhhK9QkKYlqQnBxC6WSpo6k.qI5Tpy3lpOA4p4BdnoGUTgnQI-eAcDsYtY4VBBLoyVA&amp;dib_tag=se&amp;keywords=perfect+petzzz+cats&amp;qid=1777496385&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+petzzz+cats%2Ctoys-and-games%2C203&amp;sr=1-8" xr:uid="{10510C29-E591-47CB-A65E-91A9694F53AC}"/>
-    <hyperlink ref="I30" r:id="rId25" display="https://www.amazon.com/dp/B004M42ER2/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B004M42ER2&amp;pd_rd_w=AjABt&amp;content-id=amzn1.sym.386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_p=386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_r=7VNR97CX8AWABRX62554&amp;pd_rd_wg=zOSGV&amp;pd_rd_r=20ddc17d-c84f-4870-9b91-0bc9f9332ef1&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM" xr:uid="{D9F8D30D-E2C0-40A9-8471-6903B21AA511}"/>
-    <hyperlink ref="I25" r:id="rId26" xr:uid="{F81372EB-9409-45C8-8BCF-85AC4DD003A3}"/>
-    <hyperlink ref="I35" r:id="rId27" display="https://www.amazon.com/Electronic-Walking-Pomeranian-Realistic-Interactive/dp/B0B7MR3CFP/ref=sr_1_3?crid=YWYC6W0LFAXU&amp;dib=eyJ2IjoiMSJ9.wy5-rpjLPrH786btWTET4c25tGgrSfmH7yKUeHBPqnNkmrB2oigYxDkAS7pVsRNkle8aIk3XYMn2h6clGEEQcDaTE8t8aymZDBt05FYlJ-GH4eGGxBbf7Ig1s82GEwRBiKKOV3G2irleHtBP4F_hv6NMJyknPUtqTpJNj65pspZ7KCByQF56t6QJoxu1YZszw0l8o5_aanUuqTVumwrAlGR2tYS2v5PkCErJz2hiJqJqxLkwsmxHJ9oNRquwCySespKIiJE5o0e8RvyR4sO2Eq00KFSOsAqh0ajB3kjC0xI.NEkZKEQBsFNiMNN-4QrmamwZ0fcTnwcKi8CtPmlcjkQ&amp;dib_tag=se&amp;keywords=milo%2Brobot%2Bpuppy&amp;qid=1777581403&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=milo%2Briobot%2Bpuppy%2Ctoys-and-games%2C181&amp;sr=1-3&amp;th=1" xr:uid="{5EBB9AF1-324C-41A3-9FB0-558087967E28}"/>
-    <hyperlink ref="I36" r:id="rId28" display="https://www.amazon.com/Ruko-18011-Interactive-Expressions-Programmable/dp/B0FLXCXPHD/ref=sr_1_3_sspa?crid=1SVOVUI4YUECO&amp;dib=eyJ2IjoiMSJ9.3hF_MQV4B-IHq5j4jAivqbkOHRO5zitzXHgCaYvxePjfLUaF8FzF13Y5z96sut9I4qI5NacM67aJmQh2fSG_rHl06dBM8XRt-KQiTrQqsdg_DRAMAF6O2o8lA5jxdXD__uSV2k8ElSHQjEhlGuuQU4HNMy8zX_b59y97EMoH341qgn5DLZswbGe9aX94vwYL1Kof4VsrUXg5ppj37Pn6qy_mDKyJRehzAk_7sH96IM1FzhzruTNqKQi1NhP6B6QfJITWm4p1DIKJ-Ocoq5LFohCkcuulJ2yTLS8bprH7tio.qCkDoDZhqdLp3BeSDLRcSP4eqtKCXiY08ZhypI70hPU&amp;dib_tag=se&amp;keywords=robot%2Bdog&amp;qid=1777581735&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot%2Bdog%2Caps%2C227&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{21A8C767-EC55-4D08-AE65-5476028865EE}"/>
-    <hyperlink ref="I37" r:id="rId29" display="https://www.amazon.com/dp/B0DCF53PCH/ref=sspa_dk_detail_right_aax_0?sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfcmlnaHRfc2hhcmVk&amp;th=1" xr:uid="{C1CD4974-517B-4A12-B980-BE333F29C866}"/>
-    <hyperlink ref="I38" r:id="rId30" display="https://www.amazon.com/EMOPET-Desk-Robot-Companion-Interactive/dp/B0DDT2MT9K/ref=sr_1_21?crid=2O5HMBCMPZSCM&amp;dib=eyJ2IjoiMSJ9.tBPkvanml9eOr0jCsfrK3VkgBNveY9G09eBULXTgAJV7bjEY2Hj-IJNQpEKRA7TKPSMtXw8BST0SGzoLoNo4Oj6XaW93ezKXzKP2bpkxhFazfuqf5bcmpjLqtIVqZDb_r1kzyZ3zwqZYDq6f9Asg-Rhq_lB6kZ1exnNbn_ujAMpmNN8RymnrltXuFQPJdqIi0R8rSCt12bvf_aOwVbJlgADdMcJ-ziQh9c0Pw1aZBQRB53IXKJgh3MtIMeEz4i0Arwv7UAXZML42MrR2mrHvuRBnBjvnCkaVLIybi2r8-as.Ct2NuHfWrC-dOFAgBR1gJErliZzv32ERIpSeMowSokg&amp;dib_tag=se&amp;keywords=robot+pets&amp;qid=1777583022&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot+pets%2Ctoys-and-games%2C180&amp;sr=1-21" xr:uid="{971B5E96-FF15-4688-9704-1BDA0E592A7B}"/>
-    <hyperlink ref="I39" r:id="rId31" xr:uid="{A3108714-65E7-4B89-BD81-DD27A31D4994}"/>
-    <hyperlink ref="I14" r:id="rId32" xr:uid="{84BECE61-5789-45D2-9870-323428A767C6}"/>
+    <hyperlink ref="J20" r:id="rId1" display="https://chongker.com/products/matecat10-interactive-cat" xr:uid="{6A6B66E7-EFA9-4C01-A8EA-9FC28D138092}"/>
+    <hyperlink ref="J21" r:id="rId2" display="https://chongker.com/products/percy-robotic-dog-companion-designed-for-comfort" xr:uid="{33B7E068-D39E-4359-A980-4956C64F28BD}"/>
+    <hyperlink ref="J22" r:id="rId3" display="https://chongker.com/products/ragdoll-percy-interactive-cat-1-1" xr:uid="{56A80108-DC52-4F38-B5B7-E6F38E8F3ECC}"/>
+    <hyperlink ref="J23" r:id="rId4" display="https://chongker.com/products/breathing-red-panda" xr:uid="{213BB2E5-5459-4A38-992E-7E2658523271}"/>
+    <hyperlink ref="J15" r:id="rId5" xr:uid="{D237B42D-17AA-460F-B784-E8F07972476C}"/>
+    <hyperlink ref="J16" r:id="rId6" xr:uid="{4FB1BAAD-1B59-459D-B076-BEC8534C5468}"/>
+    <hyperlink ref="J18" r:id="rId7" xr:uid="{12CB9543-D99E-401B-A92D-8A43D39066E9}"/>
+    <hyperlink ref="J17" r:id="rId8" xr:uid="{01AA717A-8251-4D9A-981C-C86F4068EC19}"/>
+    <hyperlink ref="J2" r:id="rId9" xr:uid="{61986D39-AC73-4733-851F-E4D8DA4135B4}"/>
+    <hyperlink ref="J3" r:id="rId10" display="https://www.enabot.com/home-robot/ebo-air-2-plus" xr:uid="{4E06DA7A-7CAD-4054-BBE6-70F8B6093B84}"/>
+    <hyperlink ref="J4" r:id="rId11" display="https://www.enabot.com/home-robot/ebo-x" xr:uid="{ADA71D89-8C1B-4B93-A048-545BC5C00388}"/>
+    <hyperlink ref="J5" r:id="rId12" xr:uid="{CB14D57D-F38C-4C0B-8515-8FA7E1CD6C43}"/>
+    <hyperlink ref="J8" r:id="rId13" display="https://www.enabot.com/home-robot/ebo-se" xr:uid="{FA8B4958-90B9-45F8-8B56-98CFC90D7C48}"/>
+    <hyperlink ref="J9" r:id="rId14" display="https://www.enabot.com/pet-robot/rola-mini" xr:uid="{27A699FA-EF41-449B-A688-367BB2D2FF9B}"/>
+    <hyperlink ref="J6" r:id="rId15" display="https://www.enabot.com/home-robot/ebo-air-2" xr:uid="{647575FE-3C8A-4A98-B07B-48ECD59D1F50}"/>
+    <hyperlink ref="J7" r:id="rId16" display="https://www.enabot.com/home-robot/ebo-air-2s" xr:uid="{9101E83F-ACD4-4CDE-9DCD-76DA195E0ADF}"/>
+    <hyperlink ref="J24" r:id="rId17" display="https://www.amazon.com/chinatera-Wuffy-Robot-Dog-Lifelike/dp/B0GBVGT2TT/ref=sr_1_11?crid=2ZSJTOWRVH3MM&amp;dib=eyJ2IjoiMSJ9.VS90R1zgFrlwmdQJILWsx8m56kTkq9RI8It8FjE6_EsPGshcuFzUHkYPqgtgO3b94hrRhUCeyIZ5TnmhSVHMRIPO2MaXyv8QFBSllfa10huT9VK2WYjvmngpudJWd1rnHAu1bkPiUKRv-UOO-4Gc7oJnLIe5BJhTJsHsp-U4N_E81XPcHef9US6-JWA2YsvOGXw69ZtKIRlYFj3lkLKDUVuERCcbVo8DpKDkFb-Vp2yktqw7RhsPrf1nD1SLe8pHpfqHkeo8Hbp8kDoUiEu4TF2zRnLlNliNXwzhHL1u2zE.GyQtPiCSX6a8bzQBO82HXb9lsAlnDFyQzSpsnNErlKQ&amp;dib_tag=se&amp;keywords=wuffy%2Brobot%2Bdog&amp;qid=1777493502&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=wuffy%2Caps%2C189&amp;sr=8-11&amp;th=1" xr:uid="{D87F9739-8EB7-4B96-8724-048ECAD6590B}"/>
+    <hyperlink ref="J26" r:id="rId18" display="https://www.amazon.com/Perfect-Petzzz-Realistic-Battery-Operated-Interactive/dp/B002PJ37XG/ref=sr_1_1?crid=1LZYEDXW3RV5I&amp;dib=eyJ2IjoiMSJ9.pUlBEkNhfUa4eyzR6zknHIS2YWFT7NFoBnBzNTSb084ARoJgJUsPbq3F1yeWbgPAiE_SE0xe5MWy0y9QLchfwXhi3ceqCN6rD-jmDSXrA0yQxSruxDzk95BxVnqmBIsTTpjw91BYEiV5liGGpZmCKBd2pxsvNWTRk0Eh62VlUb-_5wpaIanBhKn9HwwtQ64CN-ZaeyHPy2Ru0e32vtz84euLzKlZrkooYg9Ao9xkjKNL2Ai-O6H1Dt6MugojLSq5BgQFnsModHhuLtdPaS2IV-Mh2oojRPCRBTC1Rpk4cXQ.RQwNtdUMob0iyv9kxlQ0L7Xmavug8bJnsjamlMM7t7E&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1777495169&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+petzzz%2Caps%2C194&amp;sr=8-1" xr:uid="{5C86EB84-F893-43DE-A55B-125E1B73C946}"/>
+    <hyperlink ref="J27" r:id="rId19" display="https://www.amazon.com/dp/B008Y0QTV2/ref=sspa_dk_hqp_detail_aax_0?psc=1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9ocXBfc2hhcmVk" xr:uid="{5EA03AE2-75D8-46FF-A323-6F9E13327F5E}"/>
+    <hyperlink ref="J28" r:id="rId20" display="https://www.amazon.com/Perfect-Petzzz-Realistic-Interactive-Handcrafted/dp/B0040127N8?pd_rd_w=jx9sh&amp;content-id=amzn1.sym.ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_p=ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_r=6W8C01JJ3VNPS3GPTM6E&amp;pd_rd_wg=EScz2&amp;pd_rd_r=8b92b89c-acde-4bab-8c85-f00ac605c149&amp;ref_=sspa_dk_detail_sbt_1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM&amp;th=1" xr:uid="{8D9599B6-7DF6-44AD-B20E-1ABC37923A89}"/>
+    <hyperlink ref="J29" r:id="rId21" display="https://www.amazon.com/Perfect-Pets-International-Sleeping-Beagle/dp/B00279NUFY?psc=1&amp;pd_rd_w=mNONg&amp;content-id=amzn1.sym.ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_p=ea1d9533-fbb7-4608-bb6f-bfdceb6f6336&amp;pf_rd_r=W199027EDH8MX7GDECC3&amp;pd_rd_wg=Kn80z&amp;pd_rd_r=46bdf95b-223f-4163-be9a-8a1d241d6683&amp;ref_=sspa_dk_detail_sbt_1&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM=" xr:uid="{0F7C88EE-BD60-40FB-9C03-C5276E99C4ED}"/>
+    <hyperlink ref="J32" r:id="rId22" display="https://www.amazon.com/dp/B0039Y3YOI/ref=sspa_dk_detail_2?psc=1&amp;pd_rd_i=B0039Y3YOI&amp;pd_rd_w=jV6FN&amp;content-id=amzn1.sym.7dc70186-c171-4ad3-b982-b0b7c53e2f49&amp;pf_rd_p=7dc70186-c171-4ad3-b982-b0b7c53e2f49&amp;pf_rd_r=3DRP3XZZ66P886VD0ZFC&amp;pd_rd_wg=uugqL&amp;pd_rd_r=8a18b43f-7351-4cbb-b6ef-1a274737daec&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWw" xr:uid="{46700710-23E6-43AA-8971-BF6A11239C4A}"/>
+    <hyperlink ref="J33" r:id="rId23" xr:uid="{4687C11F-7031-4058-A6D5-B94251851D80}"/>
+    <hyperlink ref="J34" r:id="rId24" display="https://www.amazon.com/Perfect-Petzzz-Siamese-Breathing-Puppy/dp/B06ZY3CYX4/ref=sr_1_8?crid=1XJLXJYXVYQ0N&amp;dib=eyJ2IjoiMSJ9.6FAL5yqb0pMjyqjFtFff8rapxTJu7wMCuvWT1oB0FoiCW57t5bub7u1NfN0AA5zBFsU4gc4ytAnzqJApDDdbP0hHkEStYFQ35EFnDZxNAK5TFJM69-45Y77dUTPoYIG8__C0urwPJwptiB9FoReL8Ecf6rveMLte519ejCIqK2WBEkxV_yMxUnuPVSl6wowjx0nWJI1nn61k61TTjBmGiLTxc7Ngd3-geAWUShdDsOGxPjweoq0vBlaSg9orzCV7ZWaOF5itfJDmYObEAQpFHhhK9QkKYlqQnBxC6WSpo6k.qI5Tpy3lpOA4p4BdnoGUTgnQI-eAcDsYtY4VBBLoyVA&amp;dib_tag=se&amp;keywords=perfect+petzzz+cats&amp;qid=1777496385&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=perfect+petzzz+cats%2Ctoys-and-games%2C203&amp;sr=1-8" xr:uid="{10510C29-E591-47CB-A65E-91A9694F53AC}"/>
+    <hyperlink ref="J30" r:id="rId25" display="https://www.amazon.com/dp/B004M42ER2/ref=sspa_dk_detail_0?psc=1&amp;pd_rd_i=B004M42ER2&amp;pd_rd_w=AjABt&amp;content-id=amzn1.sym.386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_p=386c274b-4bfe-4421-9052-a1a56db557ab&amp;pf_rd_r=7VNR97CX8AWABRX62554&amp;pd_rd_wg=zOSGV&amp;pd_rd_r=20ddc17d-c84f-4870-9b91-0bc9f9332ef1&amp;s=toys-and-games&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfdGhlbWF0aWM" xr:uid="{D9F8D30D-E2C0-40A9-8471-6903B21AA511}"/>
+    <hyperlink ref="J25" r:id="rId26" xr:uid="{F81372EB-9409-45C8-8BCF-85AC4DD003A3}"/>
+    <hyperlink ref="J35" r:id="rId27" display="https://www.amazon.com/Electronic-Walking-Pomeranian-Realistic-Interactive/dp/B0B7MR3CFP/ref=sr_1_3?crid=YWYC6W0LFAXU&amp;dib=eyJ2IjoiMSJ9.wy5-rpjLPrH786btWTET4c25tGgrSfmH7yKUeHBPqnNkmrB2oigYxDkAS7pVsRNkle8aIk3XYMn2h6clGEEQcDaTE8t8aymZDBt05FYlJ-GH4eGGxBbf7Ig1s82GEwRBiKKOV3G2irleHtBP4F_hv6NMJyknPUtqTpJNj65pspZ7KCByQF56t6QJoxu1YZszw0l8o5_aanUuqTVumwrAlGR2tYS2v5PkCErJz2hiJqJqxLkwsmxHJ9oNRquwCySespKIiJE5o0e8RvyR4sO2Eq00KFSOsAqh0ajB3kjC0xI.NEkZKEQBsFNiMNN-4QrmamwZ0fcTnwcKi8CtPmlcjkQ&amp;dib_tag=se&amp;keywords=milo%2Brobot%2Bpuppy&amp;qid=1777581403&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=milo%2Briobot%2Bpuppy%2Ctoys-and-games%2C181&amp;sr=1-3&amp;th=1" xr:uid="{5EBB9AF1-324C-41A3-9FB0-558087967E28}"/>
+    <hyperlink ref="J36" r:id="rId28" display="https://www.amazon.com/Ruko-18011-Interactive-Expressions-Programmable/dp/B0FLXCXPHD/ref=sr_1_3_sspa?crid=1SVOVUI4YUECO&amp;dib=eyJ2IjoiMSJ9.3hF_MQV4B-IHq5j4jAivqbkOHRO5zitzXHgCaYvxePjfLUaF8FzF13Y5z96sut9I4qI5NacM67aJmQh2fSG_rHl06dBM8XRt-KQiTrQqsdg_DRAMAF6O2o8lA5jxdXD__uSV2k8ElSHQjEhlGuuQU4HNMy8zX_b59y97EMoH341qgn5DLZswbGe9aX94vwYL1Kof4VsrUXg5ppj37Pn6qy_mDKyJRehzAk_7sH96IM1FzhzruTNqKQi1NhP6B6QfJITWm4p1DIKJ-Ocoq5LFohCkcuulJ2yTLS8bprH7tio.qCkDoDZhqdLp3BeSDLRcSP4eqtKCXiY08ZhypI70hPU&amp;dib_tag=se&amp;keywords=robot%2Bdog&amp;qid=1777581735&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot%2Bdog%2Caps%2C227&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{21A8C767-EC55-4D08-AE65-5476028865EE}"/>
+    <hyperlink ref="J37" r:id="rId29" display="https://www.amazon.com/dp/B0DCF53PCH/ref=sspa_dk_detail_right_aax_0?sp_csd=d2lkZ2V0TmFtZT1zcF9kZXRhaWxfcmlnaHRfc2hhcmVk&amp;th=1" xr:uid="{C1CD4974-517B-4A12-B980-BE333F29C866}"/>
+    <hyperlink ref="J38" r:id="rId30" display="https://www.amazon.com/EMOPET-Desk-Robot-Companion-Interactive/dp/B0DDT2MT9K/ref=sr_1_21?crid=2O5HMBCMPZSCM&amp;dib=eyJ2IjoiMSJ9.tBPkvanml9eOr0jCsfrK3VkgBNveY9G09eBULXTgAJV7bjEY2Hj-IJNQpEKRA7TKPSMtXw8BST0SGzoLoNo4Oj6XaW93ezKXzKP2bpkxhFazfuqf5bcmpjLqtIVqZDb_r1kzyZ3zwqZYDq6f9Asg-Rhq_lB6kZ1exnNbn_ujAMpmNN8RymnrltXuFQPJdqIi0R8rSCt12bvf_aOwVbJlgADdMcJ-ziQh9c0Pw1aZBQRB53IXKJgh3MtIMeEz4i0Arwv7UAXZML42MrR2mrHvuRBnBjvnCkaVLIybi2r8-as.Ct2NuHfWrC-dOFAgBR1gJErliZzv32ERIpSeMowSokg&amp;dib_tag=se&amp;keywords=robot+pets&amp;qid=1777583022&amp;s=toys-and-games&amp;sbo=RZvfv%2F%2FHxDF%2BO5021pAnSA%3D%3D&amp;sprefix=robot+pets%2Ctoys-and-games%2C180&amp;sr=1-21" xr:uid="{971B5E96-FF15-4688-9704-1BDA0E592A7B}"/>
+    <hyperlink ref="J39" r:id="rId31" xr:uid="{A3108714-65E7-4B89-BD81-DD27A31D4994}"/>
+    <hyperlink ref="J14" r:id="rId32" xr:uid="{84BECE61-5789-45D2-9870-323428A767C6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId33"/>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDF5101-C602-40CD-9AB8-85E3D3DBE1A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925814D4-C06D-4286-A16F-D672CA96B3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="29430" yWindow="3450" windowWidth="21600" windowHeight="11295" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="130">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -1025,7 +1025,9 @@
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D2" s="3" t="s">
         <v>25</v>
       </c>
@@ -1061,7 +1063,9 @@
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="1"/>
+      <c r="C3" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
@@ -1097,7 +1101,9 @@
       <c r="B4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
@@ -1133,7 +1139,9 @@
       <c r="B5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1"/>
+      <c r="C5" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
@@ -1169,7 +1177,9 @@
       <c r="B6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C6" s="1"/>
+      <c r="C6" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
@@ -1205,7 +1215,9 @@
       <c r="B7" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C7" s="1"/>
+      <c r="C7" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D7" s="3" t="s">
         <v>25</v>
       </c>
@@ -1241,7 +1253,9 @@
       <c r="B8" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
@@ -1277,7 +1291,9 @@
       <c r="B9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1" t="s">
+        <v>127</v>
+      </c>
       <c r="D9" s="3" t="s">
         <v>25</v>
       </c>
@@ -1313,7 +1329,9 @@
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="D10" s="3" t="s">
         <v>26</v>
       </c>
@@ -1352,7 +1370,9 @@
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
       </c>
@@ -1391,7 +1411,9 @@
       <c r="B12" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
       </c>
@@ -1430,7 +1452,9 @@
       <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="1"/>
+      <c r="C13" s="1" t="s">
+        <v>128</v>
+      </c>
       <c r="D13" s="3" t="s">
         <v>26</v>
       </c>
@@ -1469,7 +1493,9 @@
       <c r="B14" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
@@ -1506,7 +1532,9 @@
       <c r="B15" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1" t="s">
+        <v>129</v>
+      </c>
       <c r="D15" s="3" t="s">
         <v>26</v>
       </c>
@@ -1543,7 +1571,9 @@
       <c r="B16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="D16" s="3" t="s">
         <v>26</v>
       </c>
@@ -1580,7 +1610,9 @@
       <c r="B17" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="D17" s="3" t="s">
         <v>26</v>
       </c>
@@ -1617,7 +1649,9 @@
       <c r="B18" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1" t="s">
+        <v>126</v>
+      </c>
       <c r="D18" s="3" t="s">
         <v>26</v>
       </c>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925814D4-C06D-4286-A16F-D672CA96B3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405AB452-4624-4231-88FF-97249EE70EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="29430" yWindow="3450" windowWidth="21600" windowHeight="11295" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="130">
   <si>
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
@@ -2101,6 +2101,9 @@
       <c r="B30" s="3" t="s">
         <v>81</v>
       </c>
+      <c r="C30" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="D30" s="3" t="s">
         <v>26</v>
       </c>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9950C54A-CB0D-4B92-9B2D-30C9C61AC787}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D286B1-3F33-4503-82F7-74543C637280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Lists" sheetId="2" r:id="rId2"/>
-    <sheet name="Maybe Later" sheetId="3" r:id="rId3"/>
+    <sheet name="NOTES on Pasting URLs" sheetId="4" r:id="rId2"/>
+    <sheet name="Lists" sheetId="2" r:id="rId3"/>
+    <sheet name="Maybe Later" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="252">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -577,9 +578,6 @@
     <t>Original Beagle</t>
   </si>
   <si>
-    <t>Original Calico Cat</t>
-  </si>
-  <si>
     <t>Original Plush White Cat</t>
   </si>
   <si>
@@ -707,6 +705,99 @@
   </si>
   <si>
     <t>Affordable  breathing, super cuddly cat.</t>
+  </si>
+  <si>
+    <t>Product URL</t>
+  </si>
+  <si>
+    <t>https://joyforall.com/products/companion-pet-pup?variant=37624426102967</t>
+  </si>
+  <si>
+    <t>https://joyforall.com/products/companion-cats?variant=10404273487915</t>
+  </si>
+  <si>
+    <t>https://joyforall.com/products/companion-cats?variant=10404273455147</t>
+  </si>
+  <si>
+    <t>https://joyforall.com/products/companion-cats?variant=12931092676651</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/matecat-pro-hyper-realistic-bionic-cat</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/matecat10-interactive-cat</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/percy-robotic-dog-companion-designed-for-comfort</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/percy-interactive-cat</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/breathing-red-panda</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=wuffy+robot+dog&amp;crid=19CKEYDLEBH6A&amp;sprefix=wuffy%2Caps%2C185&amp;ref=nb_sb_ss_p13n-expert-pd-ops-ranker_1_5</t>
+  </si>
+  <si>
+    <t>1) Paste using "Pastes Special" then " Text".</t>
+  </si>
+  <si>
+    <t>https://ropetai.com/products/ropet%E2%84%A2-ai-comfort-companion-plush-robot</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Petzzz-Realistic-Battery-Operated-Interactive/dp/B002PJ37XG/ref=sr_1_2_sspa?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1778523937&amp;sprefix=perfect+petzzz%2Caps%2C211&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Petzzz-Chocolate-Lab-Plush/dp/B008Y0QTV2/ref=sr_1_8?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1778523937&amp;sprefix=perfect+petzzz%2Caps%2C211&amp;sr=8-8</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Petzzz-Realistic-Interactive-Handcrafted/dp/B0040127N8/ref=sr_1_3_sspa?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect%2Bpetzzz&amp;qid=1778523937&amp;sprefix=perfect%2Bpetzzz%2Caps%2C211&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Pets-International-Sleeping-Beagle/dp/B00279NUFY/ref=sr_1_5_sspa?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1778523937&amp;sprefix=perfect+petzzz%2Caps%2C211&amp;sr=8-5-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>Grey Tabby Cat</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Petzzz-Grey-Tabby-Cat/dp/B001TEYF84/ref=sr_1_8?crid=2T22Q9EUUJM90&amp;dib=eyJ2IjoiMSJ9.hw6TypsZgESbto-buC1HDI4zkFKuEs_aZuDM1EyKtr6WMK5ujTDCsWqeBHo8NQXCQtSa2IvHEO7U7N5C9BqYswU3xQD4TTNS-o45TDdrU0HnP_VoaxAErFkDkTd1rvIrVmhSyuNik71aum-TjrRD2GX09FJnAP0OK02Hum5oU0BmsaEYvdvVa-8GYzPoFgs-oRfgW4NaXCGNL1Pq7yYK_t2KOpHjRz3ZY6vhT6O2HP4sYnESDaBDi5ox5WCZXFGJXfp-JCufCzCnRahRloAUi6PfXofSLhrC8i-96X4Vi3w.4yMBJHpLoLosQajGsVB3apXivL14iW3bkJBuB2GL6rI&amp;dib_tag=se&amp;keywords=perfect+petzzz+cat&amp;qid=1778524149&amp;sprefix=perfect+petzzz+cat%2Caps%2C158&amp;sr=8-8</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Petzzz-4934-Peluche-Blanc/dp/B00CZC87Y2/ref=sr_1_7?crid=2T22Q9EUUJM90&amp;dib=eyJ2IjoiMSJ9.hw6TypsZgESbto-buC1HDI4zkFKuEs_aZuDM1EyKtr6WMK5ujTDCsWqeBHo8NQXCQtSa2IvHEO7U7N5C9BqYswU3xQD4TTNS-o45TDdrU0HnP_VoaxAErFkDkTd1rvIrVmhSyuNik71aum-TjrRD2GX09FJnAP0OK02Hum5oU0BmsaEYvdvVa-8GYzPoFgs-oRfgW4NaXCGNL1Pq7yYK_t2KOpHjRz3ZY6vhT6O2HP4sYnESDaBDi5ox5WCZXFGJXfp-JCufCzCnRahRloAUi6PfXofSLhrC8i-96X4Vi3w.4yMBJHpLoLosQajGsVB3apXivL14iW3bkJBuB2GL6rI&amp;dib_tag=se&amp;keywords=perfect+petzzz+cat&amp;qid=1778524149&amp;sprefix=perfect+petzzz+cat%2Caps%2C158&amp;sr=8-7</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Petzzz-Black-Shorthair-Kitten/dp/B003XSJ4YE/ref=sr_1_3_sspa?crid=2T22Q9EUUJM90&amp;dib=eyJ2IjoiMSJ9.hw6TypsZgESbto-buC1HDI4zkFKuEs_aZuDM1EyKtr6WMK5ujTDCsWqeBHo8NQXCQtSa2IvHEO7U7N5C9BqYswU3xQD4TTNS-o45TDdrU0HnP_VoaxAErFkDkTd1rvIrVmhSyuNik71aum-TjrRD2GX09FJnAP0OK02Hum5oU0BmsaEYvdvVa-8GYzPoFgs-oRfgW4NaXCGNL1Pq7yYK_t2KOpHjRz3ZY6vhT6O2HP4sYnESDaBDi5ox5WCZXFGJXfp-JCufCzCnRahRloAUi6PfXofSLhrC8i-96X4Vi3w.4yMBJHpLoLosQajGsVB3apXivL14iW3bkJBuB2GL6rI&amp;dib_tag=se&amp;keywords=perfect+petzzz+cat&amp;qid=1778524149&amp;sprefix=perfect+petzzz+cat%2Caps%2C158&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Perfect-Petzzz-Siamese-Breathing-Puppy/dp/B06ZY3CYX4/ref=sr_1_6?crid=2T22Q9EUUJM90&amp;dib=eyJ2IjoiMSJ9.hw6TypsZgESbto-buC1HDI4zkFKuEs_aZuDM1EyKtr6WMK5ujTDCsWqeBHo8NQXCQtSa2IvHEO7U7N5C9BqYswU3xQD4TTNS-o45TDdrU0HnP_VoaxAErFkDkTd1rvIrVmhSyuNik71aum-TjrRD2GX09FJnAP0OK02Hum5oU0BmsaEYvdvVa-8GYzPoFgs-oRfgW4NaXCGNL1Pq7yYK_t2KOpHjRz3ZY6vhT6O2HP4sYnESDaBDi5ox5WCZXFGJXfp-JCufCzCnRahRloAUi6PfXofSLhrC8i-96X4Vi3w.4yMBJHpLoLosQajGsVB3apXivL14iW3bkJBuB2GL6rI&amp;dib_tag=se&amp;keywords=perfect+petzzz+cat&amp;qid=1778524149&amp;sprefix=perfect+petzzz+cat%2Caps%2C158&amp;sr=8-6</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Ruko-18011-Interactive-Expressions-Programmable/dp/B0FLXCXPHD/ref=sr_1_2_sspa?crid=3Q84O44BMP4I1&amp;dib=eyJ2IjoiMSJ9.5Gly7Ov9TtkvwLAe4rZwH2l-BTiwaFOMLi92o4eo2efL59RBhuAyz5dL1llQO9Oq3VOvL554UZdKGuCvEr0aULc0FuaW-0tXMv-Su3A0pJUYX216NZD-8OUNQh6gxNKl8ATh6D7HDFqXqh-HftmgAQSnm2CAImjyhEseHeartYBrk0RKnk_qongpk7N2LmhhFwKFgq-JlfQJBXAYeXfjdZ53H5tQAmhJmbXnYWxOCYV0NtCgyyMVmml1rR7tZkoyjG_4I2LrxuOnAJYrH2drb6GCU0NIUssYnsjouZhfUF4.-br2EkX1bjJZyuScMeKTaBh68fd6MSebkMG0MoeTeO0&amp;dib_tag=se&amp;keywords=ruko%2Brobot&amp;qid=1778524458&amp;sprefix=ruko%2Caps%2C210&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=furby+dj&amp;crid=1U6BER2BCWJV5&amp;sprefix=furby+%2Caps%2C205&amp;ref=nb_sb_ss_p13n-expert-pd-ops-ranker_7_6</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Loona-ChatGPT-4o-AI-Powered-Interaction-Monitoring/dp/B0DCF53PCH/ref=sr_1_1_sspa?crid=2DBOX8S0Q2AR6&amp;dib=eyJ2IjoiMSJ9.fRTz6IKj5O3hiZ4V3RbIiqzYkMvGWX1yxIfmBNQ2bPG8a8X70ewO_kByz-KXp50JfmUuJx9rrIjkexZxX4nWSVxWP_bUrHWGWHPfZnhgH5GMVf6Rltx3FiivEWa9A_74tX_ykUsCTRmHEZ_IwI-5pdDeOvDpmzf07kmD73czlJ5S56lz7gAFPcJ9cgVfwD2yW0a7rgFB4N8XbcF4FmsoLN4nTZhHdGzE2qW01-CozMdL5maZB9Wotwoz672FPyl4IOivur7Z3Gj71yWxlpzykJORSvNzc5nhys8YwW1Zl90.csUcqcC85C04azO69LCOq0bdtEXSzk6YfX_vospSKeE&amp;dib_tag=se&amp;keywords=loona%2Brobot%2Bdog&amp;qid=1778524541&amp;sprefix=loona%2Caps%2C177&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-x</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-max</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-air-2-plus</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-air-2s</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-air-2</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/pet-robot/rola-mini</t>
   </si>
 </sst>
 </file>
@@ -829,7 +920,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -900,6 +991,19 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1302,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.140625" style="3" customWidth="1"/>
@@ -1332,12 +1436,13 @@
     <col min="26" max="26" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="3"/>
+    <col min="29" max="29" width="200.7109375" style="26" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" s="6" customFormat="1" ht="30">
+    <row r="1" spans="1:29" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>16</v>
@@ -1397,7 +1502,7 @@
         <v>86</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>25</v>
@@ -1420,10 +1525,13 @@
       <c r="AB1" s="6" t="s">
         <v>33</v>
       </c>
+      <c r="AC1" s="24" t="s">
+        <v>221</v>
+      </c>
     </row>
-    <row r="2" spans="1:28" ht="75">
+    <row r="2" spans="1:29" ht="75">
       <c r="A2" s="3" t="str">
-        <f>_xlfn.CONCAT(B2, " ", C2)</f>
+        <f t="shared" ref="A2:A31" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> Enabot EBO X FamiyBot</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1445,7 +1553,7 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>89</v>
@@ -1472,7 +1580,7 @@
         <v>46149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R2" s="11">
         <v>789</v>
@@ -1498,17 +1606,20 @@
       <c r="AB2" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC2" s="26" t="s">
+        <v>246</v>
+      </c>
     </row>
-    <row r="3" spans="1:28" ht="75">
+    <row r="3" spans="1:29" ht="75">
       <c r="A3" s="3" t="str">
-        <f>_xlfn.CONCAT(B3, " ", C3)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Max FamiyBot </v>
       </c>
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>72</v>
@@ -1523,7 +1634,7 @@
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>89</v>
@@ -1550,7 +1661,7 @@
         <v>46149</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R3" s="11">
         <v>549</v>
@@ -1576,17 +1687,20 @@
       <c r="AB3" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC3" s="26" t="s">
+        <v>247</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" ht="75">
+    <row r="4" spans="1:29" ht="75">
       <c r="A4" s="3" t="str">
-        <f>_xlfn.CONCAT(B4, " ", C4)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Air 2 Plus FamiyBot </v>
       </c>
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>72</v>
@@ -1601,7 +1715,7 @@
         <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>87</v>
@@ -1628,7 +1742,7 @@
         <v>46149</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R4" s="11">
         <v>359</v>
@@ -1654,17 +1768,20 @@
       <c r="AB4" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC4" s="26" t="s">
+        <v>248</v>
+      </c>
     </row>
-    <row r="5" spans="1:28" ht="75">
+    <row r="5" spans="1:29" ht="75">
       <c r="A5" s="3" t="str">
-        <f>_xlfn.CONCAT(B5, " ", C5)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Air 2S FamiyBot </v>
       </c>
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>72</v>
@@ -1679,7 +1796,7 @@
         <v>22</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>103</v>
@@ -1706,7 +1823,7 @@
         <v>46149</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R5" s="11">
         <v>279</v>
@@ -1732,17 +1849,20 @@
       <c r="AB5" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC5" s="26" t="s">
+        <v>249</v>
+      </c>
     </row>
-    <row r="6" spans="1:28" ht="75">
+    <row r="6" spans="1:29" ht="75">
       <c r="A6" s="3" t="str">
-        <f>_xlfn.CONCAT(B6, " ", C6)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Air 2 FamiyBot </v>
       </c>
       <c r="B6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>72</v>
@@ -1757,7 +1877,7 @@
         <v>22</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>90</v>
@@ -1784,7 +1904,7 @@
         <v>46149</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="R6" s="11">
         <v>179</v>
@@ -1796,7 +1916,7 @@
         <v>46152</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V6" s="3" t="s">
         <v>27</v>
@@ -1810,17 +1930,20 @@
       <c r="AB6" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC6" s="26" t="s">
+        <v>250</v>
+      </c>
     </row>
-    <row r="7" spans="1:28" ht="45">
+    <row r="7" spans="1:29" ht="45">
       <c r="A7" s="3" t="str">
-        <f>_xlfn.CONCAT(B7, " ", C7)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>72</v>
@@ -1862,7 +1985,7 @@
         <v>46149</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="R7" s="11">
         <v>139</v>
@@ -1874,7 +1997,7 @@
         <v>46153</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>27</v>
@@ -1888,10 +2011,13 @@
       <c r="AB7" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC7" s="26" t="s">
+        <v>251</v>
+      </c>
     </row>
-    <row r="8" spans="1:28" ht="90">
+    <row r="8" spans="1:29" ht="90">
       <c r="A8" s="3" t="str">
-        <f>_xlfn.CONCAT(B8, " ", C8)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1952,7 +2078,7 @@
         <v>46150</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>27</v>
@@ -1967,10 +2093,13 @@
       <c r="AB8" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC8" s="27" t="s">
+        <v>222</v>
+      </c>
     </row>
-    <row r="9" spans="1:28" ht="90">
+    <row r="9" spans="1:29" ht="90">
       <c r="A9" s="3" t="str">
-        <f>_xlfn.CONCAT(B9, " ", C9)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2031,7 +2160,7 @@
         <v>46150</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>27</v>
@@ -2046,10 +2175,13 @@
       <c r="AB9" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC9" s="27" t="s">
+        <v>222</v>
+      </c>
     </row>
-    <row r="10" spans="1:28" ht="90">
+    <row r="10" spans="1:29" ht="90">
       <c r="A10" s="3" t="str">
-        <f>_xlfn.CONCAT(B10, " ", C10)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2110,7 +2242,7 @@
         <v>46150</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>27</v>
@@ -2125,10 +2257,13 @@
       <c r="AB10" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC10" s="27" t="s">
+        <v>223</v>
+      </c>
     </row>
-    <row r="11" spans="1:28" ht="90">
+    <row r="11" spans="1:29" ht="90">
       <c r="A11" s="3" t="str">
-        <f>_xlfn.CONCAT(B11, " ", C11)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2189,7 +2324,7 @@
         <v>46150</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V11" s="3" t="s">
         <v>27</v>
@@ -2204,10 +2339,13 @@
       <c r="AB11" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC11" s="25" t="s">
+        <v>224</v>
+      </c>
     </row>
-    <row r="12" spans="1:28" ht="60" customHeight="1">
+    <row r="12" spans="1:29" ht="60" customHeight="1">
       <c r="A12" s="3" t="str">
-        <f>_xlfn.CONCAT(B12, " ", C12)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2268,7 +2406,7 @@
         <v>46150</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>27</v>
@@ -2283,10 +2421,13 @@
       <c r="AB12" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC12" s="26" t="s">
+        <v>225</v>
+      </c>
     </row>
-    <row r="13" spans="1:28" ht="60.75" thickBot="1">
+    <row r="13" spans="1:29" ht="60.75" thickBot="1">
       <c r="A13" s="3" t="str">
-        <f>_xlfn.CONCAT(B13, " ", C13)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2308,7 +2449,7 @@
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>128</v>
@@ -2347,7 +2488,7 @@
         <v>46150</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>27</v>
@@ -2361,10 +2502,13 @@
       <c r="AB13" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC13" s="26" t="s">
+        <v>226</v>
+      </c>
     </row>
-    <row r="14" spans="1:28" ht="75.75" thickBot="1">
+    <row r="14" spans="1:29" ht="75.75" thickBot="1">
       <c r="A14" s="3" t="str">
-        <f>_xlfn.CONCAT(B14, " ", C14)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2425,7 +2569,7 @@
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>27</v>
@@ -2440,10 +2584,13 @@
       <c r="AB14" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC14" s="26" t="s">
+        <v>227</v>
+      </c>
     </row>
-    <row r="15" spans="1:28" ht="75">
+    <row r="15" spans="1:29" ht="75">
       <c r="A15" s="3" t="str">
-        <f>_xlfn.CONCAT(B15, " ", C15)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy 1.1 Robotic Dog </v>
       </c>
       <c r="B15" s="3" t="s">
@@ -2519,10 +2666,13 @@
       <c r="AB15" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC15" s="25" t="s">
+        <v>228</v>
+      </c>
     </row>
-    <row r="16" spans="1:28" ht="60" customHeight="1">
+    <row r="16" spans="1:29" ht="60" customHeight="1">
       <c r="A16" s="3" t="str">
-        <f>_xlfn.CONCAT(B16, " ", C16)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2598,10 +2748,13 @@
       <c r="AB16" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC16" s="26" t="s">
+        <v>229</v>
+      </c>
     </row>
-    <row r="17" spans="1:28" ht="60">
+    <row r="17" spans="1:29" ht="60">
       <c r="A17" s="3" t="str">
-        <f>_xlfn.CONCAT(B17, " ", C17)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2662,7 +2815,7 @@
         <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>27</v>
@@ -2677,10 +2830,13 @@
       <c r="AB17" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC17" s="25" t="s">
+        <v>230</v>
+      </c>
     </row>
-    <row r="18" spans="1:28" ht="75">
+    <row r="18" spans="1:29" ht="75">
       <c r="A18" s="3" t="str">
-        <f>_xlfn.CONCAT(B18, " ", C18)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2755,10 +2911,13 @@
       <c r="AB18" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC18" s="25" t="s">
+        <v>231</v>
+      </c>
     </row>
-    <row r="19" spans="1:28" ht="74.25" customHeight="1">
+    <row r="19" spans="1:29" ht="74.25" customHeight="1">
       <c r="A19" s="3" t="str">
-        <f>_xlfn.CONCAT(B19, " ", C19)</f>
+        <f t="shared" si="0"/>
         <v>Ropet KAMOMO</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -2789,7 +2948,7 @@
         <v>165</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="L19" s="3" t="s">
         <v>167</v>
@@ -2807,7 +2966,7 @@
         <v>46152</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="R19" s="11">
         <v>329</v>
@@ -2839,10 +2998,13 @@
       <c r="AB19" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="AC19" s="25" t="s">
+        <v>233</v>
+      </c>
     </row>
-    <row r="20" spans="1:28" ht="60">
+    <row r="20" spans="1:29" ht="60">
       <c r="A20" s="3" t="str">
-        <f>_xlfn.CONCAT(B20, " ", C20)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -2873,10 +3035,10 @@
         <v>170</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M20" s="16">
         <v>4.3</v>
@@ -2891,7 +3053,7 @@
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R20" s="11">
         <v>44.45</v>
@@ -2914,10 +3076,13 @@
       <c r="X20" s="2" t="s">
         <v>48</v>
       </c>
+      <c r="AC20" s="25" t="s">
+        <v>234</v>
+      </c>
     </row>
-    <row r="21" spans="1:28" ht="75">
+    <row r="21" spans="1:29" ht="75">
       <c r="A21" s="3" t="str">
-        <f>_xlfn.CONCAT(B21, " ", C21)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -2942,7 +3107,7 @@
         <v>171</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>169</v>
@@ -2951,7 +3116,7 @@
         <v>170</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M21" s="16">
         <v>4.3</v>
@@ -2966,7 +3131,7 @@
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R21" s="11">
         <v>44.45</v>
@@ -2989,10 +3154,13 @@
       <c r="X21" s="2" t="s">
         <v>49</v>
       </c>
+      <c r="AC21" s="25" t="s">
+        <v>235</v>
+      </c>
     </row>
-    <row r="22" spans="1:28" ht="60">
+    <row r="22" spans="1:29" ht="60">
       <c r="A22" s="3" t="str">
-        <f>_xlfn.CONCAT(B22, " ", C22)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Shih Tzu</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -3020,13 +3188,13 @@
         <v>170</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>169</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M22" s="16">
         <v>4.2</v>
@@ -3041,7 +3209,7 @@
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
@@ -3064,10 +3232,13 @@
       <c r="X22" s="2" t="s">
         <v>50</v>
       </c>
+      <c r="AC22" s="25" t="s">
+        <v>236</v>
+      </c>
     </row>
-    <row r="23" spans="1:28" ht="60">
+    <row r="23" spans="1:29" ht="60">
       <c r="A23" s="3" t="str">
-        <f>_xlfn.CONCAT(B23, " ", C23)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Beagle</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -3089,7 +3260,7 @@
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>169</v>
@@ -3098,10 +3269,10 @@
         <v>170</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="M23" s="16">
         <v>4.4000000000000004</v>
@@ -3116,7 +3287,7 @@
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
@@ -3139,17 +3310,20 @@
       <c r="X23" s="2" t="s">
         <v>51</v>
       </c>
+      <c r="AC23" s="25" t="s">
+        <v>237</v>
+      </c>
     </row>
-    <row r="24" spans="1:28" ht="60" customHeight="1">
+    <row r="24" spans="1:29" ht="60" customHeight="1">
       <c r="A24" s="3" t="str">
-        <f>_xlfn.CONCAT(B24, " ", C24)</f>
-        <v>Perfect Petzzz Original Calico Cat</v>
+        <f t="shared" si="0"/>
+        <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>178</v>
+        <v>238</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>71</v>
@@ -3164,10 +3338,10 @@
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>169</v>
@@ -3176,7 +3350,7 @@
         <v>170</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M24" s="16">
         <v>4.3</v>
@@ -3191,7 +3365,7 @@
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
@@ -3214,17 +3388,20 @@
       <c r="X24" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="AC24" s="25" t="s">
+        <v>239</v>
+      </c>
     </row>
-    <row r="25" spans="1:28" ht="60" customHeight="1">
+    <row r="25" spans="1:29" ht="60" customHeight="1">
       <c r="A25" s="3" t="str">
-        <f>_xlfn.CONCAT(B25, " ", C25)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>71</v>
@@ -3239,19 +3416,19 @@
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I25" s="3" t="s">
         <v>170</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K25" s="3" t="s">
         <v>169</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M25" s="16">
         <v>4</v>
@@ -3266,7 +3443,7 @@
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R25" s="11">
         <v>53.9</v>
@@ -3289,17 +3466,20 @@
       <c r="X25" s="2" t="s">
         <v>66</v>
       </c>
+      <c r="AC25" s="25" t="s">
+        <v>240</v>
+      </c>
     </row>
-    <row r="26" spans="1:28" ht="60" customHeight="1">
+    <row r="26" spans="1:29" ht="60" customHeight="1">
       <c r="A26" s="3" t="str">
-        <f>_xlfn.CONCAT(B26, " ", C26)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>71</v>
@@ -3314,10 +3494,10 @@
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J26" s="3" t="s">
         <v>169</v>
@@ -3326,7 +3506,7 @@
         <v>170</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M26" s="16">
         <v>4.4000000000000004</v>
@@ -3341,7 +3521,7 @@
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R26" s="11">
         <v>44.45</v>
@@ -3364,17 +3544,20 @@
       <c r="X26" s="2" t="s">
         <v>52</v>
       </c>
+      <c r="AC26" s="25" t="s">
+        <v>241</v>
+      </c>
     </row>
-    <row r="27" spans="1:28" ht="60" customHeight="1">
+    <row r="27" spans="1:29" ht="60" customHeight="1">
       <c r="A27" s="3" t="str">
-        <f>_xlfn.CONCAT(B27, " ", C27)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>71</v>
@@ -3389,19 +3572,19 @@
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>170</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>169</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="M27" s="16">
         <v>4.0999999999999996</v>
@@ -3416,7 +3599,7 @@
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="R27" s="11">
         <v>53.9</v>
@@ -3439,10 +3622,13 @@
       <c r="X27" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="AC27" s="25" t="s">
+        <v>242</v>
+      </c>
     </row>
-    <row r="28" spans="1:28" ht="75">
+    <row r="28" spans="1:29" ht="75">
       <c r="A28" s="3" t="str">
-        <f>_xlfn.CONCAT(B28, " ", C28)</f>
+        <f t="shared" si="0"/>
         <v>Ruko 18011 Smart Robot Dog</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -3464,19 +3650,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="M28" s="16">
         <v>4.4000000000000004</v>
@@ -3514,17 +3700,20 @@
       <c r="X28" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="AC28" s="25" t="s">
+        <v>243</v>
+      </c>
     </row>
-    <row r="29" spans="1:28" ht="27.75" customHeight="1">
+    <row r="29" spans="1:29" ht="27.75" customHeight="1">
       <c r="A29" s="3" t="str">
-        <f>_xlfn.CONCAT(B29, " ", C29)</f>
+        <f t="shared" si="0"/>
         <v>Furby DJ Furby</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>72</v>
@@ -3539,19 +3728,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="M29" s="16">
         <v>4.8</v>
@@ -3566,7 +3755,7 @@
         <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R29" s="11">
         <v>50.11</v>
@@ -3589,10 +3778,13 @@
       <c r="X29" s="2" t="s">
         <v>45</v>
       </c>
+      <c r="AC29" s="25" t="s">
+        <v>244</v>
+      </c>
     </row>
-    <row r="30" spans="1:28" ht="75">
+    <row r="30" spans="1:29" ht="75">
       <c r="A30" s="3" t="str">
-        <f>_xlfn.CONCAT(B30, " ", C30)</f>
+        <f t="shared" si="0"/>
         <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -3614,16 +3806,16 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="M30" s="16">
         <v>4.2</v>
@@ -3661,10 +3853,13 @@
       <c r="X30" s="2" t="s">
         <v>57</v>
       </c>
+      <c r="AC30" s="25" t="s">
+        <v>245</v>
+      </c>
     </row>
-    <row r="31" spans="1:28">
+    <row r="31" spans="1:29">
       <c r="A31" s="3" t="str">
-        <f>_xlfn.CONCAT(B31, " ", C31)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
@@ -3674,10 +3869,12 @@
     <hyperlink ref="Q15:Q17" r:id="rId2" display="https://chongker.com/collections/interactive-stuffed-animals" xr:uid="{463F1AA5-9B50-4055-AB15-B754D3838990}"/>
     <hyperlink ref="Q14" r:id="rId3" display="https://chongker.com/collections/interactive-stuffed-animals" xr:uid="{D9BC2ECF-9D49-455D-AB7A-AD5A56B3A32A}"/>
     <hyperlink ref="Q13" r:id="rId4" display="https://chongker.com/collections/interactive-stuffed-animals" xr:uid="{00B8DB52-D0BF-4C5F-81E4-B934F2771184}"/>
+    <hyperlink ref="AC8" r:id="rId5" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
+    <hyperlink ref="AC9" r:id="rId6" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId5"/>
-  <drawing r:id="rId6"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
+  <drawing r:id="rId8"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -3685,7 +3882,7 @@
           <x14:formula1>
             <xm:f>Lists!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:U7 U8:U1048576</xm:sqref>
+          <xm:sqref>U1:U1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37BE27F9-E75E-4C54-9192-7DED9B8091B0}">
           <x14:formula1>
@@ -3700,6 +3897,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85AD3756-FD5A-4125-A8F0-83929037F229}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="106.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="28"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABE60FF-1DCC-4956-9447-8879E50144AD}">
   <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3714,7 +3932,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3737,12 +3955,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3587DF7-27DE-4C49-A0D7-210E14A8420B}">
   <dimension ref="A1:AC4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:29" s="12" customFormat="1">
+    <row r="1" spans="1:29" s="12" customFormat="1" ht="75">
       <c r="A1" s="3" t="str">
         <f>_xlfn.CONCAT(B1, " ", C1)</f>
         <v xml:space="preserve"> Elephant Robotics MarsCat </v>
@@ -3843,7 +4061,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="12" customFormat="1" ht="60">
+    <row r="3" spans="1:29" s="12" customFormat="1" ht="405">
       <c r="A3" s="3" t="str">
         <f>_xlfn.CONCAT(B3, " ", C3)</f>
         <v xml:space="preserve"> Elephant Robotics metaDog </v>
@@ -3895,7 +4113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="12" customFormat="1" ht="60">
+    <row r="4" spans="1:29" s="12" customFormat="1" ht="360">
       <c r="A4" s="3" t="str">
         <f>_xlfn.CONCAT(B4, " ", C4)</f>
         <v xml:space="preserve"> Elephant Robotics metaPanda </v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2D286B1-3F33-4503-82F7-74543C637280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3904BE-B73E-4827-8530-281AF409F287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Product Matrix" sheetId="1" r:id="rId1"/>
     <sheet name="NOTES on Pasting URLs" sheetId="4" r:id="rId2"/>
     <sheet name="Lists" sheetId="2" r:id="rId3"/>
     <sheet name="Maybe Later" sheetId="3" r:id="rId4"/>
@@ -323,9 +323,6 @@
     <t>Enabot Store</t>
   </si>
   <si>
-    <t>EBO X FamiyBot</t>
-  </si>
-  <si>
     <t>Walmart</t>
   </si>
   <si>
@@ -668,27 +665,9 @@
     <t>Amazon.com : Enabot robot</t>
   </si>
   <si>
-    <t xml:space="preserve">EBO Max FamiyBot </t>
-  </si>
-  <si>
-    <t>FamiyBot – Enabot Store</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBO Air 2 Plus FamiyBot </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBO Air 2S FamiyBot </t>
-  </si>
-  <si>
-    <t xml:space="preserve">EBO Air 2 FamiyBot </t>
-  </si>
-  <si>
     <t>ROLA Mini Pet Monitor</t>
   </si>
   <si>
-    <t>ROLA Mini FamiyBot – 2K Movable Camera &amp; Monitor – Enabot Store</t>
-  </si>
-  <si>
     <t>Hyper-realistic robotic cat with voice wake-up, blinking, purring, and tail movement. Provides emotional support, companionship, and anxiety relief. Handcrafted fur for a premium feel.</t>
   </si>
   <si>
@@ -798,6 +777,27 @@
   </si>
   <si>
     <t>https://www.enabot.com/pet-robot/rola-mini</t>
+  </si>
+  <si>
+    <t>EBO X FamilyBot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBO Max FamilyBot </t>
+  </si>
+  <si>
+    <t>FamilyBot – Enabot Store</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBO Air 2 Plus FamilyBot </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBO Air 2S FamilyBot </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EBO Air 2 FamilyBot </t>
+  </si>
+  <si>
+    <t>ROLA Mini FamilyBot – 2K Movable Camera &amp; Monitor – Enabot Store</t>
   </si>
 </sst>
 </file>
@@ -1442,7 +1442,7 @@
   <sheetData>
     <row r="1" spans="1:29" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>16</v>
@@ -1490,7 +1490,7 @@
         <v>83</v>
       </c>
       <c r="Q1" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R1" s="10" t="s">
         <v>84</v>
@@ -1502,7 +1502,7 @@
         <v>86</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>25</v>
@@ -1526,19 +1526,19 @@
         <v>33</v>
       </c>
       <c r="AC1" s="24" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="75">
       <c r="A2" s="3" t="str">
         <f t="shared" ref="A2:A31" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
-        <v xml:space="preserve"> Enabot EBO X FamiyBot</v>
+        <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>93</v>
+        <v>245</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>72</v>
@@ -1553,7 +1553,7 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>89</v>
@@ -1562,7 +1562,7 @@
         <v>90</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>88</v>
@@ -1574,13 +1574,13 @@
         <v>8</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P2" s="9">
         <v>46149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R2" s="11">
         <v>789</v>
@@ -1607,19 +1607,19 @@
         <v>28</v>
       </c>
       <c r="AC2" s="26" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="75">
       <c r="A3" s="3" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Max FamiyBot </v>
+        <v xml:space="preserve"> Enabot EBO Max FamilyBot </v>
       </c>
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>208</v>
+        <v>246</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>72</v>
@@ -1634,7 +1634,7 @@
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>89</v>
@@ -1643,10 +1643,10 @@
         <v>90</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M3" s="16">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>46149</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>209</v>
+        <v>247</v>
       </c>
       <c r="R3" s="11">
         <v>549</v>
@@ -1688,19 +1688,19 @@
         <v>28</v>
       </c>
       <c r="AC3" s="26" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="75">
       <c r="A4" s="3" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamiyBot </v>
+        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>210</v>
+        <v>248</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>72</v>
@@ -1715,19 +1715,19 @@
         <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>87</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M4" s="16">
         <v>4.0999999999999996</v>
@@ -1742,7 +1742,7 @@
         <v>46149</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R4" s="11">
         <v>359</v>
@@ -1769,19 +1769,19 @@
         <v>28</v>
       </c>
       <c r="AC4" s="26" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="75">
       <c r="A5" s="3" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2S FamiyBot </v>
+        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>211</v>
+        <v>249</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>72</v>
@@ -1796,19 +1796,19 @@
         <v>22</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="M5" s="16">
         <v>4.0999999999999996</v>
@@ -1823,7 +1823,7 @@
         <v>46149</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R5" s="11">
         <v>279</v>
@@ -1850,19 +1850,19 @@
         <v>28</v>
       </c>
       <c r="AC5" s="26" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="75">
       <c r="A6" s="3" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2 FamiyBot </v>
+        <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
       </c>
       <c r="B6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>212</v>
+        <v>250</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>72</v>
@@ -1877,19 +1877,19 @@
         <v>22</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>90</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M6" s="16">
         <v>4</v>
@@ -1904,7 +1904,7 @@
         <v>46149</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="R6" s="11">
         <v>179</v>
@@ -1916,7 +1916,7 @@
         <v>46152</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V6" s="3" t="s">
         <v>27</v>
@@ -1931,7 +1931,7 @@
         <v>28</v>
       </c>
       <c r="AC6" s="26" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="45">
@@ -1943,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>72</v>
@@ -1952,25 +1952,25 @@
         <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>108</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>109</v>
       </c>
       <c r="M7" s="16">
         <v>4.8</v>
@@ -1985,7 +1985,7 @@
         <v>46149</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>214</v>
+        <v>251</v>
       </c>
       <c r="R7" s="11">
         <v>139</v>
@@ -1997,7 +1997,7 @@
         <v>46153</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>27</v>
@@ -2012,7 +2012,7 @@
         <v>28</v>
       </c>
       <c r="AC7" s="26" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="90">
@@ -2039,19 +2039,19 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="L8" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M8" s="16">
         <v>4.5</v>
@@ -2066,7 +2066,7 @@
         <v>46150</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R8" s="11">
         <v>179</v>
@@ -2078,7 +2078,7 @@
         <v>46150</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>27</v>
@@ -2094,7 +2094,7 @@
         <v>28</v>
       </c>
       <c r="AC8" s="27" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="90">
@@ -2121,19 +2121,19 @@
         <v>22</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M9" s="16">
         <v>4.5</v>
@@ -2148,7 +2148,7 @@
         <v>46150</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R9" s="11">
         <v>179</v>
@@ -2160,7 +2160,7 @@
         <v>46150</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>27</v>
@@ -2176,7 +2176,7 @@
         <v>28</v>
       </c>
       <c r="AC9" s="27" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="90">
@@ -2203,19 +2203,19 @@
         <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M10" s="16">
         <v>4.5</v>
@@ -2230,7 +2230,7 @@
         <v>46150</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R10" s="11">
         <v>159.99</v>
@@ -2242,7 +2242,7 @@
         <v>46150</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>27</v>
@@ -2258,7 +2258,7 @@
         <v>28</v>
       </c>
       <c r="AC10" s="27" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="90">
@@ -2285,19 +2285,19 @@
         <v>22</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="K11" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M11" s="16">
         <v>4.5</v>
@@ -2312,7 +2312,7 @@
         <v>46150</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R11" s="11">
         <v>159.99</v>
@@ -2324,7 +2324,7 @@
         <v>46150</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V11" s="3" t="s">
         <v>27</v>
@@ -2340,7 +2340,7 @@
         <v>28</v>
       </c>
       <c r="AC11" s="25" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="60" customHeight="1">
@@ -2367,19 +2367,19 @@
         <v>22</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="L12" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M12" s="16">
         <v>4.5</v>
@@ -2394,7 +2394,7 @@
         <v>46150</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="R12" s="11">
         <v>159.99</v>
@@ -2406,7 +2406,7 @@
         <v>46150</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>27</v>
@@ -2422,7 +2422,7 @@
         <v>28</v>
       </c>
       <c r="AC12" s="26" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="60.75" thickBot="1">
@@ -2449,19 +2449,19 @@
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="L13" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M13" s="16">
         <v>5</v>
@@ -2470,25 +2470,25 @@
         <v>16</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P13" s="9">
         <v>46150</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R13" s="11">
         <v>178</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T13" s="9">
         <v>46150</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>27</v>
@@ -2503,7 +2503,7 @@
         <v>28</v>
       </c>
       <c r="AC13" s="26" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="75.75" thickBot="1">
@@ -2530,19 +2530,19 @@
         <v>22</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="K14" s="21" t="s">
-        <v>134</v>
-      </c>
       <c r="L14" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M14" s="16">
         <v>4</v>
@@ -2551,25 +2551,25 @@
         <v>2</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P14" s="9">
         <v>46150</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R14" s="11">
         <v>149</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T14" s="9">
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>27</v>
@@ -2585,7 +2585,7 @@
         <v>28</v>
       </c>
       <c r="AC14" s="26" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="75">
@@ -2612,19 +2612,19 @@
         <v>22</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>138</v>
-      </c>
       <c r="L15" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M15" s="16">
         <v>5</v>
@@ -2633,25 +2633,25 @@
         <v>4</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P15" s="9">
         <v>46150</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R15" s="11">
         <v>89</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T15" s="9">
         <v>46150</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>27</v>
@@ -2667,7 +2667,7 @@
         <v>28</v>
       </c>
       <c r="AC15" s="25" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="60" customHeight="1">
@@ -2694,19 +2694,19 @@
         <v>22</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="L16" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M16" s="16">
         <v>5</v>
@@ -2715,25 +2715,25 @@
         <v>16</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P16" s="9">
         <v>46150</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R16" s="11">
         <v>89</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T16" s="9">
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>27</v>
@@ -2749,7 +2749,7 @@
         <v>28</v>
       </c>
       <c r="AC16" s="26" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="60">
@@ -2776,19 +2776,19 @@
         <v>22</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>145</v>
-      </c>
       <c r="L17" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M17" s="16">
         <v>5</v>
@@ -2797,25 +2797,25 @@
         <v>2</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="P17" s="9">
         <v>46150</v>
       </c>
       <c r="Q17" s="22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R17" s="11">
         <v>119</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T17" s="9">
         <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>27</v>
@@ -2831,7 +2831,7 @@
         <v>28</v>
       </c>
       <c r="AC17" s="25" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="75">
@@ -2858,19 +2858,19 @@
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="L18" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M18" s="16">
         <v>3</v>
@@ -2897,7 +2897,7 @@
         <v>46151</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>27</v>
@@ -2912,7 +2912,7 @@
         <v>28</v>
       </c>
       <c r="AC18" s="25" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="74.25" customHeight="1">
@@ -2933,25 +2933,25 @@
         <v>18</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>165</v>
-      </c>
       <c r="K19" s="3" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M19" s="16">
         <v>4.3</v>
@@ -2966,7 +2966,7 @@
         <v>46152</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="R19" s="11">
         <v>329</v>
@@ -2999,7 +2999,7 @@
         <v>28</v>
       </c>
       <c r="AC19" s="25" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="60">
@@ -3011,7 +3011,7 @@
         <v>44</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>74</v>
@@ -3026,19 +3026,19 @@
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="K20" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M20" s="16">
         <v>4.3</v>
@@ -3053,7 +3053,7 @@
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="R20" s="11">
         <v>44.45</v>
@@ -3065,7 +3065,7 @@
         <v>46150</v>
       </c>
       <c r="U20" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>27</v>
@@ -3077,7 +3077,7 @@
         <v>48</v>
       </c>
       <c r="AC20" s="25" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="75">
@@ -3089,7 +3089,7 @@
         <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>74</v>
@@ -3104,19 +3104,19 @@
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="L21" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M21" s="16">
         <v>4.3</v>
@@ -3131,7 +3131,7 @@
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="R21" s="11">
         <v>44.45</v>
@@ -3143,7 +3143,7 @@
         <v>46150</v>
       </c>
       <c r="U21" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>27</v>
@@ -3155,10 +3155,10 @@
         <v>49</v>
       </c>
       <c r="AC21" s="25" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="60">
+    <row r="22" spans="1:29" ht="63.75">
       <c r="A22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Shih Tzu</v>
@@ -3167,7 +3167,7 @@
         <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>74</v>
@@ -3182,19 +3182,19 @@
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M22" s="16">
         <v>4.2</v>
@@ -3209,7 +3209,7 @@
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
@@ -3221,7 +3221,7 @@
         <v>46150</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>27</v>
@@ -3233,7 +3233,7 @@
         <v>50</v>
       </c>
       <c r="AC22" s="25" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="60">
@@ -3245,7 +3245,7 @@
         <v>44</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>74</v>
@@ -3260,19 +3260,19 @@
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="K23" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="M23" s="16">
         <v>4.4000000000000004</v>
@@ -3287,7 +3287,7 @@
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
@@ -3299,7 +3299,7 @@
         <v>46150</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>27</v>
@@ -3311,7 +3311,7 @@
         <v>51</v>
       </c>
       <c r="AC23" s="25" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="60" customHeight="1">
@@ -3323,7 +3323,7 @@
         <v>44</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>71</v>
@@ -3338,19 +3338,19 @@
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="L24" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="M24" s="16">
         <v>4.3</v>
@@ -3365,7 +3365,7 @@
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
@@ -3377,7 +3377,7 @@
         <v>46150</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>27</v>
@@ -3389,7 +3389,7 @@
         <v>52</v>
       </c>
       <c r="AC24" s="25" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="60" customHeight="1">
@@ -3401,7 +3401,7 @@
         <v>44</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>71</v>
@@ -3416,19 +3416,19 @@
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="M25" s="16">
         <v>4</v>
@@ -3443,7 +3443,7 @@
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="R25" s="11">
         <v>53.9</v>
@@ -3455,7 +3455,7 @@
         <v>46150</v>
       </c>
       <c r="U25" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V25" s="3" t="s">
         <v>27</v>
@@ -3467,7 +3467,7 @@
         <v>66</v>
       </c>
       <c r="AC25" s="25" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="60" customHeight="1">
@@ -3479,7 +3479,7 @@
         <v>44</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>71</v>
@@ -3494,19 +3494,19 @@
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="L26" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="M26" s="16">
         <v>4.4000000000000004</v>
@@ -3521,7 +3521,7 @@
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="R26" s="11">
         <v>44.45</v>
@@ -3533,7 +3533,7 @@
         <v>46150</v>
       </c>
       <c r="U26" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>27</v>
@@ -3545,7 +3545,7 @@
         <v>52</v>
       </c>
       <c r="AC26" s="25" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="60" customHeight="1">
@@ -3557,7 +3557,7 @@
         <v>44</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>71</v>
@@ -3572,19 +3572,19 @@
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="M27" s="16">
         <v>4.0999999999999996</v>
@@ -3599,7 +3599,7 @@
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="R27" s="11">
         <v>53.9</v>
@@ -3611,7 +3611,7 @@
         <v>46150</v>
       </c>
       <c r="U27" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>27</v>
@@ -3623,7 +3623,7 @@
         <v>53</v>
       </c>
       <c r="AC27" s="25" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="75">
@@ -3650,19 +3650,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>191</v>
       </c>
       <c r="M28" s="16">
         <v>4.4000000000000004</v>
@@ -3689,7 +3689,7 @@
         <v>46150</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V28" s="3" t="s">
         <v>27</v>
@@ -3701,7 +3701,7 @@
         <v>57</v>
       </c>
       <c r="AC28" s="25" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="27.75" customHeight="1">
@@ -3713,7 +3713,7 @@
         <v>61</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>72</v>
@@ -3728,19 +3728,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M29" s="16">
         <v>4.8</v>
@@ -3755,7 +3755,7 @@
         <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R29" s="11">
         <v>50.11</v>
@@ -3767,7 +3767,7 @@
         <v>46150</v>
       </c>
       <c r="U29" s="9" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>27</v>
@@ -3779,7 +3779,7 @@
         <v>45</v>
       </c>
       <c r="AC29" s="25" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="75">
@@ -3806,16 +3806,16 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="M30" s="16">
         <v>4.2</v>
@@ -3854,7 +3854,7 @@
         <v>57</v>
       </c>
       <c r="AC30" s="25" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" spans="1:29">
@@ -3906,7 +3906,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -3932,12 +3932,12 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -4033,7 +4033,7 @@
         <v>22</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M2" s="17"/>
       <c r="N2" s="20"/>
@@ -4085,7 +4085,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="20"/>
@@ -4137,7 +4137,7 @@
         <v>22</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="20"/>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3904BE-B73E-4827-8530-281AF409F287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E9DDE6-49A1-455E-A235-316DE444D7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -18,6 +18,9 @@
     <sheet name="Lists" sheetId="2" r:id="rId3"/>
     <sheet name="Maybe Later" sheetId="3" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AC$31</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="251">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -150,9 +153,6 @@
   </si>
   <si>
     <t>/images/products/Mr-Dog.png</t>
-  </si>
-  <si>
-    <t>/images/products/Sweetie-Cat.png</t>
   </si>
   <si>
     <t>Companion Pet Pup Golden</t>
@@ -1406,6 +1406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1442,7 +1443,7 @@
   <sheetData>
     <row r="1" spans="1:29" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>16</v>
@@ -1451,7 +1452,7 @@
         <v>15</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>19</v>
@@ -1463,58 +1464,58 @@
         <v>21</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="O1" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="Q1" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="T1" s="8" t="s">
-        <v>86</v>
-      </c>
       <c r="U1" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>34</v>
       </c>
       <c r="Y1" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z1" s="6" t="s">
         <v>31</v>
@@ -1526,10 +1527,10 @@
         <v>33</v>
       </c>
       <c r="AC1" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="75">
+    <row r="2" spans="1:29" ht="75" hidden="1">
       <c r="A2" s="3" t="str">
         <f t="shared" ref="A2:A31" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
@@ -1538,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>17</v>
@@ -1553,19 +1554,19 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="K2" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M2" s="16">
         <v>4.5</v>
@@ -1574,19 +1575,19 @@
         <v>8</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="P2" s="9">
         <v>46149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R2" s="11">
         <v>789</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T2" s="9">
         <v>46149</v>
@@ -1601,16 +1602,16 @@
         <v>28</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AB2" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC2" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="75">
+    <row r="3" spans="1:29" ht="75" hidden="1">
       <c r="A3" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Max FamilyBot </v>
@@ -1619,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>17</v>
@@ -1634,19 +1635,19 @@
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="K3" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M3" s="16">
         <v>0</v>
@@ -1655,19 +1656,19 @@
         <v>0</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P3" s="9">
         <v>46149</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R3" s="11">
         <v>549</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T3" s="9">
         <v>46149</v>
@@ -1682,13 +1683,13 @@
         <v>28</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC3" s="26" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="75">
@@ -1700,10 +1701,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>17</v>
@@ -1715,19 +1716,19 @@
         <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M4" s="16">
         <v>4.0999999999999996</v>
@@ -1736,19 +1737,19 @@
         <v>98</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P4" s="9">
         <v>46149</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R4" s="11">
         <v>359</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T4" s="9">
         <v>46150</v>
@@ -1763,16 +1764,16 @@
         <v>27</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AB4" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC4" s="26" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="75">
+    <row r="5" spans="1:29" ht="75" hidden="1">
       <c r="A5" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
@@ -1781,10 +1782,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>17</v>
@@ -1796,19 +1797,19 @@
         <v>22</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="M5" s="16">
         <v>4.0999999999999996</v>
@@ -1817,19 +1818,19 @@
         <v>38</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P5" s="9">
         <v>46149</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R5" s="11">
         <v>279</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T5" s="9">
         <v>46151</v>
@@ -1844,13 +1845,13 @@
         <v>28</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC5" s="26" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="75">
@@ -1862,10 +1863,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>17</v>
@@ -1877,19 +1878,19 @@
         <v>22</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M6" s="16">
         <v>4</v>
@@ -1898,25 +1899,25 @@
         <v>300</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P6" s="9">
         <v>46149</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="R6" s="11">
         <v>179</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T6" s="9">
         <v>46152</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V6" s="3" t="s">
         <v>27</v>
@@ -1925,16 +1926,16 @@
         <v>27</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AB6" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC6" s="26" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="45">
+    <row r="7" spans="1:29" ht="45" hidden="1">
       <c r="A7" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
@@ -1943,34 +1944,34 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>107</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>108</v>
       </c>
       <c r="M7" s="16">
         <v>4.8</v>
@@ -1979,25 +1980,25 @@
         <v>30</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P7" s="9">
         <v>46149</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="R7" s="11">
         <v>139</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T7" s="9">
         <v>46153</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>27</v>
@@ -2006,13 +2007,13 @@
         <v>28</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AB7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC7" s="26" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="90">
@@ -2024,10 +2025,10 @@
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>18</v>
@@ -2039,19 +2040,19 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="L8" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M8" s="16">
         <v>4.5</v>
@@ -2060,25 +2061,25 @@
         <v>5163</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P8" s="9">
         <v>46150</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R8" s="11">
         <v>179</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T8" s="9">
         <v>46150</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>27</v>
@@ -2094,10 +2095,10 @@
         <v>28</v>
       </c>
       <c r="AC8" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="90">
+    <row r="9" spans="1:29" ht="90" hidden="1">
       <c r="A9" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
@@ -2106,10 +2107,10 @@
         <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>18</v>
@@ -2121,19 +2122,19 @@
         <v>22</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="K9" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="M9" s="16">
         <v>4.5</v>
@@ -2142,25 +2143,25 @@
         <v>5163</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P9" s="9">
         <v>46150</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R9" s="11">
         <v>179</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T9" s="9">
         <v>46150</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>27</v>
@@ -2176,10 +2177,10 @@
         <v>28</v>
       </c>
       <c r="AC9" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="90">
+    <row r="10" spans="1:29" ht="90" hidden="1">
       <c r="A10" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
@@ -2188,10 +2189,10 @@
         <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>18</v>
@@ -2203,19 +2204,19 @@
         <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="M10" s="16">
         <v>4.5</v>
@@ -2224,25 +2225,25 @@
         <v>11640</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P10" s="9">
         <v>46150</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R10" s="11">
         <v>159.99</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T10" s="9">
         <v>46150</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>27</v>
@@ -2251,17 +2252,17 @@
         <v>28</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="Y10" s="4"/>
       <c r="AB10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC10" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="90">
+    <row r="11" spans="1:29" ht="90" hidden="1">
       <c r="A11" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
@@ -2270,10 +2271,10 @@
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>18</v>
@@ -2285,19 +2286,19 @@
         <v>22</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="K11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M11" s="16">
         <v>4.5</v>
@@ -2306,25 +2307,25 @@
         <v>11640</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P11" s="9">
         <v>46150</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R11" s="11">
         <v>159.99</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T11" s="9">
         <v>46150</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V11" s="3" t="s">
         <v>27</v>
@@ -2333,14 +2334,14 @@
         <v>28</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Y11" s="4"/>
       <c r="AB11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC11" s="25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="60" customHeight="1">
@@ -2352,10 +2353,10 @@
         <v>14</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>18</v>
@@ -2367,19 +2368,19 @@
         <v>22</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="L12" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="M12" s="16">
         <v>4.5</v>
@@ -2388,25 +2389,25 @@
         <v>11640</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P12" s="9">
         <v>46150</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="R12" s="11">
         <v>159.99</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T12" s="9">
         <v>46150</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>27</v>
@@ -2415,17 +2416,17 @@
         <v>27</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="Y12" s="4"/>
       <c r="AB12" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC12" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="60.75" thickBot="1">
+    <row r="13" spans="1:29" ht="60">
       <c r="A13" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
@@ -2437,7 +2438,7 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>18</v>
@@ -2449,19 +2450,19 @@
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="L13" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="M13" s="16">
         <v>5</v>
@@ -2470,25 +2471,25 @@
         <v>16</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P13" s="9">
         <v>46150</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R13" s="11">
         <v>178</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T13" s="9">
         <v>46150</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>27</v>
@@ -2497,16 +2498,16 @@
         <v>27</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="AB13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC13" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="75.75" thickBot="1">
+    <row r="14" spans="1:29" ht="75.75" hidden="1" thickBot="1">
       <c r="A14" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
@@ -2518,7 +2519,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>18</v>
@@ -2530,19 +2531,19 @@
         <v>22</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="K14" s="21" t="s">
-        <v>133</v>
-      </c>
       <c r="L14" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M14" s="16">
         <v>4</v>
@@ -2551,25 +2552,25 @@
         <v>2</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P14" s="9">
         <v>46150</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R14" s="11">
         <v>149</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T14" s="9">
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>27</v>
@@ -2578,14 +2579,14 @@
         <v>28</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y14" s="4"/>
       <c r="AB14" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC14" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="75">
@@ -2600,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>18</v>
@@ -2612,19 +2613,19 @@
         <v>22</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="L15" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M15" s="16">
         <v>5</v>
@@ -2633,25 +2634,25 @@
         <v>4</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P15" s="9">
         <v>46150</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R15" s="11">
         <v>89</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T15" s="9">
         <v>46150</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>27</v>
@@ -2667,7 +2668,7 @@
         <v>28</v>
       </c>
       <c r="AC15" s="25" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="60" customHeight="1">
@@ -2682,7 +2683,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>18</v>
@@ -2694,19 +2695,19 @@
         <v>22</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="K16" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="L16" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M16" s="16">
         <v>5</v>
@@ -2715,44 +2716,44 @@
         <v>16</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P16" s="9">
         <v>46150</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R16" s="11">
         <v>89</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T16" s="9">
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Y16" s="4"/>
       <c r="AB16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC16" s="26" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="60">
+    <row r="17" spans="1:29" ht="60" hidden="1">
       <c r="A17" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
@@ -2764,7 +2765,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>18</v>
@@ -2776,19 +2777,19 @@
         <v>22</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>144</v>
-      </c>
       <c r="L17" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M17" s="16">
         <v>5</v>
@@ -2797,25 +2798,25 @@
         <v>2</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="P17" s="9">
         <v>46150</v>
       </c>
       <c r="Q17" s="22" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R17" s="11">
         <v>119</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="T17" s="9">
         <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>27</v>
@@ -2824,17 +2825,17 @@
         <v>28</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Y17" s="5"/>
       <c r="AB17" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC17" s="25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="75">
+    <row r="18" spans="1:29" ht="75" hidden="1">
       <c r="A18" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
@@ -2846,7 +2847,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>18</v>
@@ -2858,19 +2859,19 @@
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>160</v>
-      </c>
       <c r="L18" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="M18" s="16">
         <v>3</v>
@@ -2879,25 +2880,25 @@
         <v>80</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P18" s="9">
         <v>46151</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="R18" s="11">
         <v>25.99</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T18" s="9">
         <v>46151</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>27</v>
@@ -2906,13 +2907,13 @@
         <v>28</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC18" s="25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="74.25" customHeight="1">
@@ -2927,31 +2928,31 @@
         <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="K19" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="M19" s="16">
         <v>4.3</v>
@@ -2960,19 +2961,19 @@
         <v>17</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P19" s="9">
         <v>46152</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R19" s="11">
         <v>329</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T19" s="9">
         <v>46152</v>
@@ -2987,7 +2988,7 @@
         <v>27</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>27</v>
@@ -2999,22 +3000,22 @@
         <v>28</v>
       </c>
       <c r="AC19" s="25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="60">
+    <row r="20" spans="1:29" ht="60" hidden="1">
       <c r="A20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>18</v>
@@ -3026,19 +3027,19 @@
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="K20" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M20" s="16">
         <v>4.3</v>
@@ -3047,25 +3048,25 @@
         <v>403</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P20" s="9">
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R20" s="11">
         <v>44.45</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T20" s="9">
         <v>46150</v>
       </c>
       <c r="U20" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>27</v>
@@ -3074,25 +3075,25 @@
         <v>28</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AC20" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="75">
+    <row r="21" spans="1:29" ht="75" hidden="1">
       <c r="A21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>18</v>
@@ -3104,19 +3105,19 @@
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="L21" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M21" s="16">
         <v>4.3</v>
@@ -3125,25 +3126,25 @@
         <v>553</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P21" s="9">
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R21" s="11">
         <v>44.45</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T21" s="9">
         <v>46150</v>
       </c>
       <c r="U21" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>27</v>
@@ -3152,10 +3153,10 @@
         <v>28</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AC21" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="63.75">
@@ -3164,13 +3165,13 @@
         <v>Perfect Petzzz Original Shih Tzu</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>18</v>
@@ -3182,19 +3183,19 @@
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M22" s="16">
         <v>4.2</v>
@@ -3203,25 +3204,25 @@
         <v>878</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P22" s="9">
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T22" s="9">
         <v>46150</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>27</v>
@@ -3230,25 +3231,25 @@
         <v>27</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AC22" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="60">
+    <row r="23" spans="1:29" ht="60" hidden="1">
       <c r="A23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Beagle</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>18</v>
@@ -3260,19 +3261,19 @@
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="K23" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="M23" s="16">
         <v>4.4000000000000004</v>
@@ -3281,25 +3282,25 @@
         <v>466</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P23" s="9">
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T23" s="9">
         <v>46150</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>27</v>
@@ -3308,25 +3309,25 @@
         <v>28</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AC23" s="25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="60" customHeight="1">
+    <row r="24" spans="1:29" ht="60" hidden="1" customHeight="1">
       <c r="A24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>18</v>
@@ -3338,19 +3339,19 @@
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="L24" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M24" s="16">
         <v>4.3</v>
@@ -3359,25 +3360,25 @@
         <v>848</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P24" s="9">
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T24" s="9">
         <v>46150</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>27</v>
@@ -3386,25 +3387,25 @@
         <v>28</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AC24" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="60" customHeight="1">
+    <row r="25" spans="1:29" ht="60" hidden="1" customHeight="1">
       <c r="A25" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>18</v>
@@ -3416,19 +3417,19 @@
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M25" s="16">
         <v>4</v>
@@ -3437,25 +3438,25 @@
         <v>54</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P25" s="9">
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R25" s="11">
         <v>53.9</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T25" s="9">
         <v>46150</v>
       </c>
       <c r="U25" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V25" s="3" t="s">
         <v>27</v>
@@ -3464,10 +3465,10 @@
         <v>28</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AC25" s="25" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="60" customHeight="1">
@@ -3476,13 +3477,13 @@
         <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>18</v>
@@ -3494,19 +3495,19 @@
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>169</v>
-      </c>
       <c r="L26" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M26" s="16">
         <v>4.4000000000000004</v>
@@ -3515,25 +3516,25 @@
         <v>1200</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P26" s="9">
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R26" s="11">
         <v>44.45</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T26" s="9">
         <v>46150</v>
       </c>
       <c r="U26" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>27</v>
@@ -3542,25 +3543,25 @@
         <v>27</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AC26" s="25" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="60" customHeight="1">
+    <row r="27" spans="1:29" ht="60" hidden="1" customHeight="1">
       <c r="A27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>18</v>
@@ -3572,19 +3573,19 @@
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="M27" s="16">
         <v>4.0999999999999996</v>
@@ -3593,25 +3594,25 @@
         <v>16</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P27" s="9">
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="R27" s="11">
         <v>53.9</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T27" s="9">
         <v>46150</v>
       </c>
       <c r="U27" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>27</v>
@@ -3620,10 +3621,10 @@
         <v>28</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AC27" s="25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="75">
@@ -3632,13 +3633,13 @@
         <v>Ruko 18011 Smart Robot Dog</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="D28" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>17</v>
@@ -3650,19 +3651,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I28" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="M28" s="16">
         <v>4.4000000000000004</v>
@@ -3671,25 +3672,25 @@
         <v>283</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P28" s="9">
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R28" s="11">
         <v>69.989999999999995</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T28" s="9">
         <v>46150</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V28" s="3" t="s">
         <v>27</v>
@@ -3698,10 +3699,10 @@
         <v>27</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC28" s="25" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="27.75" customHeight="1">
@@ -3710,13 +3711,13 @@
         <v>Furby DJ Furby</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>17</v>
@@ -3728,19 +3729,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M29" s="16">
         <v>4.8</v>
@@ -3749,25 +3750,25 @@
         <v>772</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P29" s="9">
         <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R29" s="11">
         <v>50.11</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T29" s="9">
         <v>46150</v>
       </c>
       <c r="U29" s="9" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>27</v>
@@ -3776,10 +3777,10 @@
         <v>27</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AC29" s="25" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="75">
@@ -3788,13 +3789,13 @@
         <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="D30" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>17</v>
@@ -3806,16 +3807,16 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>191</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>192</v>
       </c>
       <c r="M30" s="16">
         <v>4.2</v>
@@ -3824,19 +3825,19 @@
         <v>1199</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="P30" s="9">
         <v>46150</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R30" s="11">
         <v>499</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T30" s="9">
         <v>46150</v>
@@ -3851,19 +3852,26 @@
         <v>27</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="AC30" s="25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
-    <row r="31" spans="1:29">
+    <row r="31" spans="1:29" hidden="1">
       <c r="A31" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AC31" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
+    <filterColumn colId="22">
+      <filters>
+        <filter val="yes"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <hyperlinks>
     <hyperlink ref="Q7" r:id="rId1" display="https://store.enabot.com/products/rola-mini-familybot" xr:uid="{D49343E0-D5EC-4C50-A249-B612E5577C2E}"/>
     <hyperlink ref="Q15:Q17" r:id="rId2" display="https://chongker.com/collections/interactive-stuffed-animals" xr:uid="{463F1AA5-9B50-4055-AB15-B754D3838990}"/>
@@ -3906,7 +3914,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -3932,12 +3940,12 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -3972,7 +3980,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>18</v>
@@ -4000,10 +4008,10 @@
         <v>28</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Z1" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AC1" s="12" t="s">
         <v>28</v>
@@ -4021,7 +4029,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>18</v>
@@ -4033,7 +4041,7 @@
         <v>22</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M2" s="17"/>
       <c r="N2" s="20"/>
@@ -4052,10 +4060,10 @@
         <v>28</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AC2" s="12" t="s">
         <v>28</v>
@@ -4073,7 +4081,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>18</v>
@@ -4085,7 +4093,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="20"/>
@@ -4104,10 +4112,10 @@
         <v>28</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AC3" s="12" t="s">
         <v>28</v>
@@ -4125,7 +4133,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>18</v>
@@ -4137,7 +4145,7 @@
         <v>22</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="20"/>
@@ -4156,10 +4164,10 @@
         <v>28</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AC4" s="12" t="s">
         <v>28</v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43E9DDE6-49A1-455E-A235-316DE444D7E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AE531C-7574-47D4-9619-B349E9564E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="267">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -212,9 +212,6 @@
     <t>18011 Smart Robot Dog</t>
   </si>
   <si>
-    <t>Amazon.com: Ruko 18011 Smart Robot Dog, Interactive Puppy with 30 LED Expressions, Programmable Play, 2.4 GHz Remote &amp; Gesture Control, Toy for Kids Age 3+ : Toys &amp; Games</t>
-  </si>
-  <si>
     <t>/images/products/futuristic_ai_pets.png</t>
   </si>
   <si>
@@ -224,9 +221,6 @@
     <t>Robot Pet Dog</t>
   </si>
   <si>
-    <t>Amazon.com: Loona Robot Pet Dog ChatGPT-4o Smart AI-Powered Companion Voice &amp; Gesture Control, Real-Time Interaction Robotics Toys for Kids, Home Monitoring - Includes Charging Dock : Toys &amp; Games</t>
-  </si>
-  <si>
     <t>Furby</t>
   </si>
   <si>
@@ -323,9 +317,6 @@
     <t>Enabot Store</t>
   </si>
   <si>
-    <t>Walmart</t>
-  </si>
-  <si>
     <t>Rating URL</t>
   </si>
   <si>
@@ -512,12 +503,6 @@
     <t>Unique anxiety relief</t>
   </si>
   <si>
-    <t>Interactive Stuffed Animals &amp; Robot Cats for Emotional Support – Chongker</t>
-  </si>
-  <si>
-    <t>Amazon.com: JOY FOR ALL Ageless Innovation Companion Pet for Seniors - Lifelike Animatronic Dog - Realistic Soft-Touch Coat &amp; Heartbeat - Therapy Stuffed Animal - Toy for Alzheimer's &amp; Dementia - Golden Pup : Hasbro: Everything Else</t>
-  </si>
-  <si>
     <t>Affordable interactive robot puppy featuring touch sensors, walking, barking, and tail wagging. Runs on AA batteries with no app or Wi-Fi setup needed — instant out-of-box play. A kid-friendly starter pet alternative.</t>
   </si>
   <si>
@@ -647,9 +632,6 @@
     <t>Affordable Super-fun intelligent toy</t>
   </si>
   <si>
-    <t>Amazon.com: FURBY DJ Interactive Toy, Neon Star, Snuggly Electronic Plush, Music, Lights, Motion, &amp; Games, Speaks English &amp; Furbish, 32 in Long, 6+ Years (Amazon Exclusive) : Toys &amp; Games</t>
-  </si>
-  <si>
     <t>Price Category</t>
   </si>
   <si>
@@ -662,9 +644,6 @@
     <t>AI home monitoring robot and AI Assistant designed to keep your home, pets, and loved ones connected and secure. The robot pet camera lets you check in and visit anytime from your smartphone. Monitors home and family. Sends alerts when anomalies are detected.</t>
   </si>
   <si>
-    <t>Amazon.com : Enabot robot</t>
-  </si>
-  <si>
     <t>ROLA Mini Pet Monitor</t>
   </si>
   <si>
@@ -674,15 +653,9 @@
     <t>Builds personal connections</t>
   </si>
   <si>
-    <t>Amazon.com: Ropet KAMOMO Companion Interactive Robot Pet, Emotional Support for Kids and Adults, AI Desk Robots, Anxiety Relief Comfort Gift : Toys &amp; Games</t>
-  </si>
-  <si>
     <t>Affordable  breathing, super cuddly dog.</t>
   </si>
   <si>
-    <t>Amazon.com : perfect Petzzz cat</t>
-  </si>
-  <si>
     <t>Affordable  breathing, super cuddly cat.</t>
   </si>
   <si>
@@ -785,9 +758,6 @@
     <t xml:space="preserve">EBO Max FamilyBot </t>
   </si>
   <si>
-    <t>FamilyBot – Enabot Store</t>
-  </si>
-  <si>
     <t xml:space="preserve">EBO Air 2 Plus FamilyBot </t>
   </si>
   <si>
@@ -797,7 +767,85 @@
     <t xml:space="preserve">EBO Air 2 FamilyBot </t>
   </si>
   <si>
-    <t>ROLA Mini FamilyBot – 2K Movable Camera &amp; Monitor – Enabot Store</t>
+    <t>https://store.enabot.com/products/ebo-x-familybot</t>
+  </si>
+  <si>
+    <t>https://store.enabot.com/collections/ebo-robots/products/ebo-air-2-plus-familybot</t>
+  </si>
+  <si>
+    <t>https://store.enabot.com/collections/ebo-robots/products/ebo-air-2s-familybot</t>
+  </si>
+  <si>
+    <t>https://store.enabot.com/collections/ebo-robots/products/ebo-air-2-familybot</t>
+  </si>
+  <si>
+    <t>https://store.enabot.com/collections/rola-pets-products/products/rola-mini-pet-monitor</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=joy+to+all+freckled+pup&amp;crid=HVLEN7B8L0CM&amp;sprefix=joy+to+all+freck%2Caps%2C217&amp;ref=nb_sb_ss_saint-nlq-prefix_1_16</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=joy+to+all+golden+pup+companion+pet&amp;crid=16QG42Z3FK9T4&amp;sprefix=joy+to+all+golden+pup%2Caps%2C140&amp;ref=nb_sb_ss_saint-nlq-prefix_2_21</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/gp/aw/d/B017JQQ00Q/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=26b144b9e41ef53861347d694467f399&amp;hsa_cr_id=0&amp;qid=1778537785&amp;sr=1-3-f02f01d6-adaf-4bef-9a7c-29308eff9043&amp;ref_=sbx__sbtcd2_asin_2_title&amp;pd_rd_w=5Clqa&amp;content-id=amzn1.sym.d3360101-5266-4e0e-8e4a-de7eb0be6ed9%3Aamzn1.sym.d3360101-5266-4e0e-8e4a-de7eb0be6ed9&amp;pf_rd_p=d3360101-5266-4e0e-8e4a-de7eb0be6ed9&amp;pf_rd_r=Q120JN1G319GV2TDDATM&amp;pd_rd_wg=ItEfQ&amp;pd_rd_r=974a233e-23b5-4b5e-85dc-e40815a254bd&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/gp/aw/d/B017JQQ01A/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=26b144b9e41ef53861347d694467f399&amp;hsa_cr_id=0&amp;qid=1778537785&amp;sr=1-2-f02f01d6-adaf-4bef-9a7c-29308eff9043&amp;ref_=sbx__sbtcd2_asin_1_title&amp;pd_rd_w=5Clqa&amp;content-id=amzn1.sym.d3360101-5266-4e0e-8e4a-de7eb0be6ed9%3Aamzn1.sym.d3360101-5266-4e0e-8e4a-de7eb0be6ed9&amp;pf_rd_p=d3360101-5266-4e0e-8e4a-de7eb0be6ed9&amp;pf_rd_r=Q120JN1G319GV2TDDATM&amp;pd_rd_wg=ItEfQ&amp;pd_rd_r=974a233e-23b5-4b5e-85dc-e40815a254bd&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/gp/aw/d/B078FFX7Q8/?_encoding=UTF8&amp;pd_rd_plhdr=t&amp;aaxitk=26b144b9e41ef53861347d694467f399&amp;hsa_cr_id=0&amp;qid=1778537785&amp;sr=1-2-f02f01d6-adaf-4bef-9a7c-29308eff9043&amp;ref_=sbx__sbtcd2_asin_1_title&amp;pd_rd_w=5Clqa&amp;content-id=amzn1.sym.d3360101-5266-4e0e-8e4a-de7eb0be6ed9%3Aamzn1.sym.d3360101-5266-4e0e-8e4a-de7eb0be6ed9&amp;pf_rd_p=d3360101-5266-4e0e-8e4a-de7eb0be6ed9&amp;pf_rd_r=Q120JN1G319GV2TDDATM&amp;pd_rd_wg=ItEfQ&amp;pd_rd_r=974a233e-23b5-4b5e-85dc-e40815a254bd&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Chongker-Interactive-Companion-Realistic-Heartbeat/dp/B0DHCHNV55/ref=sr_1_1_sspa?crid=2DOK2GE9TSUMY&amp;dib=eyJ2IjoiMSJ9.blq-mxH_UyFFsgR4NuaokdKZXCuc_B6ZopdvtHFH1vmhZaQ1N6bsQCRU47AJ4NTUUhqQNPS6AIaWFTmRc6ZOpc8cgdz3_VlBZUblnjJUJ0M4qjqxqPw_JlamMyAp-r1iavA3ERRJ_Q5K4pASxAATgvaCw0mlD3T00PaC6y0Gq8bser6LGPRC4eOIQNlLEMvquEDUU_69EeQgaoWAR9icKnsSWnvAN6OsixWWUqnWDDE53X0HVCy4vTFKzLoVHQBUHhLCn2oO0mWHjsr7ALpooeimEGQ4OHLzrddCqDgnoek.rwnjDnk15-CaCpXxxH4Ekkcv3UcUzelOakmqm1Wto3Y&amp;dib_tag=se&amp;keywords=chongker&amp;qid=1778538061&amp;s=toys-and-games&amp;sprefix=chongker%2Ctoys-and-games%2C205&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>Chongker website</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/percy-1-1-robotic-dog-border-collie-robotic-companion-dog</t>
+  </si>
+  <si>
+    <t>https://chongker.com/collections/interactive-stuffed-animals</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/chinatera-Wuffy-Robot-Dog-Lifelike/dp/B0GBVGT2TT/ref=sr_1_4?crid=MNXD8CZH5YEV&amp;dib=eyJ2IjoiMSJ9.i_tCHpgxpk0FPJlKxc8tmurS2drN-O1cFpparDV-5dl35TwFC6ems-tsDiAyskF_9B3xvBbUvjP5x56dyVD6f5sGhY-qSNHcZyvjgSmxMAYieOB52GM1W-1z4-2NgoN3.a7Ck7KBmtYBU37IrxfgTYHNpJnij0qyKGBGoj0bq5Pk&amp;dib_tag=se&amp;keywords=wuffy&amp;qid=1778538852&amp;s=toys-and-games&amp;sprefix=wuffy%2Ctoys-and-games%2C198&amp;sr=1-4&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/ropet-Companion-Interactive-Emotional-Support/dp/B0GTPZ4N4M/ref=sr_1_1_sspa?crid=X2VCF2RXTW0X&amp;dib=eyJ2IjoiMSJ9.9kRHdzgs52yEbstiCw5zkAPTqsRrmdj6gtNMFXMLDlJkGhu-bMFjN2LPlQeMj_e5sIeb5ythEPfeSxEXaQ7SJNt6miVnmQauQGaBVBQr-uHpeqC0g9-FoCvhSY-M0M0g_ViUa98yIz9hfQ6zBvbvtKtEGq5_c9U6vgqbi7-bmgOjUxCEjM0undxnj77JdOTRshgmW-1cJJGhBPKrkqh8zJAa5LvZ8CA-_HfQmfk-R06uBcBkELLdF6WaOOON7xE2dQPBH2QaCNB93wVYWobCpXjdRSQwghIJV3xYyxknb7E.UfBT7o_7AglidAtI5mfWXYBglVtblPYmTisiFlaKA3M&amp;dib_tag=se&amp;keywords=ropet&amp;qid=1778538905&amp;s=toys-and-games&amp;sprefix=ropet+%2Ctoys-and-games%2C220&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_7</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_8</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_9</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_10</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_11</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_12</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_13</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_14</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Ruko-18011-Interactive-Expressions-Programmable/dp/B0FLXCXPHD/ref=sr_1_2_sspa?crid=46F3EM563RH2&amp;dib=eyJ2IjoiMSJ9.5Gly7Ov9TtkvwLAe4rZwH2l-BTiwaFOMLi92o4eo2efL59RBhuAyz5dL1llQO9Oq3VOvL554UZdKGuCvEr0aULc0FuaW-0tXMv-Su3A0pJUYX216NZD-8OUNQh6gxNKl8ATh6D7HDFqXqh-HftmgAbHCQTy9hU7JIHWTap9VCLBOTqG63pGqH1CMk2nheo8GFwKFgq-JlfQJBXAYeXfjdZ53H5tQAmhJmbXnYWxOCYV0NtCgyyMVmml1rR7tZkoyjG_4I2LrxuOnAJYrH2drbxe-cORLKoeEvdhhs7eZVRM.AAyl4FwdoPkwE97T990tA9oBb3kFfNjZ571FnV0wajE&amp;dib_tag=se&amp;keywords=ruko%2Brobot&amp;qid=1778539008&amp;s=toys-and-games&amp;sprefix=ruko%2Ctoys-and-games%2C220&amp;sr=1-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Furby-G0668-FURBY-Fur-Rainbow/dp/B0DNG9FXL7/ref=sr_1_1?crid=VY6MLD53A1RT&amp;dib=eyJ2IjoiMSJ9.402EMJ7f_ZC-s54vTZnqiH4syK2v1SdhINs9tpdLNBUZU-w2GGYe8yQd0pzwTMs9xBxXp3-p30mlQ5vqZ0x-TVipBXGK333YL6dqyGMLcsVc5ZGlnk24QbqVRe9ODOJ5jRKRiacfWluZN1jaNhhuW1fa74-j2vUqFp6iVCd0uShAgLzTbttA6Cwb8nfCxayd9uwWdS4-jggKQLp-IYF6r34HfqfCAhFmnV2cl8xFtQxxvTNcN27JPFrX4zmMtuk_b4ZEwOuowITDwWtGN6ucXHJXCX7JdZtE-oPg5YmbcdM.UjE4yUXMjGw7yDfDGl8HdUM8QBcBWMPWjK550TccAmM&amp;dib_tag=se&amp;keywords=dj%2Bfurby&amp;qid=1778539054&amp;s=toys-and-games&amp;sprefix=dj%2Bfurby%2Ctoys-and-games%2C235&amp;sr=1-1&amp;th=1</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/Loona-ChatGPT-4o-AI-Powered-Interaction-Monitoring/dp/B0DCF53PCH/ref=sr_1_1_sspa?crid=LXSZQC579ZUJ&amp;dib=eyJ2IjoiMSJ9.fRTz6IKj5O3hiZ4V3RbIiqzYkMvGWX1yxIfmBNQ2bPEXhXF8Ry2nqncmMGEv7evRpJaa3U9aWxY1MQkhTgdPIV6Wjq-bFAK8cz4LIVjlEwH6W3j7kAEh6OD6pXtvOtnElQhMvBxTEwFpCiEYHVGyhpXxpCYzj1C2k8p3eIaIxYpRdd5pCvCtpNx-q-dgV8LfuIsu2pUkkgQks54gIUrjn4mpoOq0hqlBJXm_aPrP6Bi0oNJqD9loGYkwNNTqGtcUJYHc5fRntYIBPwj9_pE6lRUuH1CiB6ijg6RWmc0N6oE.9xo2lpag-NNW4-lvsbZ84aWH32CcaxXnQJs2fXDBXV8&amp;dib_tag=se&amp;keywords=loona%2Brobot&amp;qid=1778539102&amp;s=toys-and-games&amp;sprefix=loona%2Ctoys-and-games%2C257&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
   </si>
 </sst>
 </file>
@@ -808,7 +856,7 @@
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -876,6 +924,12 @@
       <color rgb="FF412402"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1406,7 +1460,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1443,7 +1496,7 @@
   <sheetData>
     <row r="1" spans="1:29" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>16</v>
@@ -1452,7 +1505,7 @@
         <v>15</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>19</v>
@@ -1464,52 +1517,52 @@
         <v>21</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="O1" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="P1" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="S1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="Q1" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="R1" s="10" t="s">
+      <c r="T1" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="S1" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>85</v>
-      </c>
       <c r="U1" s="8" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>25</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>34</v>
@@ -1527,10 +1580,10 @@
         <v>33</v>
       </c>
       <c r="AC1" s="24" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="75" hidden="1">
+    <row r="2" spans="1:29" ht="75">
       <c r="A2" s="3" t="str">
         <f t="shared" ref="A2:A31" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
@@ -1539,10 +1592,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>17</v>
@@ -1554,40 +1607,40 @@
         <v>24</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M2" s="16">
         <v>4.5</v>
       </c>
       <c r="N2" s="19">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="P2" s="9">
         <v>46149</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>205</v>
+        <v>240</v>
       </c>
       <c r="R2" s="11">
         <v>789</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T2" s="9">
         <v>46149</v>
@@ -1608,10 +1661,10 @@
         <v>28</v>
       </c>
       <c r="AC2" s="26" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="75" hidden="1">
+    <row r="3" spans="1:29" ht="75">
       <c r="A3" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Max FamilyBot </v>
@@ -1620,10 +1673,10 @@
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>17</v>
@@ -1635,19 +1688,19 @@
         <v>23</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M3" s="16">
         <v>0</v>
@@ -1656,19 +1709,19 @@
         <v>0</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P3" s="9">
         <v>46149</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="R3" s="11">
         <v>549</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T3" s="9">
         <v>46149</v>
@@ -1689,7 +1742,7 @@
         <v>28</v>
       </c>
       <c r="AC3" s="26" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="75">
@@ -1701,10 +1754,10 @@
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>17</v>
@@ -1716,40 +1769,40 @@
         <v>22</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="M4" s="16">
-        <v>4.0999999999999996</v>
+        <v>5</v>
       </c>
       <c r="N4" s="19">
-        <v>98</v>
+        <v>42</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P4" s="9">
         <v>46149</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>205</v>
+        <v>241</v>
       </c>
       <c r="R4" s="11">
         <v>359</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T4" s="9">
         <v>46150</v>
@@ -1770,10 +1823,10 @@
         <v>28</v>
       </c>
       <c r="AC4" s="26" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="75" hidden="1">
+    <row r="5" spans="1:29" ht="75">
       <c r="A5" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
@@ -1782,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>17</v>
@@ -1797,40 +1850,40 @@
         <v>22</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="J5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="M5" s="16">
-        <v>4.0999999999999996</v>
+        <v>5</v>
       </c>
       <c r="N5" s="19">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="P5" s="9">
         <v>46149</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>205</v>
+        <v>242</v>
       </c>
       <c r="R5" s="11">
         <v>279</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T5" s="9">
         <v>46151</v>
@@ -1851,7 +1904,7 @@
         <v>28</v>
       </c>
       <c r="AC5" s="26" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="75">
@@ -1863,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>17</v>
@@ -1878,46 +1931,46 @@
         <v>22</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M6" s="16">
+        <v>4.5</v>
+      </c>
+      <c r="N6" s="19">
+        <v>72</v>
+      </c>
+      <c r="O6" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="M6" s="16">
-        <v>4</v>
-      </c>
-      <c r="N6" s="19">
-        <v>300</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="P6" s="9">
         <v>46149</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>205</v>
+        <v>243</v>
       </c>
       <c r="R6" s="11">
         <v>179</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T6" s="9">
         <v>46152</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V6" s="3" t="s">
         <v>27</v>
@@ -1932,10 +1985,10 @@
         <v>28</v>
       </c>
       <c r="AC6" s="26" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="45" hidden="1">
+    <row r="7" spans="1:29" ht="45">
       <c r="A7" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
@@ -1944,61 +1997,61 @@
         <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="M7" s="16">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="N7" s="19">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="P7" s="9">
         <v>46149</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="R7" s="11">
         <v>139</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="T7" s="9">
         <v>46153</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>27</v>
@@ -2013,10 +2066,10 @@
         <v>28</v>
       </c>
       <c r="AC7" s="26" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="90">
+    <row r="8" spans="1:29" ht="60">
       <c r="A8" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
@@ -2028,7 +2081,7 @@
         <v>36</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>18</v>
@@ -2040,46 +2093,46 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="J8" s="3" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="M8" s="16">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N8" s="19">
-        <v>5163</v>
+        <v>5164</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P8" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>156</v>
+        <v>246</v>
       </c>
       <c r="R8" s="11">
         <v>179</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T8" s="9">
         <v>46150</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>27</v>
@@ -2095,10 +2148,10 @@
         <v>28</v>
       </c>
       <c r="AC8" s="27" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="90" hidden="1">
+    <row r="9" spans="1:29" ht="60">
       <c r="A9" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
@@ -2110,7 +2163,7 @@
         <v>37</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>18</v>
@@ -2122,46 +2175,46 @@
         <v>22</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="L9" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="M9" s="16">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N9" s="19">
         <v>5163</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P9" s="9">
         <v>46150</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>156</v>
+        <v>245</v>
       </c>
       <c r="R9" s="11">
         <v>179</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T9" s="9">
         <v>46150</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>27</v>
@@ -2177,10 +2230,10 @@
         <v>28</v>
       </c>
       <c r="AC9" s="27" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="90" hidden="1">
+    <row r="10" spans="1:29" ht="210">
       <c r="A10" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
@@ -2192,7 +2245,7 @@
         <v>38</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>18</v>
@@ -2204,19 +2257,19 @@
         <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="M10" s="16">
         <v>4.5</v>
@@ -2225,25 +2278,25 @@
         <v>11640</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P10" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>156</v>
+        <v>247</v>
       </c>
       <c r="R10" s="11">
         <v>159.99</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T10" s="9">
         <v>46150</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>27</v>
@@ -2252,17 +2305,17 @@
         <v>28</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Y10" s="4"/>
       <c r="AB10" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC10" s="27" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="90" hidden="1">
+    <row r="11" spans="1:29" ht="45">
       <c r="A11" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
@@ -2274,7 +2327,7 @@
         <v>40</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>18</v>
@@ -2286,19 +2339,19 @@
         <v>22</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="L11" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M11" s="16">
         <v>4.5</v>
@@ -2307,25 +2360,25 @@
         <v>11640</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P11" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>156</v>
+        <v>248</v>
       </c>
       <c r="R11" s="11">
         <v>159.99</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T11" s="9">
         <v>46150</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V11" s="3" t="s">
         <v>27</v>
@@ -2334,14 +2387,14 @@
         <v>28</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Y11" s="4"/>
       <c r="AB11" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC11" s="25" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="60" customHeight="1">
@@ -2356,7 +2409,7 @@
         <v>39</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>18</v>
@@ -2368,19 +2421,19 @@
         <v>22</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="M12" s="16">
         <v>4.5</v>
@@ -2389,25 +2442,25 @@
         <v>11640</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P12" s="9">
         <v>46150</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>156</v>
+        <v>249</v>
       </c>
       <c r="R12" s="11">
         <v>159.99</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T12" s="9">
         <v>46150</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>27</v>
@@ -2416,17 +2469,17 @@
         <v>27</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Y12" s="4"/>
       <c r="AB12" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC12" s="26" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="60">
+    <row r="13" spans="1:29" ht="60.75" thickBot="1">
       <c r="A13" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
@@ -2438,7 +2491,7 @@
         <v>6</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>18</v>
@@ -2450,46 +2503,46 @@
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="M13" s="16">
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N13" s="19">
-        <v>16</v>
+        <v>456</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="P13" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>155</v>
+        <v>250</v>
       </c>
       <c r="R13" s="11">
         <v>178</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T13" s="9">
         <v>46150</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>27</v>
@@ -2498,16 +2551,16 @@
         <v>27</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AB13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC13" s="26" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="75.75" hidden="1" thickBot="1">
+    <row r="14" spans="1:29" ht="75.75" thickBot="1">
       <c r="A14" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
@@ -2519,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>18</v>
@@ -2531,19 +2584,19 @@
         <v>22</v>
       </c>
       <c r="H14" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K14" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>132</v>
-      </c>
       <c r="L14" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="M14" s="16">
         <v>4</v>
@@ -2552,25 +2605,25 @@
         <v>2</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="P14" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="R14" s="11">
         <v>149</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T14" s="9">
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>27</v>
@@ -2579,14 +2632,14 @@
         <v>28</v>
       </c>
       <c r="X14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Y14" s="4"/>
       <c r="AB14" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC14" s="26" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="75">
@@ -2601,7 +2654,7 @@
         <v>9</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>18</v>
@@ -2613,46 +2666,43 @@
         <v>22</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="L15" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="M15" s="16">
         <v>5</v>
       </c>
       <c r="N15" s="19">
-        <v>4</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>151</v>
+        <v>5</v>
       </c>
       <c r="P15" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="R15" s="11">
         <v>89</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T15" s="9">
         <v>46150</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>27</v>
@@ -2668,7 +2718,7 @@
         <v>28</v>
       </c>
       <c r="AC15" s="25" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="60" customHeight="1">
@@ -2683,7 +2733,7 @@
         <v>10</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>18</v>
@@ -2695,19 +2745,19 @@
         <v>22</v>
       </c>
       <c r="H16" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="L16" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="M16" s="16">
         <v>5</v>
@@ -2716,25 +2766,25 @@
         <v>16</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="P16" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>155</v>
+        <v>212</v>
       </c>
       <c r="R16" s="11">
         <v>89</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T16" s="9">
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>27</v>
@@ -2743,17 +2793,17 @@
         <v>28</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="Y16" s="4"/>
       <c r="AB16" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC16" s="26" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="60" hidden="1">
+    <row r="17" spans="1:29" ht="60">
       <c r="A17" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
@@ -2765,7 +2815,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>18</v>
@@ -2777,19 +2827,19 @@
         <v>22</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="J17" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="L17" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="M17" s="16">
         <v>5</v>
@@ -2798,25 +2848,25 @@
         <v>2</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>151</v>
+        <v>251</v>
       </c>
       <c r="P17" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q17" s="22" t="s">
-        <v>155</v>
+        <v>253</v>
       </c>
       <c r="R17" s="11">
         <v>119</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="T17" s="9">
         <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>27</v>
@@ -2832,10 +2882,10 @@
         <v>28</v>
       </c>
       <c r="AC17" s="25" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="75" hidden="1">
+    <row r="18" spans="1:29" ht="60">
       <c r="A18" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
@@ -2847,7 +2897,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>18</v>
@@ -2859,19 +2909,19 @@
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="K18" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>164</v>
       </c>
       <c r="M18" s="16">
         <v>3</v>
@@ -2880,25 +2930,25 @@
         <v>80</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P18" s="9">
         <v>46151</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>42</v>
+        <v>254</v>
       </c>
       <c r="R18" s="11">
         <v>25.99</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T18" s="9">
         <v>46151</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>27</v>
@@ -2913,7 +2963,7 @@
         <v>28</v>
       </c>
       <c r="AC18" s="25" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="74.25" customHeight="1">
@@ -2928,31 +2978,31 @@
         <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="M19" s="16">
         <v>4.3</v>
@@ -2961,19 +3011,19 @@
         <v>17</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P19" s="9">
         <v>46152</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>209</v>
+        <v>255</v>
       </c>
       <c r="R19" s="11">
         <v>329</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T19" s="9">
         <v>46152</v>
@@ -3000,10 +3050,10 @@
         <v>28</v>
       </c>
       <c r="AC19" s="25" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="60" hidden="1">
+    <row r="20" spans="1:29" ht="60">
       <c r="A20" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Border Collie</v>
@@ -3012,10 +3062,10 @@
         <v>43</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>18</v>
@@ -3027,19 +3077,19 @@
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="M20" s="16">
         <v>4.3</v>
@@ -3048,25 +3098,25 @@
         <v>403</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P20" s="9">
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>211</v>
+        <v>256</v>
       </c>
       <c r="R20" s="11">
         <v>44.45</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T20" s="9">
         <v>46150</v>
       </c>
       <c r="U20" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>27</v>
@@ -3078,10 +3128,10 @@
         <v>47</v>
       </c>
       <c r="AC20" s="25" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="75" hidden="1">
+    <row r="21" spans="1:29" ht="75">
       <c r="A21" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Chocolate Lab</v>
@@ -3090,10 +3140,10 @@
         <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>18</v>
@@ -3105,19 +3155,19 @@
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="M21" s="16">
         <v>4.3</v>
@@ -3126,25 +3176,25 @@
         <v>553</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P21" s="9">
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>211</v>
+        <v>257</v>
       </c>
       <c r="R21" s="11">
         <v>44.45</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T21" s="9">
         <v>46150</v>
       </c>
       <c r="U21" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>27</v>
@@ -3156,10 +3206,10 @@
         <v>48</v>
       </c>
       <c r="AC21" s="25" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="63.75">
+    <row r="22" spans="1:29" ht="75">
       <c r="A22" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Shih Tzu</v>
@@ -3168,10 +3218,10 @@
         <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>18</v>
@@ -3183,19 +3233,19 @@
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="M22" s="16">
         <v>4.2</v>
@@ -3204,25 +3254,25 @@
         <v>878</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P22" s="9">
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>211</v>
+        <v>258</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T22" s="9">
         <v>46150</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>27</v>
@@ -3234,10 +3284,10 @@
         <v>49</v>
       </c>
       <c r="AC22" s="25" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="60" hidden="1">
+    <row r="23" spans="1:29" ht="75">
       <c r="A23" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Beagle</v>
@@ -3246,10 +3296,10 @@
         <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>18</v>
@@ -3261,19 +3311,19 @@
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="M23" s="16">
         <v>4.4000000000000004</v>
@@ -3282,25 +3332,25 @@
         <v>466</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P23" s="9">
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>211</v>
+        <v>259</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T23" s="9">
         <v>46150</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>27</v>
@@ -3312,10 +3362,10 @@
         <v>50</v>
       </c>
       <c r="AC23" s="25" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="60" hidden="1" customHeight="1">
+    <row r="24" spans="1:29" ht="60" customHeight="1">
       <c r="A24" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Grey Tabby Cat</v>
@@ -3324,10 +3374,10 @@
         <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>18</v>
@@ -3339,19 +3389,19 @@
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="M24" s="16">
         <v>4.3</v>
@@ -3360,25 +3410,25 @@
         <v>848</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P24" s="9">
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T24" s="9">
         <v>46150</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>27</v>
@@ -3390,10 +3440,10 @@
         <v>51</v>
       </c>
       <c r="AC24" s="25" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="60" hidden="1" customHeight="1">
+    <row r="25" spans="1:29" ht="60" customHeight="1">
       <c r="A25" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Plush White Cat</v>
@@ -3402,10 +3452,10 @@
         <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>18</v>
@@ -3417,19 +3467,19 @@
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="M25" s="16">
         <v>4</v>
@@ -3438,25 +3488,25 @@
         <v>54</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P25" s="9">
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>211</v>
+        <v>261</v>
       </c>
       <c r="R25" s="11">
         <v>53.9</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T25" s="9">
         <v>46150</v>
       </c>
       <c r="U25" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V25" s="3" t="s">
         <v>27</v>
@@ -3465,10 +3515,10 @@
         <v>28</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AC25" s="25" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="60" customHeight="1">
@@ -3480,10 +3530,10 @@
         <v>43</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>18</v>
@@ -3495,19 +3545,19 @@
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="M26" s="16">
         <v>4.4000000000000004</v>
@@ -3516,25 +3566,25 @@
         <v>1200</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P26" s="9">
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>211</v>
+        <v>262</v>
       </c>
       <c r="R26" s="11">
         <v>44.45</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T26" s="9">
         <v>46150</v>
       </c>
       <c r="U26" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>27</v>
@@ -3546,10 +3596,10 @@
         <v>51</v>
       </c>
       <c r="AC26" s="25" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="60" hidden="1" customHeight="1">
+    <row r="27" spans="1:29" ht="60" customHeight="1">
       <c r="A27" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Siamese Cat</v>
@@ -3558,10 +3608,10 @@
         <v>43</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>18</v>
@@ -3573,19 +3623,19 @@
         <v>24</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="M27" s="16">
         <v>4.0999999999999996</v>
@@ -3594,25 +3644,25 @@
         <v>16</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P27" s="9">
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>211</v>
+        <v>263</v>
       </c>
       <c r="R27" s="11">
         <v>53.9</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T27" s="9">
         <v>46150</v>
       </c>
       <c r="U27" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>27</v>
@@ -3624,7 +3674,7 @@
         <v>52</v>
       </c>
       <c r="AC27" s="25" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="75">
@@ -3639,7 +3689,7 @@
         <v>54</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>17</v>
@@ -3651,19 +3701,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="M28" s="16">
         <v>4.4000000000000004</v>
@@ -3672,25 +3722,25 @@
         <v>283</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P28" s="9">
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>55</v>
+        <v>264</v>
       </c>
       <c r="R28" s="11">
         <v>69.989999999999995</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T28" s="9">
         <v>46150</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V28" s="3" t="s">
         <v>27</v>
@@ -3699,10 +3749,10 @@
         <v>27</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AC28" s="25" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="27.75" customHeight="1">
@@ -3711,13 +3761,13 @@
         <v>Furby DJ Furby</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>17</v>
@@ -3729,19 +3779,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="K29" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>194</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="M29" s="16">
         <v>4.8</v>
@@ -3750,25 +3800,25 @@
         <v>772</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P29" s="9">
         <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>200</v>
+        <v>265</v>
       </c>
       <c r="R29" s="11">
         <v>50.11</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T29" s="9">
         <v>46150</v>
       </c>
       <c r="U29" s="9" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>27</v>
@@ -3780,7 +3830,7 @@
         <v>44</v>
       </c>
       <c r="AC29" s="25" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="75">
@@ -3789,13 +3839,13 @@
         <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C30" s="7" t="s">
-        <v>58</v>
-      </c>
       <c r="D30" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>17</v>
@@ -3807,16 +3857,16 @@
         <v>23</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M30" s="16">
         <v>4.2</v>
@@ -3825,19 +3875,19 @@
         <v>1199</v>
       </c>
       <c r="O30" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="P30" s="9">
         <v>46150</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>59</v>
+        <v>266</v>
       </c>
       <c r="R30" s="11">
         <v>499</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="T30" s="9">
         <v>46150</v>
@@ -3852,37 +3902,28 @@
         <v>27</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AC30" s="25" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="31" spans="1:29" hidden="1">
+    <row r="31" spans="1:29">
       <c r="A31" s="3" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC31" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-    <filterColumn colId="22">
-      <filters>
-        <filter val="yes"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AC31" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="Q7" r:id="rId1" display="https://store.enabot.com/products/rola-mini-familybot" xr:uid="{D49343E0-D5EC-4C50-A249-B612E5577C2E}"/>
-    <hyperlink ref="Q15:Q17" r:id="rId2" display="https://chongker.com/collections/interactive-stuffed-animals" xr:uid="{463F1AA5-9B50-4055-AB15-B754D3838990}"/>
-    <hyperlink ref="Q14" r:id="rId3" display="https://chongker.com/collections/interactive-stuffed-animals" xr:uid="{D9BC2ECF-9D49-455D-AB7A-AD5A56B3A32A}"/>
-    <hyperlink ref="Q13" r:id="rId4" display="https://chongker.com/collections/interactive-stuffed-animals" xr:uid="{00B8DB52-D0BF-4C5F-81E4-B934F2771184}"/>
-    <hyperlink ref="AC8" r:id="rId5" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
-    <hyperlink ref="AC9" r:id="rId6" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
+    <hyperlink ref="AC8" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
+    <hyperlink ref="AC9" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
-  <drawing r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -3914,7 +3955,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -3940,12 +3981,12 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -3980,7 +4021,7 @@
         <v>1</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E1" s="12" t="s">
         <v>18</v>
@@ -4008,7 +4049,7 @@
         <v>28</v>
       </c>
       <c r="Y1" s="12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="Z1" s="12" t="s">
         <v>45</v>
@@ -4029,7 +4070,7 @@
         <v>3</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>18</v>
@@ -4041,7 +4082,7 @@
         <v>22</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="M2" s="17"/>
       <c r="N2" s="20"/>
@@ -4060,7 +4101,7 @@
         <v>28</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Z2" s="12" t="s">
         <v>45</v>
@@ -4081,7 +4122,7 @@
         <v>4</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>18</v>
@@ -4093,7 +4134,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="20"/>
@@ -4112,7 +4153,7 @@
         <v>28</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Z3" s="12" t="s">
         <v>45</v>
@@ -4133,7 +4174,7 @@
         <v>5</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>18</v>
@@ -4145,7 +4186,7 @@
         <v>22</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="20"/>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AE531C-7574-47D4-9619-B349E9564E47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E94FDD9-8B89-47CE-BB7C-E4D3C469C70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Maybe Later" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AC$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AC$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1083,13 +1083,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1460,7 +1460,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.140625" style="3" customWidth="1"/>
@@ -1585,7 +1585,7 @@
     </row>
     <row r="2" spans="1:29" ht="75">
       <c r="A2" s="3" t="str">
-        <f t="shared" ref="A2:A31" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
+        <f>_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1666,14 +1666,14 @@
     </row>
     <row r="3" spans="1:29" ht="75">
       <c r="A3" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Max FamilyBot </v>
+        <f>_xlfn.CONCAT(B3, " ", C3)</f>
+        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>69</v>
@@ -1682,31 +1682,31 @@
         <v>17</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>198</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>99</v>
       </c>
       <c r="M3" s="16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N3" s="19">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>89</v>
@@ -1715,16 +1715,16 @@
         <v>46149</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="R3" s="11">
-        <v>549</v>
+        <v>359</v>
       </c>
       <c r="S3" s="3" t="s">
         <v>89</v>
       </c>
       <c r="T3" s="9">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="U3" s="9" t="s">
         <v>26</v>
@@ -1733,7 +1733,7 @@
         <v>27</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X3" s="2" t="s">
         <v>44</v>
@@ -1742,19 +1742,19 @@
         <v>28</v>
       </c>
       <c r="AC3" s="26" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="75">
       <c r="A4" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
+        <f>_xlfn.CONCAT(B4, " ", C4)</f>
+        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
       <c r="B4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>69</v>
@@ -1772,13 +1772,13 @@
         <v>198</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>99</v>
@@ -1787,7 +1787,7 @@
         <v>5</v>
       </c>
       <c r="N4" s="19">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>89</v>
@@ -1796,16 +1796,16 @@
         <v>46149</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R4" s="11">
-        <v>359</v>
+        <v>279</v>
       </c>
       <c r="S4" s="3" t="s">
         <v>89</v>
       </c>
       <c r="T4" s="9">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="U4" s="9" t="s">
         <v>26</v>
@@ -1814,7 +1814,7 @@
         <v>27</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X4" s="2" t="s">
         <v>44</v>
@@ -1823,19 +1823,19 @@
         <v>28</v>
       </c>
       <c r="AC4" s="26" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="75">
       <c r="A5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
+        <f>_xlfn.CONCAT(B5, " ", C5)</f>
+        <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
       </c>
       <c r="B5" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>69</v>
@@ -1853,22 +1853,22 @@
         <v>198</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="L5" s="3" t="s">
         <v>99</v>
       </c>
       <c r="M5" s="16">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N5" s="19">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>89</v>
@@ -1877,25 +1877,25 @@
         <v>46149</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="R5" s="11">
-        <v>279</v>
+        <v>179</v>
       </c>
       <c r="S5" s="3" t="s">
         <v>89</v>
       </c>
       <c r="T5" s="9">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>26</v>
+        <v>196</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X5" s="2" t="s">
         <v>44</v>
@@ -1904,19 +1904,19 @@
         <v>28</v>
       </c>
       <c r="AC5" s="26" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="75">
+    <row r="6" spans="1:29" ht="45">
       <c r="A6" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
+        <f>_xlfn.CONCAT(B6, " ", C6)</f>
+        <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>69</v>
@@ -1925,31 +1925,31 @@
         <v>17</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" s="3" t="s">
-        <v>198</v>
+        <v>101</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="M6" s="16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N6" s="19">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>89</v>
@@ -1957,17 +1957,17 @@
       <c r="P6" s="9">
         <v>46149</v>
       </c>
-      <c r="Q6" s="3" t="s">
-        <v>243</v>
+      <c r="Q6" s="22" t="s">
+        <v>244</v>
       </c>
       <c r="R6" s="11">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="S6" s="3" t="s">
         <v>89</v>
       </c>
       <c r="T6" s="9">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="U6" s="9" t="s">
         <v>196</v>
@@ -1976,7 +1976,7 @@
         <v>27</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X6" s="2" t="s">
         <v>44</v>
@@ -1985,70 +1985,70 @@
         <v>28</v>
       </c>
       <c r="AC6" s="26" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="45">
+    <row r="7" spans="1:29" ht="60">
       <c r="A7" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
+        <f>_xlfn.CONCAT(B7, " ", C7)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>199</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="M7" s="16">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="N7" s="19">
-        <v>73</v>
+        <v>5164</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P7" s="9">
-        <v>46149</v>
-      </c>
-      <c r="Q7" s="22" t="s">
-        <v>244</v>
+        <v>46153</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>246</v>
       </c>
       <c r="R7" s="11">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T7" s="9">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="U7" s="9" t="s">
         <v>196</v>
@@ -2057,28 +2057,29 @@
         <v>27</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="Y7" s="4"/>
       <c r="AB7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AC7" s="26" t="s">
-        <v>234</v>
+      <c r="AC7" s="27" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="60">
       <c r="A8" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
+        <f>_xlfn.CONCAT(B8, " ", C8)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>71</v>
@@ -2093,7 +2094,7 @@
         <v>22</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>112</v>
@@ -2102,25 +2103,25 @@
         <v>113</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M8" s="16">
         <v>4.3</v>
       </c>
       <c r="N8" s="19">
-        <v>5164</v>
+        <v>5163</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>88</v>
       </c>
       <c r="P8" s="9">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R8" s="11">
         <v>179</v>
@@ -2138,7 +2139,7 @@
         <v>27</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X8" s="2" t="s">
         <v>35</v>
@@ -2151,19 +2152,19 @@
         <v>205</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="60">
+    <row r="9" spans="1:29" ht="210">
       <c r="A9" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
+        <f>_xlfn.CONCAT(B9, " ", C9)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>18</v>
@@ -2175,37 +2176,37 @@
         <v>22</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M9" s="16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N9" s="19">
-        <v>5163</v>
+        <v>11640</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>88</v>
       </c>
       <c r="P9" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="R9" s="11">
-        <v>179</v>
+        <v>159.99</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>88</v>
@@ -2223,26 +2224,26 @@
         <v>28</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="Y9" s="4"/>
       <c r="AB9" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC9" s="27" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="210">
       <c r="A10" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
+        <f>_xlfn.CONCAT(B10, " ", C10)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>68</v>
@@ -2257,7 +2258,7 @@
         <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>117</v>
@@ -2266,10 +2267,10 @@
         <v>118</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M10" s="16">
         <v>4.5</v>
@@ -2284,7 +2285,7 @@
         <v>46153</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="R10" s="11">
         <v>159.99</v>
@@ -2305,26 +2306,26 @@
         <v>28</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Y10" s="4"/>
       <c r="AB10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AC10" s="27" t="s">
-        <v>206</v>
+      <c r="AC10" s="25" t="s">
+        <v>207</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="45">
+    <row r="11" spans="1:29" ht="60" customHeight="1">
       <c r="A11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
+        <f>_xlfn.CONCAT(B11, " ", C11)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>68</v>
@@ -2339,7 +2340,7 @@
         <v>22</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>117</v>
@@ -2348,10 +2349,10 @@
         <v>118</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M11" s="16">
         <v>4.5</v>
@@ -2363,10 +2364,10 @@
         <v>88</v>
       </c>
       <c r="P11" s="9">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="R11" s="11">
         <v>159.99</v>
@@ -2384,29 +2385,29 @@
         <v>27</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>62</v>
+        <v>27</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="Y11" s="4"/>
       <c r="AB11" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AC11" s="25" t="s">
-        <v>207</v>
+      <c r="AC11" s="26" t="s">
+        <v>208</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="60" customHeight="1">
+    <row r="12" spans="1:29" ht="285.75" thickBot="1">
       <c r="A12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
+        <f>_xlfn.CONCAT(B12, " ", C12)</f>
+        <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>68</v>
@@ -2421,40 +2422,40 @@
         <v>22</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>121</v>
+        <v>200</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M12" s="16">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N12" s="19">
-        <v>11640</v>
+        <v>456</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>88</v>
       </c>
       <c r="P12" s="9">
-        <v>46150</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>249</v>
+        <v>46153</v>
+      </c>
+      <c r="Q12" s="22" t="s">
+        <v>250</v>
       </c>
       <c r="R12" s="11">
-        <v>159.99</v>
+        <v>178</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="T12" s="9">
         <v>46150</v>
@@ -2469,26 +2470,25 @@
         <v>27</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y12" s="4"/>
+        <v>59</v>
+      </c>
       <c r="AB12" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC12" s="26" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="60.75" thickBot="1">
+    <row r="13" spans="1:29" ht="75.75" thickBot="1">
       <c r="A13" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Chongker MateCat Pro </v>
+        <f>_xlfn.CONCAT(B13, " ", C13)</f>
+        <v xml:space="preserve"> Chongker MateCat 1.1 </v>
       </c>
       <c r="B13" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>68</v>
@@ -2503,37 +2503,37 @@
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>200</v>
+        <v>126</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>129</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M13" s="16">
-        <v>4.5999999999999996</v>
+        <v>4</v>
       </c>
       <c r="N13" s="19">
-        <v>456</v>
+        <v>2</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>88</v>
+        <v>251</v>
       </c>
       <c r="P13" s="9">
         <v>46153</v>
       </c>
       <c r="Q13" s="22" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="R13" s="11">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="S13" s="3" t="s">
         <v>148</v>
@@ -2548,31 +2548,32 @@
         <v>27</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X13" s="3" t="s">
         <v>59</v>
       </c>
+      <c r="Y13" s="4"/>
       <c r="AB13" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC13" s="26" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="75.75" thickBot="1">
+    <row r="14" spans="1:29" ht="75">
       <c r="A14" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Chongker MateCat 1.1 </v>
+        <f>_xlfn.CONCAT(B14, " ", C14)</f>
+        <v xml:space="preserve"> Chongker Percy 1.1 Robotic Dog </v>
       </c>
       <c r="B14" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>18</v>
@@ -2584,37 +2585,34 @@
         <v>22</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K14" s="21" t="s">
-        <v>129</v>
+        <v>132</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>133</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M14" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N14" s="19">
-        <v>2</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>251</v>
+        <v>5</v>
       </c>
       <c r="P14" s="9">
         <v>46153</v>
       </c>
       <c r="Q14" s="22" t="s">
-        <v>210</v>
+        <v>252</v>
       </c>
       <c r="R14" s="11">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>148</v>
@@ -2623,38 +2621,38 @@
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="Y14" s="4"/>
       <c r="AB14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AC14" s="26" t="s">
-        <v>210</v>
+      <c r="AC14" s="25" t="s">
+        <v>211</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="75">
+    <row r="15" spans="1:29" ht="60" customHeight="1">
       <c r="A15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Chongker Percy 1.1 Robotic Dog </v>
+        <f>_xlfn.CONCAT(B15, " ", C15)</f>
+        <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
       <c r="B15" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>18</v>
@@ -2666,31 +2664,34 @@
         <v>22</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M15" s="16">
         <v>5</v>
       </c>
       <c r="N15" s="19">
-        <v>5</v>
+        <v>16</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>251</v>
       </c>
       <c r="P15" s="9">
         <v>46153</v>
       </c>
       <c r="Q15" s="22" t="s">
-        <v>252</v>
+        <v>212</v>
       </c>
       <c r="R15" s="11">
         <v>89</v>
@@ -2708,32 +2709,32 @@
         <v>27</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="Y15" s="4"/>
       <c r="AB15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AC15" s="25" t="s">
-        <v>211</v>
+      <c r="AC15" s="26" t="s">
+        <v>212</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="60" customHeight="1">
+    <row r="16" spans="1:29" ht="60">
       <c r="A16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Chongker Percy Robot Cat </v>
+        <f>_xlfn.CONCAT(B16, " ", C16)</f>
+        <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
       <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>18</v>
@@ -2745,25 +2746,25 @@
         <v>22</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M16" s="16">
         <v>5</v>
       </c>
       <c r="N16" s="19">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>251</v>
@@ -2772,10 +2773,10 @@
         <v>46153</v>
       </c>
       <c r="Q16" s="22" t="s">
-        <v>212</v>
+        <v>253</v>
       </c>
       <c r="R16" s="11">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>148</v>
@@ -2784,7 +2785,7 @@
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>93</v>
+        <v>196</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>27</v>
@@ -2792,81 +2793,81 @@
       <c r="W16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="X16" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y16" s="4"/>
+      <c r="X16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y16" s="5"/>
       <c r="AB16" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="AC16" s="26" t="s">
-        <v>212</v>
+      <c r="AC16" s="25" t="s">
+        <v>213</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="60">
+    <row r="17" spans="1:29" ht="180">
       <c r="A17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
+        <f>_xlfn.CONCAT(B17, " ", C17)</f>
+        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="M17" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N17" s="19">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>251</v>
+        <v>88</v>
       </c>
       <c r="P17" s="9">
-        <v>46153</v>
-      </c>
-      <c r="Q17" s="22" t="s">
-        <v>253</v>
+        <v>46151</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>254</v>
       </c>
       <c r="R17" s="11">
-        <v>119</v>
+        <v>25.99</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="T17" s="9">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>196</v>
+        <v>93</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>27</v>
@@ -2875,194 +2876,190 @@
         <v>28</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y17" s="5"/>
+        <v>42</v>
+      </c>
       <c r="AB17" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC17" s="25" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="60">
+    <row r="18" spans="1:29" ht="74.25" customHeight="1">
       <c r="A18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
+        <f>_xlfn.CONCAT(B18, " ", C18)</f>
+        <v>Ropet KAMOMO</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>154</v>
+        <v>201</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M18" s="16">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N18" s="19">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>88</v>
       </c>
       <c r="P18" s="9">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="R18" s="11">
-        <v>25.99</v>
+        <v>329</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>88</v>
       </c>
       <c r="T18" s="9">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>28</v>
       </c>
       <c r="AC18" s="25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="74.25" customHeight="1">
+    <row r="19" spans="1:29" ht="75">
       <c r="A19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Ropet KAMOMO</v>
+        <f>_xlfn.CONCAT(B19, " ", C19)</f>
+        <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>69</v>
+        <v>43</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>71</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>156</v>
+        <v>22</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>160</v>
+        <v>202</v>
       </c>
       <c r="M19" s="16">
         <v>4.3</v>
       </c>
       <c r="N19" s="19">
-        <v>17</v>
+        <v>403</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>88</v>
       </c>
       <c r="P19" s="9">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R19" s="11">
-        <v>329</v>
+        <v>44.45</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>88</v>
       </c>
       <c r="T19" s="9">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="U19" s="9" t="s">
-        <v>26</v>
+        <v>93</v>
       </c>
       <c r="V19" s="3" t="s">
         <v>27</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB19" s="3" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="AC19" s="25" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="60">
+    <row r="20" spans="1:29" ht="75">
       <c r="A20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Border Collie</v>
+        <f>_xlfn.CONCAT(B20, " ", C20)</f>
+        <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>71</v>
@@ -3077,16 +3074,16 @@
         <v>24</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>202</v>
@@ -3095,7 +3092,7 @@
         <v>4.3</v>
       </c>
       <c r="N20" s="19">
-        <v>403</v>
+        <v>553</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>88</v>
@@ -3104,7 +3101,7 @@
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="R20" s="11">
         <v>44.45</v>
@@ -3125,22 +3122,22 @@
         <v>28</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AC20" s="25" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="75">
       <c r="A21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Chocolate Lab</v>
+        <f>_xlfn.CONCAT(B21, " ", C21)</f>
+        <v>Perfect Petzzz Original Shih Tzu</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>71</v>
@@ -3155,25 +3152,25 @@
         <v>24</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>202</v>
       </c>
       <c r="M21" s="16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N21" s="19">
-        <v>553</v>
+        <v>878</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>88</v>
@@ -3182,7 +3179,7 @@
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="R21" s="11">
         <v>44.45</v>
@@ -3200,25 +3197,25 @@
         <v>27</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AC21" s="25" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="75">
       <c r="A22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Shih Tzu</v>
+        <f>_xlfn.CONCAT(B22, " ", C22)</f>
+        <v>Perfect Petzzz Original Beagle</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>71</v>
@@ -3233,25 +3230,25 @@
         <v>24</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>202</v>
       </c>
       <c r="M22" s="16">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N22" s="19">
-        <v>878</v>
+        <v>466</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>88</v>
@@ -3260,7 +3257,7 @@
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
@@ -3278,28 +3275,28 @@
         <v>27</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC22" s="25" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="75">
+    <row r="23" spans="1:29" ht="60" customHeight="1">
       <c r="A23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Beagle</v>
+        <f>_xlfn.CONCAT(B23, " ", C23)</f>
+        <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>170</v>
+        <v>221</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>18</v>
@@ -3311,25 +3308,25 @@
         <v>24</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="L23" s="3" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M23" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="N23" s="19">
-        <v>466</v>
+        <v>848</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>88</v>
@@ -3338,7 +3335,7 @@
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
@@ -3359,22 +3356,22 @@
         <v>28</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC23" s="25" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="60" customHeight="1">
       <c r="A24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Grey Tabby Cat</v>
+        <f>_xlfn.CONCAT(B24, " ", C24)</f>
+        <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>221</v>
+        <v>171</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>68</v>
@@ -3389,25 +3386,25 @@
         <v>24</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>203</v>
       </c>
       <c r="M24" s="16">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N24" s="19">
-        <v>848</v>
+        <v>54</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>88</v>
@@ -3416,10 +3413,10 @@
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="R24" s="11">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="S24" s="3" t="s">
         <v>88</v>
@@ -3437,22 +3434,22 @@
         <v>28</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="AC24" s="25" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="60" customHeight="1">
       <c r="A25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Plush White Cat</v>
+        <f>_xlfn.CONCAT(B25, " ", C25)</f>
+        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>68</v>
@@ -3467,25 +3464,25 @@
         <v>24</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>163</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>203</v>
       </c>
       <c r="M25" s="16">
-        <v>4</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N25" s="19">
-        <v>54</v>
+        <v>1200</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>88</v>
@@ -3494,10 +3491,10 @@
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="R25" s="11">
-        <v>53.9</v>
+        <v>44.45</v>
       </c>
       <c r="S25" s="3" t="s">
         <v>88</v>
@@ -3512,25 +3509,25 @@
         <v>27</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="AC25" s="25" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="60" customHeight="1">
       <c r="A26" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
+        <f>_xlfn.CONCAT(B26, " ", C26)</f>
+        <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>68</v>
@@ -3545,25 +3542,25 @@
         <v>24</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>203</v>
       </c>
       <c r="M26" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N26" s="19">
-        <v>1200</v>
+        <v>16</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>88</v>
@@ -3572,10 +3569,10 @@
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="R26" s="11">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>88</v>
@@ -3590,58 +3587,58 @@
         <v>27</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AC26" s="25" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="60" customHeight="1">
+    <row r="27" spans="1:29" ht="300">
       <c r="A27" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Siamese Cat</v>
+        <f>_xlfn.CONCAT(B27, " ", C27)</f>
+        <v>Ruko 18011 Smart Robot Dog</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>68</v>
+        <v>53</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>22</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>203</v>
+        <v>184</v>
       </c>
       <c r="M27" s="16">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N27" s="19">
-        <v>16</v>
+        <v>283</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>88</v>
@@ -3650,10 +3647,10 @@
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="R27" s="11">
-        <v>53.9</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>88</v>
@@ -3668,28 +3665,28 @@
         <v>27</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AC27" s="25" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="75">
+    <row r="28" spans="1:29" ht="27.75" customHeight="1">
       <c r="A28" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Ruko 18011 Smart Robot Dog</v>
+        <f>_xlfn.CONCAT(B28, " ", C28)</f>
+        <v>Furby DJ Furby</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>71</v>
+        <v>58</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>69</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>17</v>
@@ -3701,25 +3698,25 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="M28" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="N28" s="19">
-        <v>283</v>
+        <v>772</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>88</v>
@@ -3728,10 +3725,10 @@
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="R28" s="11">
-        <v>69.989999999999995</v>
+        <v>50.11</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>88</v>
@@ -3749,25 +3746,25 @@
         <v>27</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AC28" s="25" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="27.75" customHeight="1">
+    <row r="29" spans="1:29" ht="300">
       <c r="A29" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Furby DJ Furby</v>
+        <f>_xlfn.CONCAT(B29, " ", C29)</f>
+        <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>69</v>
+        <v>56</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>17</v>
@@ -3779,25 +3776,22 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="M29" s="16">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="N29" s="19">
-        <v>772</v>
+        <v>1199</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>88</v>
@@ -3806,10 +3800,10 @@
         <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="R29" s="11">
-        <v>50.11</v>
+        <v>499</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>88</v>
@@ -3818,7 +3812,7 @@
         <v>46150</v>
       </c>
       <c r="U29" s="9" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>27</v>
@@ -3827,99 +3821,24 @@
         <v>27</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="AC29" s="25" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="75">
+    <row r="30" spans="1:29">
       <c r="A30" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Loona Robot Pet Dog</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="M30" s="16">
-        <v>4.2</v>
-      </c>
-      <c r="N30" s="19">
-        <v>1199</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="P30" s="9">
-        <v>46150</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="R30" s="11">
-        <v>499</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="T30" s="9">
-        <v>46150</v>
-      </c>
-      <c r="U30" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="V30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="W30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X30" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC30" s="25" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29">
-      <c r="A31" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B30, " ", C30)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC31" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}"/>
+  <autoFilter ref="A1:AC30" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}"/>
   <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="AC8" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
-    <hyperlink ref="AC9" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
+    <hyperlink ref="AC7" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
+    <hyperlink ref="AC8" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -3931,13 +3850,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:U1048576</xm:sqref>
+          <xm:sqref>U1:U2 U3:U1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37BE27F9-E75E-4C54-9192-7DED9B8091B0}">
           <x14:formula1>
             <xm:f>Lists!$A$7:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>W1:W1048576</xm:sqref>
+          <xm:sqref>W1:W2 W3:W1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4006,68 +3925,101 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3587DF7-27DE-4C49-A0D7-210E14A8420B}">
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:29" s="12" customFormat="1" ht="75">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="75">
       <c r="A1" s="3" t="str">
         <f>_xlfn.CONCAT(B1, " ", C1)</f>
-        <v xml:space="preserve"> Elephant Robotics MarsCat </v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="12" t="s">
+        <v xml:space="preserve"> Enabot EBO Max FamilyBot </v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G1" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="20"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="14"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="W1" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="X1" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y1" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z1" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC1" s="12" t="s">
-        <v>28</v>
+      <c r="H1" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="M1" s="16">
+        <v>0</v>
+      </c>
+      <c r="N1" s="19">
+        <v>0</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="P1" s="9">
+        <v>46149</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="R1" s="11">
+        <v>549</v>
+      </c>
+      <c r="S1" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="T1" s="9">
+        <v>46149</v>
+      </c>
+      <c r="U1" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="V1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="W1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y1" s="6"/>
+      <c r="AB1" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AC1" s="26" t="s">
+        <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="12" customFormat="1" ht="15" customHeight="1">
+    <row r="2" spans="1:29" s="12" customFormat="1" ht="75">
       <c r="A2" s="3" t="str">
         <f>_xlfn.CONCAT(B2, " ", C2)</f>
-        <v xml:space="preserve"> Elephant Robotics metaCat </v>
+        <v xml:space="preserve"> Elephant Robotics MarsCat </v>
       </c>
       <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
         <v>68</v>
@@ -4076,13 +4028,10 @@
         <v>18</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G2" s="12" t="s">
         <v>22</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>106</v>
       </c>
       <c r="M2" s="17"/>
       <c r="N2" s="20"/>
@@ -4095,13 +4044,13 @@
         <v>27</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X2" s="12" t="s">
         <v>28</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="Z2" s="12" t="s">
         <v>45</v>
@@ -4110,19 +4059,19 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="12" customFormat="1" ht="405">
+    <row r="3" spans="1:29" s="12" customFormat="1" ht="15" customHeight="1">
       <c r="A3" s="3" t="str">
         <f>_xlfn.CONCAT(B3, " ", C3)</f>
-        <v xml:space="preserve"> Elephant Robotics metaDog </v>
+        <v xml:space="preserve"> Elephant Robotics metaCat </v>
       </c>
       <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>18</v>
@@ -4134,7 +4083,7 @@
         <v>22</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="20"/>
@@ -4153,7 +4102,7 @@
         <v>28</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="Z3" s="12" t="s">
         <v>45</v>
@@ -4162,19 +4111,19 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="12" customFormat="1" ht="360">
+    <row r="4" spans="1:29" s="12" customFormat="1" ht="405">
       <c r="A4" s="3" t="str">
         <f>_xlfn.CONCAT(B4, " ", C4)</f>
-        <v xml:space="preserve"> Elephant Robotics metaPanda </v>
+        <v xml:space="preserve"> Elephant Robotics metaDog </v>
       </c>
       <c r="B4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>18</v>
@@ -4186,7 +4135,7 @@
         <v>22</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="20"/>
@@ -4205,12 +4154,64 @@
         <v>28</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="Z4" s="12" t="s">
         <v>45</v>
       </c>
       <c r="AC4" s="12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" s="12" customFormat="1" ht="360">
+      <c r="A5" s="3" t="str">
+        <f>_xlfn.CONCAT(B5, " ", C5)</f>
+        <v xml:space="preserve"> Elephant Robotics metaPanda </v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="H5" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="M5" s="17"/>
+      <c r="N5" s="20"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="23"/>
+      <c r="R5" s="14"/>
+      <c r="T5" s="13"/>
+      <c r="U5" s="13"/>
+      <c r="V5" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="X5" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="Y5" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z5" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC5" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -4218,12 +4219,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{33C992CF-22D4-4E94-80E1-2C06CE97D7D6}">
           <x14:formula1>
             <xm:f>Lists!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:U4</xm:sqref>
+          <xm:sqref>U1:U5</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37BE27F9-E75E-4C54-9192-7DED9B8091B0}">
+          <x14:formula1>
+            <xm:f>Lists!$A$7:$A$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>W1</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E94FDD9-8B89-47CE-BB7C-E4D3C469C70D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8092049-54FC-45CA-BE2B-173C3A16F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="284">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -74,9 +74,6 @@
     <t xml:space="preserve">MateCat 1.1 </t>
   </si>
   <si>
-    <t xml:space="preserve">Percy 1.1 Robotic Dog </t>
-  </si>
-  <si>
     <t xml:space="preserve">Percy Robot Cat </t>
   </si>
   <si>
@@ -146,15 +143,9 @@
     <t>Internet Access</t>
   </si>
   <si>
-    <t>Affiliate Agreement</t>
-  </si>
-  <si>
     <t>Image URL</t>
   </si>
   <si>
-    <t>/images/products/Mr-Dog.png</t>
-  </si>
-  <si>
     <t>Companion Pet Pup Golden</t>
   </si>
   <si>
@@ -173,9 +164,6 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>Amazon.com: chinatera 2026 Wuffy Robot Dog Lifelike Toy Dog, Interactive Robot with Touch Sensing Voice Mimic Licking Motion Leash Remote Soft Fur for Kids Battery Powered (Style-G) : Toys &amp; Games</t>
-  </si>
-  <si>
     <t>Perfect Petzzz</t>
   </si>
   <si>
@@ -212,9 +200,6 @@
     <t>18011 Smart Robot Dog</t>
   </si>
   <si>
-    <t>/images/products/futuristic_ai_pets.png</t>
-  </si>
-  <si>
     <t>Loona</t>
   </si>
   <si>
@@ -350,9 +335,6 @@
     <t>Pets</t>
   </si>
   <si>
-    <t xml:space="preserve">AI home monitoring robot designed to keep your pets entertained, connected, and secure. Check in and interact with your pet anytime from your smartphone. </t>
-  </si>
-  <si>
     <t>Night Vision</t>
   </si>
   <si>
@@ -846,6 +828,75 @@
   </si>
   <si>
     <t>https://www.amazon.com/Loona-ChatGPT-4o-AI-Powered-Interaction-Monitoring/dp/B0DCF53PCH/ref=sr_1_1_sspa?crid=LXSZQC579ZUJ&amp;dib=eyJ2IjoiMSJ9.fRTz6IKj5O3hiZ4V3RbIiqzYkMvGWX1yxIfmBNQ2bPEXhXF8Ry2nqncmMGEv7evRpJaa3U9aWxY1MQkhTgdPIV6Wjq-bFAK8cz4LIVjlEwH6W3j7kAEh6OD6pXtvOtnElQhMvBxTEwFpCiEYHVGyhpXxpCYzj1C2k8p3eIaIxYpRdd5pCvCtpNx-q-dgV8LfuIsu2pUkkgQks54gIUrjn4mpoOq0hqlBJXm_aPrP6Bi0oNJqD9loGYkwNNTqGtcUJYHc5fRntYIBPwj9_pE6lRUuH1CiB6ijg6RWmc0N6oE.9xo2lpag-NNW4-lvsbZ84aWH32CcaxXnQJs2fXDBXV8&amp;dib_tag=se&amp;keywords=loona%2Brobot&amp;qid=1778539102&amp;s=toys-and-games&amp;sprefix=loona%2Ctoys-and-games%2C257&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t>Enabot's emtry level robot. AI home monitoring robot designed to keep your home, pets, and loved ones connected and secure. Interactive laser point allows you to entertain your pets while you are away.</t>
+  </si>
+  <si>
+    <t>Newer genration than the EBO Air 2 with more features. AI home monitoring robot designed to keep your home, pets, and loved ones connected and secure. Does not include the AI Assistant. White option only.</t>
+  </si>
+  <si>
+    <t>High resolution camera. Home monitoring robot with AI Assistant keeps your home, pets, and loved ones connected and secure. Includes Smart Tracking and Sound Source Location for enhanced monitoring.</t>
+  </si>
+  <si>
+    <t>AI home monitoring robot with AI Assistant designed to keep your home, pets, and loved ones connected and secure. Has all of the features of the EBO 2S plus an AI assistant. Also comes in multiple colors.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> AI home monitoring robot with 2-way remote communication designed to keep your pets entertained, connected, and secure. </t>
+  </si>
+  <si>
+    <t>/images/products/EBO-X.png</t>
+  </si>
+  <si>
+    <t>/images/products/EBO-Air-2.png</t>
+  </si>
+  <si>
+    <t>/images/products/EBO-Air-2-Plus.png</t>
+  </si>
+  <si>
+    <t>/images/products/EBO-Air-2S.png</t>
+  </si>
+  <si>
+    <t>/images/products/Enabot-ROLA-Mini.png</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-For-All-Golden-Pup.png</t>
+  </si>
+  <si>
+    <t>/images/products/Joy-For-All-Freckled-Pup.png</t>
+  </si>
+  <si>
+    <t>/images/products/wuffy.png</t>
+  </si>
+  <si>
+    <t>/images/products/Percy-1.1-Robotic-Companion-Dog.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percy 1.1 Robotic Companion Dog </t>
+  </si>
+  <si>
+    <t>/images/products/Chongker-Percy-Pro-Mate-Cat.jpg</t>
+  </si>
+  <si>
+    <t>/images/products/Chongker-Percy-Mate-Cat-1.1.jpg</t>
+  </si>
+  <si>
+    <t>/images/products/Ruko-18001-Smart-Robot-Dog.png</t>
+  </si>
+  <si>
+    <t>Affiliate Program</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>/images/products/Loona-Robot-Pet-Dog.png</t>
+  </si>
+  <si>
+    <t>/images/products/Ropet-Kamomo.png</t>
+  </si>
+  <si>
+    <t>/images/products/DJ-Furby.png</t>
   </si>
 </sst>
 </file>
@@ -974,7 +1025,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1036,9 +1087,6 @@
     <xf numFmtId="1" fontId="8" fillId="2" borderId="0" xfId="2" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1058,6 +1106,12 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1490,112 +1544,112 @@
     <col min="26" max="26" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="200.7109375" style="26" customWidth="1"/>
+    <col min="29" max="29" width="200.7109375" style="25" customWidth="1"/>
     <col min="30" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D1" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="N1" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="P1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="S1" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="T1" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="O1" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="R1" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>83</v>
-      </c>
       <c r="U1" s="8" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="X1" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y1" s="6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="Z1" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AA1" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="AB1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC1" s="24" t="s">
-        <v>204</v>
+        <v>279</v>
+      </c>
+      <c r="AC1" s="23" t="s">
+        <v>198</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="75">
+    <row r="2" spans="1:29" ht="285">
       <c r="A2" s="3" t="str">
         <f>_xlfn.CONCAT(B2, " ", C2)</f>
-        <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
+        <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>235</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>17</v>
@@ -1604,79 +1658,79 @@
         <v>23</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="M2" s="16">
-        <v>4.5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N2" s="19">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="P2" s="9">
-        <v>46149</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>240</v>
+        <v>46153</v>
+      </c>
+      <c r="Q2" s="21" t="s">
+        <v>244</v>
       </c>
       <c r="R2" s="11">
-        <v>789</v>
+        <v>178</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="T2" s="9">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="U2" s="9" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>276</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC2" s="26" t="s">
-        <v>229</v>
+        <v>27</v>
+      </c>
+      <c r="AC2" s="25" t="s">
+        <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="75">
+    <row r="3" spans="1:29" ht="60">
       <c r="A3" s="3" t="str">
         <f>_xlfn.CONCAT(B3, " ", C3)</f>
-        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
+        <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>237</v>
+        <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>17</v>
@@ -1685,79 +1739,80 @@
         <v>23</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>198</v>
+        <v>128</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>84</v>
+        <v>129</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>92</v>
+        <v>130</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="M3" s="16">
         <v>5</v>
       </c>
       <c r="N3" s="19">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="O3" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="P3" s="9">
+        <v>46153</v>
+      </c>
+      <c r="Q3" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="R3" s="11">
         <v>89</v>
       </c>
-      <c r="P3" s="9">
-        <v>46149</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="R3" s="11">
-        <v>359</v>
-      </c>
       <c r="S3" s="3" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="T3" s="9">
         <v>46150</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="V3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="X3" s="2" t="s">
-        <v>44</v>
-      </c>
+      <c r="X3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y3" s="4"/>
       <c r="AB3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC3" s="26" t="s">
-        <v>231</v>
+        <v>27</v>
+      </c>
+      <c r="AC3" s="25" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="4" spans="1:29" ht="75">
       <c r="A4" s="3" t="str">
         <f>_xlfn.CONCAT(B4, " ", C4)</f>
-        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
+        <v xml:space="preserve"> Chongker MateCat 1.1 </v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>238</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>17</v>
@@ -1766,67 +1821,68 @@
         <v>23</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>93</v>
+        <v>122</v>
+      </c>
+      <c r="K4" s="28" t="s">
+        <v>123</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="M4" s="16">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N4" s="19">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>89</v>
+        <v>245</v>
       </c>
       <c r="P4" s="9">
-        <v>46149</v>
-      </c>
-      <c r="Q4" s="3" t="s">
-        <v>242</v>
+        <v>46153</v>
+      </c>
+      <c r="Q4" s="21" t="s">
+        <v>204</v>
       </c>
       <c r="R4" s="11">
-        <v>279</v>
+        <v>149</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="T4" s="9">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="V4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="X4" s="2" t="s">
-        <v>44</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="Y4" s="4"/>
       <c r="AB4" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC4" s="26" t="s">
-        <v>232</v>
+        <v>27</v>
+      </c>
+      <c r="AC4" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="75">
+    <row r="5" spans="1:29" ht="60">
       <c r="A5" s="3" t="str">
         <f>_xlfn.CONCAT(B5, " ", C5)</f>
         <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
@@ -1835,34 +1891,34 @@
         <v>0</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>198</v>
+        <v>261</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="M5" s="16">
         <v>4.5</v>
@@ -1871,1960 +1927,1964 @@
         <v>72</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="P5" s="9">
         <v>46149</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="R5" s="11">
         <v>179</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="T5" s="9">
         <v>46152</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="V5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X5" s="2" t="s">
-        <v>44</v>
+        <v>267</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC5" s="26" t="s">
-        <v>233</v>
+        <v>27</v>
+      </c>
+      <c r="AC5" s="25" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:29" ht="45">
       <c r="A6" s="3" t="str">
         <f>_xlfn.CONCAT(B6, " ", C6)</f>
-        <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
+        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
       <c r="B6" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>199</v>
+        <v>231</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>100</v>
+        <v>22</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>101</v>
+        <v>264</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="M6" s="16">
         <v>5</v>
       </c>
       <c r="N6" s="19">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="P6" s="9">
         <v>46149</v>
       </c>
-      <c r="Q6" s="22" t="s">
-        <v>244</v>
+      <c r="Q6" s="3" t="s">
+        <v>235</v>
       </c>
       <c r="R6" s="11">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="T6" s="9">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="V6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>44</v>
+        <v>268</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC6" s="26" t="s">
-        <v>234</v>
+        <v>27</v>
+      </c>
+      <c r="AC6" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="60">
       <c r="A7" s="3" t="str">
         <f>_xlfn.CONCAT(B7, " ", C7)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
+        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>36</v>
+        <v>232</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>109</v>
+        <v>262</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="M7" s="16">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="N7" s="19">
-        <v>5164</v>
+        <v>16</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P7" s="9">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="R7" s="11">
-        <v>179</v>
+        <v>279</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="T7" s="9">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="V7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y7" s="4"/>
+        <v>269</v>
+      </c>
       <c r="AB7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC7" s="27" t="s">
-        <v>205</v>
+        <v>27</v>
+      </c>
+      <c r="AC7" s="25" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="60">
       <c r="A8" s="3" t="str">
         <f>_xlfn.CONCAT(B8, " ", C8)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
+        <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>37</v>
+        <v>229</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>110</v>
+        <v>263</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>112</v>
+        <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="M8" s="16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N8" s="19">
-        <v>5163</v>
+        <v>20</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P8" s="9">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="R8" s="11">
-        <v>179</v>
+        <v>789</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="T8" s="9">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="V8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Y8" s="4"/>
+        <v>266</v>
+      </c>
       <c r="AB8" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC8" s="27" t="s">
-        <v>205</v>
+        <v>27</v>
+      </c>
+      <c r="AC8" s="25" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:29" ht="210">
       <c r="A9" s="3" t="str">
         <f>_xlfn.CONCAT(B9, " ", C9)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
+        <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>193</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="G9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>116</v>
+        <v>265</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>117</v>
+        <v>96</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="M9" s="16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N9" s="19">
-        <v>11640</v>
+        <v>73</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="P9" s="9">
+        <v>46149</v>
+      </c>
+      <c r="Q9" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="R9" s="11">
+        <v>139</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="T9" s="9">
         <v>46153</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="R9" s="11">
-        <v>159.99</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="T9" s="9">
-        <v>46150</v>
-      </c>
       <c r="U9" s="9" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="V9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y9" s="4"/>
+        <v>270</v>
+      </c>
       <c r="AB9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC9" s="27" t="s">
-        <v>206</v>
+        <v>27</v>
+      </c>
+      <c r="AC9" s="25" t="s">
+        <v>228</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="210">
+    <row r="10" spans="1:29" ht="300">
       <c r="A10" s="3" t="str">
         <f>_xlfn.CONCAT(B10, " ", C10)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
+        <v>Ruko 18011 Smart Robot Dog</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>49</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>118</v>
+        <v>176</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>144</v>
+        <v>178</v>
       </c>
       <c r="M10" s="16">
-        <v>4.5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N10" s="19">
-        <v>11640</v>
+        <v>283</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P10" s="9">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="R10" s="11">
-        <v>159.99</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T10" s="9">
         <v>46150</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="V10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y10" s="4"/>
+        <v>278</v>
+      </c>
       <c r="AB10" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC10" s="25" t="s">
-        <v>207</v>
+        <v>26</v>
+      </c>
+      <c r="AC10" s="24" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="60" customHeight="1">
       <c r="A11" s="3" t="str">
         <f>_xlfn.CONCAT(B11, " ", C11)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
+        <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>68</v>
+        <v>51</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G11" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>121</v>
+        <v>179</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>117</v>
+        <v>181</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>118</v>
+        <v>182</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>145</v>
+        <v>180</v>
       </c>
       <c r="M11" s="16">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N11" s="19">
-        <v>11640</v>
+        <v>1199</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P11" s="9">
         <v>46150</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="R11" s="11">
-        <v>159.99</v>
+        <v>499</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T11" s="9">
         <v>46150</v>
       </c>
       <c r="U11" s="9" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="V11" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y11" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="AB11" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC11" s="26" t="s">
-        <v>208</v>
+        <v>280</v>
+      </c>
+      <c r="AC11" s="24" t="s">
+        <v>222</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="285.75" thickBot="1">
+    <row r="12" spans="1:29" ht="270.75" thickBot="1">
       <c r="A12" s="3" t="str">
         <f>_xlfn.CONCAT(B12, " ", C12)</f>
-        <v xml:space="preserve"> Chongker MateCat Pro </v>
+        <v>Ropet KAMOMO</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>200</v>
+        <v>151</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M12" s="16">
-        <v>4.5999999999999996</v>
+        <v>4.3</v>
       </c>
       <c r="N12" s="19">
-        <v>456</v>
+        <v>17</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P12" s="9">
-        <v>46153</v>
-      </c>
-      <c r="Q12" s="22" t="s">
-        <v>250</v>
+        <v>46152</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="R12" s="11">
-        <v>178</v>
+        <v>329</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="T12" s="9">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>196</v>
+        <v>25</v>
       </c>
       <c r="V12" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>59</v>
+        <v>26</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC12" s="26" t="s">
-        <v>209</v>
+        <v>26</v>
+      </c>
+      <c r="AC12" s="24" t="s">
+        <v>210</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="75.75" thickBot="1">
+    <row r="13" spans="1:29" ht="270.75" thickBot="1">
       <c r="A13" s="3" t="str">
         <f>_xlfn.CONCAT(B13, " ", C13)</f>
-        <v xml:space="preserve"> Chongker MateCat 1.1 </v>
+        <v>Furby DJ Furby</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>68</v>
+        <v>53</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>64</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>126</v>
+        <v>186</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="K13" s="21" t="s">
-        <v>129</v>
+        <v>184</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>183</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="M13" s="16">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="N13" s="19">
-        <v>2</v>
+        <v>772</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="P13" s="9">
-        <v>46153</v>
-      </c>
-      <c r="Q13" s="22" t="s">
-        <v>210</v>
+        <v>46150</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>259</v>
       </c>
       <c r="R13" s="11">
-        <v>149</v>
+        <v>50.11</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="T13" s="9">
         <v>46150</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>196</v>
+        <v>88</v>
       </c>
       <c r="V13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y13" s="4"/>
-      <c r="AB13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC13" s="26" t="s">
-        <v>210</v>
+        <v>26</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="AC13" s="24" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:29" ht="75">
       <c r="A14" s="3" t="str">
         <f>_xlfn.CONCAT(B14, " ", C14)</f>
-        <v xml:space="preserve"> Chongker Percy 1.1 Robotic Dog </v>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="M14" s="16">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N14" s="19">
-        <v>5</v>
+        <v>11640</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>83</v>
       </c>
       <c r="P14" s="9">
         <v>46153</v>
       </c>
-      <c r="Q14" s="22" t="s">
-        <v>252</v>
+      <c r="Q14" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="R14" s="11">
-        <v>89</v>
+        <v>159.99</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="T14" s="9">
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="V14" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="Y14" s="4"/>
       <c r="AB14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC14" s="25" t="s">
-        <v>211</v>
+        <v>27</v>
+      </c>
+      <c r="AC14" s="24" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="60" customHeight="1">
       <c r="A15" s="3" t="str">
         <f>_xlfn.CONCAT(B15, " ", C15)</f>
-        <v xml:space="preserve"> Chongker Percy Robot Cat </v>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="K15" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="M15" s="16">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N15" s="19">
-        <v>16</v>
+        <v>11640</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="P15" s="9">
         <v>46153</v>
       </c>
-      <c r="Q15" s="22" t="s">
-        <v>212</v>
+      <c r="Q15" s="3" t="s">
+        <v>241</v>
       </c>
       <c r="R15" s="11">
-        <v>89</v>
+        <v>159.99</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="T15" s="9">
         <v>46150</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="V15" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>59</v>
+        <v>27</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="Y15" s="4"/>
       <c r="AB15" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC15" s="26" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="60">
+    <row r="16" spans="1:29" ht="210">
       <c r="A16" s="3" t="str">
         <f>_xlfn.CONCAT(B16, " ", C16)</f>
-        <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="M16" s="16">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N16" s="19">
-        <v>2</v>
+        <v>11640</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="P16" s="9">
-        <v>46153</v>
-      </c>
-      <c r="Q16" s="22" t="s">
-        <v>253</v>
+        <v>46150</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>243</v>
       </c>
       <c r="R16" s="11">
-        <v>119</v>
+        <v>159.99</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>148</v>
+        <v>83</v>
       </c>
       <c r="T16" s="9">
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="V16" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y16" s="5"/>
+        <v>26</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y16" s="4"/>
       <c r="AB16" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC16" s="25" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="180">
       <c r="A17" s="3" t="str">
         <f>_xlfn.CONCAT(B17, " ", C17)</f>
-        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
+        <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>152</v>
+        <v>104</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>153</v>
+        <v>107</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="M17" s="16">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N17" s="19">
-        <v>80</v>
+        <v>5163</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P17" s="9">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="R17" s="11">
-        <v>25.99</v>
+        <v>179</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T17" s="9">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="V17" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>42</v>
-      </c>
+        <v>272</v>
+      </c>
+      <c r="Y17" s="4"/>
       <c r="AB17" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC17" s="25" t="s">
-        <v>214</v>
+        <v>27</v>
+      </c>
+      <c r="AC17" s="26" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="74.25" customHeight="1">
       <c r="A18" s="3" t="str">
         <f>_xlfn.CONCAT(B18, " ", C18)</f>
-        <v>Ropet KAMOMO</v>
+        <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>156</v>
+        <v>23</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>157</v>
+        <v>103</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>201</v>
+        <v>108</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>160</v>
+        <v>135</v>
       </c>
       <c r="M18" s="16">
         <v>4.3</v>
       </c>
       <c r="N18" s="19">
-        <v>17</v>
+        <v>5164</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P18" s="9">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="R18" s="11">
-        <v>329</v>
+        <v>179</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T18" s="9">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>26</v>
+        <v>190</v>
       </c>
       <c r="V18" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA18" s="3" t="s">
-        <v>27</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="Y18" s="4"/>
       <c r="AB18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC18" s="25" t="s">
-        <v>216</v>
+        <v>27</v>
+      </c>
+      <c r="AC18" s="26" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="75">
       <c r="A19" s="3" t="str">
         <f>_xlfn.CONCAT(B19, " ", C19)</f>
-        <v>Perfect Petzzz Original Border Collie</v>
+        <v>Perfect Petzzz Original Beagle</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M19" s="16">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N19" s="19">
-        <v>403</v>
+        <v>466</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P19" s="9">
         <v>46150</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="R19" s="11">
         <v>44.45</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T19" s="9">
         <v>46150</v>
       </c>
       <c r="U19" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC19" s="25" t="s">
-        <v>217</v>
+        <v>46</v>
+      </c>
+      <c r="AC19" s="24" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="75">
       <c r="A20" s="3" t="str">
         <f>_xlfn.CONCAT(B20, " ", C20)</f>
-        <v>Perfect Petzzz Original Chocolate Lab</v>
+        <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="L20" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M20" s="16">
         <v>4.3</v>
       </c>
       <c r="N20" s="19">
-        <v>553</v>
+        <v>403</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P20" s="9">
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="R20" s="11">
         <v>44.45</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T20" s="9">
         <v>46150</v>
       </c>
       <c r="U20" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC20" s="25" t="s">
-        <v>218</v>
+        <v>43</v>
+      </c>
+      <c r="AC20" s="24" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="75">
       <c r="A21" s="3" t="str">
         <f>_xlfn.CONCAT(B21, " ", C21)</f>
-        <v>Perfect Petzzz Original Shih Tzu</v>
+        <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M21" s="16">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="N21" s="19">
-        <v>878</v>
+        <v>553</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P21" s="9">
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="R21" s="11">
         <v>44.45</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T21" s="9">
         <v>46150</v>
       </c>
       <c r="U21" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>27</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC21" s="25" t="s">
-        <v>219</v>
+        <v>44</v>
+      </c>
+      <c r="AC21" s="24" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="75">
       <c r="A22" s="3" t="str">
         <f>_xlfn.CONCAT(B22, " ", C22)</f>
-        <v>Perfect Petzzz Original Beagle</v>
+        <v>Perfect Petzzz Original Shih Tzu</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="M22" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.2</v>
       </c>
       <c r="N22" s="19">
-        <v>466</v>
+        <v>878</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P22" s="9">
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T22" s="9">
         <v>46150</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V22" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AC22" s="25" t="s">
-        <v>220</v>
+        <v>45</v>
+      </c>
+      <c r="AC22" s="24" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="60" customHeight="1">
       <c r="A23" s="3" t="str">
         <f>_xlfn.CONCAT(B23, " ", C23)</f>
-        <v>Perfect Petzzz Grey Tabby Cat</v>
+        <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>68</v>
+        <v>7</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>162</v>
+        <v>126</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>163</v>
+        <v>127</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>203</v>
+        <v>143</v>
       </c>
       <c r="M23" s="16">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="N23" s="19">
-        <v>848</v>
-      </c>
-      <c r="O23" s="3" t="s">
-        <v>88</v>
+        <v>5</v>
       </c>
       <c r="P23" s="9">
-        <v>46150</v>
-      </c>
-      <c r="Q23" s="3" t="s">
-        <v>260</v>
+        <v>46153</v>
+      </c>
+      <c r="Q23" s="21" t="s">
+        <v>246</v>
       </c>
       <c r="R23" s="11">
-        <v>44.45</v>
+        <v>89</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="T23" s="9">
         <v>46150</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC23" s="25" t="s">
-        <v>222</v>
+        <v>274</v>
+      </c>
+      <c r="Y23" s="4"/>
+      <c r="AB23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC23" s="24" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="60" customHeight="1">
       <c r="A24" s="3" t="str">
         <f>_xlfn.CONCAT(B24, " ", C24)</f>
-        <v>Perfect Petzzz Original Plush White Cat</v>
+        <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>68</v>
+        <v>7</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>177</v>
+        <v>132</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>174</v>
+        <v>131</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>162</v>
+        <v>134</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>203</v>
+        <v>145</v>
       </c>
       <c r="M24" s="16">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N24" s="19">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>88</v>
+        <v>245</v>
       </c>
       <c r="P24" s="9">
-        <v>46150</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>261</v>
+        <v>46153</v>
+      </c>
+      <c r="Q24" s="21" t="s">
+        <v>247</v>
       </c>
       <c r="R24" s="11">
-        <v>53.9</v>
+        <v>119</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="T24" s="9">
         <v>46150</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>93</v>
+        <v>190</v>
       </c>
       <c r="V24" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC24" s="25" t="s">
-        <v>223</v>
+        <v>42</v>
+      </c>
+      <c r="Y24" s="5"/>
+      <c r="AB24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC24" s="24" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="60" customHeight="1">
       <c r="A25" s="3" t="str">
         <f>_xlfn.CONCAT(B25, " ", C25)</f>
-        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
+        <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M25" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="N25" s="19">
-        <v>1200</v>
+        <v>848</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P25" s="9">
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="R25" s="11">
         <v>44.45</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T25" s="9">
         <v>46150</v>
       </c>
       <c r="U25" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V25" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W25" s="3" t="s">
         <v>27</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC25" s="25" t="s">
-        <v>224</v>
+        <v>47</v>
+      </c>
+      <c r="AC25" s="24" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="60" customHeight="1">
       <c r="A26" s="3" t="str">
         <f>_xlfn.CONCAT(B26, " ", C26)</f>
-        <v>Perfect Petzzz Original Siamese Cat</v>
+        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="M26" s="16">
-        <v>4.0999999999999996</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N26" s="19">
-        <v>16</v>
+        <v>1200</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P26" s="9">
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="R26" s="11">
-        <v>53.9</v>
+        <v>44.45</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T26" s="9">
         <v>46150</v>
       </c>
       <c r="U26" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V26" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="AC26" s="25" t="s">
-        <v>225</v>
+        <v>47</v>
+      </c>
+      <c r="AC26" s="24" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:29" ht="300">
       <c r="A27" s="3" t="str">
         <f>_xlfn.CONCAT(B27, " ", C27)</f>
-        <v>Ruko 18011 Smart Robot Dog</v>
+        <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>71</v>
+        <v>39</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>183</v>
+        <v>156</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="M27" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N27" s="19">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P27" s="9">
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="R27" s="11">
-        <v>69.989999999999995</v>
+        <v>53.9</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T27" s="9">
         <v>46150</v>
       </c>
       <c r="U27" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>27</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC27" s="25" t="s">
-        <v>226</v>
+        <v>48</v>
+      </c>
+      <c r="AC27" s="24" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="27.75" customHeight="1">
       <c r="A28" s="3" t="str">
         <f>_xlfn.CONCAT(B28, " ", C28)</f>
-        <v>Furby DJ Furby</v>
+        <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G28" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>192</v>
+        <v>171</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>191</v>
+        <v>157</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>190</v>
+        <v>168</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>189</v>
+        <v>156</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="M28" s="16">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="N28" s="19">
-        <v>772</v>
+        <v>54</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="P28" s="9">
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="R28" s="11">
-        <v>50.11</v>
+        <v>53.9</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="T28" s="9">
         <v>46150</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="V28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W28" s="3" t="s">
         <v>27</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AC28" s="25" t="s">
-        <v>227</v>
+        <v>58</v>
+      </c>
+      <c r="AC28" s="24" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="29" spans="1:29" ht="300">
       <c r="A29" s="3" t="str">
         <f>_xlfn.CONCAT(B29, " ", C29)</f>
-        <v>Loona Robot Pet Dog</v>
+        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>71</v>
+        <v>12</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>23</v>
-      </c>
       <c r="H29" s="3" t="s">
-        <v>185</v>
+        <v>146</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>187</v>
+        <v>149</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>188</v>
+        <v>147</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>186</v>
+        <v>148</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="M29" s="16">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="N29" s="19">
-        <v>1199</v>
+        <v>80</v>
       </c>
       <c r="O29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P29" s="9">
+        <v>46151</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="R29" s="11">
+        <v>25.99</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="T29" s="9">
+        <v>46151</v>
+      </c>
+      <c r="U29" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="P29" s="9">
-        <v>46150</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="R29" s="11">
-        <v>499</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="T29" s="9">
-        <v>46150</v>
-      </c>
-      <c r="U29" s="9" t="s">
-        <v>26</v>
-      </c>
       <c r="V29" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>27</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AC29" s="25" t="s">
-        <v>228</v>
+        <v>273</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC29" s="24" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:29">
@@ -3834,11 +3894,15 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC30" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}"/>
+  <autoFilter ref="A1:AC30" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC30">
+      <sortCondition ref="X16:X30"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="AC7" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
-    <hyperlink ref="AC8" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
+    <hyperlink ref="AC18" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
+    <hyperlink ref="AC17" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -3850,13 +3914,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:U2 U3:U1048576</xm:sqref>
+          <xm:sqref>U1:U1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37BE27F9-E75E-4C54-9192-7DED9B8091B0}">
           <x14:formula1>
             <xm:f>Lists!$A$7:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>W1:W2 W3:W1048576</xm:sqref>
+          <xm:sqref>W1:W1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3874,11 +3938,11 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" s="28"/>
+      <c r="A8" s="27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3895,27 +3959,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -3928,7 +3992,7 @@
   <dimension ref="A1:AC5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:29" s="3" customFormat="1" ht="75">
+    <row r="1" spans="1:29" s="3" customFormat="1" ht="409.5">
       <c r="A1" s="3" t="str">
         <f>_xlfn.CONCAT(B1, " ", C1)</f>
         <v xml:space="preserve"> Enabot EBO Max FamilyBot </v>
@@ -3937,34 +4001,34 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="L1" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="M1" s="16">
         <v>0</v>
@@ -3973,41 +4037,41 @@
         <v>0</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="P1" s="9">
         <v>46149</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="R1" s="11">
         <v>549</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="T1" s="9">
         <v>46149</v>
       </c>
       <c r="U1" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="Y1" s="6"/>
       <c r="AB1" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="AC1" s="26" t="s">
-        <v>230</v>
+        <v>27</v>
+      </c>
+      <c r="AC1" s="25" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="2" spans="1:29" s="12" customFormat="1" ht="75">
@@ -4022,41 +4086,41 @@
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M2" s="17"/>
       <c r="N2" s="20"/>
       <c r="P2" s="13"/>
-      <c r="Q2" s="23"/>
+      <c r="Q2" s="22"/>
       <c r="R2" s="14"/>
       <c r="T2" s="13"/>
       <c r="U2" s="13"/>
       <c r="V2" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AC2" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:29" s="12" customFormat="1" ht="15" customHeight="1">
@@ -4071,44 +4135,44 @@
         <v>3</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="20"/>
       <c r="P3" s="13"/>
-      <c r="Q3" s="23"/>
+      <c r="Q3" s="22"/>
       <c r="R3" s="14"/>
       <c r="T3" s="13"/>
       <c r="U3" s="13"/>
       <c r="V3" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X3" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="Z3" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AC3" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:29" s="12" customFormat="1" ht="405">
@@ -4123,44 +4187,44 @@
         <v>4</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="20"/>
       <c r="P4" s="13"/>
-      <c r="Q4" s="23"/>
+      <c r="Q4" s="22"/>
       <c r="R4" s="14"/>
       <c r="T4" s="13"/>
       <c r="U4" s="13"/>
       <c r="V4" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W4" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X4" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="Z4" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AC4" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:29" s="12" customFormat="1" ht="360">
@@ -4175,44 +4239,44 @@
         <v>5</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="20"/>
       <c r="P5" s="13"/>
-      <c r="Q5" s="23"/>
+      <c r="Q5" s="22"/>
       <c r="R5" s="14"/>
       <c r="T5" s="13"/>
       <c r="U5" s="13"/>
       <c r="V5" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="W5" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X5" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y5" s="12" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Z5" s="12" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="AC5" s="12" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8092049-54FC-45CA-BE2B-173C3A16F1E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42679C0-EAF2-443D-BC09-CE77654E13DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="284">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="285">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -188,9 +188,6 @@
     <t>/images/products/Mr-Beagle.png</t>
   </si>
   <si>
-    <t>/images/products/Sweetie-Calico-Cat.png</t>
-  </si>
-  <si>
     <t>/images/products/Sweetie-Siamese-Cat.png</t>
   </si>
   <si>
@@ -897,6 +894,12 @@
   </si>
   <si>
     <t>/images/products/DJ-Furby.png</t>
+  </si>
+  <si>
+    <t>/images/products/Perfect-Petzzz-Grey-Tabby-Cat.png</t>
+  </si>
+  <si>
+    <t>/images/products/Perfect-Petzzz-Original-Black-and-White-Shorthair-Cat.png</t>
   </si>
 </sst>
 </file>
@@ -1025,7 +1028,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1106,10 +1109,13 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1550,7 +1556,7 @@
   <sheetData>
     <row r="1" spans="1:29" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>15</v>
@@ -1559,7 +1565,7 @@
         <v>14</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>18</v>
@@ -1571,52 +1577,52 @@
         <v>20</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="O1" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="T1" s="8" t="s">
-        <v>78</v>
-      </c>
       <c r="U1" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>24</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>32</v>
@@ -1631,106 +1637,31 @@
         <v>31</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AC1" s="23" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:29" ht="285">
       <c r="A2" s="3" t="str">
         <f>_xlfn.CONCAT(B2, " ", C2)</f>
-        <v xml:space="preserve"> Chongker MateCat Pro </v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="M2" s="16">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="N2" s="19">
-        <v>456</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="P2" s="9">
-        <v>46153</v>
-      </c>
-      <c r="Q2" s="21" t="s">
-        <v>244</v>
-      </c>
-      <c r="R2" s="11">
-        <v>178</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="T2" s="9">
-        <v>46150</v>
-      </c>
-      <c r="U2" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="V2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X2" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="AB2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC2" s="25" t="s">
-        <v>203</v>
+        <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="60">
       <c r="A3" s="3" t="str">
         <f>_xlfn.CONCAT(B3, " ", C3)</f>
-        <v xml:space="preserve"> Chongker Percy Robot Cat </v>
+        <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
       <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>17</v>
@@ -1742,16 +1673,16 @@
         <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>130</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>144</v>
@@ -1760,28 +1691,28 @@
         <v>5</v>
       </c>
       <c r="N3" s="19">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P3" s="9">
         <v>46153</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>206</v>
+        <v>246</v>
       </c>
       <c r="R3" s="11">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T3" s="9">
         <v>46150</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>26</v>
@@ -1789,14 +1720,14 @@
       <c r="W3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="X3" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y3" s="4"/>
+      <c r="X3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y3" s="5"/>
       <c r="AB3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC3" s="25" t="s">
+      <c r="AC3" s="24" t="s">
         <v>206</v>
       </c>
     </row>
@@ -1812,7 +1743,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>17</v>
@@ -1824,19 +1755,19 @@
         <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="K4" s="28" t="s">
-        <v>123</v>
-      </c>
       <c r="L4" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="M4" s="16">
         <v>4</v>
@@ -1845,25 +1776,25 @@
         <v>2</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="P4" s="9">
         <v>46153</v>
       </c>
       <c r="Q4" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="R4" s="11">
         <v>149</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="T4" s="9">
         <v>46150</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>26</v>
@@ -1872,80 +1803,80 @@
         <v>27</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="Y4" s="4"/>
       <c r="AB4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC4" s="25" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:29" ht="60">
       <c r="A5" s="3" t="str">
         <f>_xlfn.CONCAT(B5, " ", C5)</f>
-        <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
+        <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>233</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G5" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>261</v>
+        <v>193</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="M5" s="16">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="N5" s="19">
+        <v>456</v>
+      </c>
+      <c r="O5" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="M5" s="16">
-        <v>4.5</v>
-      </c>
-      <c r="N5" s="19">
-        <v>72</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="P5" s="9">
-        <v>46149</v>
-      </c>
-      <c r="Q5" s="3" t="s">
-        <v>237</v>
+        <v>46153</v>
+      </c>
+      <c r="Q5" s="21" t="s">
+        <v>243</v>
       </c>
       <c r="R5" s="11">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="T5" s="9">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>26</v>
@@ -1953,80 +1884,77 @@
       <c r="W5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X5" s="2" t="s">
-        <v>267</v>
+      <c r="X5" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC5" s="25" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="45">
+    <row r="6" spans="1:29" ht="60">
       <c r="A6" s="3" t="str">
         <f>_xlfn.CONCAT(B6, " ", C6)</f>
-        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
+        <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>264</v>
+        <v>123</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="M6" s="16">
         <v>5</v>
       </c>
       <c r="N6" s="19">
-        <v>42</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="P6" s="9">
-        <v>46149</v>
-      </c>
-      <c r="Q6" s="3" t="s">
-        <v>235</v>
+        <v>46153</v>
+      </c>
+      <c r="Q6" s="21" t="s">
+        <v>245</v>
       </c>
       <c r="R6" s="11">
-        <v>359</v>
+        <v>89</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="T6" s="9">
         <v>46150</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="V6" s="3" t="s">
         <v>26</v>
@@ -2035,52 +1963,53 @@
         <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>268</v>
-      </c>
+        <v>273</v>
+      </c>
+      <c r="Y6" s="4"/>
       <c r="AB6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC6" s="25" t="s">
-        <v>225</v>
+      <c r="AC6" s="24" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:29" ht="60">
       <c r="A7" s="3" t="str">
         <f>_xlfn.CONCAT(B7, " ", C7)</f>
-        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
+        <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>232</v>
+        <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G7" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>93</v>
+        <v>128</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="M7" s="16">
         <v>5</v>
@@ -2089,25 +2018,25 @@
         <v>16</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>84</v>
+        <v>244</v>
       </c>
       <c r="P7" s="9">
-        <v>46149</v>
-      </c>
-      <c r="Q7" s="3" t="s">
-        <v>236</v>
+        <v>46153</v>
+      </c>
+      <c r="Q7" s="21" t="s">
+        <v>205</v>
       </c>
       <c r="R7" s="11">
-        <v>279</v>
+        <v>89</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>84</v>
+        <v>141</v>
       </c>
       <c r="T7" s="9">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>26</v>
@@ -2115,29 +2044,30 @@
       <c r="W7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>269</v>
-      </c>
+      <c r="X7" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y7" s="4"/>
       <c r="AB7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC7" s="25" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:29" ht="60">
       <c r="A8" s="3" t="str">
         <f>_xlfn.CONCAT(B8, " ", C8)</f>
-        <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
+        <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
       </c>
       <c r="B8" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>16</v>
@@ -2146,55 +2076,55 @@
         <v>22</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="M8" s="16">
         <v>4.5</v>
       </c>
       <c r="N8" s="19">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P8" s="9">
         <v>46149</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="R8" s="11">
-        <v>789</v>
+        <v>179</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T8" s="9">
-        <v>46149</v>
+        <v>46152</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X8" s="2" t="s">
         <v>266</v>
@@ -2203,229 +2133,232 @@
         <v>27</v>
       </c>
       <c r="AC8" s="25" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="210">
+    <row r="9" spans="1:29" ht="45">
       <c r="A9" s="3" t="str">
         <f>_xlfn.CONCAT(B9, " ", C9)</f>
-        <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
+        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
       <c r="B9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>95</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="M9" s="16">
         <v>5</v>
       </c>
       <c r="N9" s="19">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P9" s="9">
         <v>46149</v>
       </c>
-      <c r="Q9" s="21" t="s">
-        <v>238</v>
+      <c r="Q9" s="3" t="s">
+        <v>234</v>
       </c>
       <c r="R9" s="11">
-        <v>139</v>
+        <v>359</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T9" s="9">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>190</v>
+        <v>25</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC9" s="25" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:29" ht="300">
       <c r="A10" s="3" t="str">
         <f>_xlfn.CONCAT(B10, " ", C10)</f>
-        <v>Ruko 18011 Smart Robot Dog</v>
+        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>66</v>
+        <v>0</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="H10" s="3" t="s">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>175</v>
+        <v>92</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>177</v>
+        <v>87</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>178</v>
+        <v>93</v>
       </c>
       <c r="M10" s="16">
-        <v>4.4000000000000004</v>
+        <v>5</v>
       </c>
       <c r="N10" s="19">
-        <v>283</v>
+        <v>16</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>83</v>
       </c>
       <c r="P10" s="9">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="R10" s="11">
-        <v>69.989999999999995</v>
+        <v>279</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>83</v>
       </c>
       <c r="T10" s="9">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="U10" s="9" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="V10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC10" s="24" t="s">
-        <v>220</v>
+        <v>27</v>
+      </c>
+      <c r="AC10" s="25" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="1:29" ht="60" customHeight="1">
       <c r="A11" s="3" t="str">
         <f>_xlfn.CONCAT(B11, " ", C11)</f>
-        <v>Loona Robot Pet Dog</v>
+        <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>66</v>
+        <v>0</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>179</v>
+        <v>262</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>181</v>
+        <v>80</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>182</v>
+        <v>81</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>180</v>
+        <v>89</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>79</v>
       </c>
       <c r="M11" s="16">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="N11" s="19">
-        <v>1199</v>
+        <v>20</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>83</v>
       </c>
       <c r="P11" s="9">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="R11" s="11">
-        <v>499</v>
+        <v>789</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>83</v>
       </c>
       <c r="T11" s="9">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="U11" s="9" t="s">
         <v>25</v>
@@ -2434,196 +2367,194 @@
         <v>26</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>281</v>
+        <v>265</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="AC11" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC11" s="25" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="12" spans="1:29" ht="270.75" thickBot="1">
       <c r="A12" s="3" t="str">
         <f>_xlfn.CONCAT(B12, " ", C12)</f>
-        <v>Ropet KAMOMO</v>
+        <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>151</v>
+        <v>264</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>155</v>
+        <v>95</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>195</v>
+        <v>96</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>154</v>
+        <v>97</v>
       </c>
       <c r="M12" s="16">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="N12" s="19">
-        <v>17</v>
+        <v>73</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>83</v>
       </c>
       <c r="P12" s="9">
-        <v>46152</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>249</v>
+        <v>46149</v>
+      </c>
+      <c r="Q12" s="21" t="s">
+        <v>237</v>
       </c>
       <c r="R12" s="11">
-        <v>329</v>
+        <v>139</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>83</v>
       </c>
       <c r="T12" s="9">
-        <v>46152</v>
+        <v>46153</v>
       </c>
       <c r="U12" s="9" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="V12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>26</v>
+        <v>269</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC12" s="24" t="s">
-        <v>210</v>
+        <v>27</v>
+      </c>
+      <c r="AC12" s="25" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="13" spans="1:29" ht="270.75" thickBot="1">
       <c r="A13" s="3" t="str">
         <f>_xlfn.CONCAT(B13, " ", C13)</f>
-        <v>Furby DJ Furby</v>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>64</v>
+        <v>13</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="H13" s="3" t="s">
-        <v>186</v>
+        <v>104</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>185</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="K13" s="29" t="s">
-        <v>183</v>
+        <v>113</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>188</v>
+        <v>137</v>
       </c>
       <c r="M13" s="16">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="N13" s="19">
-        <v>772</v>
+        <v>11640</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P13" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q13" s="3" t="s">
-        <v>259</v>
+        <v>241</v>
       </c>
       <c r="R13" s="11">
-        <v>50.11</v>
+        <v>159.99</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T13" s="9">
         <v>46150</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>88</v>
+        <v>189</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>283</v>
+        <v>56</v>
+      </c>
+      <c r="Y13" s="4"/>
+      <c r="AB13" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC13" s="24" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="75">
+    <row r="14" spans="1:29" ht="210">
       <c r="A14" s="3" t="str">
         <f>_xlfn.CONCAT(B14, " ", C14)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>17</v>
@@ -2635,19 +2566,19 @@
         <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="L14" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M14" s="16">
         <v>4.5</v>
@@ -2656,25 +2587,25 @@
         <v>11640</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P14" s="9">
         <v>46153</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R14" s="11">
         <v>159.99</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T14" s="9">
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>26</v>
@@ -2683,29 +2614,29 @@
         <v>27</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Y14" s="4"/>
       <c r="AB14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC14" s="24" t="s">
-        <v>201</v>
+      <c r="AC14" s="26" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:29" ht="60" customHeight="1">
       <c r="A15" s="3" t="str">
         <f>_xlfn.CONCAT(B15, " ", C15)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>17</v>
@@ -2717,19 +2648,19 @@
         <v>21</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M15" s="16">
         <v>4.5</v>
@@ -2738,56 +2669,56 @@
         <v>11640</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P15" s="9">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="R15" s="11">
         <v>159.99</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T15" s="9">
         <v>46150</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X15" s="2" t="s">
-        <v>56</v>
+        <v>26</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="Y15" s="4"/>
       <c r="AB15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC15" s="26" t="s">
-        <v>200</v>
+      <c r="AC15" s="25" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="16" spans="1:29" ht="210">
       <c r="A16" s="3" t="str">
         <f>_xlfn.CONCAT(B16, " ", C16)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
+        <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>17</v>
@@ -2799,77 +2730,77 @@
         <v>21</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="M16" s="16">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N16" s="19">
-        <v>11640</v>
+        <v>5163</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P16" s="9">
         <v>46150</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="R16" s="11">
-        <v>159.99</v>
+        <v>179</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T16" s="9">
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X16" s="3" t="s">
-        <v>55</v>
+        <v>27</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="Y16" s="4"/>
       <c r="AB16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC16" s="25" t="s">
-        <v>202</v>
+      <c r="AC16" s="26" t="s">
+        <v>198</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="180">
+    <row r="17" spans="1:29" ht="60">
       <c r="A17" s="3" t="str">
         <f>_xlfn.CONCAT(B17, " ", C17)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
+        <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>17</v>
@@ -2881,31 +2812,31 @@
         <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="L17" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M17" s="16">
         <v>4.3</v>
       </c>
       <c r="N17" s="19">
-        <v>5163</v>
+        <v>5164</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P17" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q17" s="3" t="s">
         <v>239</v>
@@ -2914,282 +2845,281 @@
         <v>179</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T17" s="9">
         <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Y17" s="4"/>
       <c r="AB17" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC17" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="74.25" customHeight="1">
       <c r="A18" s="3" t="str">
         <f>_xlfn.CONCAT(B18, " ", C18)</f>
-        <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
+        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="M18" s="16">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="N18" s="19">
-        <v>5164</v>
+        <v>80</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P18" s="9">
-        <v>46153</v>
+        <v>46151</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="R18" s="11">
-        <v>179</v>
+        <v>25.99</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T18" s="9">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>190</v>
+        <v>87</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="Y18" s="4"/>
+        <v>272</v>
+      </c>
       <c r="AB18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC18" s="26" t="s">
-        <v>199</v>
+      <c r="AC18" s="24" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="75">
       <c r="A19" s="3" t="str">
         <f>_xlfn.CONCAT(B19, " ", C19)</f>
-        <v>Perfect Petzzz Original Beagle</v>
+        <v>Furby DJ Furby</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>168</v>
+        <v>183</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>182</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="M19" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.8</v>
       </c>
       <c r="N19" s="19">
-        <v>466</v>
+        <v>772</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P19" s="9">
         <v>46150</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="R19" s="11">
-        <v>44.45</v>
+        <v>50.11</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T19" s="9">
         <v>46150</v>
       </c>
       <c r="U19" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V19" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>46</v>
+        <v>282</v>
       </c>
       <c r="AC19" s="24" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="75">
       <c r="A20" s="3" t="str">
         <f>_xlfn.CONCAT(B20, " ", C20)</f>
-        <v>Perfect Petzzz Original Border Collie</v>
+        <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>66</v>
+        <v>50</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>156</v>
+        <v>180</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>157</v>
+        <v>181</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="M20" s="16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N20" s="19">
-        <v>403</v>
+        <v>1199</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P20" s="9">
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="R20" s="11">
-        <v>44.45</v>
+        <v>499</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T20" s="9">
         <v>46150</v>
       </c>
       <c r="U20" s="9" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>43</v>
+        <v>280</v>
+      </c>
+      <c r="AB20" s="3" t="s">
+        <v>279</v>
       </c>
       <c r="AC20" s="24" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="75">
       <c r="A21" s="3" t="str">
         <f>_xlfn.CONCAT(B21, " ", C21)</f>
-        <v>Perfect Petzzz Original Chocolate Lab</v>
+        <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>162</v>
+        <v>214</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>17</v>
@@ -3201,16 +3131,16 @@
         <v>23</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J21" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>157</v>
       </c>
       <c r="L21" s="3" t="s">
         <v>196</v>
@@ -3219,28 +3149,28 @@
         <v>4.3</v>
       </c>
       <c r="N21" s="19">
-        <v>553</v>
+        <v>848</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P21" s="9">
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="R21" s="11">
         <v>44.45</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T21" s="9">
         <v>46150</v>
       </c>
       <c r="U21" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>26</v>
@@ -3249,16 +3179,16 @@
         <v>27</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>44</v>
+        <v>283</v>
       </c>
       <c r="AC21" s="24" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="75">
       <c r="A22" s="3" t="str">
         <f>_xlfn.CONCAT(B22, " ", C22)</f>
-        <v>Perfect Petzzz Original Shih Tzu</v>
+        <v>Perfect Petzzz Original Beagle</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -3267,7 +3197,7 @@
         <v>163</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>17</v>
@@ -3279,28 +3209,28 @@
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M22" s="16">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N22" s="19">
-        <v>878</v>
+        <v>466</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P22" s="9">
         <v>46150</v>
@@ -3312,22 +3242,22 @@
         <v>44.45</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T22" s="9">
         <v>46150</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AC22" s="24" t="s">
         <v>213</v>
@@ -3336,64 +3266,67 @@
     <row r="23" spans="1:29" ht="60" customHeight="1">
       <c r="A23" s="3" t="str">
         <f>_xlfn.CONCAT(B23, " ", C23)</f>
-        <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
+        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="H23" s="3" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>125</v>
+        <v>167</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>127</v>
+        <v>156</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="M23" s="16">
-        <v>5</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N23" s="19">
-        <v>5</v>
+        <v>1200</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="P23" s="9">
-        <v>46153</v>
-      </c>
-      <c r="Q23" s="21" t="s">
-        <v>246</v>
+        <v>46150</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>255</v>
       </c>
       <c r="R23" s="11">
-        <v>89</v>
+        <v>44.45</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="T23" s="9">
         <v>46150</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>26</v>
@@ -3402,80 +3335,76 @@
         <v>26</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="Y23" s="4"/>
-      <c r="AB23" s="3" t="s">
-        <v>27</v>
+        <v>284</v>
       </c>
       <c r="AC23" s="24" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="60" customHeight="1">
       <c r="A24" s="3" t="str">
         <f>_xlfn.CONCAT(B24, " ", C24)</f>
-        <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
+        <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>65</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="3" t="s">
-        <v>21</v>
-      </c>
       <c r="H24" s="3" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>133</v>
+        <v>155</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>134</v>
+        <v>167</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>145</v>
+        <v>195</v>
       </c>
       <c r="M24" s="16">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="N24" s="19">
-        <v>2</v>
+        <v>403</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="P24" s="9">
-        <v>46153</v>
-      </c>
-      <c r="Q24" s="21" t="s">
-        <v>247</v>
+        <v>46150</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>249</v>
       </c>
       <c r="R24" s="11">
-        <v>119</v>
+        <v>44.45</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>142</v>
+        <v>82</v>
       </c>
       <c r="T24" s="9">
         <v>46150</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>190</v>
+        <v>87</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>26</v>
@@ -3484,29 +3413,25 @@
         <v>27</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y24" s="5"/>
-      <c r="AB24" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="AC24" s="24" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:29" ht="60" customHeight="1">
       <c r="A25" s="3" t="str">
         <f>_xlfn.CONCAT(B25, " ", C25)</f>
-        <v>Perfect Petzzz Grey Tabby Cat</v>
+        <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>215</v>
+        <v>161</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>17</v>
@@ -3518,46 +3443,46 @@
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>157</v>
-      </c>
       <c r="L25" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M25" s="16">
         <v>4.3</v>
       </c>
       <c r="N25" s="19">
-        <v>848</v>
+        <v>553</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P25" s="9">
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="R25" s="11">
         <v>44.45</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T25" s="9">
         <v>46150</v>
       </c>
       <c r="U25" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V25" s="3" t="s">
         <v>26</v>
@@ -3566,25 +3491,25 @@
         <v>27</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="AC25" s="24" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:29" ht="60" customHeight="1">
       <c r="A26" s="3" t="str">
         <f>_xlfn.CONCAT(B26, " ", C26)</f>
-        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
+        <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>17</v>
@@ -3596,73 +3521,73 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M26" s="16">
-        <v>4.4000000000000004</v>
+        <v>4</v>
       </c>
       <c r="N26" s="19">
-        <v>1200</v>
+        <v>54</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P26" s="9">
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="R26" s="11">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T26" s="9">
         <v>46150</v>
       </c>
       <c r="U26" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="AC26" s="24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="300">
+    <row r="27" spans="1:29" ht="75">
       <c r="A27" s="3" t="str">
         <f>_xlfn.CONCAT(B27, " ", C27)</f>
-        <v>Perfect Petzzz Original Siamese Cat</v>
+        <v>Perfect Petzzz Original Shih Tzu</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>17</v>
@@ -3674,73 +3599,73 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="M27" s="16">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="N27" s="19">
-        <v>16</v>
+        <v>878</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P27" s="9">
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="R27" s="11">
-        <v>53.9</v>
+        <v>44.45</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T27" s="9">
         <v>46150</v>
       </c>
       <c r="U27" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="AC27" s="24" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="28" spans="1:29" ht="27.75" customHeight="1">
       <c r="A28" s="3" t="str">
         <f>_xlfn.CONCAT(B28, " ", C28)</f>
-        <v>Perfect Petzzz Original Plush White Cat</v>
+        <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>17</v>
@@ -3752,46 +3677,46 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M28" s="16">
-        <v>4</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N28" s="19">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P28" s="9">
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="R28" s="11">
         <v>53.9</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T28" s="9">
         <v>46150</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="V28" s="3" t="s">
         <v>26</v>
@@ -3800,109 +3725,190 @@
         <v>27</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="AC28" s="24" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="300">
+    <row r="29" spans="1:29" ht="180">
       <c r="A29" s="3" t="str">
         <f>_xlfn.CONCAT(B29, " ", C29)</f>
-        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
+        <v>Ropet KAMOMO</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>148</v>
+        <v>194</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>153</v>
       </c>
       <c r="M29" s="16">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N29" s="19">
-        <v>80</v>
+        <v>17</v>
       </c>
       <c r="O29" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P29" s="9">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>248</v>
       </c>
       <c r="R29" s="11">
-        <v>25.99</v>
+        <v>329</v>
       </c>
       <c r="S29" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T29" s="9">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="U29" s="9" t="s">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
+      </c>
+      <c r="Z29" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA29" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AB29" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AC29" s="24" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="30" spans="1:29">
       <c r="A30" s="3" t="str">
         <f>_xlfn.CONCAT(B30, " ", C30)</f>
-        <v xml:space="preserve"> </v>
+        <v>Ruko 18011 Smart Robot Dog</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M30" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N30" s="19">
+        <v>283</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P30" s="9">
+        <v>46150</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="R30" s="11">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T30" s="9">
+        <v>46150</v>
+      </c>
+      <c r="U30" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="V30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="W30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC30" s="24" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC30" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC30">
-      <sortCondition ref="X16:X30"/>
+      <sortCondition ref="A1:A30"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="AC18" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
-    <hyperlink ref="AC17" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
+    <hyperlink ref="AC17" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
+    <hyperlink ref="AC16" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -3938,7 +3944,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -3964,12 +3970,12 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -4001,10 +4007,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>16</v>
@@ -4016,19 +4022,19 @@
         <v>22</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="K1" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M1" s="16">
         <v>0</v>
@@ -4037,19 +4043,19 @@
         <v>0</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P1" s="9">
         <v>46149</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R1" s="11">
         <v>549</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="T1" s="9">
         <v>46149</v>
@@ -4071,7 +4077,7 @@
         <v>27</v>
       </c>
       <c r="AC1" s="25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:29" s="12" customFormat="1" ht="75">
@@ -4086,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>17</v>
@@ -4114,7 +4120,7 @@
         <v>27</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Z2" s="12" t="s">
         <v>41</v>
@@ -4135,7 +4141,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>17</v>
@@ -4147,7 +4153,7 @@
         <v>21</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="20"/>
@@ -4166,7 +4172,7 @@
         <v>27</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Z3" s="12" t="s">
         <v>41</v>
@@ -4187,7 +4193,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>17</v>
@@ -4199,7 +4205,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="20"/>
@@ -4218,7 +4224,7 @@
         <v>27</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Z4" s="12" t="s">
         <v>41</v>
@@ -4239,7 +4245,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>17</v>
@@ -4251,7 +4257,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="20"/>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E42679C0-EAF2-443D-BC09-CE77654E13DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC899878-B425-4AFC-815C-6D4B46B45CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="285">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -827,12 +827,6 @@
     <t>https://www.amazon.com/Loona-ChatGPT-4o-AI-Powered-Interaction-Monitoring/dp/B0DCF53PCH/ref=sr_1_1_sspa?crid=LXSZQC579ZUJ&amp;dib=eyJ2IjoiMSJ9.fRTz6IKj5O3hiZ4V3RbIiqzYkMvGWX1yxIfmBNQ2bPEXhXF8Ry2nqncmMGEv7evRpJaa3U9aWxY1MQkhTgdPIV6Wjq-bFAK8cz4LIVjlEwH6W3j7kAEh6OD6pXtvOtnElQhMvBxTEwFpCiEYHVGyhpXxpCYzj1C2k8p3eIaIxYpRdd5pCvCtpNx-q-dgV8LfuIsu2pUkkgQks54gIUrjn4mpoOq0hqlBJXm_aPrP6Bi0oNJqD9loGYkwNNTqGtcUJYHc5fRntYIBPwj9_pE6lRUuH1CiB6ijg6RWmc0N6oE.9xo2lpag-NNW4-lvsbZ84aWH32CcaxXnQJs2fXDBXV8&amp;dib_tag=se&amp;keywords=loona%2Brobot&amp;qid=1778539102&amp;s=toys-and-games&amp;sprefix=loona%2Ctoys-and-games%2C257&amp;sr=1-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
   </si>
   <si>
-    <t>Enabot's emtry level robot. AI home monitoring robot designed to keep your home, pets, and loved ones connected and secure. Interactive laser point allows you to entertain your pets while you are away.</t>
-  </si>
-  <si>
-    <t>Newer genration than the EBO Air 2 with more features. AI home monitoring robot designed to keep your home, pets, and loved ones connected and secure. Does not include the AI Assistant. White option only.</t>
-  </si>
-  <si>
     <t>High resolution camera. Home monitoring robot with AI Assistant keeps your home, pets, and loved ones connected and secure. Includes Smart Tracking and Sound Source Location for enhanced monitoring.</t>
   </si>
   <si>
@@ -900,6 +894,12 @@
   </si>
   <si>
     <t>/images/products/Perfect-Petzzz-Original-Black-and-White-Shorthair-Cat.png</t>
+  </si>
+  <si>
+    <t>Enabot's entry level robot. AI home monitoring robot designed to keep your home, pets, and loved ones connected and secure. Interactive laser point allows you to entertain your pets while you are away.</t>
+  </si>
+  <si>
+    <t>Newer generation than the EBO Air 2 with more features. AI home monitoring robot designed to keep your home, pets, and loved ones connected and secure. Does not include the AI Assistant. White option only.</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1028,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1113,9 +1113,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1637,21 +1634,21 @@
         <v>31</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AC1" s="23" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:29" ht="285">
+    <row r="2" spans="1:29">
       <c r="A2" s="3" t="str">
-        <f>_xlfn.CONCAT(B2, " ", C2)</f>
+        <f t="shared" ref="A2:A30" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="3" spans="1:29" ht="60">
       <c r="A3" s="3" t="str">
-        <f>_xlfn.CONCAT(B3, " ", C3)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1724,6 +1721,9 @@
         <v>42</v>
       </c>
       <c r="Y3" s="5"/>
+      <c r="Z3" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1733,7 +1733,7 @@
     </row>
     <row r="4" spans="1:29" ht="75">
       <c r="A4" s="3" t="str">
-        <f>_xlfn.CONCAT(B4, " ", C4)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1803,9 +1803,12 @@
         <v>27</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Y4" s="4"/>
+      <c r="Z4" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1813,9 +1816,9 @@
         <v>203</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="60">
+    <row r="5" spans="1:29" ht="285">
       <c r="A5" s="3" t="str">
-        <f>_xlfn.CONCAT(B5, " ", C5)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1885,7 +1888,10 @@
         <v>26</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
+      </c>
+      <c r="Z5" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AB5" s="3" t="s">
         <v>27</v>
@@ -1894,16 +1900,16 @@
         <v>202</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="60">
+    <row r="6" spans="1:29" ht="75">
       <c r="A6" s="3" t="str">
-        <f>_xlfn.CONCAT(B6, " ", C6)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
       </c>
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>65</v>
@@ -1963,9 +1969,12 @@
         <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="Y6" s="4"/>
+      <c r="Z6" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB6" s="3" t="s">
         <v>27</v>
       </c>
@@ -1975,7 +1984,7 @@
     </row>
     <row r="7" spans="1:29" ht="60">
       <c r="A7" s="3" t="str">
-        <f>_xlfn.CONCAT(B7, " ", C7)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2048,6 +2057,9 @@
         <v>53</v>
       </c>
       <c r="Y7" s="4"/>
+      <c r="Z7" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB7" s="3" t="s">
         <v>27</v>
       </c>
@@ -2057,7 +2069,7 @@
     </row>
     <row r="8" spans="1:29" ht="60">
       <c r="A8" s="3" t="str">
-        <f>_xlfn.CONCAT(B8, " ", C8)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
       </c>
       <c r="B8" s="3" t="s">
@@ -2079,7 +2091,7 @@
         <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>81</v>
@@ -2127,7 +2139,10 @@
         <v>26</v>
       </c>
       <c r="X8" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AB8" s="3" t="s">
         <v>27</v>
@@ -2136,9 +2151,9 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="45">
+    <row r="9" spans="1:29" ht="60">
       <c r="A9" s="3" t="str">
-        <f>_xlfn.CONCAT(B9, " ", C9)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2160,7 +2175,7 @@
         <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>78</v>
@@ -2208,7 +2223,10 @@
         <v>26</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
+      </c>
+      <c r="Z9" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AB9" s="3" t="s">
         <v>27</v>
@@ -2217,9 +2235,9 @@
         <v>224</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="300">
+    <row r="10" spans="1:29" ht="60">
       <c r="A10" s="3" t="str">
-        <f>_xlfn.CONCAT(B10, " ", C10)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2241,7 +2259,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>92</v>
@@ -2289,7 +2307,10 @@
         <v>27</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
+      </c>
+      <c r="Z10" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AB10" s="3" t="s">
         <v>27</v>
@@ -2300,7 +2321,7 @@
     </row>
     <row r="11" spans="1:29" ht="60" customHeight="1">
       <c r="A11" s="3" t="str">
-        <f>_xlfn.CONCAT(B11, " ", C11)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2322,7 +2343,7 @@
         <v>23</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>80</v>
@@ -2370,7 +2391,10 @@
         <v>27</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
+      </c>
+      <c r="Z11" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AB11" s="3" t="s">
         <v>27</v>
@@ -2379,9 +2403,9 @@
         <v>222</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="270.75" thickBot="1">
+    <row r="12" spans="1:29" ht="45.75" thickBot="1">
       <c r="A12" s="3" t="str">
-        <f>_xlfn.CONCAT(B12, " ", C12)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2403,7 +2427,7 @@
         <v>22</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>95</v>
@@ -2451,7 +2475,10 @@
         <v>27</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AB12" s="3" t="s">
         <v>27</v>
@@ -2460,9 +2487,9 @@
         <v>227</v>
       </c>
     </row>
-    <row r="13" spans="1:29" ht="270.75" thickBot="1">
+    <row r="13" spans="1:29" ht="210.75" thickBot="1">
       <c r="A13" s="3" t="str">
-        <f>_xlfn.CONCAT(B13, " ", C13)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2535,6 +2562,9 @@
         <v>56</v>
       </c>
       <c r="Y13" s="4"/>
+      <c r="Z13" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB13" s="3" t="s">
         <v>27</v>
       </c>
@@ -2544,7 +2574,7 @@
     </row>
     <row r="14" spans="1:29" ht="210">
       <c r="A14" s="3" t="str">
-        <f>_xlfn.CONCAT(B14, " ", C14)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2617,6 +2647,9 @@
         <v>55</v>
       </c>
       <c r="Y14" s="4"/>
+      <c r="Z14" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB14" s="3" t="s">
         <v>27</v>
       </c>
@@ -2626,7 +2659,7 @@
     </row>
     <row r="15" spans="1:29" ht="60" customHeight="1">
       <c r="A15" s="3" t="str">
-        <f>_xlfn.CONCAT(B15, " ", C15)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -2699,6 +2732,9 @@
         <v>54</v>
       </c>
       <c r="Y15" s="4"/>
+      <c r="Z15" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB15" s="3" t="s">
         <v>27</v>
       </c>
@@ -2706,9 +2742,9 @@
         <v>201</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="210">
+    <row r="16" spans="1:29" ht="60">
       <c r="A16" s="3" t="str">
-        <f>_xlfn.CONCAT(B16, " ", C16)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2778,9 +2814,12 @@
         <v>27</v>
       </c>
       <c r="X16" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Y16" s="4"/>
+      <c r="Z16" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB16" s="3" t="s">
         <v>27</v>
       </c>
@@ -2790,7 +2829,7 @@
     </row>
     <row r="17" spans="1:29" ht="60">
       <c r="A17" s="3" t="str">
-        <f>_xlfn.CONCAT(B17, " ", C17)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2860,9 +2899,12 @@
         <v>26</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Y17" s="4"/>
+      <c r="Z17" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB17" s="3" t="s">
         <v>27</v>
       </c>
@@ -2872,7 +2914,7 @@
     </row>
     <row r="18" spans="1:29" ht="74.25" customHeight="1">
       <c r="A18" s="3" t="str">
-        <f>_xlfn.CONCAT(B18, " ", C18)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
       </c>
       <c r="B18" s="3" t="s">
@@ -2942,7 +2984,10 @@
         <v>27</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
+      </c>
+      <c r="Z18" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>27</v>
@@ -2951,9 +2996,9 @@
         <v>207</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="75">
+    <row r="19" spans="1:29" ht="270">
       <c r="A19" s="3" t="str">
-        <f>_xlfn.CONCAT(B19, " ", C19)</f>
+        <f t="shared" si="0"/>
         <v>Furby DJ Furby</v>
       </c>
       <c r="B19" s="3" t="s">
@@ -2983,7 +3028,7 @@
       <c r="J19" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="K19" s="30" t="s">
+      <c r="K19" s="3" t="s">
         <v>182</v>
       </c>
       <c r="L19" s="3" t="s">
@@ -3023,15 +3068,18 @@
         <v>26</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
+      </c>
+      <c r="Z19" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC19" s="24" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="75">
+    <row r="20" spans="1:29" ht="300">
       <c r="A20" s="3" t="str">
-        <f>_xlfn.CONCAT(B20, " ", C20)</f>
+        <f t="shared" si="0"/>
         <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -3098,10 +3146,13 @@
         <v>26</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AC20" s="24" t="s">
         <v>221</v>
@@ -3109,7 +3160,7 @@
     </row>
     <row r="21" spans="1:29" ht="75">
       <c r="A21" s="3" t="str">
-        <f>_xlfn.CONCAT(B21, " ", C21)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -3179,7 +3230,10 @@
         <v>27</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC21" s="24" t="s">
         <v>215</v>
@@ -3187,7 +3241,7 @@
     </row>
     <row r="22" spans="1:29" ht="75">
       <c r="A22" s="3" t="str">
-        <f>_xlfn.CONCAT(B22, " ", C22)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Beagle</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -3258,6 +3312,9 @@
       </c>
       <c r="X22" s="2" t="s">
         <v>46</v>
+      </c>
+      <c r="Z22" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC22" s="24" t="s">
         <v>213</v>
@@ -3265,7 +3322,7 @@
     </row>
     <row r="23" spans="1:29" ht="60" customHeight="1">
       <c r="A23" s="3" t="str">
-        <f>_xlfn.CONCAT(B23, " ", C23)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -3335,7 +3392,10 @@
         <v>26</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
+      </c>
+      <c r="Z23" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC23" s="24" t="s">
         <v>217</v>
@@ -3343,7 +3403,7 @@
     </row>
     <row r="24" spans="1:29" ht="60" customHeight="1">
       <c r="A24" s="3" t="str">
-        <f>_xlfn.CONCAT(B24, " ", C24)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3414,6 +3474,9 @@
       </c>
       <c r="X24" s="2" t="s">
         <v>43</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC24" s="24" t="s">
         <v>210</v>
@@ -3421,7 +3484,7 @@
     </row>
     <row r="25" spans="1:29" ht="60" customHeight="1">
       <c r="A25" s="3" t="str">
-        <f>_xlfn.CONCAT(B25, " ", C25)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -3492,6 +3555,9 @@
       </c>
       <c r="X25" s="2" t="s">
         <v>44</v>
+      </c>
+      <c r="Z25" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC25" s="24" t="s">
         <v>211</v>
@@ -3499,7 +3565,7 @@
     </row>
     <row r="26" spans="1:29" ht="60" customHeight="1">
       <c r="A26" s="3" t="str">
-        <f>_xlfn.CONCAT(B26, " ", C26)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -3570,6 +3636,9 @@
       </c>
       <c r="X26" s="2" t="s">
         <v>57</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC26" s="24" t="s">
         <v>216</v>
@@ -3577,7 +3646,7 @@
     </row>
     <row r="27" spans="1:29" ht="75">
       <c r="A27" s="3" t="str">
-        <f>_xlfn.CONCAT(B27, " ", C27)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Shih Tzu</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -3648,6 +3717,9 @@
       </c>
       <c r="X27" s="2" t="s">
         <v>45</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AC27" s="24" t="s">
         <v>212</v>
@@ -3655,7 +3727,7 @@
     </row>
     <row r="28" spans="1:29" ht="27.75" customHeight="1">
       <c r="A28" s="3" t="str">
-        <f>_xlfn.CONCAT(B28, " ", C28)</f>
+        <f t="shared" si="0"/>
         <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -3727,13 +3799,16 @@
       <c r="X28" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="Z28" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AC28" s="24" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="180">
+    <row r="29" spans="1:29" ht="270">
       <c r="A29" s="3" t="str">
-        <f>_xlfn.CONCAT(B29, " ", C29)</f>
+        <f t="shared" si="0"/>
         <v>Ropet KAMOMO</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -3803,7 +3878,7 @@
         <v>26</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>26</v>
@@ -3818,9 +3893,9 @@
         <v>209</v>
       </c>
     </row>
-    <row r="30" spans="1:29">
+    <row r="30" spans="1:29" ht="300">
       <c r="A30" s="3" t="str">
-        <f>_xlfn.CONCAT(B30, " ", C30)</f>
+        <f t="shared" si="0"/>
         <v>Ruko 18011 Smart Robot Dog</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -3890,7 +3965,10 @@
         <v>26</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
+      </c>
+      <c r="Z30" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="AB30" s="3" t="s">
         <v>26</v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC899878-B425-4AFC-815C-6D4B46B45CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0DE929-EE3B-4312-ACED-E60E7E238EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="32085" yWindow="1530" windowWidth="21600" windowHeight="11295" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Matrix" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="285">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -1724,6 +1724,9 @@
       <c r="Z3" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA3" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB3" s="3" t="s">
         <v>27</v>
       </c>
@@ -1809,6 +1812,9 @@
       <c r="Z4" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA4" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB4" s="3" t="s">
         <v>27</v>
       </c>
@@ -1893,6 +1899,9 @@
       <c r="Z5" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA5" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB5" s="3" t="s">
         <v>27</v>
       </c>
@@ -1975,6 +1984,9 @@
       <c r="Z6" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA6" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB6" s="3" t="s">
         <v>27</v>
       </c>
@@ -2060,6 +2072,9 @@
       <c r="Z7" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA7" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB7" s="3" t="s">
         <v>27</v>
       </c>
@@ -2144,6 +2159,9 @@
       <c r="Z8" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="AA8" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AB8" s="3" t="s">
         <v>27</v>
       </c>
@@ -2228,6 +2246,9 @@
       <c r="Z9" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="AA9" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AB9" s="3" t="s">
         <v>27</v>
       </c>
@@ -2312,6 +2333,9 @@
       <c r="Z10" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="AA10" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AB10" s="3" t="s">
         <v>27</v>
       </c>
@@ -2396,6 +2420,9 @@
       <c r="Z11" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="AA11" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AB11" s="3" t="s">
         <v>27</v>
       </c>
@@ -2480,6 +2507,9 @@
       <c r="Z12" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="AA12" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AB12" s="3" t="s">
         <v>27</v>
       </c>
@@ -2565,6 +2595,9 @@
       <c r="Z13" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA13" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB13" s="3" t="s">
         <v>27</v>
       </c>
@@ -2650,6 +2683,9 @@
       <c r="Z14" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA14" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB14" s="3" t="s">
         <v>27</v>
       </c>
@@ -2735,6 +2771,9 @@
       <c r="Z15" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA15" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB15" s="3" t="s">
         <v>27</v>
       </c>
@@ -2820,6 +2859,9 @@
       <c r="Z16" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA16" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB16" s="3" t="s">
         <v>27</v>
       </c>
@@ -2905,6 +2947,9 @@
       <c r="Z17" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA17" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB17" s="3" t="s">
         <v>27</v>
       </c>
@@ -2989,6 +3034,9 @@
       <c r="Z18" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA18" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AB18" s="3" t="s">
         <v>27</v>
       </c>
@@ -3073,6 +3121,12 @@
       <c r="Z19" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB19" s="3" t="s">
+        <v>277</v>
+      </c>
       <c r="AC19" s="24" t="s">
         <v>220</v>
       </c>
@@ -3151,6 +3205,9 @@
       <c r="Z20" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="AA20" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="AB20" s="3" t="s">
         <v>277</v>
       </c>
@@ -3235,6 +3292,9 @@
       <c r="Z21" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA21" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AC21" s="24" t="s">
         <v>215</v>
       </c>
@@ -3316,6 +3376,9 @@
       <c r="Z22" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA22" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AC22" s="24" t="s">
         <v>213</v>
       </c>
@@ -3397,6 +3460,9 @@
       <c r="Z23" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA23" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AC23" s="24" t="s">
         <v>217</v>
       </c>
@@ -3478,6 +3544,9 @@
       <c r="Z24" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA24" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AC24" s="24" t="s">
         <v>210</v>
       </c>
@@ -3559,6 +3628,9 @@
       <c r="Z25" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA25" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AC25" s="24" t="s">
         <v>211</v>
       </c>
@@ -3640,6 +3712,9 @@
       <c r="Z26" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA26" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AC26" s="24" t="s">
         <v>216</v>
       </c>
@@ -3721,6 +3796,9 @@
       <c r="Z27" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="AA27" s="3" t="s">
+        <v>27</v>
+      </c>
       <c r="AC27" s="24" t="s">
         <v>212</v>
       </c>
@@ -3800,6 +3878,9 @@
         <v>47</v>
       </c>
       <c r="Z28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA28" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AC28" s="24" t="s">

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0DE929-EE3B-4312-ACED-E60E7E238EAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6EB11D-409C-4DFF-B214-8D54CD3EB4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32085" yWindow="1530" windowWidth="21600" windowHeight="11295" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Matrix" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Maybe Later" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AC$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AD$31</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="302">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -653,21 +653,12 @@
     <t>https://joyforall.com/products/companion-cats?variant=12931092676651</t>
   </si>
   <si>
-    <t>https://chongker.com/products/matecat-pro-hyper-realistic-bionic-cat</t>
-  </si>
-  <si>
     <t>https://chongker.com/products/matecat10-interactive-cat</t>
   </si>
   <si>
-    <t>https://chongker.com/products/percy-robotic-dog-companion-designed-for-comfort</t>
-  </si>
-  <si>
     <t>https://chongker.com/products/percy-interactive-cat</t>
   </si>
   <si>
-    <t>https://chongker.com/products/breathing-red-panda</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/s?k=wuffy+robot+dog&amp;crid=19CKEYDLEBH6A&amp;sprefix=wuffy%2Caps%2C185&amp;ref=nb_sb_ss_p13n-expert-pd-ops-ranker_1_5</t>
   </si>
   <si>
@@ -900,6 +891,66 @@
   </si>
   <si>
     <t>Newer generation than the EBO Air 2 with more features. AI home monitoring robot designed to keep your home, pets, and loved ones connected and secure. Does not include the AI Assistant. White option only.</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/breathing-red-panda?ref=qhsxizxw</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/matecat10-interactive-cat?ref=qhsxizxw</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/matecat-pro-hyper-realistic-bionic-cat?ref=qhsxizxw</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/percy-robotic-dog-companion-designed-for-comfort?ref=qhsxizxw</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/percy-interactive-cat?ref=qhsxizxw</t>
+  </si>
+  <si>
+    <t>Match to site?</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chongker Percy Robot Ginger Cat 1,1</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/percy-robot-ginger-cat-1-1-voice-purring-heartbeat-for-comfort?ref=qhsxizxw</t>
+  </si>
+  <si>
+    <t>https://chongker.com/products/breathing-calico-percy-2-0-heartbeat-pur-voice-robonic-cat?ref=qhsxizxw</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Chongker Breathing Calico Percy 2.0</t>
+  </si>
+  <si>
+    <t>Percy Robot Ginger Cat 1,1</t>
+  </si>
+  <si>
+    <t>Breathing Calico Percy 2.0</t>
+  </si>
+  <si>
+    <t>Helps with Sleep</t>
+  </si>
+  <si>
+    <t>Voice Interaction</t>
+  </si>
+  <si>
+    <t>Has voice, purring, and heartbeat. Brings a calming presence wherever it goes.</t>
+  </si>
+  <si>
+    <t>Fully interactive breathing, purring and meowing cat. Just like the real thing without the care and respnsilities of a real pet</t>
+  </si>
+  <si>
+    <t>Hearrtbeat</t>
+  </si>
+  <si>
+    <t>Purrs and meows</t>
+  </si>
+  <si>
+    <t>Breathing Calico Percy 2.0- Heartbeat Pur,Voice Robonic Cat – Chongker</t>
+  </si>
+  <si>
+    <t>/images/products/ Chongker Breathing Calico Percy 2.0</t>
   </si>
 </sst>
 </file>
@@ -1028,7 +1079,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1115,6 +1166,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1140,13 +1194,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>65</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1517,7 +1571,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:AC30"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.140625" style="3" customWidth="1"/>
@@ -1536,7 +1590,7 @@
     <col min="14" max="14" width="10.7109375" style="19" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" style="3" customWidth="1"/>
     <col min="16" max="16" width="13.28515625" style="9" customWidth="1"/>
-    <col min="17" max="17" width="43.85546875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="80.7109375" style="3" customWidth="1"/>
     <col min="18" max="18" width="8.85546875" style="11" customWidth="1"/>
     <col min="19" max="19" width="10" style="3" customWidth="1"/>
     <col min="20" max="21" width="13.28515625" style="9" customWidth="1"/>
@@ -1547,11 +1601,12 @@
     <col min="26" max="26" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.140625" style="3" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="200.7109375" style="25" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="3"/>
+    <col min="29" max="29" width="10.5703125" style="3" customWidth="1"/>
+    <col min="30" max="30" width="200.7109375" style="25" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" s="6" customFormat="1" ht="30">
+    <row r="1" spans="1:30" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
         <v>190</v>
       </c>
@@ -1634,21 +1689,24 @@
         <v>31</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="AC1" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="AD1" s="23" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="2" spans="1:29">
+    <row r="2" spans="1:30">
       <c r="A2" s="3" t="str">
-        <f t="shared" ref="A2:A30" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
+        <f>_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="60">
+    <row r="3" spans="1:30" ht="60">
       <c r="A3" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B3, " ", C3)</f>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1691,13 +1749,13 @@
         <v>2</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P3" s="9">
         <v>46153</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="R3" s="11">
         <v>119</v>
@@ -1728,15 +1786,18 @@
         <v>27</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC3" s="24" t="s">
-        <v>206</v>
+        <v>26</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD3" s="24" t="s">
+        <v>282</v>
       </c>
     </row>
-    <row r="4" spans="1:29" ht="75">
+    <row r="4" spans="1:30" ht="75">
       <c r="A4" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B4, " ", C4)</f>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1779,13 +1840,13 @@
         <v>2</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P4" s="9">
         <v>46153</v>
       </c>
       <c r="Q4" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R4" s="11">
         <v>149</v>
@@ -1806,7 +1867,7 @@
         <v>27</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="3" t="s">
@@ -1816,15 +1877,18 @@
         <v>27</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC4" s="25" t="s">
-        <v>203</v>
+        <v>26</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD4" s="25" t="s">
+        <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:29" ht="285">
+    <row r="5" spans="1:30" ht="165">
       <c r="A5" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B5, " ", C5)</f>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1873,7 +1937,7 @@
         <v>46153</v>
       </c>
       <c r="Q5" s="21" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="R5" s="11">
         <v>178</v>
@@ -1894,7 +1958,7 @@
         <v>26</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>27</v>
@@ -1903,22 +1967,25 @@
         <v>27</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC5" s="25" t="s">
-        <v>202</v>
+        <v>26</v>
+      </c>
+      <c r="AC5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD5" s="25" t="s">
+        <v>284</v>
       </c>
     </row>
-    <row r="6" spans="1:29" ht="75">
+    <row r="6" spans="1:30" ht="75">
       <c r="A6" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B6, " ", C6)</f>
         <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
       </c>
       <c r="B6" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>65</v>
@@ -1957,7 +2024,7 @@
         <v>46153</v>
       </c>
       <c r="Q6" s="21" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="R6" s="11">
         <v>89</v>
@@ -1978,7 +2045,7 @@
         <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="3" t="s">
@@ -1988,15 +2055,18 @@
         <v>27</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC6" s="24" t="s">
-        <v>204</v>
+        <v>26</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD6" s="24" t="s">
+        <v>285</v>
       </c>
     </row>
-    <row r="7" spans="1:29" ht="60">
+    <row r="7" spans="1:30" ht="60">
       <c r="A7" s="3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B7, " ", C7)</f>
         <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2039,13 +2109,13 @@
         <v>16</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="P7" s="9">
         <v>46153</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="R7" s="11">
         <v>89</v>
@@ -2076,73 +2146,72 @@
         <v>27</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC7" s="25" t="s">
-        <v>205</v>
+        <v>26</v>
+      </c>
+      <c r="AC7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD7" s="25" t="s">
+        <v>286</v>
       </c>
     </row>
-    <row r="8" spans="1:29" ht="60">
-      <c r="A8" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
+    <row r="8" spans="1:30" ht="45">
+      <c r="A8" s="3" t="s">
+        <v>291</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>232</v>
+        <v>293</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>81</v>
+        <v>155</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>87</v>
+        <v>295</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>93</v>
+        <v>294</v>
       </c>
       <c r="M8" s="16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N8" s="19">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>83</v>
+        <v>241</v>
       </c>
       <c r="P8" s="9">
-        <v>46149</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>236</v>
+        <v>46161</v>
+      </c>
+      <c r="Q8" s="30" t="s">
+        <v>300</v>
       </c>
       <c r="R8" s="11">
-        <v>179</v>
+        <v>109</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>83</v>
+        <v>141</v>
       </c>
       <c r="T8" s="9">
-        <v>46152</v>
+        <v>46161</v>
       </c>
       <c r="U8" s="9" t="s">
         <v>189</v>
@@ -2153,32 +2222,36 @@
       <c r="W8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X8" s="2" t="s">
-        <v>264</v>
-      </c>
+      <c r="X8" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y8" s="4"/>
       <c r="Z8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC8" s="25" t="s">
-        <v>226</v>
+        <v>26</v>
+      </c>
+      <c r="AC8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD8" s="25" t="s">
+        <v>290</v>
       </c>
     </row>
-    <row r="9" spans="1:29" ht="60">
+    <row r="9" spans="1:30" ht="60">
       <c r="A9" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
+        <f>_xlfn.CONCAT(B9, " ", C9)</f>
+        <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
       </c>
       <c r="B9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>63</v>
@@ -2193,25 +2266,25 @@
         <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="L9" s="3" t="s">
         <v>93</v>
       </c>
       <c r="M9" s="16">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N9" s="19">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="O9" s="3" t="s">
         <v>83</v>
@@ -2220,19 +2293,19 @@
         <v>46149</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="R9" s="11">
-        <v>359</v>
+        <v>179</v>
       </c>
       <c r="S9" s="3" t="s">
         <v>83</v>
       </c>
       <c r="T9" s="9">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>25</v>
+        <v>189</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>26</v>
@@ -2241,7 +2314,7 @@
         <v>26</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>26</v>
@@ -2252,20 +2325,20 @@
       <c r="AB9" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC9" s="25" t="s">
-        <v>224</v>
+      <c r="AD9" s="25" t="s">
+        <v>223</v>
       </c>
     </row>
-    <row r="10" spans="1:29" ht="60">
+    <row r="10" spans="1:30" ht="60">
       <c r="A10" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
+        <f>_xlfn.CONCAT(B10, " ", C10)</f>
+        <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
       <c r="B10" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>63</v>
@@ -2280,16 +2353,16 @@
         <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L10" s="3" t="s">
         <v>93</v>
@@ -2298,7 +2371,7 @@
         <v>5</v>
       </c>
       <c r="N10" s="19">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="O10" s="3" t="s">
         <v>83</v>
@@ -2307,16 +2380,16 @@
         <v>46149</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="R10" s="11">
-        <v>279</v>
+        <v>359</v>
       </c>
       <c r="S10" s="3" t="s">
         <v>83</v>
       </c>
       <c r="T10" s="9">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="U10" s="9" t="s">
         <v>25</v>
@@ -2325,10 +2398,10 @@
         <v>26</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>26</v>
@@ -2339,14 +2412,14 @@
       <c r="AB10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC10" s="25" t="s">
-        <v>225</v>
+      <c r="AD10" s="25" t="s">
+        <v>221</v>
       </c>
     </row>
-    <row r="11" spans="1:29" ht="60" customHeight="1">
+    <row r="11" spans="1:30" ht="60">
       <c r="A11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
+        <f>_xlfn.CONCAT(B11, " ", C11)</f>
+        <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
       <c r="B11" s="3" t="s">
         <v>0</v>
@@ -2364,28 +2437,28 @@
         <v>22</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="M11" s="16">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="N11" s="19">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O11" s="3" t="s">
         <v>83</v>
@@ -2394,16 +2467,16 @@
         <v>46149</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="R11" s="11">
-        <v>789</v>
+        <v>279</v>
       </c>
       <c r="S11" s="3" t="s">
         <v>83</v>
       </c>
       <c r="T11" s="9">
-        <v>46149</v>
+        <v>46151</v>
       </c>
       <c r="U11" s="9" t="s">
         <v>25</v>
@@ -2426,20 +2499,20 @@
       <c r="AB11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC11" s="25" t="s">
+      <c r="AD11" s="25" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="12" spans="1:29" ht="45.75" thickBot="1">
+    <row r="12" spans="1:30" ht="60" customHeight="1">
       <c r="A12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
+        <f>_xlfn.CONCAT(B12, " ", C12)</f>
+        <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>63</v>
@@ -2448,31 +2521,31 @@
         <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>94</v>
+        <v>22</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="M12" s="16">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="N12" s="19">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>83</v>
@@ -2480,104 +2553,104 @@
       <c r="P12" s="9">
         <v>46149</v>
       </c>
-      <c r="Q12" s="21" t="s">
-        <v>237</v>
+      <c r="Q12" s="3" t="s">
+        <v>230</v>
       </c>
       <c r="R12" s="11">
-        <v>139</v>
+        <v>789</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>83</v>
       </c>
       <c r="T12" s="9">
+        <v>46149</v>
+      </c>
+      <c r="U12" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="W12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="Z12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD12" s="25" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" ht="45.75" thickBot="1">
+      <c r="A13" s="3" t="str">
+        <f>_xlfn.CONCAT(B13, " ", C13)</f>
+        <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="M13" s="16">
+        <v>5</v>
+      </c>
+      <c r="N13" s="19">
+        <v>73</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P13" s="9">
+        <v>46149</v>
+      </c>
+      <c r="Q13" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="R13" s="11">
+        <v>139</v>
+      </c>
+      <c r="S13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="T13" s="9">
         <v>46153</v>
-      </c>
-      <c r="U12" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="V12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="Z12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC12" s="25" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:29" ht="210.75" thickBot="1">
-      <c r="A13" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K13" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="M13" s="16">
-        <v>4.5</v>
-      </c>
-      <c r="N13" s="19">
-        <v>11640</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P13" s="9">
-        <v>46153</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="R13" s="11">
-        <v>159.99</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="T13" s="9">
-        <v>46150</v>
       </c>
       <c r="U13" s="9" t="s">
         <v>189</v>
@@ -2589,32 +2662,31 @@
         <v>27</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y13" s="4"/>
+        <v>264</v>
+      </c>
       <c r="Z13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC13" s="24" t="s">
-        <v>200</v>
+      <c r="AD13" s="25" t="s">
+        <v>224</v>
       </c>
     </row>
-    <row r="14" spans="1:29" ht="210">
+    <row r="14" spans="1:30" ht="105.75" thickBot="1">
       <c r="A14" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
+        <f>_xlfn.CONCAT(B14, " ", C14)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>62</v>
@@ -2629,7 +2701,7 @@
         <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>110</v>
@@ -2637,11 +2709,11 @@
       <c r="J14" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>112</v>
+      <c r="K14" s="29" t="s">
+        <v>113</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M14" s="16">
         <v>4.5</v>
@@ -2656,7 +2728,7 @@
         <v>46153</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R14" s="11">
         <v>159.99</v>
@@ -2677,7 +2749,7 @@
         <v>27</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y14" s="4"/>
       <c r="Z14" s="3" t="s">
@@ -2689,20 +2761,20 @@
       <c r="AB14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC14" s="26" t="s">
-        <v>199</v>
+      <c r="AD14" s="24" t="s">
+        <v>200</v>
       </c>
     </row>
-    <row r="15" spans="1:29" ht="60" customHeight="1">
+    <row r="15" spans="1:30" ht="105">
       <c r="A15" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
+        <f>_xlfn.CONCAT(B15, " ", C15)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>62</v>
@@ -2717,7 +2789,7 @@
         <v>21</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>110</v>
@@ -2726,10 +2798,10 @@
         <v>111</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M15" s="16">
         <v>4.5</v>
@@ -2741,10 +2813,10 @@
         <v>82</v>
       </c>
       <c r="P15" s="9">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="R15" s="11">
         <v>159.99</v>
@@ -2762,10 +2834,10 @@
         <v>26</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>54</v>
+        <v>27</v>
+      </c>
+      <c r="X15" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="Y15" s="4"/>
       <c r="Z15" s="3" t="s">
@@ -2777,23 +2849,23 @@
       <c r="AB15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC15" s="25" t="s">
-        <v>201</v>
+      <c r="AD15" s="26" t="s">
+        <v>199</v>
       </c>
     </row>
-    <row r="16" spans="1:29" ht="60">
+    <row r="16" spans="1:30" ht="60" customHeight="1">
       <c r="A16" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
+        <f>_xlfn.CONCAT(B16, " ", C16)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>17</v>
@@ -2805,25 +2877,25 @@
         <v>21</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="M16" s="16">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="N16" s="19">
-        <v>5163</v>
+        <v>11640</v>
       </c>
       <c r="O16" s="3" t="s">
         <v>82</v>
@@ -2832,10 +2904,10 @@
         <v>46150</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="R16" s="11">
-        <v>179</v>
+        <v>159.99</v>
       </c>
       <c r="S16" s="3" t="s">
         <v>82</v>
@@ -2850,10 +2922,10 @@
         <v>26</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X16" s="2" t="s">
-        <v>269</v>
+        <v>26</v>
+      </c>
+      <c r="X16" s="3" t="s">
+        <v>54</v>
       </c>
       <c r="Y16" s="4"/>
       <c r="Z16" s="3" t="s">
@@ -2865,20 +2937,20 @@
       <c r="AB16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC16" s="26" t="s">
-        <v>198</v>
+      <c r="AD16" s="25" t="s">
+        <v>201</v>
       </c>
     </row>
-    <row r="17" spans="1:29" ht="60">
+    <row r="17" spans="1:30" ht="60">
       <c r="A17" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
+        <f>_xlfn.CONCAT(B17, " ", C17)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>13</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>65</v>
@@ -2893,7 +2965,7 @@
         <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>105</v>
@@ -2902,25 +2974,25 @@
         <v>106</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M17" s="16">
         <v>4.3</v>
       </c>
       <c r="N17" s="19">
-        <v>5164</v>
+        <v>5163</v>
       </c>
       <c r="O17" s="3" t="s">
         <v>82</v>
       </c>
       <c r="P17" s="9">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="R17" s="11">
         <v>179</v>
@@ -2938,10 +3010,10 @@
         <v>26</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="3" t="s">
@@ -2953,20 +3025,20 @@
       <c r="AB17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC17" s="26" t="s">
+      <c r="AD17" s="26" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="18" spans="1:29" ht="74.25" customHeight="1">
+    <row r="18" spans="1:30" ht="60">
       <c r="A18" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
+        <f>_xlfn.CONCAT(B18, " ", C18)</f>
+        <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>65</v>
@@ -2975,62 +3047,63 @@
         <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="H18" s="3" t="s">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>148</v>
+        <v>105</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>146</v>
+        <v>106</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>147</v>
+        <v>107</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="M18" s="16">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="N18" s="19">
-        <v>80</v>
+        <v>5164</v>
       </c>
       <c r="O18" s="3" t="s">
         <v>82</v>
       </c>
       <c r="P18" s="9">
-        <v>46151</v>
+        <v>46153</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="R18" s="11">
-        <v>25.99</v>
+        <v>179</v>
       </c>
       <c r="S18" s="3" t="s">
         <v>82</v>
       </c>
       <c r="T18" s="9">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>87</v>
+        <v>189</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>270</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="Y18" s="4"/>
       <c r="Z18" s="3" t="s">
         <v>27</v>
       </c>
@@ -3040,26 +3113,26 @@
       <c r="AB18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC18" s="24" t="s">
-        <v>207</v>
+      <c r="AD18" s="26" t="s">
+        <v>198</v>
       </c>
     </row>
-    <row r="19" spans="1:29" ht="270">
+    <row r="19" spans="1:30" ht="74.25" customHeight="1">
       <c r="A19" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Furby DJ Furby</v>
+        <f>_xlfn.CONCAT(B19, " ", C19)</f>
+        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>63</v>
+        <v>12</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>21</v>
@@ -3068,43 +3141,43 @@
         <v>22</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>184</v>
+        <v>148</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>183</v>
+        <v>146</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>187</v>
+        <v>152</v>
       </c>
       <c r="M19" s="16">
-        <v>4.8</v>
+        <v>3</v>
       </c>
       <c r="N19" s="19">
-        <v>772</v>
+        <v>80</v>
       </c>
       <c r="O19" s="3" t="s">
         <v>82</v>
       </c>
       <c r="P19" s="9">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>258</v>
+        <v>244</v>
       </c>
       <c r="R19" s="11">
-        <v>50.11</v>
+        <v>25.99</v>
       </c>
       <c r="S19" s="3" t="s">
         <v>82</v>
       </c>
       <c r="T19" s="9">
-        <v>46150</v>
+        <v>46151</v>
       </c>
       <c r="U19" s="9" t="s">
         <v>87</v>
@@ -3113,10 +3186,10 @@
         <v>26</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>27</v>
@@ -3125,25 +3198,25 @@
         <v>27</v>
       </c>
       <c r="AB19" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC19" s="24" t="s">
-        <v>220</v>
+        <v>27</v>
+      </c>
+      <c r="AD19" s="24" t="s">
+        <v>204</v>
       </c>
     </row>
-    <row r="20" spans="1:29" ht="300">
+    <row r="20" spans="1:30" ht="150">
       <c r="A20" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Loona Robot Pet Dog</v>
+        <f>_xlfn.CONCAT(B20, " ", C20)</f>
+        <v>Furby DJ Furby</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>65</v>
+        <v>52</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>16</v>
@@ -3155,22 +3228,25 @@
         <v>22</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>187</v>
       </c>
       <c r="M20" s="16">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="N20" s="19">
-        <v>1199</v>
+        <v>772</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>82</v>
@@ -3179,10 +3255,10 @@
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="R20" s="11">
-        <v>499</v>
+        <v>50.11</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>82</v>
@@ -3191,7 +3267,7 @@
         <v>46150</v>
       </c>
       <c r="U20" s="9" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>26</v>
@@ -3200,64 +3276,61 @@
         <v>26</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="Z20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC20" s="24" t="s">
-        <v>221</v>
+        <v>274</v>
+      </c>
+      <c r="AD20" s="24" t="s">
+        <v>217</v>
       </c>
     </row>
-    <row r="21" spans="1:29" ht="75">
+    <row r="21" spans="1:30" ht="165">
       <c r="A21" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Grey Tabby Cat</v>
+        <f>_xlfn.CONCAT(B21, " ", C21)</f>
+        <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>167</v>
+        <v>180</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>155</v>
+        <v>181</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="M21" s="16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="N21" s="19">
-        <v>848</v>
+        <v>1199</v>
       </c>
       <c r="O21" s="3" t="s">
         <v>82</v>
@@ -3266,10 +3339,10 @@
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="R21" s="11">
-        <v>44.45</v>
+        <v>499</v>
       </c>
       <c r="S21" s="3" t="s">
         <v>82</v>
@@ -3278,40 +3351,43 @@
         <v>46150</v>
       </c>
       <c r="U21" s="9" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC21" s="24" t="s">
-        <v>215</v>
+        <v>26</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD21" s="24" t="s">
+        <v>218</v>
       </c>
     </row>
-    <row r="22" spans="1:29" ht="75">
+    <row r="22" spans="1:30" ht="60">
       <c r="A22" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Beagle</v>
+        <f>_xlfn.CONCAT(B22, " ", C22)</f>
+        <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>17</v>
@@ -3323,25 +3399,25 @@
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="L22" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M22" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="N22" s="19">
-        <v>466</v>
+        <v>848</v>
       </c>
       <c r="O22" s="3" t="s">
         <v>82</v>
@@ -3350,7 +3426,7 @@
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
@@ -3371,7 +3447,7 @@
         <v>27</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>46</v>
+        <v>278</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>27</v>
@@ -3379,23 +3455,23 @@
       <c r="AA22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC22" s="24" t="s">
-        <v>213</v>
+      <c r="AD22" s="24" t="s">
+        <v>212</v>
       </c>
     </row>
-    <row r="23" spans="1:29" ht="60" customHeight="1">
+    <row r="23" spans="1:30" ht="60">
       <c r="A23" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
+        <f>_xlfn.CONCAT(B23, " ", C23)</f>
+        <v>Perfect Petzzz Original Beagle</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>17</v>
@@ -3407,25 +3483,25 @@
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="L23" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M23" s="16">
         <v>4.4000000000000004</v>
       </c>
       <c r="N23" s="19">
-        <v>1200</v>
+        <v>466</v>
       </c>
       <c r="O23" s="3" t="s">
         <v>82</v>
@@ -3434,7 +3510,7 @@
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
@@ -3452,10 +3528,10 @@
         <v>26</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>282</v>
+        <v>46</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>27</v>
@@ -3463,23 +3539,23 @@
       <c r="AA23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC23" s="24" t="s">
-        <v>217</v>
+      <c r="AD23" s="24" t="s">
+        <v>210</v>
       </c>
     </row>
-    <row r="24" spans="1:29" ht="60" customHeight="1">
+    <row r="24" spans="1:30" ht="60" customHeight="1">
       <c r="A24" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Border Collie</v>
+        <f>_xlfn.CONCAT(B24, " ", C24)</f>
+        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>17</v>
@@ -3491,25 +3567,25 @@
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>167</v>
-      </c>
       <c r="L24" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M24" s="16">
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N24" s="19">
-        <v>403</v>
+        <v>1200</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>82</v>
@@ -3518,7 +3594,7 @@
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
@@ -3536,10 +3612,10 @@
         <v>26</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>43</v>
+        <v>279</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>27</v>
@@ -3547,20 +3623,20 @@
       <c r="AA24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC24" s="24" t="s">
-        <v>210</v>
+      <c r="AD24" s="24" t="s">
+        <v>214</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="60" customHeight="1">
+    <row r="25" spans="1:30" ht="60" customHeight="1">
       <c r="A25" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Chocolate Lab</v>
+        <f>_xlfn.CONCAT(B25, " ", C25)</f>
+        <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>65</v>
@@ -3575,16 +3651,16 @@
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>195</v>
@@ -3593,7 +3669,7 @@
         <v>4.3</v>
       </c>
       <c r="N25" s="19">
-        <v>553</v>
+        <v>403</v>
       </c>
       <c r="O25" s="3" t="s">
         <v>82</v>
@@ -3602,7 +3678,7 @@
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="R25" s="11">
         <v>44.45</v>
@@ -3623,7 +3699,7 @@
         <v>27</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Z25" s="3" t="s">
         <v>27</v>
@@ -3631,23 +3707,23 @@
       <c r="AA25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC25" s="24" t="s">
-        <v>211</v>
+      <c r="AD25" s="24" t="s">
+        <v>207</v>
       </c>
     </row>
-    <row r="26" spans="1:29" ht="60" customHeight="1">
+    <row r="26" spans="1:30" ht="60" customHeight="1">
       <c r="A26" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Plush White Cat</v>
+        <f>_xlfn.CONCAT(B26, " ", C26)</f>
+        <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>17</v>
@@ -3659,25 +3735,25 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="L26" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M26" s="16">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="N26" s="19">
-        <v>54</v>
+        <v>553</v>
       </c>
       <c r="O26" s="3" t="s">
         <v>82</v>
@@ -3686,10 +3762,10 @@
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="R26" s="11">
-        <v>53.9</v>
+        <v>44.45</v>
       </c>
       <c r="S26" s="3" t="s">
         <v>82</v>
@@ -3707,7 +3783,7 @@
         <v>27</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>27</v>
@@ -3715,23 +3791,23 @@
       <c r="AA26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC26" s="24" t="s">
-        <v>216</v>
+      <c r="AD26" s="24" t="s">
+        <v>208</v>
       </c>
     </row>
-    <row r="27" spans="1:29" ht="75">
+    <row r="27" spans="1:30" ht="60" customHeight="1">
       <c r="A27" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Shih Tzu</v>
+        <f>_xlfn.CONCAT(B27, " ", C27)</f>
+        <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>17</v>
@@ -3743,7 +3819,7 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>156</v>
@@ -3755,13 +3831,13 @@
         <v>155</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M27" s="16">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="N27" s="19">
-        <v>878</v>
+        <v>54</v>
       </c>
       <c r="O27" s="3" t="s">
         <v>82</v>
@@ -3773,7 +3849,7 @@
         <v>251</v>
       </c>
       <c r="R27" s="11">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="S27" s="3" t="s">
         <v>82</v>
@@ -3788,10 +3864,10 @@
         <v>26</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>27</v>
@@ -3799,23 +3875,23 @@
       <c r="AA27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC27" s="24" t="s">
-        <v>212</v>
+      <c r="AD27" s="24" t="s">
+        <v>213</v>
       </c>
     </row>
-    <row r="28" spans="1:29" ht="27.75" customHeight="1">
+    <row r="28" spans="1:30" ht="63.75">
       <c r="A28" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Perfect Petzzz Original Siamese Cat</v>
+        <f>_xlfn.CONCAT(B28, " ", C28)</f>
+        <v>Perfect Petzzz Original Shih Tzu</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>17</v>
@@ -3827,7 +3903,7 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="I28" s="3" t="s">
         <v>156</v>
@@ -3839,13 +3915,13 @@
         <v>155</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M28" s="16">
-        <v>4.0999999999999996</v>
+        <v>4.2</v>
       </c>
       <c r="N28" s="19">
-        <v>16</v>
+        <v>878</v>
       </c>
       <c r="O28" s="3" t="s">
         <v>82</v>
@@ -3854,10 +3930,10 @@
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="R28" s="11">
-        <v>53.9</v>
+        <v>44.45</v>
       </c>
       <c r="S28" s="3" t="s">
         <v>82</v>
@@ -3872,10 +3948,10 @@
         <v>26</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="Z28" s="3" t="s">
         <v>27</v>
@@ -3883,191 +3959,275 @@
       <c r="AA28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AC28" s="24" t="s">
-        <v>218</v>
+      <c r="AD28" s="24" t="s">
+        <v>209</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="270">
+    <row r="29" spans="1:30" ht="27.75" customHeight="1">
       <c r="A29" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Ropet KAMOMO</v>
+        <f>_xlfn.CONCAT(B29, " ", C29)</f>
+        <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>63</v>
+        <v>39</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>150</v>
+        <v>172</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>194</v>
+        <v>155</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>153</v>
+        <v>196</v>
       </c>
       <c r="M29" s="16">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N29" s="19">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>82</v>
       </c>
       <c r="P29" s="9">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="R29" s="11">
-        <v>329</v>
+        <v>53.9</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>82</v>
       </c>
       <c r="T29" s="9">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="U29" s="9" t="s">
-        <v>25</v>
+        <v>87</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W29" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X29" s="2" t="s">
-        <v>279</v>
+        <v>47</v>
       </c>
       <c r="Z29" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC29" s="24" t="s">
-        <v>209</v>
+        <v>27</v>
+      </c>
+      <c r="AD29" s="24" t="s">
+        <v>215</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="300">
+    <row r="30" spans="1:30" ht="150">
       <c r="A30" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Ruko 18011 Smart Robot Dog</v>
+        <f>_xlfn.CONCAT(B30, " ", C30)</f>
+        <v>Ropet KAMOMO</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>65</v>
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>21</v>
+        <v>149</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="M30" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="N30" s="19">
-        <v>283</v>
+        <v>17</v>
       </c>
       <c r="O30" s="3" t="s">
         <v>82</v>
       </c>
       <c r="P30" s="9">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="R30" s="11">
-        <v>69.989999999999995</v>
+        <v>329</v>
       </c>
       <c r="S30" s="3" t="s">
         <v>82</v>
       </c>
       <c r="T30" s="9">
+        <v>46152</v>
+      </c>
+      <c r="U30" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="V30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="W30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="X30" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="Z30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD30" s="24" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" ht="165">
+      <c r="A31" s="3" t="str">
+        <f>_xlfn.CONCAT(B31, " ", C31)</f>
+        <v>Ruko 18011 Smart Robot Dog</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="M31" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="N31" s="19">
+        <v>283</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="P31" s="9">
         <v>46150</v>
       </c>
-      <c r="U30" s="9" t="s">
+      <c r="Q31" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="R31" s="11">
+        <v>69.989999999999995</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="T31" s="9">
+        <v>46150</v>
+      </c>
+      <c r="U31" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="V30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X30" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="Z30" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC30" s="24" t="s">
-        <v>219</v>
+      <c r="V31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="W31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="X31" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="Z31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB31" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AD31" s="24" t="s">
+        <v>216</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC30" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC30">
-      <sortCondition ref="A1:A30"/>
+  <autoFilter ref="A1:AD31" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD31">
+      <sortCondition ref="A1:A31"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="10" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="AC17" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
-    <hyperlink ref="AC16" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
+    <hyperlink ref="AD18" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
+    <hyperlink ref="AD17" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
@@ -4103,7 +4263,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -4154,10 +4314,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3587DF7-27DE-4C49-A0D7-210E14A8420B}">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:29" s="3" customFormat="1" ht="409.5">
+    <row r="1" spans="1:30" s="3" customFormat="1" ht="409.5">
       <c r="A1" s="3" t="str">
         <f>_xlfn.CONCAT(B1, " ", C1)</f>
         <v xml:space="preserve"> Enabot EBO Max FamilyBot </v>
@@ -4166,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>63</v>
@@ -4208,7 +4368,7 @@
         <v>46149</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="R1" s="11">
         <v>549</v>
@@ -4236,68 +4396,73 @@
         <v>27</v>
       </c>
       <c r="AC1" s="25" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="12" customFormat="1" ht="75">
-      <c r="A2" s="3" t="str">
-        <f>_xlfn.CONCAT(B2, " ", C2)</f>
-        <v xml:space="preserve"> Elephant Robotics MarsCat </v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="12" t="s">
+    <row r="2" spans="1:30" s="3" customFormat="1" ht="30">
+      <c r="A2" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="12" t="s">
+      <c r="F2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="M2" s="17"/>
-      <c r="N2" s="20"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="14"/>
-      <c r="T2" s="13"/>
-      <c r="U2" s="13"/>
-      <c r="V2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="W2" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="X2" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y2" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="AC2" s="12" t="s">
-        <v>27</v>
+      <c r="H2" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="M2" s="16"/>
+      <c r="N2" s="19"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="21"/>
+      <c r="R2" s="11">
+        <v>89</v>
+      </c>
+      <c r="S2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="Y2" s="4"/>
+      <c r="AD2" s="25" t="s">
+        <v>289</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="12" customFormat="1" ht="15" customHeight="1">
+    <row r="3" spans="1:30" s="12" customFormat="1" ht="75">
       <c r="A3" s="3" t="str">
         <f>_xlfn.CONCAT(B3, " ", C3)</f>
-        <v xml:space="preserve"> Elephant Robotics metaCat </v>
+        <v xml:space="preserve"> Elephant Robotics MarsCat </v>
       </c>
       <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>62</v>
@@ -4306,13 +4471,10 @@
         <v>17</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>21</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>99</v>
       </c>
       <c r="M3" s="17"/>
       <c r="N3" s="20"/>
@@ -4325,13 +4487,13 @@
         <v>26</v>
       </c>
       <c r="W3" s="12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X3" s="12" t="s">
         <v>27</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Z3" s="12" t="s">
         <v>41</v>
@@ -4340,19 +4502,19 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="12" customFormat="1" ht="405">
+    <row r="4" spans="1:30" s="12" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="3" t="str">
         <f>_xlfn.CONCAT(B4, " ", C4)</f>
-        <v xml:space="preserve"> Elephant Robotics metaDog </v>
+        <v xml:space="preserve"> Elephant Robotics metaCat </v>
       </c>
       <c r="B4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>17</v>
@@ -4364,7 +4526,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="20"/>
@@ -4383,7 +4545,7 @@
         <v>27</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z4" s="12" t="s">
         <v>41</v>
@@ -4392,19 +4554,19 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="12" customFormat="1" ht="360">
+    <row r="5" spans="1:30" s="12" customFormat="1" ht="405">
       <c r="A5" s="3" t="str">
         <f>_xlfn.CONCAT(B5, " ", C5)</f>
-        <v xml:space="preserve"> Elephant Robotics metaPanda </v>
+        <v xml:space="preserve"> Elephant Robotics metaDog </v>
       </c>
       <c r="B5" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>17</v>
@@ -4416,7 +4578,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="20"/>
@@ -4435,12 +4597,64 @@
         <v>27</v>
       </c>
       <c r="Y5" s="12" t="s">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="Z5" s="12" t="s">
         <v>41</v>
       </c>
       <c r="AC5" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" s="12" customFormat="1" ht="360">
+      <c r="A6" s="3" t="str">
+        <f>_xlfn.CONCAT(B6, " ", C6)</f>
+        <v xml:space="preserve"> Elephant Robotics metaPanda </v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="M6" s="17"/>
+      <c r="N6" s="20"/>
+      <c r="P6" s="13"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="14"/>
+      <c r="T6" s="13"/>
+      <c r="U6" s="13"/>
+      <c r="V6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="W6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="X6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y6" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="AC6" s="12" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4453,13 +4667,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:U5</xm:sqref>
+          <xm:sqref>U1:U6</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37BE27F9-E75E-4C54-9192-7DED9B8091B0}">
           <x14:formula1>
             <xm:f>Lists!$A$7:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>W1</xm:sqref>
+          <xm:sqref>W1:W2</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE6EB11D-409C-4DFF-B214-8D54CD3EB4C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7FAD10-A9B6-4D8F-BDCE-345C50856A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -950,7 +950,7 @@
     <t>Breathing Calico Percy 2.0- Heartbeat Pur,Voice Robonic Cat – Chongker</t>
   </si>
   <si>
-    <t>/images/products/ Chongker Breathing Calico Percy 2.0</t>
+    <t>/images/products/ Chongker-Breathing-Calico-Percy 2.0.png</t>
   </si>
 </sst>
 </file>
@@ -1700,13 +1700,13 @@
     </row>
     <row r="2" spans="1:30">
       <c r="A2" s="3" t="str">
-        <f>_xlfn.CONCAT(B2, " ", C2)</f>
+        <f t="shared" ref="A2:A7" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="60">
       <c r="A3" s="3" t="str">
-        <f>_xlfn.CONCAT(B3, " ", C3)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1797,7 +1797,7 @@
     </row>
     <row r="4" spans="1:30" ht="75">
       <c r="A4" s="3" t="str">
-        <f>_xlfn.CONCAT(B4, " ", C4)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1888,7 +1888,7 @@
     </row>
     <row r="5" spans="1:30" ht="165">
       <c r="A5" s="3" t="str">
-        <f>_xlfn.CONCAT(B5, " ", C5)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1978,7 +1978,7 @@
     </row>
     <row r="6" spans="1:30" ht="75">
       <c r="A6" s="3" t="str">
-        <f>_xlfn.CONCAT(B6, " ", C6)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
       </c>
       <c r="B6" s="3" t="s">
@@ -2066,7 +2066,7 @@
     </row>
     <row r="7" spans="1:30" ht="60">
       <c r="A7" s="3" t="str">
-        <f>_xlfn.CONCAT(B7, " ", C7)</f>
+        <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2244,7 +2244,7 @@
     </row>
     <row r="9" spans="1:30" ht="60">
       <c r="A9" s="3" t="str">
-        <f>_xlfn.CONCAT(B9, " ", C9)</f>
+        <f t="shared" ref="A9:A31" si="1">_xlfn.CONCAT(B9, " ", C9)</f>
         <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2331,7 +2331,7 @@
     </row>
     <row r="10" spans="1:30" ht="60">
       <c r="A10" s="3" t="str">
-        <f>_xlfn.CONCAT(B10, " ", C10)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2418,7 +2418,7 @@
     </row>
     <row r="11" spans="1:30" ht="60">
       <c r="A11" s="3" t="str">
-        <f>_xlfn.CONCAT(B11, " ", C11)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2505,7 +2505,7 @@
     </row>
     <row r="12" spans="1:30" ht="60" customHeight="1">
       <c r="A12" s="3" t="str">
-        <f>_xlfn.CONCAT(B12, " ", C12)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2592,7 +2592,7 @@
     </row>
     <row r="13" spans="1:30" ht="45.75" thickBot="1">
       <c r="A13" s="3" t="str">
-        <f>_xlfn.CONCAT(B13, " ", C13)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2679,7 +2679,7 @@
     </row>
     <row r="14" spans="1:30" ht="105.75" thickBot="1">
       <c r="A14" s="3" t="str">
-        <f>_xlfn.CONCAT(B14, " ", C14)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2767,7 +2767,7 @@
     </row>
     <row r="15" spans="1:30" ht="105">
       <c r="A15" s="3" t="str">
-        <f>_xlfn.CONCAT(B15, " ", C15)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -2855,7 +2855,7 @@
     </row>
     <row r="16" spans="1:30" ht="60" customHeight="1">
       <c r="A16" s="3" t="str">
-        <f>_xlfn.CONCAT(B16, " ", C16)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2943,7 +2943,7 @@
     </row>
     <row r="17" spans="1:30" ht="60">
       <c r="A17" s="3" t="str">
-        <f>_xlfn.CONCAT(B17, " ", C17)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -3031,7 +3031,7 @@
     </row>
     <row r="18" spans="1:30" ht="60">
       <c r="A18" s="3" t="str">
-        <f>_xlfn.CONCAT(B18, " ", C18)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -3119,7 +3119,7 @@
     </row>
     <row r="19" spans="1:30" ht="74.25" customHeight="1">
       <c r="A19" s="3" t="str">
-        <f>_xlfn.CONCAT(B19, " ", C19)</f>
+        <f t="shared" si="1"/>
         <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
       </c>
       <c r="B19" s="3" t="s">
@@ -3206,7 +3206,7 @@
     </row>
     <row r="20" spans="1:30" ht="150">
       <c r="A20" s="3" t="str">
-        <f>_xlfn.CONCAT(B20, " ", C20)</f>
+        <f t="shared" si="1"/>
         <v>Furby DJ Furby</v>
       </c>
       <c r="B20" s="3" t="s">
@@ -3293,7 +3293,7 @@
     </row>
     <row r="21" spans="1:30" ht="165">
       <c r="A21" s="3" t="str">
-        <f>_xlfn.CONCAT(B21, " ", C21)</f>
+        <f t="shared" si="1"/>
         <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B21" s="3" t="s">
@@ -3377,7 +3377,7 @@
     </row>
     <row r="22" spans="1:30" ht="60">
       <c r="A22" s="3" t="str">
-        <f>_xlfn.CONCAT(B22, " ", C22)</f>
+        <f t="shared" si="1"/>
         <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -3461,7 +3461,7 @@
     </row>
     <row r="23" spans="1:30" ht="60">
       <c r="A23" s="3" t="str">
-        <f>_xlfn.CONCAT(B23, " ", C23)</f>
+        <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Beagle</v>
       </c>
       <c r="B23" s="3" t="s">
@@ -3545,7 +3545,7 @@
     </row>
     <row r="24" spans="1:30" ht="60" customHeight="1">
       <c r="A24" s="3" t="str">
-        <f>_xlfn.CONCAT(B24, " ", C24)</f>
+        <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
       </c>
       <c r="B24" s="3" t="s">
@@ -3629,7 +3629,7 @@
     </row>
     <row r="25" spans="1:30" ht="60" customHeight="1">
       <c r="A25" s="3" t="str">
-        <f>_xlfn.CONCAT(B25, " ", C25)</f>
+        <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B25" s="3" t="s">
@@ -3713,7 +3713,7 @@
     </row>
     <row r="26" spans="1:30" ht="60" customHeight="1">
       <c r="A26" s="3" t="str">
-        <f>_xlfn.CONCAT(B26, " ", C26)</f>
+        <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -3797,7 +3797,7 @@
     </row>
     <row r="27" spans="1:30" ht="60" customHeight="1">
       <c r="A27" s="3" t="str">
-        <f>_xlfn.CONCAT(B27, " ", C27)</f>
+        <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B27" s="3" t="s">
@@ -3881,7 +3881,7 @@
     </row>
     <row r="28" spans="1:30" ht="63.75">
       <c r="A28" s="3" t="str">
-        <f>_xlfn.CONCAT(B28, " ", C28)</f>
+        <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Shih Tzu</v>
       </c>
       <c r="B28" s="3" t="s">
@@ -3965,7 +3965,7 @@
     </row>
     <row r="29" spans="1:30" ht="27.75" customHeight="1">
       <c r="A29" s="3" t="str">
-        <f>_xlfn.CONCAT(B29, " ", C29)</f>
+        <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B29" s="3" t="s">
@@ -4049,7 +4049,7 @@
     </row>
     <row r="30" spans="1:30" ht="150">
       <c r="A30" s="3" t="str">
-        <f>_xlfn.CONCAT(B30, " ", C30)</f>
+        <f t="shared" si="1"/>
         <v>Ropet KAMOMO</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -4136,7 +4136,7 @@
     </row>
     <row r="31" spans="1:30" ht="165">
       <c r="A31" s="3" t="str">
-        <f>_xlfn.CONCAT(B31, " ", C31)</f>
+        <f t="shared" si="1"/>
         <v>Ruko 18011 Smart Robot Dog</v>
       </c>
       <c r="B31" s="3" t="s">
@@ -4399,7 +4399,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="3" customFormat="1" ht="30">
+    <row r="2" spans="1:30" s="3" customFormat="1" ht="210">
       <c r="A2" s="3" t="s">
         <v>288</v>
       </c>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A7FAD10-A9B6-4D8F-BDCE-345C50856A26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E3335A-A755-424E-B2D0-D195CC0003EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -950,7 +950,7 @@
     <t>Breathing Calico Percy 2.0- Heartbeat Pur,Voice Robonic Cat – Chongker</t>
   </si>
   <si>
-    <t>/images/products/ Chongker-Breathing-Calico-Percy 2.0.png</t>
+    <t>/images/products/ Chongker-Breathing-Calico-Percy-2.0.png</t>
   </si>
 </sst>
 </file>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E3335A-A755-424E-B2D0-D195CC0003EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2FEB04-B9E7-4AC6-B268-FF3E74785781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -950,7 +950,7 @@
     <t>Breathing Calico Percy 2.0- Heartbeat Pur,Voice Robonic Cat – Chongker</t>
   </si>
   <si>
-    <t>/images/products/ Chongker-Breathing-Calico-Percy-2.0.png</t>
+    <t>/images/products/Chongker-Breathing-Calico-Percy-2.0.png</t>
   </si>
 </sst>
 </file>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F2FEB04-B9E7-4AC6-B268-FF3E74785781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BFECC5-A4C0-4A6A-8C1C-88541C5DCBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -494,9 +494,6 @@
     <t>Touch sensor responses</t>
   </si>
   <si>
-    <t>children</t>
-  </si>
-  <si>
     <t>Ropet KAMOMO AI Robot Pet is an interactive AI robot pet with lifelike emotions, touch response, and voice interaction. Designed for companionship, stress relief, and family fun, it reacts to attention and creates engaging daily interactions.</t>
   </si>
   <si>
@@ -665,9 +662,6 @@
     <t>1) Paste using "Pastes Special" then " Text".</t>
   </si>
   <si>
-    <t>https://ropetai.com/products/ropet%E2%84%A2-ai-comfort-companion-plush-robot</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/Perfect-Petzzz-Realistic-Battery-Operated-Interactive/dp/B002PJ37XG/ref=sr_1_2_sspa?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1778523937&amp;sprefix=perfect+petzzz%2Caps%2C211&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
   </si>
   <si>
@@ -951,6 +945,12 @@
   </si>
   <si>
     <t>/images/products/Chongker-Breathing-Calico-Percy-2.0.png</t>
+  </si>
+  <si>
+    <t>https://ropetai.com/products/ropet%E2%84%A2-ai-comfort-companion-plush-robot?ref=bbtrkjsp</t>
+  </si>
+  <si>
+    <t>Ropetai.com</t>
   </si>
 </sst>
 </file>
@@ -1608,7 +1608,7 @@
   <sheetData>
     <row r="1" spans="1:30" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>15</v>
@@ -1668,7 +1668,7 @@
         <v>77</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>24</v>
@@ -1689,13 +1689,13 @@
         <v>31</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AC1" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AD1" s="23" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -1749,13 +1749,13 @@
         <v>2</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P3" s="9">
         <v>46153</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="R3" s="11">
         <v>119</v>
@@ -1767,7 +1767,7 @@
         <v>46150</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>26</v>
@@ -1792,7 +1792,7 @@
         <v>26</v>
       </c>
       <c r="AD3" s="24" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="75">
@@ -1840,13 +1840,13 @@
         <v>2</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P4" s="9">
         <v>46153</v>
       </c>
       <c r="Q4" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R4" s="11">
         <v>149</v>
@@ -1858,7 +1858,7 @@
         <v>46150</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>26</v>
@@ -1867,7 +1867,7 @@
         <v>27</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="3" t="s">
@@ -1883,7 +1883,7 @@
         <v>26</v>
       </c>
       <c r="AD4" s="25" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="165">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>116</v>
@@ -1937,7 +1937,7 @@
         <v>46153</v>
       </c>
       <c r="Q5" s="21" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="R5" s="11">
         <v>178</v>
@@ -1949,7 +1949,7 @@
         <v>46150</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>26</v>
@@ -1958,7 +1958,7 @@
         <v>26</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>27</v>
@@ -1973,7 +1973,7 @@
         <v>26</v>
       </c>
       <c r="AD5" s="25" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="75">
@@ -1985,7 +1985,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>65</v>
@@ -2024,7 +2024,7 @@
         <v>46153</v>
       </c>
       <c r="Q6" s="21" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="R6" s="11">
         <v>89</v>
@@ -2045,7 +2045,7 @@
         <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="3" t="s">
@@ -2061,7 +2061,7 @@
         <v>26</v>
       </c>
       <c r="AD6" s="24" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="60">
@@ -2109,13 +2109,13 @@
         <v>16</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P7" s="9">
         <v>46153</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="R7" s="11">
         <v>89</v>
@@ -2152,18 +2152,18 @@
         <v>26</v>
       </c>
       <c r="AD7" s="25" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="45">
       <c r="A8" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>62</v>
@@ -2178,16 +2178,16 @@
         <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M8" s="16">
         <v>5</v>
@@ -2196,13 +2196,13 @@
         <v>10</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="P8" s="9">
         <v>46161</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="R8" s="11">
         <v>109</v>
@@ -2214,7 +2214,7 @@
         <v>46161</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>26</v>
@@ -2223,7 +2223,7 @@
         <v>26</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="Y8" s="4"/>
       <c r="Z8" s="3" t="s">
@@ -2239,7 +2239,7 @@
         <v>26</v>
       </c>
       <c r="AD8" s="25" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="60">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>63</v>
@@ -2266,7 +2266,7 @@
         <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>81</v>
@@ -2293,7 +2293,7 @@
         <v>46149</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="R9" s="11">
         <v>179</v>
@@ -2305,7 +2305,7 @@
         <v>46152</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>26</v>
@@ -2314,7 +2314,7 @@
         <v>26</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>26</v>
@@ -2326,7 +2326,7 @@
         <v>27</v>
       </c>
       <c r="AD9" s="25" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="60">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>63</v>
@@ -2353,7 +2353,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>78</v>
@@ -2380,7 +2380,7 @@
         <v>46149</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="R10" s="11">
         <v>359</v>
@@ -2401,7 +2401,7 @@
         <v>26</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>26</v>
@@ -2413,7 +2413,7 @@
         <v>27</v>
       </c>
       <c r="AD10" s="25" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="60">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>63</v>
@@ -2440,7 +2440,7 @@
         <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>92</v>
@@ -2467,7 +2467,7 @@
         <v>46149</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="R11" s="11">
         <v>279</v>
@@ -2488,7 +2488,7 @@
         <v>27</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>26</v>
@@ -2500,7 +2500,7 @@
         <v>27</v>
       </c>
       <c r="AD11" s="25" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="60" customHeight="1">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>63</v>
@@ -2527,7 +2527,7 @@
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>80</v>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="R12" s="11">
         <v>789</v>
@@ -2575,7 +2575,7 @@
         <v>27</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>26</v>
@@ -2587,7 +2587,7 @@
         <v>27</v>
       </c>
       <c r="AD12" s="25" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="45.75" thickBot="1">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>63</v>
@@ -2614,7 +2614,7 @@
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>95</v>
@@ -2641,7 +2641,7 @@
         <v>46149</v>
       </c>
       <c r="Q13" s="21" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="R13" s="11">
         <v>139</v>
@@ -2653,7 +2653,7 @@
         <v>46153</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>26</v>
@@ -2662,7 +2662,7 @@
         <v>27</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>26</v>
@@ -2674,7 +2674,7 @@
         <v>27</v>
       </c>
       <c r="AD13" s="25" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="105.75" thickBot="1">
@@ -2728,7 +2728,7 @@
         <v>46153</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="R14" s="11">
         <v>159.99</v>
@@ -2740,7 +2740,7 @@
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>26</v>
@@ -2762,7 +2762,7 @@
         <v>27</v>
       </c>
       <c r="AD14" s="24" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="105">
@@ -2816,7 +2816,7 @@
         <v>46153</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="R15" s="11">
         <v>159.99</v>
@@ -2828,7 +2828,7 @@
         <v>46150</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>26</v>
@@ -2850,7 +2850,7 @@
         <v>27</v>
       </c>
       <c r="AD15" s="26" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="60" customHeight="1">
@@ -2904,7 +2904,7 @@
         <v>46150</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="R16" s="11">
         <v>159.99</v>
@@ -2916,7 +2916,7 @@
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>26</v>
@@ -2938,7 +2938,7 @@
         <v>27</v>
       </c>
       <c r="AD16" s="25" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="60">
@@ -2992,7 +2992,7 @@
         <v>46150</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="R17" s="11">
         <v>179</v>
@@ -3004,7 +3004,7 @@
         <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>26</v>
@@ -3013,7 +3013,7 @@
         <v>27</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="3" t="s">
@@ -3026,7 +3026,7 @@
         <v>27</v>
       </c>
       <c r="AD17" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="60">
@@ -3080,7 +3080,7 @@
         <v>46153</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="R18" s="11">
         <v>179</v>
@@ -3092,7 +3092,7 @@
         <v>46150</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>26</v>
@@ -3101,7 +3101,7 @@
         <v>26</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="Y18" s="4"/>
       <c r="Z18" s="3" t="s">
@@ -3114,7 +3114,7 @@
         <v>27</v>
       </c>
       <c r="AD18" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="74.25" customHeight="1">
@@ -3153,7 +3153,7 @@
         <v>147</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="M19" s="16">
         <v>3</v>
@@ -3168,7 +3168,7 @@
         <v>46151</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="R19" s="11">
         <v>25.99</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>27</v>
@@ -3201,7 +3201,7 @@
         <v>27</v>
       </c>
       <c r="AD19" s="24" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="150">
@@ -3213,7 +3213,7 @@
         <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>63</v>
@@ -3228,19 +3228,19 @@
         <v>22</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="M20" s="16">
         <v>4.8</v>
@@ -3255,7 +3255,7 @@
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="R20" s="11">
         <v>50.11</v>
@@ -3276,7 +3276,7 @@
         <v>26</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>27</v>
@@ -3285,10 +3285,10 @@
         <v>27</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AD20" s="24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="165">
@@ -3315,16 +3315,16 @@
         <v>22</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="M21" s="16">
         <v>4.2</v>
@@ -3339,7 +3339,7 @@
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="R21" s="11">
         <v>499</v>
@@ -3360,7 +3360,7 @@
         <v>26</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>26</v>
@@ -3369,10 +3369,10 @@
         <v>26</v>
       </c>
       <c r="AB21" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="AD21" s="24" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="60">
@@ -3384,7 +3384,7 @@
         <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>62</v>
@@ -3399,19 +3399,19 @@
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="L22" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M22" s="16">
         <v>4.3</v>
@@ -3426,7 +3426,7 @@
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
@@ -3447,7 +3447,7 @@
         <v>27</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>27</v>
@@ -3456,7 +3456,7 @@
         <v>27</v>
       </c>
       <c r="AD22" s="24" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="60">
@@ -3468,7 +3468,7 @@
         <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>65</v>
@@ -3483,19 +3483,19 @@
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K23" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M23" s="16">
         <v>4.4000000000000004</v>
@@ -3510,7 +3510,7 @@
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
@@ -3540,7 +3540,7 @@
         <v>27</v>
       </c>
       <c r="AD23" s="24" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="60" customHeight="1">
@@ -3552,7 +3552,7 @@
         <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>62</v>
@@ -3567,19 +3567,19 @@
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="L24" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M24" s="16">
         <v>4.4000000000000004</v>
@@ -3594,7 +3594,7 @@
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
@@ -3615,7 +3615,7 @@
         <v>26</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>27</v>
@@ -3624,7 +3624,7 @@
         <v>27</v>
       </c>
       <c r="AD24" s="24" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="60" customHeight="1">
@@ -3636,7 +3636,7 @@
         <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>65</v>
@@ -3651,19 +3651,19 @@
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="K25" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M25" s="16">
         <v>4.3</v>
@@ -3678,7 +3678,7 @@
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="R25" s="11">
         <v>44.45</v>
@@ -3708,7 +3708,7 @@
         <v>27</v>
       </c>
       <c r="AD25" s="24" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="60" customHeight="1">
@@ -3720,7 +3720,7 @@
         <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>65</v>
@@ -3735,19 +3735,19 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J26" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>156</v>
-      </c>
       <c r="L26" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M26" s="16">
         <v>4.3</v>
@@ -3762,7 +3762,7 @@
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="R26" s="11">
         <v>44.45</v>
@@ -3792,7 +3792,7 @@
         <v>27</v>
       </c>
       <c r="AD26" s="24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="60" customHeight="1">
@@ -3804,7 +3804,7 @@
         <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>62</v>
@@ -3819,19 +3819,19 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M27" s="16">
         <v>4</v>
@@ -3846,7 +3846,7 @@
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="R27" s="11">
         <v>53.9</v>
@@ -3876,7 +3876,7 @@
         <v>27</v>
       </c>
       <c r="AD27" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="63.75">
@@ -3888,7 +3888,7 @@
         <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>65</v>
@@ -3903,19 +3903,19 @@
         <v>23</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M28" s="16">
         <v>4.2</v>
@@ -3930,7 +3930,7 @@
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="R28" s="11">
         <v>44.45</v>
@@ -3960,7 +3960,7 @@
         <v>27</v>
       </c>
       <c r="AD28" s="24" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="27.75" customHeight="1">
@@ -3972,7 +3972,7 @@
         <v>39</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>62</v>
@@ -3987,19 +3987,19 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="M29" s="16">
         <v>4.0999999999999996</v>
@@ -4014,7 +4014,7 @@
         <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="R29" s="11">
         <v>53.9</v>
@@ -4044,7 +4044,7 @@
         <v>27</v>
       </c>
       <c r="AD29" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="150">
@@ -4065,25 +4065,25 @@
         <v>17</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>149</v>
+        <v>21</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I30" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>151</v>
-      </c>
       <c r="K30" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="M30" s="16">
         <v>4.3</v>
@@ -4098,16 +4098,16 @@
         <v>46152</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="R30" s="11">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>82</v>
+        <v>301</v>
       </c>
       <c r="T30" s="9">
-        <v>46152</v>
+        <v>46163</v>
       </c>
       <c r="U30" s="9" t="s">
         <v>25</v>
@@ -4119,7 +4119,7 @@
         <v>26</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Z30" s="3" t="s">
         <v>26</v>
@@ -4131,7 +4131,7 @@
         <v>26</v>
       </c>
       <c r="AD30" s="24" t="s">
-        <v>206</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="165">
@@ -4158,19 +4158,19 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="K31" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="L31" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>177</v>
       </c>
       <c r="M31" s="16">
         <v>4.4000000000000004</v>
@@ -4185,7 +4185,7 @@
         <v>46150</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="R31" s="11">
         <v>69.989999999999995</v>
@@ -4206,7 +4206,7 @@
         <v>26</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>27</v>
@@ -4215,7 +4215,7 @@
         <v>26</v>
       </c>
       <c r="AD31" s="24" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
   </sheetData>
@@ -4263,7 +4263,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -4289,7 +4289,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>63</v>
@@ -4341,7 +4341,7 @@
         <v>22</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>80</v>
@@ -4368,7 +4368,7 @@
         <v>46149</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="R1" s="11">
         <v>549</v>
@@ -4396,18 +4396,18 @@
         <v>27</v>
       </c>
       <c r="AC1" s="25" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="2" spans="1:30" s="3" customFormat="1" ht="210">
       <c r="A2" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>62</v>
@@ -4422,13 +4422,13 @@
         <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>298</v>
-      </c>
       <c r="J2" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>130</v>
@@ -4450,7 +4450,7 @@
       <c r="U2" s="9"/>
       <c r="Y2" s="4"/>
       <c r="AD2" s="25" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" spans="1:30" s="12" customFormat="1" ht="75">

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3BFECC5-A4C0-4A6A-8C1C-88541C5DCBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB0F4C6-9151-43C1-BDE6-79AC237B7DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -2311,7 +2311,7 @@
         <v>26</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X9" s="2" t="s">
         <v>259</v>
@@ -4062,13 +4062,13 @@
         <v>63</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>149</v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EB0F4C6-9151-43C1-BDE6-79AC237B7DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549E81D9-020E-47FB-A291-9FD1612FFE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -698,24 +698,9 @@
     <t>https://www.amazon.com/Loona-ChatGPT-4o-AI-Powered-Interaction-Monitoring/dp/B0DCF53PCH/ref=sr_1_1_sspa?crid=2DBOX8S0Q2AR6&amp;dib=eyJ2IjoiMSJ9.fRTz6IKj5O3hiZ4V3RbIiqzYkMvGWX1yxIfmBNQ2bPG8a8X70ewO_kByz-KXp50JfmUuJx9rrIjkexZxX4nWSVxWP_bUrHWGWHPfZnhgH5GMVf6Rltx3FiivEWa9A_74tX_ykUsCTRmHEZ_IwI-5pdDeOvDpmzf07kmD73czlJ5S56lz7gAFPcJ9cgVfwD2yW0a7rgFB4N8XbcF4FmsoLN4nTZhHdGzE2qW01-CozMdL5maZB9Wotwoz672FPyl4IOivur7Z3Gj71yWxlpzykJORSvNzc5nhys8YwW1Zl90.csUcqcC85C04azO69LCOq0bdtEXSzk6YfX_vospSKeE&amp;dib_tag=se&amp;keywords=loona%2Brobot%2Bdog&amp;qid=1778524541&amp;sprefix=loona%2Caps%2C177&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
   </si>
   <si>
-    <t>https://www.enabot.com/home-robot/ebo-x</t>
-  </si>
-  <si>
     <t>https://www.enabot.com/home-robot/ebo-max</t>
   </si>
   <si>
-    <t>https://www.enabot.com/home-robot/ebo-air-2-plus</t>
-  </si>
-  <si>
-    <t>https://www.enabot.com/home-robot/ebo-air-2s</t>
-  </si>
-  <si>
-    <t>https://www.enabot.com/home-robot/ebo-air-2</t>
-  </si>
-  <si>
-    <t>https://www.enabot.com/pet-robot/rola-mini</t>
-  </si>
-  <si>
     <t>EBO X FamilyBot</t>
   </si>
   <si>
@@ -951,6 +936,21 @@
   </si>
   <si>
     <t>Ropetai.com</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-air-2?ref=sgpedoaa</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-air-2-plus?ref=sgpedoaa</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-air-2s?ref=sgpedoaa</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/home-robot/ebo-x?ref=sgpedoaa</t>
+  </si>
+  <si>
+    <t>https://www.enabot.com/pet-robot/rola-mini?ref=sgpedoaa</t>
   </si>
 </sst>
 </file>
@@ -1689,10 +1689,10 @@
         <v>31</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="AC1" s="6" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AD1" s="23" t="s">
         <v>196</v>
@@ -1749,13 +1749,13 @@
         <v>2</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P3" s="9">
         <v>46153</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="R3" s="11">
         <v>119</v>
@@ -1792,7 +1792,7 @@
         <v>26</v>
       </c>
       <c r="AD3" s="24" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="75">
@@ -1840,7 +1840,7 @@
         <v>2</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P4" s="9">
         <v>46153</v>
@@ -1867,7 +1867,7 @@
         <v>27</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="3" t="s">
@@ -1883,7 +1883,7 @@
         <v>26</v>
       </c>
       <c r="AD4" s="25" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="165">
@@ -1937,7 +1937,7 @@
         <v>46153</v>
       </c>
       <c r="Q5" s="21" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="R5" s="11">
         <v>178</v>
@@ -1958,7 +1958,7 @@
         <v>26</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>27</v>
@@ -1973,7 +1973,7 @@
         <v>26</v>
       </c>
       <c r="AD5" s="25" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="75">
@@ -1985,7 +1985,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>65</v>
@@ -2024,7 +2024,7 @@
         <v>46153</v>
       </c>
       <c r="Q6" s="21" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="R6" s="11">
         <v>89</v>
@@ -2045,7 +2045,7 @@
         <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="3" t="s">
@@ -2061,7 +2061,7 @@
         <v>26</v>
       </c>
       <c r="AD6" s="24" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="60">
@@ -2109,7 +2109,7 @@
         <v>16</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P7" s="9">
         <v>46153</v>
@@ -2152,18 +2152,18 @@
         <v>26</v>
       </c>
       <c r="AD7" s="25" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="45">
       <c r="A8" s="3" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>62</v>
@@ -2178,16 +2178,16 @@
         <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>154</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="M8" s="16">
         <v>5</v>
@@ -2196,13 +2196,13 @@
         <v>10</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="P8" s="9">
         <v>46161</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="R8" s="11">
         <v>109</v>
@@ -2223,7 +2223,7 @@
         <v>26</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Y8" s="4"/>
       <c r="Z8" s="3" t="s">
@@ -2239,7 +2239,7 @@
         <v>26</v>
       </c>
       <c r="AD8" s="25" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="60">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>63</v>
@@ -2266,7 +2266,7 @@
         <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>81</v>
@@ -2293,7 +2293,7 @@
         <v>46149</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="R9" s="11">
         <v>179</v>
@@ -2314,7 +2314,7 @@
         <v>27</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>26</v>
@@ -2326,7 +2326,7 @@
         <v>27</v>
       </c>
       <c r="AD9" s="25" t="s">
-        <v>221</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="60">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>63</v>
@@ -2353,7 +2353,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>78</v>
@@ -2380,7 +2380,7 @@
         <v>46149</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="R10" s="11">
         <v>359</v>
@@ -2401,7 +2401,7 @@
         <v>26</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>26</v>
@@ -2413,7 +2413,7 @@
         <v>27</v>
       </c>
       <c r="AD10" s="25" t="s">
-        <v>219</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="60">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>63</v>
@@ -2440,7 +2440,7 @@
         <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>92</v>
@@ -2467,7 +2467,7 @@
         <v>46149</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="R11" s="11">
         <v>279</v>
@@ -2488,7 +2488,7 @@
         <v>27</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>26</v>
@@ -2500,7 +2500,7 @@
         <v>27</v>
       </c>
       <c r="AD11" s="25" t="s">
-        <v>220</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="60" customHeight="1">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>63</v>
@@ -2527,7 +2527,7 @@
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>80</v>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R12" s="11">
         <v>789</v>
@@ -2575,7 +2575,7 @@
         <v>27</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>26</v>
@@ -2587,7 +2587,7 @@
         <v>27</v>
       </c>
       <c r="AD12" s="25" t="s">
-        <v>217</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="45.75" thickBot="1">
@@ -2614,7 +2614,7 @@
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>95</v>
@@ -2641,7 +2641,7 @@
         <v>46149</v>
       </c>
       <c r="Q13" s="21" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="R13" s="11">
         <v>139</v>
@@ -2662,7 +2662,7 @@
         <v>27</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>26</v>
@@ -2674,7 +2674,7 @@
         <v>27</v>
       </c>
       <c r="AD13" s="25" t="s">
-        <v>222</v>
+        <v>301</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="105.75" thickBot="1">
@@ -2728,7 +2728,7 @@
         <v>46153</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="R14" s="11">
         <v>159.99</v>
@@ -2816,7 +2816,7 @@
         <v>46153</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="R15" s="11">
         <v>159.99</v>
@@ -2904,7 +2904,7 @@
         <v>46150</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R16" s="11">
         <v>159.99</v>
@@ -2992,7 +2992,7 @@
         <v>46150</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="R17" s="11">
         <v>179</v>
@@ -3013,7 +3013,7 @@
         <v>27</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="3" t="s">
@@ -3080,7 +3080,7 @@
         <v>46153</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="R18" s="11">
         <v>179</v>
@@ -3101,7 +3101,7 @@
         <v>26</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="Y18" s="4"/>
       <c r="Z18" s="3" t="s">
@@ -3168,7 +3168,7 @@
         <v>46151</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="R19" s="11">
         <v>25.99</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>27</v>
@@ -3255,7 +3255,7 @@
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="R20" s="11">
         <v>50.11</v>
@@ -3276,7 +3276,7 @@
         <v>26</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>27</v>
@@ -3285,7 +3285,7 @@
         <v>27</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AD20" s="24" t="s">
         <v>215</v>
@@ -3339,7 +3339,7 @@
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="R21" s="11">
         <v>499</v>
@@ -3360,7 +3360,7 @@
         <v>26</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>26</v>
@@ -3369,7 +3369,7 @@
         <v>26</v>
       </c>
       <c r="AB21" s="3" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="AD21" s="24" t="s">
         <v>216</v>
@@ -3426,7 +3426,7 @@
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
@@ -3447,7 +3447,7 @@
         <v>27</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>27</v>
@@ -3510,7 +3510,7 @@
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
@@ -3594,7 +3594,7 @@
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
@@ -3615,7 +3615,7 @@
         <v>26</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>27</v>
@@ -3678,7 +3678,7 @@
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="R25" s="11">
         <v>44.45</v>
@@ -3762,7 +3762,7 @@
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="R26" s="11">
         <v>44.45</v>
@@ -3846,7 +3846,7 @@
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="R27" s="11">
         <v>53.9</v>
@@ -3930,7 +3930,7 @@
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="R28" s="11">
         <v>44.45</v>
@@ -4014,7 +4014,7 @@
         <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="R29" s="11">
         <v>53.9</v>
@@ -4098,13 +4098,13 @@
         <v>46152</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="R30" s="11">
         <v>349</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="T30" s="9">
         <v>46163</v>
@@ -4119,7 +4119,7 @@
         <v>26</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="Z30" s="3" t="s">
         <v>26</v>
@@ -4131,7 +4131,7 @@
         <v>26</v>
       </c>
       <c r="AD30" s="24" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="165">
@@ -4185,7 +4185,7 @@
         <v>46150</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="R31" s="11">
         <v>69.989999999999995</v>
@@ -4206,7 +4206,7 @@
         <v>26</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>27</v>
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>63</v>
@@ -4368,7 +4368,7 @@
         <v>46149</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R1" s="11">
         <v>549</v>
@@ -4396,18 +4396,18 @@
         <v>27</v>
       </c>
       <c r="AC1" s="25" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:30" s="3" customFormat="1" ht="210">
       <c r="A2" s="3" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>62</v>
@@ -4422,13 +4422,13 @@
         <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>130</v>
@@ -4450,7 +4450,7 @@
       <c r="U2" s="9"/>
       <c r="Y2" s="4"/>
       <c r="AD2" s="25" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:30" s="12" customFormat="1" ht="75">

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549E81D9-020E-47FB-A291-9FD1612FFE7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A0CE0D-01B2-4BCB-804A-B44E9ADF8B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A0CE0D-01B2-4BCB-804A-B44E9ADF8B1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC048D9D-CABC-413E-9BDB-5248AB830697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Matrix" sheetId="1" r:id="rId1"/>
@@ -548,9 +548,6 @@
     <t>Very affordable</t>
   </si>
   <si>
-    <t>Perfect Petzzz Original Calico Cat is a lifelike breathing plush cat with soft fur and realistic sleeping motions. Provides calming companionship for seniors, children, and cat lovers without the care and upkeep of a live pet.</t>
-  </si>
-  <si>
     <t>Perfect Petzzz Original Beagle is a lifelike breathing plush dog with soft fur, realistic sleeping motions, and calming companionship. Ideal for seniors, children, and pet lovers seeking comfort without the care of a live pet.</t>
   </si>
   <si>
@@ -917,9 +914,6 @@
     <t>Has voice, purring, and heartbeat. Brings a calming presence wherever it goes.</t>
   </si>
   <si>
-    <t>Fully interactive breathing, purring and meowing cat. Just like the real thing without the care and respnsilities of a real pet</t>
-  </si>
-  <si>
     <t>Hearrtbeat</t>
   </si>
   <si>
@@ -951,6 +945,12 @@
   </si>
   <si>
     <t>https://www.enabot.com/pet-robot/rola-mini?ref=sgpedoaa</t>
+  </si>
+  <si>
+    <t>Fully interactive breathing, purring and meowing cat. Just like the real thing without the care and responsibilities of a real pet.</t>
+  </si>
+  <si>
+    <t>Perfect Petzzz Grey Tabby Cat is a lifelike breathing plush cat with soft fur and realistic sleeping motions. Provides calming companionship for seniors, children, and cat lovers without the care and upkeep of a live pet.</t>
   </si>
 </sst>
 </file>
@@ -1608,7 +1608,7 @@
   <sheetData>
     <row r="1" spans="1:30" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>15</v>
@@ -1668,7 +1668,7 @@
         <v>77</v>
       </c>
       <c r="U1" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>24</v>
@@ -1689,13 +1689,13 @@
         <v>31</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AC1" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AD1" s="23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:30">
@@ -1749,13 +1749,13 @@
         <v>2</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P3" s="9">
         <v>46153</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R3" s="11">
         <v>119</v>
@@ -1767,7 +1767,7 @@
         <v>46150</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>26</v>
@@ -1792,7 +1792,7 @@
         <v>26</v>
       </c>
       <c r="AD3" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="75">
@@ -1840,13 +1840,13 @@
         <v>2</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P4" s="9">
         <v>46153</v>
       </c>
       <c r="Q4" s="21" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="R4" s="11">
         <v>149</v>
@@ -1858,7 +1858,7 @@
         <v>46150</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>26</v>
@@ -1867,7 +1867,7 @@
         <v>27</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="3" t="s">
@@ -1883,7 +1883,7 @@
         <v>26</v>
       </c>
       <c r="AD4" s="25" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="165">
@@ -1910,7 +1910,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I5" s="3" t="s">
         <v>116</v>
@@ -1937,7 +1937,7 @@
         <v>46153</v>
       </c>
       <c r="Q5" s="21" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="R5" s="11">
         <v>178</v>
@@ -1949,7 +1949,7 @@
         <v>46150</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>26</v>
@@ -1958,7 +1958,7 @@
         <v>26</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>27</v>
@@ -1973,7 +1973,7 @@
         <v>26</v>
       </c>
       <c r="AD5" s="25" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="75">
@@ -1985,7 +1985,7 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>65</v>
@@ -2024,7 +2024,7 @@
         <v>46153</v>
       </c>
       <c r="Q6" s="21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="11">
         <v>89</v>
@@ -2045,7 +2045,7 @@
         <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="3" t="s">
@@ -2061,7 +2061,7 @@
         <v>26</v>
       </c>
       <c r="AD6" s="24" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="60">
@@ -2109,13 +2109,13 @@
         <v>16</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P7" s="9">
         <v>46153</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="R7" s="11">
         <v>89</v>
@@ -2152,18 +2152,18 @@
         <v>26</v>
       </c>
       <c r="AD7" s="25" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="45">
       <c r="A8" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>62</v>
@@ -2178,16 +2178,16 @@
         <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>154</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="M8" s="16">
         <v>5</v>
@@ -2196,13 +2196,13 @@
         <v>10</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="P8" s="9">
         <v>46161</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="R8" s="11">
         <v>109</v>
@@ -2214,7 +2214,7 @@
         <v>46161</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>26</v>
@@ -2223,7 +2223,7 @@
         <v>26</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="Y8" s="4"/>
       <c r="Z8" s="3" t="s">
@@ -2239,7 +2239,7 @@
         <v>26</v>
       </c>
       <c r="AD8" s="25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="60">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>63</v>
@@ -2266,7 +2266,7 @@
         <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>81</v>
@@ -2293,7 +2293,7 @@
         <v>46149</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="R9" s="11">
         <v>179</v>
@@ -2305,7 +2305,7 @@
         <v>46152</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>26</v>
@@ -2314,7 +2314,7 @@
         <v>27</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>26</v>
@@ -2326,7 +2326,7 @@
         <v>27</v>
       </c>
       <c r="AD9" s="25" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="60">
@@ -2338,7 +2338,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>63</v>
@@ -2353,7 +2353,7 @@
         <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>78</v>
@@ -2380,7 +2380,7 @@
         <v>46149</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="R10" s="11">
         <v>359</v>
@@ -2401,7 +2401,7 @@
         <v>26</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>26</v>
@@ -2413,7 +2413,7 @@
         <v>27</v>
       </c>
       <c r="AD10" s="25" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="60">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>63</v>
@@ -2440,7 +2440,7 @@
         <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>92</v>
@@ -2467,7 +2467,7 @@
         <v>46149</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="R11" s="11">
         <v>279</v>
@@ -2488,7 +2488,7 @@
         <v>27</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>26</v>
@@ -2500,7 +2500,7 @@
         <v>27</v>
       </c>
       <c r="AD11" s="25" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="60" customHeight="1">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>63</v>
@@ -2527,7 +2527,7 @@
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I12" s="3" t="s">
         <v>80</v>
@@ -2554,7 +2554,7 @@
         <v>46149</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R12" s="11">
         <v>789</v>
@@ -2575,7 +2575,7 @@
         <v>27</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>26</v>
@@ -2587,7 +2587,7 @@
         <v>27</v>
       </c>
       <c r="AD12" s="25" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="45.75" thickBot="1">
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>63</v>
@@ -2614,7 +2614,7 @@
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I13" s="3" t="s">
         <v>95</v>
@@ -2641,7 +2641,7 @@
         <v>46149</v>
       </c>
       <c r="Q13" s="21" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R13" s="11">
         <v>139</v>
@@ -2653,7 +2653,7 @@
         <v>46153</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>26</v>
@@ -2662,7 +2662,7 @@
         <v>27</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>26</v>
@@ -2674,7 +2674,7 @@
         <v>27</v>
       </c>
       <c r="AD13" s="25" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="105.75" thickBot="1">
@@ -2728,7 +2728,7 @@
         <v>46153</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="R14" s="11">
         <v>159.99</v>
@@ -2740,7 +2740,7 @@
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>26</v>
@@ -2762,7 +2762,7 @@
         <v>27</v>
       </c>
       <c r="AD14" s="24" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="105">
@@ -2816,7 +2816,7 @@
         <v>46153</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="R15" s="11">
         <v>159.99</v>
@@ -2828,7 +2828,7 @@
         <v>46150</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>26</v>
@@ -2850,7 +2850,7 @@
         <v>27</v>
       </c>
       <c r="AD15" s="26" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="60" customHeight="1">
@@ -2904,7 +2904,7 @@
         <v>46150</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="R16" s="11">
         <v>159.99</v>
@@ -2916,7 +2916,7 @@
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>26</v>
@@ -2938,7 +2938,7 @@
         <v>27</v>
       </c>
       <c r="AD16" s="25" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="60">
@@ -2992,7 +2992,7 @@
         <v>46150</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R17" s="11">
         <v>179</v>
@@ -3004,7 +3004,7 @@
         <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>26</v>
@@ -3013,7 +3013,7 @@
         <v>27</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="3" t="s">
@@ -3026,7 +3026,7 @@
         <v>27</v>
       </c>
       <c r="AD17" s="26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="60">
@@ -3080,7 +3080,7 @@
         <v>46153</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R18" s="11">
         <v>179</v>
@@ -3092,7 +3092,7 @@
         <v>46150</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>26</v>
@@ -3101,7 +3101,7 @@
         <v>26</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="Y18" s="4"/>
       <c r="Z18" s="3" t="s">
@@ -3114,7 +3114,7 @@
         <v>27</v>
       </c>
       <c r="AD18" s="26" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="74.25" customHeight="1">
@@ -3168,7 +3168,7 @@
         <v>46151</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="R19" s="11">
         <v>25.99</v>
@@ -3189,7 +3189,7 @@
         <v>27</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>27</v>
@@ -3201,7 +3201,7 @@
         <v>27</v>
       </c>
       <c r="AD19" s="24" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="150">
@@ -3213,7 +3213,7 @@
         <v>52</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>63</v>
@@ -3228,19 +3228,19 @@
         <v>22</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M20" s="16">
         <v>4.8</v>
@@ -3255,7 +3255,7 @@
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R20" s="11">
         <v>50.11</v>
@@ -3276,7 +3276,7 @@
         <v>26</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>27</v>
@@ -3285,10 +3285,10 @@
         <v>27</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AD20" s="24" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="165">
@@ -3315,16 +3315,16 @@
         <v>22</v>
       </c>
       <c r="H21" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="M21" s="16">
         <v>4.2</v>
@@ -3339,7 +3339,7 @@
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="R21" s="11">
         <v>499</v>
@@ -3360,7 +3360,7 @@
         <v>26</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>26</v>
@@ -3369,10 +3369,10 @@
         <v>26</v>
       </c>
       <c r="AB21" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AD21" s="24" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="60">
@@ -3384,7 +3384,7 @@
         <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>62</v>
@@ -3399,7 +3399,7 @@
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>167</v>
+        <v>301</v>
       </c>
       <c r="I22" s="3" t="s">
         <v>166</v>
@@ -3411,7 +3411,7 @@
         <v>155</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M22" s="16">
         <v>4.3</v>
@@ -3426,7 +3426,7 @@
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
@@ -3447,7 +3447,7 @@
         <v>27</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>27</v>
@@ -3456,7 +3456,7 @@
         <v>27</v>
       </c>
       <c r="AD22" s="24" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="23" spans="1:30" ht="60">
@@ -3483,7 +3483,7 @@
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I23" s="3" t="s">
         <v>154</v>
@@ -3495,7 +3495,7 @@
         <v>166</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M23" s="16">
         <v>4.4000000000000004</v>
@@ -3510,7 +3510,7 @@
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
@@ -3540,7 +3540,7 @@
         <v>27</v>
       </c>
       <c r="AD23" s="24" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="60" customHeight="1">
@@ -3567,7 +3567,7 @@
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>166</v>
@@ -3579,7 +3579,7 @@
         <v>155</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M24" s="16">
         <v>4.4000000000000004</v>
@@ -3594,7 +3594,7 @@
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
@@ -3615,7 +3615,7 @@
         <v>26</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>27</v>
@@ -3624,7 +3624,7 @@
         <v>27</v>
       </c>
       <c r="AD24" s="24" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="60" customHeight="1">
@@ -3663,7 +3663,7 @@
         <v>166</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M25" s="16">
         <v>4.3</v>
@@ -3678,7 +3678,7 @@
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="R25" s="11">
         <v>44.45</v>
@@ -3708,7 +3708,7 @@
         <v>27</v>
       </c>
       <c r="AD25" s="24" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:30" ht="60" customHeight="1">
@@ -3747,7 +3747,7 @@
         <v>155</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M26" s="16">
         <v>4.3</v>
@@ -3762,7 +3762,7 @@
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="R26" s="11">
         <v>44.45</v>
@@ -3792,7 +3792,7 @@
         <v>27</v>
       </c>
       <c r="AD26" s="24" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27" spans="1:30" ht="60" customHeight="1">
@@ -3819,7 +3819,7 @@
         <v>23</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>155</v>
@@ -3831,7 +3831,7 @@
         <v>154</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M27" s="16">
         <v>4</v>
@@ -3846,7 +3846,7 @@
         <v>46150</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R27" s="11">
         <v>53.9</v>
@@ -3876,7 +3876,7 @@
         <v>27</v>
       </c>
       <c r="AD27" s="24" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="28" spans="1:30" ht="63.75">
@@ -3915,7 +3915,7 @@
         <v>154</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M28" s="16">
         <v>4.2</v>
@@ -3930,7 +3930,7 @@
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="R28" s="11">
         <v>44.45</v>
@@ -3960,7 +3960,7 @@
         <v>27</v>
       </c>
       <c r="AD28" s="24" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="29" spans="1:30" ht="27.75" customHeight="1">
@@ -3987,7 +3987,7 @@
         <v>23</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I29" s="3" t="s">
         <v>155</v>
@@ -3999,7 +3999,7 @@
         <v>154</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="M29" s="16">
         <v>4.0999999999999996</v>
@@ -4014,7 +4014,7 @@
         <v>46150</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="R29" s="11">
         <v>53.9</v>
@@ -4044,7 +4044,7 @@
         <v>27</v>
       </c>
       <c r="AD29" s="24" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:30" ht="150">
@@ -4080,7 +4080,7 @@
         <v>150</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>152</v>
@@ -4098,13 +4098,13 @@
         <v>46152</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="R30" s="11">
         <v>349</v>
       </c>
       <c r="S30" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="T30" s="9">
         <v>46163</v>
@@ -4119,7 +4119,7 @@
         <v>26</v>
       </c>
       <c r="X30" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Z30" s="3" t="s">
         <v>26</v>
@@ -4131,7 +4131,7 @@
         <v>26</v>
       </c>
       <c r="AD30" s="24" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:30" ht="165">
@@ -4158,19 +4158,19 @@
         <v>22</v>
       </c>
       <c r="H31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="I31" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="J31" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="J31" s="3" t="s">
+      <c r="K31" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="L31" s="3" t="s">
         <v>175</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>176</v>
       </c>
       <c r="M31" s="16">
         <v>4.4000000000000004</v>
@@ -4185,7 +4185,7 @@
         <v>46150</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R31" s="11">
         <v>69.989999999999995</v>
@@ -4206,7 +4206,7 @@
         <v>26</v>
       </c>
       <c r="X31" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="Z31" s="3" t="s">
         <v>27</v>
@@ -4215,7 +4215,7 @@
         <v>26</v>
       </c>
       <c r="AD31" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
   </sheetData>
@@ -4263,7 +4263,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -4289,7 +4289,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -4326,7 +4326,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>63</v>
@@ -4341,7 +4341,7 @@
         <v>22</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="I1" s="3" t="s">
         <v>80</v>
@@ -4368,7 +4368,7 @@
         <v>46149</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="R1" s="11">
         <v>549</v>
@@ -4396,18 +4396,18 @@
         <v>27</v>
       </c>
       <c r="AC1" s="25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="2" spans="1:30" s="3" customFormat="1" ht="210">
       <c r="A2" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>62</v>
@@ -4422,13 +4422,13 @@
         <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>291</v>
-      </c>
       <c r="J2" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>130</v>
@@ -4450,7 +4450,7 @@
       <c r="U2" s="9"/>
       <c r="Y2" s="4"/>
       <c r="AD2" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="3" spans="1:30" s="12" customFormat="1" ht="75">

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\iCloudDrive\Interactive Pet Marketplace Design Documentation\Product Matrix\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC048D9D-CABC-413E-9BDB-5248AB830697}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2B40B7-D625-451E-8D8E-28FDB2B19966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Matrix" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Maybe Later" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AD$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AD$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="288">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -182,12 +182,6 @@
     <t>/images/products/Mr-Chocolate-Lab.png</t>
   </si>
   <si>
-    <t>/images/products/Mr-Shih-Tzu.png</t>
-  </si>
-  <si>
-    <t>/images/products/Mr-Beagle.png</t>
-  </si>
-  <si>
     <t>/images/products/Sweetie-Siamese-Cat.png</t>
   </si>
   <si>
@@ -518,9 +512,6 @@
     <t>Perfect Petzzz Original Chocolate Lab is a lifelike breathing plush dog with soft fur, realistic sleeping motions, and calming companionship. Ideal for seniors, children, and pet lovers seeking comfort without the care of a live pet.</t>
   </si>
   <si>
-    <t>Perfect Petzzz Shih Tzu is a lifelike breathing plush dog with soft fur, realistic sleeping motions, and calming companionship. Ideal for seniors, children, and pet lovers seeking comfort without the care of a live pet.</t>
-  </si>
-  <si>
     <t>Perfect Petzzz Border Collie is a lifelike breathing plush dog with soft fur, realistic sleeping motions, and calming companionship. Ideal for seniors, children, and pet lovers seeking comfort without the care of a live pet.</t>
   </si>
   <si>
@@ -530,33 +521,18 @@
     <t>Original Chocolate Lab</t>
   </si>
   <si>
-    <t>Original Shih Tzu</t>
-  </si>
-  <si>
-    <t>Original Beagle</t>
-  </si>
-  <si>
     <t>Original Plush White Cat</t>
   </si>
   <si>
-    <t>Original Black and White Shorthair Cat</t>
-  </si>
-  <si>
     <t>Original Siamese Cat</t>
   </si>
   <si>
     <t>Very affordable</t>
   </si>
   <si>
-    <t>Perfect Petzzz Original Beagle is a lifelike breathing plush dog with soft fur, realistic sleeping motions, and calming companionship. Ideal for seniors, children, and pet lovers seeking comfort without the care of a live pet.</t>
-  </si>
-  <si>
     <t>Perfect Petzzz Original Plush White Cat is a lifelike breathing plush cat with soft fur and realistic sleeping motions. Provides calming companionship for seniors, children, and cat lovers without the care and upkeep of a live pet.</t>
   </si>
   <si>
-    <t>Perfect Petzzz Original Black and White Shorthair Cat is a lifelike breathing plush cat with soft fur and realistic sleeping motions. Provides calming companionship for seniors, children, and cat lovers without the care and upkeep of a live pet.</t>
-  </si>
-  <si>
     <t>Perfect Petzzz Siamese Cat is a lifelike breathing plush cat with soft fur and realistic sleeping motions. Provides calming companionship for seniors, children, and cat lovers without the care and upkeep of a live pet.</t>
   </si>
   <si>
@@ -635,66 +611,18 @@
     <t>Product URL</t>
   </si>
   <si>
-    <t>https://joyforall.com/products/companion-pet-pup?variant=37624426102967</t>
-  </si>
-  <si>
-    <t>https://joyforall.com/products/companion-cats?variant=10404273487915</t>
-  </si>
-  <si>
-    <t>https://joyforall.com/products/companion-cats?variant=10404273455147</t>
-  </si>
-  <si>
-    <t>https://joyforall.com/products/companion-cats?variant=12931092676651</t>
-  </si>
-  <si>
     <t>https://chongker.com/products/matecat10-interactive-cat</t>
   </si>
   <si>
     <t>https://chongker.com/products/percy-interactive-cat</t>
   </si>
   <si>
-    <t>https://www.amazon.com/s?k=wuffy+robot+dog&amp;crid=19CKEYDLEBH6A&amp;sprefix=wuffy%2Caps%2C185&amp;ref=nb_sb_ss_p13n-expert-pd-ops-ranker_1_5</t>
-  </si>
-  <si>
     <t>1) Paste using "Pastes Special" then " Text".</t>
   </si>
   <si>
-    <t>https://www.amazon.com/Perfect-Petzzz-Realistic-Battery-Operated-Interactive/dp/B002PJ37XG/ref=sr_1_2_sspa?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1778523937&amp;sprefix=perfect+petzzz%2Caps%2C211&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Perfect-Petzzz-Chocolate-Lab-Plush/dp/B008Y0QTV2/ref=sr_1_8?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1778523937&amp;sprefix=perfect+petzzz%2Caps%2C211&amp;sr=8-8</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Perfect-Petzzz-Realistic-Interactive-Handcrafted/dp/B0040127N8/ref=sr_1_3_sspa?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect%2Bpetzzz&amp;qid=1778523937&amp;sprefix=perfect%2Bpetzzz%2Caps%2C211&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Perfect-Pets-International-Sleeping-Beagle/dp/B00279NUFY/ref=sr_1_5_sspa?crid=2IOK13QU3Y39L&amp;dib=eyJ2IjoiMSJ9.5idCvQyh45P0neoJ1RmhfCPIRFmNKkUOqHExgy1NckGrvJPqAP7UW2M-0R7w-CnSP0522PcNF1P9cGi6TuJZEAVtJlnkY2PmYS_wrdCeSKfTGSv6GfbTQM0UjROGll4DlZ9LriCiU1pkT0oRb0EwJS2dCOG4ve0cDOUiqTuKfDMowXf3c7LxGOEazm7ZZHiLCWBJIeELYJhg-Wz1MOIVPcxkzVB12ycX3FLjFpm-EGwEG31z63CiyoqW-3l1VRmRq2Q2M9uepGLq0sx0th6lTldAuBF8aww0-STwTsseZIs.gigFOXhWquu5yobhKyyoLwp_mkiYa01Ho9EEDEWgQHg&amp;dib_tag=se&amp;keywords=perfect+petzzz&amp;qid=1778523937&amp;sprefix=perfect+petzzz%2Caps%2C211&amp;sr=8-5-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
-  </si>
-  <si>
     <t>Grey Tabby Cat</t>
   </si>
   <si>
-    <t>https://www.amazon.com/Perfect-Petzzz-Grey-Tabby-Cat/dp/B001TEYF84/ref=sr_1_8?crid=2T22Q9EUUJM90&amp;dib=eyJ2IjoiMSJ9.hw6TypsZgESbto-buC1HDI4zkFKuEs_aZuDM1EyKtr6WMK5ujTDCsWqeBHo8NQXCQtSa2IvHEO7U7N5C9BqYswU3xQD4TTNS-o45TDdrU0HnP_VoaxAErFkDkTd1rvIrVmhSyuNik71aum-TjrRD2GX09FJnAP0OK02Hum5oU0BmsaEYvdvVa-8GYzPoFgs-oRfgW4NaXCGNL1Pq7yYK_t2KOpHjRz3ZY6vhT6O2HP4sYnESDaBDi5ox5WCZXFGJXfp-JCufCzCnRahRloAUi6PfXofSLhrC8i-96X4Vi3w.4yMBJHpLoLosQajGsVB3apXivL14iW3bkJBuB2GL6rI&amp;dib_tag=se&amp;keywords=perfect+petzzz+cat&amp;qid=1778524149&amp;sprefix=perfect+petzzz+cat%2Caps%2C158&amp;sr=8-8</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Perfect-Petzzz-4934-Peluche-Blanc/dp/B00CZC87Y2/ref=sr_1_7?crid=2T22Q9EUUJM90&amp;dib=eyJ2IjoiMSJ9.hw6TypsZgESbto-buC1HDI4zkFKuEs_aZuDM1EyKtr6WMK5ujTDCsWqeBHo8NQXCQtSa2IvHEO7U7N5C9BqYswU3xQD4TTNS-o45TDdrU0HnP_VoaxAErFkDkTd1rvIrVmhSyuNik71aum-TjrRD2GX09FJnAP0OK02Hum5oU0BmsaEYvdvVa-8GYzPoFgs-oRfgW4NaXCGNL1Pq7yYK_t2KOpHjRz3ZY6vhT6O2HP4sYnESDaBDi5ox5WCZXFGJXfp-JCufCzCnRahRloAUi6PfXofSLhrC8i-96X4Vi3w.4yMBJHpLoLosQajGsVB3apXivL14iW3bkJBuB2GL6rI&amp;dib_tag=se&amp;keywords=perfect+petzzz+cat&amp;qid=1778524149&amp;sprefix=perfect+petzzz+cat%2Caps%2C158&amp;sr=8-7</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Perfect-Petzzz-Black-Shorthair-Kitten/dp/B003XSJ4YE/ref=sr_1_3_sspa?crid=2T22Q9EUUJM90&amp;dib=eyJ2IjoiMSJ9.hw6TypsZgESbto-buC1HDI4zkFKuEs_aZuDM1EyKtr6WMK5ujTDCsWqeBHo8NQXCQtSa2IvHEO7U7N5C9BqYswU3xQD4TTNS-o45TDdrU0HnP_VoaxAErFkDkTd1rvIrVmhSyuNik71aum-TjrRD2GX09FJnAP0OK02Hum5oU0BmsaEYvdvVa-8GYzPoFgs-oRfgW4NaXCGNL1Pq7yYK_t2KOpHjRz3ZY6vhT6O2HP4sYnESDaBDi5ox5WCZXFGJXfp-JCufCzCnRahRloAUi6PfXofSLhrC8i-96X4Vi3w.4yMBJHpLoLosQajGsVB3apXivL14iW3bkJBuB2GL6rI&amp;dib_tag=se&amp;keywords=perfect+petzzz+cat&amp;qid=1778524149&amp;sprefix=perfect+petzzz+cat%2Caps%2C158&amp;sr=8-3-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Perfect-Petzzz-Siamese-Breathing-Puppy/dp/B06ZY3CYX4/ref=sr_1_6?crid=2T22Q9EUUJM90&amp;dib=eyJ2IjoiMSJ9.hw6TypsZgESbto-buC1HDI4zkFKuEs_aZuDM1EyKtr6WMK5ujTDCsWqeBHo8NQXCQtSa2IvHEO7U7N5C9BqYswU3xQD4TTNS-o45TDdrU0HnP_VoaxAErFkDkTd1rvIrVmhSyuNik71aum-TjrRD2GX09FJnAP0OK02Hum5oU0BmsaEYvdvVa-8GYzPoFgs-oRfgW4NaXCGNL1Pq7yYK_t2KOpHjRz3ZY6vhT6O2HP4sYnESDaBDi5ox5WCZXFGJXfp-JCufCzCnRahRloAUi6PfXofSLhrC8i-96X4Vi3w.4yMBJHpLoLosQajGsVB3apXivL14iW3bkJBuB2GL6rI&amp;dib_tag=se&amp;keywords=perfect+petzzz+cat&amp;qid=1778524149&amp;sprefix=perfect+petzzz+cat%2Caps%2C158&amp;sr=8-6</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Ruko-18011-Interactive-Expressions-Programmable/dp/B0FLXCXPHD/ref=sr_1_2_sspa?crid=3Q84O44BMP4I1&amp;dib=eyJ2IjoiMSJ9.5Gly7Ov9TtkvwLAe4rZwH2l-BTiwaFOMLi92o4eo2efL59RBhuAyz5dL1llQO9Oq3VOvL554UZdKGuCvEr0aULc0FuaW-0tXMv-Su3A0pJUYX216NZD-8OUNQh6gxNKl8ATh6D7HDFqXqh-HftmgAQSnm2CAImjyhEseHeartYBrk0RKnk_qongpk7N2LmhhFwKFgq-JlfQJBXAYeXfjdZ53H5tQAmhJmbXnYWxOCYV0NtCgyyMVmml1rR7tZkoyjG_4I2LrxuOnAJYrH2drb6GCU0NIUssYnsjouZhfUF4.-br2EkX1bjJZyuScMeKTaBh68fd6MSebkMG0MoeTeO0&amp;dib_tag=se&amp;keywords=ruko%2Brobot&amp;qid=1778524458&amp;sprefix=ruko%2Caps%2C210&amp;sr=8-2-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/s?k=furby+dj&amp;crid=1U6BER2BCWJV5&amp;sprefix=furby+%2Caps%2C205&amp;ref=nb_sb_ss_p13n-expert-pd-ops-ranker_7_6</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/Loona-ChatGPT-4o-AI-Powered-Interaction-Monitoring/dp/B0DCF53PCH/ref=sr_1_1_sspa?crid=2DBOX8S0Q2AR6&amp;dib=eyJ2IjoiMSJ9.fRTz6IKj5O3hiZ4V3RbIiqzYkMvGWX1yxIfmBNQ2bPG8a8X70ewO_kByz-KXp50JfmUuJx9rrIjkexZxX4nWSVxWP_bUrHWGWHPfZnhgH5GMVf6Rltx3FiivEWa9A_74tX_ykUsCTRmHEZ_IwI-5pdDeOvDpmzf07kmD73czlJ5S56lz7gAFPcJ9cgVfwD2yW0a7rgFB4N8XbcF4FmsoLN4nTZhHdGzE2qW01-CozMdL5maZB9Wotwoz672FPyl4IOivur7Z3Gj71yWxlpzykJORSvNzc5nhys8YwW1Zl90.csUcqcC85C04azO69LCOq0bdtEXSzk6YfX_vospSKeE&amp;dib_tag=se&amp;keywords=loona%2Brobot%2Bdog&amp;qid=1778524541&amp;sprefix=loona%2Caps%2C177&amp;sr=8-1-spons&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
     <t>https://www.enabot.com/home-robot/ebo-max</t>
   </si>
   <si>
@@ -767,21 +695,12 @@
     <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_8</t>
   </si>
   <si>
-    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_9</t>
-  </si>
-  <si>
-    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_10</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_11</t>
   </si>
   <si>
     <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_12</t>
   </si>
   <si>
-    <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_13</t>
-  </si>
-  <si>
     <t>https://www.amazon.com/s?k=perfect+petzzz&amp;i=toys-and-games&amp;crid=1Y0BRIT7Y8BFM&amp;sprefix=perfect%2Ctoys-and-games%2C228&amp;ref=nb_sb_ss_saint-nlq-prefix_ci_hl-bn-left_1_14</t>
   </si>
   <si>
@@ -860,9 +779,6 @@
     <t>/images/products/Perfect-Petzzz-Grey-Tabby-Cat.png</t>
   </si>
   <si>
-    <t>/images/products/Perfect-Petzzz-Original-Black-and-White-Shorthair-Cat.png</t>
-  </si>
-  <si>
     <t>Enabot's entry level robot. AI home monitoring robot designed to keep your home, pets, and loved ones connected and secure. Interactive laser point allows you to entertain your pets while you are away.</t>
   </si>
   <si>
@@ -926,9 +842,6 @@
     <t>/images/products/Chongker-Breathing-Calico-Percy-2.0.png</t>
   </si>
   <si>
-    <t>https://ropetai.com/products/ropet%E2%84%A2-ai-comfort-companion-plush-robot?ref=bbtrkjsp</t>
-  </si>
-  <si>
     <t>Ropetai.com</t>
   </si>
   <si>
@@ -951,6 +864,51 @@
   </si>
   <si>
     <t>Perfect Petzzz Grey Tabby Cat is a lifelike breathing plush cat with soft fur and realistic sleeping motions. Provides calming companionship for seniors, children, and cat lovers without the care and upkeep of a live pet.</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4f7XaEW</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3RfUq09</t>
+  </si>
+  <si>
+    <t>Lifelike Robotic Cats for Seniors - Joy for All – Ageless Innovation LLC</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3TifVxQ</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3SFzkJ3</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4fiFcRc</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4vPzP1R</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3RfV7Xj</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4fk1CBx</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4aEBmPL</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4eX2SJw</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4gnKxru</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3QU8PPw</t>
+  </si>
+  <si>
+    <t>https://amzn.to/4wrEfvE</t>
+  </si>
+  <si>
+    <t>https://amzn.to/3R3rOqG</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1037,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1169,6 +1127,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1194,13 +1155,13 @@
     <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>66</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>23</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1571,10 +1532,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:AD31"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="32.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="32.140625" style="6" customWidth="1"/>
     <col min="2" max="2" width="19" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="3" customWidth="1"/>
@@ -1608,7 +1569,7 @@
   <sheetData>
     <row r="1" spans="1:30" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>15</v>
@@ -1617,7 +1578,7 @@
         <v>14</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>18</v>
@@ -1629,52 +1590,52 @@
         <v>20</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="J1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="M1" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="N1" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="O1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="P1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="R1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="S1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="Q1" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="R1" s="10" t="s">
+      <c r="T1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="S1" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="U1" s="8" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="V1" s="6" t="s">
         <v>24</v>
       </c>
       <c r="W1" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="X1" s="6" t="s">
         <v>32</v>
@@ -1689,23 +1650,23 @@
         <v>31</v>
       </c>
       <c r="AB1" s="6" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="AC1" s="6" t="s">
-        <v>279</v>
+        <v>251</v>
       </c>
       <c r="AD1" s="23" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:30">
-      <c r="A2" s="3" t="str">
+      <c r="A2" s="6" t="str">
         <f t="shared" ref="A2:A7" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
     <row r="3" spans="1:30" ht="60">
-      <c r="A3" s="3" t="str">
+      <c r="A3" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
@@ -1716,7 +1677,7 @@
         <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>17</v>
@@ -1728,19 +1689,19 @@
         <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="M3" s="16">
         <v>5</v>
@@ -1749,25 +1710,25 @@
         <v>2</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="P3" s="9">
         <v>46153</v>
       </c>
       <c r="Q3" s="21" t="s">
-        <v>235</v>
+        <v>211</v>
       </c>
       <c r="R3" s="11">
         <v>119</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T3" s="9">
         <v>46150</v>
       </c>
       <c r="U3" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V3" s="3" t="s">
         <v>26</v>
@@ -1792,11 +1753,11 @@
         <v>26</v>
       </c>
       <c r="AD3" s="24" t="s">
-        <v>274</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="75">
-      <c r="A4" s="3" t="str">
+      <c r="A4" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
       </c>
@@ -1807,7 +1768,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>17</v>
@@ -1819,19 +1780,19 @@
         <v>21</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K4" s="28" t="s">
-        <v>122</v>
-      </c>
       <c r="L4" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M4" s="16">
         <v>4</v>
@@ -1840,25 +1801,25 @@
         <v>2</v>
       </c>
       <c r="O4" s="3" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="P4" s="9">
         <v>46153</v>
       </c>
       <c r="Q4" s="21" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="R4" s="11">
         <v>149</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T4" s="9">
         <v>46150</v>
       </c>
       <c r="U4" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V4" s="3" t="s">
         <v>26</v>
@@ -1867,7 +1828,7 @@
         <v>27</v>
       </c>
       <c r="X4" s="3" t="s">
-        <v>263</v>
+        <v>236</v>
       </c>
       <c r="Y4" s="4"/>
       <c r="Z4" s="3" t="s">
@@ -1883,11 +1844,11 @@
         <v>26</v>
       </c>
       <c r="AD4" s="25" t="s">
-        <v>275</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="165">
-      <c r="A5" s="3" t="str">
+      <c r="A5" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
@@ -1898,7 +1859,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>17</v>
@@ -1910,19 +1871,19 @@
         <v>21</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="L5" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="M5" s="16">
         <v>4.5999999999999996</v>
@@ -1931,25 +1892,25 @@
         <v>456</v>
       </c>
       <c r="O5" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P5" s="9">
         <v>46153</v>
       </c>
       <c r="Q5" s="21" t="s">
-        <v>232</v>
+        <v>208</v>
       </c>
       <c r="R5" s="11">
         <v>178</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T5" s="9">
         <v>46150</v>
       </c>
       <c r="U5" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V5" s="3" t="s">
         <v>26</v>
@@ -1958,7 +1919,7 @@
         <v>26</v>
       </c>
       <c r="X5" s="3" t="s">
-        <v>262</v>
+        <v>235</v>
       </c>
       <c r="Z5" s="3" t="s">
         <v>27</v>
@@ -1973,11 +1934,11 @@
         <v>26</v>
       </c>
       <c r="AD5" s="25" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" spans="1:30" ht="75">
-      <c r="A6" s="3" t="str">
+      <c r="A6" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
       </c>
@@ -1985,10 +1946,10 @@
         <v>7</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>261</v>
+        <v>234</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>17</v>
@@ -2000,19 +1961,19 @@
         <v>21</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="L6" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M6" s="16">
         <v>5</v>
@@ -2024,19 +1985,19 @@
         <v>46153</v>
       </c>
       <c r="Q6" s="21" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="R6" s="11">
         <v>89</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T6" s="9">
         <v>46150</v>
       </c>
       <c r="U6" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V6" s="3" t="s">
         <v>26</v>
@@ -2045,7 +2006,7 @@
         <v>26</v>
       </c>
       <c r="X6" s="2" t="s">
-        <v>260</v>
+        <v>233</v>
       </c>
       <c r="Y6" s="4"/>
       <c r="Z6" s="3" t="s">
@@ -2061,11 +2022,11 @@
         <v>26</v>
       </c>
       <c r="AD6" s="24" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:30" ht="60">
-      <c r="A7" s="3" t="str">
+      <c r="A7" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
@@ -2076,7 +2037,7 @@
         <v>9</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>17</v>
@@ -2088,19 +2049,19 @@
         <v>21</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>130</v>
-      </c>
       <c r="L7" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M7" s="16">
         <v>5</v>
@@ -2109,25 +2070,25 @@
         <v>16</v>
       </c>
       <c r="O7" s="3" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="P7" s="9">
         <v>46153</v>
       </c>
       <c r="Q7" s="21" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="R7" s="11">
         <v>89</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T7" s="9">
         <v>46150</v>
       </c>
       <c r="U7" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V7" s="3" t="s">
         <v>26</v>
@@ -2136,7 +2097,7 @@
         <v>27</v>
       </c>
       <c r="X7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Y7" s="4"/>
       <c r="Z7" s="3" t="s">
@@ -2152,21 +2113,21 @@
         <v>26</v>
       </c>
       <c r="AD7" s="25" t="s">
-        <v>278</v>
+        <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:30" ht="45">
-      <c r="A8" s="3" t="s">
-        <v>283</v>
+      <c r="A8" s="6" t="s">
+        <v>255</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>285</v>
+        <v>257</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>17</v>
@@ -2178,16 +2139,16 @@
         <v>21</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>287</v>
+        <v>259</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="M8" s="16">
         <v>5</v>
@@ -2196,25 +2157,25 @@
         <v>10</v>
       </c>
       <c r="O8" s="3" t="s">
-        <v>233</v>
+        <v>209</v>
       </c>
       <c r="P8" s="9">
         <v>46161</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>291</v>
+        <v>263</v>
       </c>
       <c r="R8" s="11">
         <v>109</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T8" s="9">
         <v>46161</v>
       </c>
       <c r="U8" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>26</v>
@@ -2223,7 +2184,7 @@
         <v>26</v>
       </c>
       <c r="X8" s="3" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="Y8" s="4"/>
       <c r="Z8" s="3" t="s">
@@ -2239,22 +2200,22 @@
         <v>26</v>
       </c>
       <c r="AD8" s="25" t="s">
-        <v>282</v>
+        <v>254</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="60">
-      <c r="A9" s="3" t="str">
-        <f t="shared" ref="A9:A31" si="1">_xlfn.CONCAT(B9, " ", C9)</f>
+      <c r="A9" s="6" t="str">
+        <f t="shared" ref="A9:A28" si="1">_xlfn.CONCAT(B9, " ", C9)</f>
         <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
       </c>
       <c r="B9" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>16</v>
@@ -2266,19 +2227,19 @@
         <v>21</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>272</v>
+        <v>244</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>91</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="M9" s="16">
         <v>4.5</v>
@@ -2287,25 +2248,25 @@
         <v>72</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P9" s="9">
         <v>46149</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="R9" s="11">
         <v>179</v>
       </c>
       <c r="S9" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T9" s="9">
         <v>46152</v>
       </c>
       <c r="U9" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V9" s="3" t="s">
         <v>26</v>
@@ -2314,7 +2275,7 @@
         <v>27</v>
       </c>
       <c r="X9" s="2" t="s">
-        <v>253</v>
+        <v>226</v>
       </c>
       <c r="Z9" s="3" t="s">
         <v>26</v>
@@ -2326,11 +2287,11 @@
         <v>27</v>
       </c>
       <c r="AD9" s="25" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10" spans="1:30" ht="60">
-      <c r="A10" s="3" t="str">
+      <c r="A10" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
@@ -2338,10 +2299,10 @@
         <v>0</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>16</v>
@@ -2353,19 +2314,19 @@
         <v>21</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>250</v>
+        <v>223</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="L10" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M10" s="16">
         <v>5</v>
@@ -2374,19 +2335,19 @@
         <v>42</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P10" s="9">
         <v>46149</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="R10" s="11">
         <v>359</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T10" s="9">
         <v>46150</v>
@@ -2401,7 +2362,7 @@
         <v>26</v>
       </c>
       <c r="X10" s="2" t="s">
-        <v>254</v>
+        <v>227</v>
       </c>
       <c r="Z10" s="3" t="s">
         <v>26</v>
@@ -2413,11 +2374,11 @@
         <v>27</v>
       </c>
       <c r="AD10" s="25" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" spans="1:30" ht="60">
-      <c r="A11" s="3" t="str">
+      <c r="A11" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
@@ -2425,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>16</v>
@@ -2440,19 +2401,19 @@
         <v>21</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M11" s="16">
         <v>5</v>
@@ -2461,19 +2422,19 @@
         <v>16</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P11" s="9">
         <v>46149</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>224</v>
+        <v>200</v>
       </c>
       <c r="R11" s="11">
         <v>279</v>
       </c>
       <c r="S11" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T11" s="9">
         <v>46151</v>
@@ -2488,7 +2449,7 @@
         <v>27</v>
       </c>
       <c r="X11" s="2" t="s">
-        <v>255</v>
+        <v>228</v>
       </c>
       <c r="Z11" s="3" t="s">
         <v>26</v>
@@ -2500,11 +2461,11 @@
         <v>27</v>
       </c>
       <c r="AD11" s="25" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:30" ht="60" customHeight="1">
-      <c r="A12" s="3" t="str">
+      <c r="A12" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
@@ -2512,10 +2473,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>16</v>
@@ -2527,19 +2488,19 @@
         <v>23</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="M12" s="16">
         <v>4.5</v>
@@ -2548,19 +2509,19 @@
         <v>20</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P12" s="9">
         <v>46149</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="R12" s="11">
         <v>789</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T12" s="9">
         <v>46149</v>
@@ -2575,7 +2536,7 @@
         <v>27</v>
       </c>
       <c r="X12" s="2" t="s">
-        <v>252</v>
+        <v>225</v>
       </c>
       <c r="Z12" s="3" t="s">
         <v>26</v>
@@ -2587,11 +2548,11 @@
         <v>27</v>
       </c>
       <c r="AD12" s="25" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" spans="1:30" ht="45.75" thickBot="1">
-      <c r="A13" s="3" t="str">
+      <c r="A13" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
       </c>
@@ -2599,34 +2560,34 @@
         <v>0</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>251</v>
+        <v>224</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="M13" s="16">
         <v>5</v>
@@ -2635,25 +2596,25 @@
         <v>73</v>
       </c>
       <c r="O13" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P13" s="9">
         <v>46149</v>
       </c>
       <c r="Q13" s="21" t="s">
-        <v>226</v>
+        <v>202</v>
       </c>
       <c r="R13" s="11">
         <v>139</v>
       </c>
       <c r="S13" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T13" s="9">
         <v>46153</v>
       </c>
       <c r="U13" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V13" s="3" t="s">
         <v>26</v>
@@ -2662,7 +2623,7 @@
         <v>27</v>
       </c>
       <c r="X13" s="2" t="s">
-        <v>256</v>
+        <v>229</v>
       </c>
       <c r="Z13" s="3" t="s">
         <v>26</v>
@@ -2674,11 +2635,11 @@
         <v>27</v>
       </c>
       <c r="AD13" s="25" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:30" ht="105.75" thickBot="1">
-      <c r="A14" s="3" t="str">
+      <c r="A14" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
@@ -2689,7 +2650,7 @@
         <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>17</v>
@@ -2701,19 +2662,19 @@
         <v>21</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J14" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="K14" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="K14" s="29" t="s">
-        <v>113</v>
-      </c>
       <c r="L14" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M14" s="16">
         <v>4.5</v>
@@ -2722,25 +2683,25 @@
         <v>11640</v>
       </c>
       <c r="O14" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P14" s="9">
         <v>46153</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="R14" s="11">
         <v>159.99</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T14" s="9">
         <v>46150</v>
       </c>
       <c r="U14" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>26</v>
@@ -2749,7 +2710,7 @@
         <v>27</v>
       </c>
       <c r="X14" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Y14" s="4"/>
       <c r="Z14" s="3" t="s">
@@ -2762,11 +2723,11 @@
         <v>27</v>
       </c>
       <c r="AD14" s="24" t="s">
-        <v>198</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" spans="1:30" ht="105">
-      <c r="A15" s="3" t="str">
+      <c r="A15" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
@@ -2777,7 +2738,7 @@
         <v>35</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>17</v>
@@ -2789,19 +2750,19 @@
         <v>21</v>
       </c>
       <c r="H15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>112</v>
-      </c>
       <c r="L15" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M15" s="16">
         <v>4.5</v>
@@ -2810,25 +2771,25 @@
         <v>11640</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P15" s="9">
         <v>46153</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>229</v>
+        <v>205</v>
       </c>
       <c r="R15" s="11">
         <v>159.99</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T15" s="9">
         <v>46150</v>
       </c>
       <c r="U15" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>26</v>
@@ -2837,7 +2798,7 @@
         <v>27</v>
       </c>
       <c r="X15" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="Y15" s="4"/>
       <c r="Z15" s="3" t="s">
@@ -2850,12 +2811,12 @@
         <v>27</v>
       </c>
       <c r="AD15" s="26" t="s">
-        <v>197</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:30" ht="60" customHeight="1">
-      <c r="A16" s="3" t="str">
-        <f t="shared" si="1"/>
+      <c r="A16" s="6" t="str">
+        <f>_xlfn.CONCAT(B16, " ", C16)</f>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
       </c>
       <c r="B16" s="3" t="s">
@@ -2865,7 +2826,7 @@
         <v>36</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>17</v>
@@ -2877,19 +2838,19 @@
         <v>21</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M16" s="16">
         <v>4.5</v>
@@ -2898,25 +2859,25 @@
         <v>11640</v>
       </c>
       <c r="O16" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P16" s="9">
         <v>46150</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
       <c r="R16" s="11">
         <v>159.99</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T16" s="9">
         <v>46150</v>
       </c>
       <c r="U16" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V16" s="3" t="s">
         <v>26</v>
@@ -2925,7 +2886,7 @@
         <v>26</v>
       </c>
       <c r="X16" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Y16" s="4"/>
       <c r="Z16" s="3" t="s">
@@ -2937,12 +2898,12 @@
       <c r="AB16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD16" s="25" t="s">
-        <v>199</v>
+      <c r="AD16" s="31" t="s">
+        <v>275</v>
       </c>
     </row>
     <row r="17" spans="1:30" ht="60">
-      <c r="A17" s="3" t="str">
+      <c r="A17" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
@@ -2953,7 +2914,7 @@
         <v>34</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>17</v>
@@ -2965,19 +2926,19 @@
         <v>21</v>
       </c>
       <c r="H17" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="J17" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>108</v>
-      </c>
       <c r="L17" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="M17" s="16">
         <v>4.3</v>
@@ -2986,25 +2947,25 @@
         <v>5163</v>
       </c>
       <c r="O17" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P17" s="9">
         <v>46150</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>227</v>
+        <v>203</v>
       </c>
       <c r="R17" s="11">
         <v>179</v>
       </c>
       <c r="S17" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T17" s="9">
         <v>46150</v>
       </c>
       <c r="U17" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>26</v>
@@ -3013,7 +2974,7 @@
         <v>27</v>
       </c>
       <c r="X17" s="2" t="s">
-        <v>258</v>
+        <v>231</v>
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="3" t="s">
@@ -3026,11 +2987,11 @@
         <v>27</v>
       </c>
       <c r="AD17" s="26" t="s">
-        <v>196</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:30" ht="60">
-      <c r="A18" s="3" t="str">
+      <c r="A18" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
@@ -3041,7 +3002,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>17</v>
@@ -3053,19 +3014,19 @@
         <v>21</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I18" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="L18" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="M18" s="16">
         <v>4.3</v>
@@ -3074,25 +3035,25 @@
         <v>5164</v>
       </c>
       <c r="O18" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P18" s="9">
         <v>46153</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>228</v>
+        <v>204</v>
       </c>
       <c r="R18" s="11">
         <v>179</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T18" s="9">
         <v>46150</v>
       </c>
       <c r="U18" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="V18" s="3" t="s">
         <v>26</v>
@@ -3101,7 +3062,7 @@
         <v>26</v>
       </c>
       <c r="X18" s="2" t="s">
-        <v>257</v>
+        <v>230</v>
       </c>
       <c r="Y18" s="4"/>
       <c r="Z18" s="3" t="s">
@@ -3114,12 +3075,12 @@
         <v>27</v>
       </c>
       <c r="AD18" s="26" t="s">
-        <v>196</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:30" ht="74.25" customHeight="1">
-      <c r="A19" s="3" t="str">
-        <f t="shared" si="1"/>
+      <c r="A19" s="6" t="str">
+        <f>_xlfn.CONCAT(B19, " ", C19)</f>
         <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
       </c>
       <c r="B19" s="3" t="s">
@@ -3129,7 +3090,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>17</v>
@@ -3141,19 +3102,19 @@
         <v>22</v>
       </c>
       <c r="H19" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>147</v>
-      </c>
       <c r="L19" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="M19" s="16">
         <v>3</v>
@@ -3162,25 +3123,25 @@
         <v>80</v>
       </c>
       <c r="O19" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P19" s="9">
         <v>46151</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>236</v>
+        <v>212</v>
       </c>
       <c r="R19" s="11">
         <v>25.99</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T19" s="9">
         <v>46151</v>
       </c>
       <c r="U19" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V19" s="3" t="s">
         <v>26</v>
@@ -3189,7 +3150,7 @@
         <v>27</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>259</v>
+        <v>232</v>
       </c>
       <c r="Z19" s="3" t="s">
         <v>27</v>
@@ -3201,22 +3162,22 @@
         <v>27</v>
       </c>
       <c r="AD19" s="24" t="s">
-        <v>202</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:30" ht="150">
-      <c r="A20" s="3" t="str">
+      <c r="A20" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Furby DJ Furby</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>16</v>
@@ -3228,19 +3189,19 @@
         <v>22</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="M20" s="16">
         <v>4.8</v>
@@ -3249,25 +3210,25 @@
         <v>772</v>
       </c>
       <c r="O20" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P20" s="9">
         <v>46150</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>247</v>
+        <v>220</v>
       </c>
       <c r="R20" s="11">
         <v>50.11</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T20" s="9">
         <v>46150</v>
       </c>
       <c r="U20" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V20" s="3" t="s">
         <v>26</v>
@@ -3276,7 +3237,7 @@
         <v>26</v>
       </c>
       <c r="X20" s="2" t="s">
-        <v>269</v>
+        <v>242</v>
       </c>
       <c r="Z20" s="3" t="s">
         <v>27</v>
@@ -3285,25 +3246,25 @@
         <v>27</v>
       </c>
       <c r="AB20" s="3" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="AD20" s="24" t="s">
-        <v>214</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:30" ht="165">
-      <c r="A21" s="3" t="str">
+      <c r="A21" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>16</v>
@@ -3315,16 +3276,16 @@
         <v>22</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="M21" s="16">
         <v>4.2</v>
@@ -3333,19 +3294,19 @@
         <v>1199</v>
       </c>
       <c r="O21" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P21" s="9">
         <v>46150</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>248</v>
+        <v>221</v>
       </c>
       <c r="R21" s="11">
         <v>499</v>
       </c>
       <c r="S21" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T21" s="9">
         <v>46150</v>
@@ -3360,7 +3321,7 @@
         <v>26</v>
       </c>
       <c r="X21" s="2" t="s">
-        <v>267</v>
+        <v>240</v>
       </c>
       <c r="Z21" s="3" t="s">
         <v>26</v>
@@ -3369,14 +3330,14 @@
         <v>26</v>
       </c>
       <c r="AB21" s="3" t="s">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="AD21" s="24" t="s">
-        <v>215</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:30" ht="60">
-      <c r="A22" s="3" t="str">
+      <c r="A22" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
@@ -3384,10 +3345,10 @@
         <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>17</v>
@@ -3399,19 +3360,19 @@
         <v>23</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="M22" s="16">
         <v>4.3</v>
@@ -3420,25 +3381,25 @@
         <v>848</v>
       </c>
       <c r="O22" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P22" s="9">
         <v>46150</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="R22" s="11">
         <v>44.45</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T22" s="9">
         <v>46150</v>
       </c>
       <c r="U22" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>26</v>
@@ -3447,7 +3408,7 @@
         <v>27</v>
       </c>
       <c r="X22" s="2" t="s">
-        <v>270</v>
+        <v>243</v>
       </c>
       <c r="Z22" s="3" t="s">
         <v>27</v>
@@ -3456,22 +3417,22 @@
         <v>27</v>
       </c>
       <c r="AD22" s="24" t="s">
-        <v>209</v>
+        <v>281</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="60">
-      <c r="A23" s="3" t="str">
+    <row r="23" spans="1:30" ht="60" customHeight="1">
+      <c r="A23" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Beagle</v>
+        <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>17</v>
@@ -3483,46 +3444,46 @@
         <v>23</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="M23" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="N23" s="19">
-        <v>466</v>
+        <v>403</v>
       </c>
       <c r="O23" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P23" s="9">
         <v>46150</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>241</v>
+        <v>214</v>
       </c>
       <c r="R23" s="11">
         <v>44.45</v>
       </c>
       <c r="S23" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T23" s="9">
         <v>46150</v>
       </c>
       <c r="U23" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>26</v>
@@ -3531,7 +3492,7 @@
         <v>27</v>
       </c>
       <c r="X23" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>27</v>
@@ -3540,22 +3501,22 @@
         <v>27</v>
       </c>
       <c r="AD23" s="24" t="s">
-        <v>207</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:30" ht="60" customHeight="1">
-      <c r="A24" s="3" t="str">
+      <c r="A24" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Black and White Shorthair Cat</v>
+        <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>17</v>
@@ -3567,55 +3528,55 @@
         <v>23</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="M24" s="16">
-        <v>4.4000000000000004</v>
+        <v>4.3</v>
       </c>
       <c r="N24" s="19">
-        <v>1200</v>
+        <v>553</v>
       </c>
       <c r="O24" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P24" s="9">
         <v>46150</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="R24" s="11">
         <v>44.45</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T24" s="9">
         <v>46150</v>
       </c>
       <c r="U24" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V24" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>271</v>
+        <v>44</v>
       </c>
       <c r="Z24" s="3" t="s">
         <v>27</v>
@@ -3624,22 +3585,22 @@
         <v>27</v>
       </c>
       <c r="AD24" s="24" t="s">
-        <v>211</v>
+        <v>283</v>
       </c>
     </row>
     <row r="25" spans="1:30" ht="60" customHeight="1">
-      <c r="A25" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Border Collie</v>
+      <c r="A25" s="6" t="str">
+        <f>_xlfn.CONCAT(B25, " ", C25)</f>
+        <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>17</v>
@@ -3651,46 +3612,46 @@
         <v>23</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M25" s="16">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="N25" s="19">
-        <v>403</v>
+        <v>54</v>
       </c>
       <c r="O25" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P25" s="9">
         <v>46150</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>238</v>
+        <v>217</v>
       </c>
       <c r="R25" s="11">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T25" s="9">
         <v>46150</v>
       </c>
       <c r="U25" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V25" s="3" t="s">
         <v>26</v>
@@ -3699,7 +3660,7 @@
         <v>27</v>
       </c>
       <c r="X25" s="2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="Z25" s="3" t="s">
         <v>27</v>
@@ -3708,22 +3669,22 @@
         <v>27</v>
       </c>
       <c r="AD25" s="24" t="s">
-        <v>204</v>
+        <v>284</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="60" customHeight="1">
-      <c r="A26" s="3" t="str">
+    <row r="26" spans="1:30" ht="27.75" customHeight="1">
+      <c r="A26" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Chocolate Lab</v>
+        <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>17</v>
@@ -3735,46 +3696,46 @@
         <v>23</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="M26" s="16">
-        <v>4.3</v>
+        <v>4.0999999999999996</v>
       </c>
       <c r="N26" s="19">
-        <v>553</v>
+        <v>16</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P26" s="9">
         <v>46150</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>239</v>
+        <v>218</v>
       </c>
       <c r="R26" s="11">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T26" s="9">
         <v>46150</v>
       </c>
       <c r="U26" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>26</v>
@@ -3783,7 +3744,7 @@
         <v>27</v>
       </c>
       <c r="X26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>27</v>
@@ -3792,157 +3753,160 @@
         <v>27</v>
       </c>
       <c r="AD26" s="24" t="s">
-        <v>205</v>
+        <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="60" customHeight="1">
-      <c r="A27" s="3" t="str">
+    <row r="27" spans="1:30" ht="150">
+      <c r="A27" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Plush White Cat</v>
+        <v>Ropet KAMOMO</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>62</v>
+        <v>28</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="E27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="M27" s="16">
+        <v>4.3</v>
+      </c>
+      <c r="N27" s="19">
         <v>17</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M27" s="16">
-        <v>4</v>
-      </c>
-      <c r="N27" s="19">
-        <v>54</v>
-      </c>
       <c r="O27" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P27" s="9">
-        <v>46150</v>
+        <v>46152</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>243</v>
+        <v>213</v>
       </c>
       <c r="R27" s="11">
-        <v>53.9</v>
+        <v>349</v>
       </c>
       <c r="S27" s="3" t="s">
-        <v>82</v>
+        <v>265</v>
       </c>
       <c r="T27" s="9">
-        <v>46150</v>
+        <v>46163</v>
       </c>
       <c r="U27" s="9" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X27" s="2" t="s">
-        <v>57</v>
+        <v>241</v>
       </c>
       <c r="Z27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA27" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="AB27" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD27" s="24" t="s">
-        <v>210</v>
+        <v>286</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="63.75">
-      <c r="A28" s="3" t="str">
+    <row r="28" spans="1:30" ht="165">
+      <c r="A28" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Shih Tzu</v>
+        <v>Ruko 18011 Smart Robot Dog</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>65</v>
+        <v>46</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J28" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K28" s="3" t="s">
-        <v>154</v>
-      </c>
       <c r="L28" s="3" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="M28" s="16">
-        <v>4.2</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="N28" s="19">
-        <v>878</v>
+        <v>283</v>
       </c>
       <c r="O28" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P28" s="9">
         <v>46150</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>240</v>
+        <v>219</v>
       </c>
       <c r="R28" s="11">
-        <v>44.45</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="T28" s="9">
         <v>46150</v>
       </c>
       <c r="U28" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V28" s="3" t="s">
         <v>26</v>
@@ -3951,287 +3915,28 @@
         <v>26</v>
       </c>
       <c r="X28" s="2" t="s">
-        <v>45</v>
+        <v>237</v>
       </c>
       <c r="Z28" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AA28" s="3" t="s">
-        <v>27</v>
+      <c r="AB28" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AD28" s="24" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="29" spans="1:30" ht="27.75" customHeight="1">
-      <c r="A29" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Siamese Cat</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="M29" s="16">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="N29" s="19">
-        <v>16</v>
-      </c>
-      <c r="O29" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P29" s="9">
-        <v>46150</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="R29" s="11">
-        <v>53.9</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="T29" s="9">
-        <v>46150</v>
-      </c>
-      <c r="U29" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD29" s="24" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="30" spans="1:30" ht="150">
-      <c r="A30" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Ropet KAMOMO</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="M30" s="16">
-        <v>4.3</v>
-      </c>
-      <c r="N30" s="19">
-        <v>17</v>
-      </c>
-      <c r="O30" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P30" s="9">
-        <v>46152</v>
-      </c>
-      <c r="Q30" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="R30" s="11">
-        <v>349</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="T30" s="9">
-        <v>46163</v>
-      </c>
-      <c r="U30" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="V30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X30" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="Z30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB30" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD30" s="24" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="31" spans="1:30" ht="165">
-      <c r="A31" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Ruko 18011 Smart Robot Dog</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="M31" s="16">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="N31" s="19">
-        <v>283</v>
-      </c>
-      <c r="O31" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="P31" s="9">
-        <v>46150</v>
-      </c>
-      <c r="Q31" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="R31" s="11">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="T31" s="9">
-        <v>46150</v>
-      </c>
-      <c r="U31" s="9" t="s">
-        <v>87</v>
-      </c>
-      <c r="V31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="W31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X31" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="Z31" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB31" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD31" s="24" t="s">
-        <v>213</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD31" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD31">
-      <sortCondition ref="A1:A31"/>
+  <autoFilter ref="A1:AD28" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD28">
+      <sortCondition ref="A1:A28"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="10" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="AD18" r:id="rId1" xr:uid="{DC5B1D1E-44B5-4F09-8C52-EC8B9A6A0D6D}"/>
-    <hyperlink ref="AD17" r:id="rId2" xr:uid="{76A5B142-2262-40B1-8235-9B8D81F5C196}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId3"/>
-  <drawing r:id="rId4"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
@@ -4263,7 +3968,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:1">
@@ -4289,12 +3994,12 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="7" spans="1:1">
@@ -4326,10 +4031,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>16</v>
@@ -4341,19 +4046,19 @@
         <v>22</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="M1" s="16">
         <v>0</v>
@@ -4362,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="P1" s="9">
         <v>46149</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="R1" s="11">
         <v>549</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="T1" s="9">
         <v>46149</v>
@@ -4396,21 +4101,21 @@
         <v>27</v>
       </c>
       <c r="AC1" s="25" t="s">
-        <v>216</v>
+        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:30" s="3" customFormat="1" ht="210">
       <c r="A2" s="3" t="s">
-        <v>280</v>
+        <v>252</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>284</v>
+        <v>256</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>17</v>
@@ -4422,19 +4127,19 @@
         <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M2" s="16"/>
       <c r="N2" s="19"/>
@@ -4444,13 +4149,13 @@
         <v>89</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="T2" s="9"/>
       <c r="U2" s="9"/>
       <c r="Y2" s="4"/>
       <c r="AD2" s="25" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
     </row>
     <row r="3" spans="1:30" s="12" customFormat="1" ht="75">
@@ -4465,7 +4170,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>17</v>
@@ -4493,7 +4198,7 @@
         <v>27</v>
       </c>
       <c r="Y3" s="12" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Z3" s="12" t="s">
         <v>41</v>
@@ -4514,7 +4219,7 @@
         <v>3</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>17</v>
@@ -4526,7 +4231,7 @@
         <v>21</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="M4" s="17"/>
       <c r="N4" s="20"/>
@@ -4545,7 +4250,7 @@
         <v>27</v>
       </c>
       <c r="Y4" s="12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Z4" s="12" t="s">
         <v>41</v>
@@ -4566,7 +4271,7 @@
         <v>4</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E5" s="12" t="s">
         <v>17</v>
@@ -4578,7 +4283,7 @@
         <v>21</v>
       </c>
       <c r="H5" s="12" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="M5" s="17"/>
       <c r="N5" s="20"/>
@@ -4597,7 +4302,7 @@
         <v>27</v>
       </c>
       <c r="Y5" s="12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Z5" s="12" t="s">
         <v>41</v>
@@ -4618,7 +4323,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E6" s="12" t="s">
         <v>17</v>
@@ -4630,7 +4335,7 @@
         <v>21</v>
       </c>
       <c r="H6" s="12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="M6" s="17"/>
       <c r="N6" s="20"/>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\iCloudDrive\Interactive Pet Marketplace Design Documentation\Product Matrix\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2B40B7-D625-451E-8D8E-28FDB2B19966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{56D75CD1-B6B7-4224-B284-25CB7A465C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56D75CD1-B6B7-4224-B284-25CB7A465C50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85AD188-19ED-4E5F-BD8A-4DBA949F616D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="2355" yWindow="2085" windowWidth="21600" windowHeight="11295" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Matrix" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="289">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -909,6 +909,9 @@
   </si>
   <si>
     <t>https://amzn.to/3R3rOqG</t>
+  </si>
+  <si>
+    <t>Other</t>
   </si>
 </sst>
 </file>
@@ -3177,7 +3180,7 @@
         <v>176</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>61</v>
+        <v>288</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>16</v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C85AD188-19ED-4E5F-BD8A-4DBA949F616D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7694B779-0410-4F59-8596-8AA8E412B177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2355" yWindow="2085" windowWidth="21600" windowHeight="11295" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Matrix" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Maybe Later" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AD$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AE$28</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="292">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -912,6 +912,15 @@
   </si>
   <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>Stationary/Mobile</t>
+  </si>
+  <si>
+    <t>Stationary</t>
+  </si>
+  <si>
+    <t>Mobile</t>
   </si>
 </sst>
 </file>
@@ -1156,13 +1165,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>23</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
+      <xdr:col>24</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
       <xdr:row>64</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1535,42 +1544,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:AD28"/>
+  <dimension ref="A1:AE28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.140625" style="6" customWidth="1"/>
     <col min="2" max="2" width="19" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.140625" style="3" customWidth="1"/>
     <col min="4" max="4" width="17.28515625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.7109375" style="3" customWidth="1"/>
-    <col min="8" max="8" width="52.140625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15" style="3" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="3" customWidth="1"/>
-    <col min="12" max="12" width="15.5703125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" style="16" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="19" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="13.28515625" style="9" customWidth="1"/>
-    <col min="17" max="17" width="80.7109375" style="3" customWidth="1"/>
-    <col min="18" max="18" width="8.85546875" style="11" customWidth="1"/>
-    <col min="19" max="19" width="10" style="3" customWidth="1"/>
-    <col min="20" max="21" width="13.28515625" style="9" customWidth="1"/>
-    <col min="22" max="22" width="6.140625" style="3" customWidth="1"/>
-    <col min="23" max="23" width="9.140625" style="3" customWidth="1"/>
-    <col min="24" max="24" width="54.140625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="32.140625" style="6" customWidth="1"/>
-    <col min="26" max="26" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="10.5703125" style="3" customWidth="1"/>
-    <col min="30" max="30" width="200.7109375" style="25" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="3"/>
+    <col min="5" max="6" width="17.85546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="52.140625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="15" style="3" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="15.5703125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="10.7109375" style="16" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" style="19" customWidth="1"/>
+    <col min="16" max="16" width="10.7109375" style="3" customWidth="1"/>
+    <col min="17" max="17" width="13.28515625" style="9" customWidth="1"/>
+    <col min="18" max="18" width="80.7109375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.85546875" style="11" customWidth="1"/>
+    <col min="20" max="20" width="10" style="3" customWidth="1"/>
+    <col min="21" max="22" width="13.28515625" style="9" customWidth="1"/>
+    <col min="23" max="23" width="6.140625" style="3" customWidth="1"/>
+    <col min="24" max="24" width="9.140625" style="3" customWidth="1"/>
+    <col min="25" max="25" width="54.140625" style="3" customWidth="1"/>
+    <col min="26" max="26" width="32.140625" style="6" customWidth="1"/>
+    <col min="27" max="27" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.5703125" style="3" customWidth="1"/>
+    <col min="31" max="31" width="200.7109375" style="25" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" s="6" customFormat="1" ht="30">
+    <row r="1" spans="1:31" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
         <v>180</v>
       </c>
@@ -1587,88 +1596,91 @@
         <v>18</v>
       </c>
       <c r="F1" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="G1" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="K1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="L1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="M1" s="15" t="s">
+      <c r="N1" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="N1" s="18" t="s">
+      <c r="O1" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="R1" s="10" t="s">
+      <c r="S1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="T1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="X1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="Y1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="AD1" s="23" t="s">
+      <c r="AE1" s="23" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:30">
+    <row r="2" spans="1:31">
       <c r="A2" s="6" t="str">
         <f t="shared" ref="A2:A7" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="60">
+    <row r="3" spans="1:31" ht="60">
       <c r="A3" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
@@ -1686,80 +1698,83 @@
         <v>17</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="M3" s="16">
+      <c r="N3" s="16">
         <v>5</v>
       </c>
-      <c r="N3" s="19">
+      <c r="O3" s="19">
         <v>2</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="P3" s="9">
+      <c r="Q3" s="9">
         <v>46153</v>
       </c>
-      <c r="Q3" s="21" t="s">
+      <c r="R3" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="R3" s="11">
+      <c r="S3" s="11">
         <v>119</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T3" s="9">
+      <c r="U3" s="9">
         <v>46150</v>
       </c>
-      <c r="U3" s="9" t="s">
+      <c r="V3" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V3" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z3" s="5"/>
       <c r="AA3" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD3" s="24" t="s">
+      <c r="AD3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" s="24" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="75">
+    <row r="4" spans="1:31" ht="75">
       <c r="A4" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
@@ -1777,80 +1792,83 @@
         <v>17</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="I4" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="L4" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="M4" s="16">
+      <c r="N4" s="16">
         <v>4</v>
       </c>
-      <c r="N4" s="19">
+      <c r="O4" s="19">
         <v>2</v>
       </c>
-      <c r="O4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="P4" s="9">
+      <c r="Q4" s="9">
         <v>46153</v>
       </c>
-      <c r="Q4" s="21" t="s">
+      <c r="R4" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="R4" s="11">
+      <c r="S4" s="11">
         <v>149</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T4" s="9">
+      <c r="U4" s="9">
         <v>46150</v>
       </c>
-      <c r="U4" s="9" t="s">
+      <c r="V4" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V4" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W4" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y4" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="Y4" s="4"/>
-      <c r="Z4" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z4" s="4"/>
       <c r="AA4" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB4" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD4" s="25" t="s">
+      <c r="AD4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE4" s="25" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="5" spans="1:30" ht="165">
+    <row r="5" spans="1:31" ht="165">
       <c r="A5" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
@@ -1868,79 +1886,82 @@
         <v>17</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="M5" s="16">
+      <c r="N5" s="16">
         <v>4.5999999999999996</v>
       </c>
-      <c r="N5" s="19">
+      <c r="O5" s="19">
         <v>456</v>
       </c>
-      <c r="O5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P5" s="9">
+      <c r="Q5" s="9">
         <v>46153</v>
       </c>
-      <c r="Q5" s="21" t="s">
+      <c r="R5" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="R5" s="11">
+      <c r="S5" s="11">
         <v>178</v>
       </c>
-      <c r="S5" s="3" t="s">
+      <c r="T5" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T5" s="9">
+      <c r="U5" s="9">
         <v>46150</v>
       </c>
-      <c r="U5" s="9" t="s">
+      <c r="V5" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V5" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W5" s="3" t="s">
         <v>26</v>
       </c>
       <c r="X5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y5" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="Z5" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="AA5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB5" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD5" s="25" t="s">
+      <c r="AD5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE5" s="25" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:30" ht="75">
+    <row r="6" spans="1:31" ht="75">
       <c r="A6" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
@@ -1958,77 +1979,80 @@
         <v>17</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="I6" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="M6" s="16">
+      <c r="N6" s="16">
         <v>5</v>
       </c>
-      <c r="N6" s="19">
+      <c r="O6" s="19">
         <v>5</v>
       </c>
-      <c r="P6" s="9">
+      <c r="Q6" s="9">
         <v>46153</v>
       </c>
-      <c r="Q6" s="21" t="s">
+      <c r="R6" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="R6" s="11">
+      <c r="S6" s="11">
         <v>89</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="T6" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T6" s="9">
+      <c r="U6" s="9">
         <v>46150</v>
       </c>
-      <c r="U6" s="9" t="s">
+      <c r="V6" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V6" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X6" s="2" t="s">
+      <c r="X6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y6" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="Y6" s="4"/>
-      <c r="Z6" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z6" s="4"/>
       <c r="AA6" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB6" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD6" s="24" t="s">
+      <c r="AD6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE6" s="24" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:30" ht="60">
+    <row r="7" spans="1:31" ht="60">
       <c r="A7" s="6" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve"> Chongker Percy Robot Cat </v>
@@ -2046,80 +2070,83 @@
         <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H7" s="3" t="s">
+      <c r="I7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="M7" s="16">
+      <c r="N7" s="16">
         <v>5</v>
       </c>
-      <c r="N7" s="19">
+      <c r="O7" s="19">
         <v>16</v>
       </c>
-      <c r="O7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="P7" s="9">
+      <c r="Q7" s="9">
         <v>46153</v>
       </c>
-      <c r="Q7" s="21" t="s">
+      <c r="R7" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="R7" s="11">
+      <c r="S7" s="11">
         <v>89</v>
       </c>
-      <c r="S7" s="3" t="s">
+      <c r="T7" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T7" s="9">
+      <c r="U7" s="9">
         <v>46150</v>
       </c>
-      <c r="U7" s="9" t="s">
+      <c r="V7" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V7" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="X7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z7" s="4"/>
       <c r="AA7" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB7" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD7" s="25" t="s">
+      <c r="AD7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE7" s="25" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:30" ht="45">
+    <row r="8" spans="1:31" ht="45">
       <c r="A8" s="6" t="s">
         <v>255</v>
       </c>
@@ -2136,77 +2163,80 @@
         <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="H8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="I8" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="M8" s="16">
+      <c r="N8" s="16">
         <v>5</v>
       </c>
-      <c r="N8" s="19">
+      <c r="O8" s="19">
         <v>10</v>
       </c>
-      <c r="O8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="P8" s="9">
+      <c r="Q8" s="9">
         <v>46161</v>
       </c>
-      <c r="Q8" s="30" t="s">
+      <c r="R8" s="30" t="s">
         <v>263</v>
       </c>
-      <c r="R8" s="11">
+      <c r="S8" s="11">
         <v>109</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="T8" s="9">
+      <c r="U8" s="9">
         <v>46161</v>
       </c>
-      <c r="U8" s="9" t="s">
+      <c r="V8" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>26</v>
       </c>
       <c r="X8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y8" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z8" s="4"/>
       <c r="AA8" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB8" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC8" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD8" s="25" t="s">
+      <c r="AD8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE8" s="25" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:30" ht="60">
+    <row r="9" spans="1:31" ht="60">
       <c r="A9" s="6" t="str">
         <f t="shared" ref="A9:A28" si="1">_xlfn.CONCAT(B9, " ", C9)</f>
         <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
@@ -2224,76 +2254,79 @@
         <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M9" s="16">
+      <c r="N9" s="16">
         <v>4.5</v>
       </c>
-      <c r="N9" s="19">
+      <c r="O9" s="19">
         <v>72</v>
       </c>
-      <c r="O9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P9" s="9">
+      <c r="Q9" s="9">
         <v>46149</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="R9" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="R9" s="11">
+      <c r="S9" s="11">
         <v>179</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="T9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="T9" s="9">
+      <c r="U9" s="9">
         <v>46152</v>
       </c>
-      <c r="U9" s="9" t="s">
+      <c r="V9" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y9" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD9" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE9" s="25" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="10" spans="1:30" ht="60">
+    <row r="10" spans="1:31" ht="60">
       <c r="A10" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
@@ -2311,76 +2344,79 @@
         <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="3" t="s">
+      <c r="I10" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M10" s="16">
+      <c r="N10" s="16">
         <v>5</v>
       </c>
-      <c r="N10" s="19">
+      <c r="O10" s="19">
         <v>42</v>
       </c>
-      <c r="O10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P10" s="9">
+      <c r="Q10" s="9">
         <v>46149</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="R10" s="11">
+      <c r="S10" s="11">
         <v>359</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="T10" s="9">
+      <c r="U10" s="9">
         <v>46150</v>
       </c>
-      <c r="U10" s="9" t="s">
+      <c r="V10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X10" s="2" t="s">
+      <c r="X10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y10" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD10" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE10" s="25" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="11" spans="1:30" ht="60">
+    <row r="11" spans="1:31" ht="60">
       <c r="A11" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
@@ -2398,76 +2434,79 @@
         <v>16</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="I11" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="M11" s="16">
+      <c r="N11" s="16">
         <v>5</v>
       </c>
-      <c r="N11" s="19">
+      <c r="O11" s="19">
         <v>16</v>
       </c>
-      <c r="O11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P11" s="9">
+      <c r="Q11" s="9">
         <v>46149</v>
       </c>
-      <c r="Q11" s="3" t="s">
+      <c r="R11" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="R11" s="11">
+      <c r="S11" s="11">
         <v>279</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="T11" s="9">
+      <c r="U11" s="9">
         <v>46151</v>
       </c>
-      <c r="U11" s="9" t="s">
+      <c r="V11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="V11" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="Z11" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AA11" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD11" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE11" s="25" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="1:30" ht="60" customHeight="1">
+    <row r="12" spans="1:31" ht="60" customHeight="1">
       <c r="A12" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
@@ -2485,76 +2524,79 @@
         <v>16</v>
       </c>
       <c r="F12" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="L12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="M12" s="16">
+      <c r="N12" s="16">
         <v>4.5</v>
       </c>
-      <c r="N12" s="19">
+      <c r="O12" s="19">
         <v>20</v>
       </c>
-      <c r="O12" s="3" t="s">
+      <c r="P12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P12" s="9">
+      <c r="Q12" s="9">
         <v>46149</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="R12" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="R12" s="11">
+      <c r="S12" s="11">
         <v>789</v>
       </c>
-      <c r="S12" s="3" t="s">
+      <c r="T12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="T12" s="9">
+      <c r="U12" s="9">
         <v>46149</v>
       </c>
-      <c r="U12" s="9" t="s">
+      <c r="V12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y12" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="Z12" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AA12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD12" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="25" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="13" spans="1:30" ht="45.75" thickBot="1">
+    <row r="13" spans="1:31" ht="45.75" thickBot="1">
       <c r="A13" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
@@ -2572,76 +2614,79 @@
         <v>16</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H13" s="3" t="s">
+      <c r="I13" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="M13" s="16">
+      <c r="N13" s="16">
         <v>5</v>
       </c>
-      <c r="N13" s="19">
+      <c r="O13" s="19">
         <v>73</v>
       </c>
-      <c r="O13" s="3" t="s">
+      <c r="P13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="P13" s="9">
+      <c r="Q13" s="9">
         <v>46149</v>
       </c>
-      <c r="Q13" s="21" t="s">
+      <c r="R13" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="R13" s="11">
+      <c r="S13" s="11">
         <v>139</v>
       </c>
-      <c r="S13" s="3" t="s">
+      <c r="T13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="T13" s="9">
+      <c r="U13" s="9">
         <v>46153</v>
       </c>
-      <c r="U13" s="9" t="s">
+      <c r="V13" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V13" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y13" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="Z13" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AA13" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD13" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE13" s="25" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:30" ht="105.75" thickBot="1">
+    <row r="14" spans="1:31" ht="105.75" thickBot="1">
       <c r="A14" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
@@ -2659,77 +2704,80 @@
         <v>17</v>
       </c>
       <c r="F14" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="H14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="J14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="K14" s="29" t="s">
+      <c r="L14" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="L14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="M14" s="16">
+      <c r="N14" s="16">
         <v>4.5</v>
       </c>
-      <c r="N14" s="19">
+      <c r="O14" s="19">
         <v>11640</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P14" s="9">
+      <c r="Q14" s="9">
         <v>46153</v>
       </c>
-      <c r="Q14" s="3" t="s">
+      <c r="R14" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="R14" s="11">
+      <c r="S14" s="11">
         <v>159.99</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T14" s="9">
+      <c r="U14" s="9">
         <v>46150</v>
       </c>
-      <c r="U14" s="9" t="s">
+      <c r="V14" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Y14" s="4"/>
-      <c r="Z14" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z14" s="4"/>
       <c r="AA14" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD14" s="24" t="s">
+      <c r="AC14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE14" s="24" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="15" spans="1:30" ht="105">
+    <row r="15" spans="1:31" ht="105">
       <c r="A15" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
@@ -2747,77 +2795,80 @@
         <v>17</v>
       </c>
       <c r="F15" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="J15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="M15" s="16">
+      <c r="N15" s="16">
         <v>4.5</v>
       </c>
-      <c r="N15" s="19">
+      <c r="O15" s="19">
         <v>11640</v>
       </c>
-      <c r="O15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P15" s="9">
+      <c r="Q15" s="9">
         <v>46153</v>
       </c>
-      <c r="Q15" s="3" t="s">
+      <c r="R15" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="R15" s="11">
+      <c r="S15" s="11">
         <v>159.99</v>
       </c>
-      <c r="S15" s="3" t="s">
+      <c r="T15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T15" s="9">
+      <c r="U15" s="9">
         <v>46150</v>
       </c>
-      <c r="U15" s="9" t="s">
+      <c r="V15" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V15" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Y15" s="4"/>
-      <c r="Z15" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z15" s="4"/>
       <c r="AA15" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD15" s="26" t="s">
+      <c r="AC15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE15" s="26" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="16" spans="1:30" ht="60" customHeight="1">
+    <row r="16" spans="1:31" ht="60" customHeight="1">
       <c r="A16" s="6" t="str">
         <f>_xlfn.CONCAT(B16, " ", C16)</f>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
@@ -2835,77 +2886,80 @@
         <v>17</v>
       </c>
       <c r="F16" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="3" t="s">
+      <c r="I16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="L16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="M16" s="16">
+      <c r="N16" s="16">
         <v>4.5</v>
       </c>
-      <c r="N16" s="19">
+      <c r="O16" s="19">
         <v>11640</v>
       </c>
-      <c r="O16" s="3" t="s">
+      <c r="P16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P16" s="9">
+      <c r="Q16" s="9">
         <v>46150</v>
       </c>
-      <c r="Q16" s="3" t="s">
+      <c r="R16" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="R16" s="11">
+      <c r="S16" s="11">
         <v>159.99</v>
       </c>
-      <c r="S16" s="3" t="s">
+      <c r="T16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T16" s="9">
+      <c r="U16" s="9">
         <v>46150</v>
       </c>
-      <c r="U16" s="9" t="s">
+      <c r="V16" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V16" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="X16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z16" s="4"/>
       <c r="AA16" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD16" s="31" t="s">
+      <c r="AC16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE16" s="31" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="17" spans="1:30" ht="60">
+    <row r="17" spans="1:31" ht="60">
       <c r="A17" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
@@ -2923,77 +2977,80 @@
         <v>17</v>
       </c>
       <c r="F17" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="H17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H17" s="3" t="s">
+      <c r="I17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="L17" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="M17" s="16">
+      <c r="N17" s="16">
         <v>4.3</v>
       </c>
-      <c r="N17" s="19">
+      <c r="O17" s="19">
         <v>5163</v>
       </c>
-      <c r="O17" s="3" t="s">
+      <c r="P17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P17" s="9">
+      <c r="Q17" s="9">
         <v>46150</v>
       </c>
-      <c r="Q17" s="3" t="s">
+      <c r="R17" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="R17" s="11">
+      <c r="S17" s="11">
         <v>179</v>
       </c>
-      <c r="S17" s="3" t="s">
+      <c r="T17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T17" s="9">
+      <c r="U17" s="9">
         <v>46150</v>
       </c>
-      <c r="U17" s="9" t="s">
+      <c r="V17" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y17" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="Y17" s="4"/>
-      <c r="Z17" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z17" s="4"/>
       <c r="AA17" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD17" s="26" t="s">
+      <c r="AC17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE17" s="26" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="18" spans="1:30" ht="60">
+    <row r="18" spans="1:31" ht="60">
       <c r="A18" s="6" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
@@ -3011,77 +3068,80 @@
         <v>17</v>
       </c>
       <c r="F18" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="H18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="I18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="J18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="M18" s="16">
+      <c r="N18" s="16">
         <v>4.3</v>
       </c>
-      <c r="N18" s="19">
+      <c r="O18" s="19">
         <v>5164</v>
       </c>
-      <c r="O18" s="3" t="s">
+      <c r="P18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P18" s="9">
+      <c r="Q18" s="9">
         <v>46153</v>
       </c>
-      <c r="Q18" s="3" t="s">
+      <c r="R18" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="R18" s="11">
+      <c r="S18" s="11">
         <v>179</v>
       </c>
-      <c r="S18" s="3" t="s">
+      <c r="T18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T18" s="9">
+      <c r="U18" s="9">
         <v>46150</v>
       </c>
-      <c r="U18" s="9" t="s">
+      <c r="V18" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X18" s="2" t="s">
+      <c r="X18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y18" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="Y18" s="4"/>
-      <c r="Z18" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="Z18" s="4"/>
       <c r="AA18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD18" s="26" t="s">
+      <c r="AC18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE18" s="26" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="19" spans="1:30" ht="74.25" customHeight="1">
+    <row r="19" spans="1:31" ht="74.25" customHeight="1">
       <c r="A19" s="6" t="str">
         <f>_xlfn.CONCAT(B19, " ", C19)</f>
         <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
@@ -3099,76 +3159,79 @@
         <v>17</v>
       </c>
       <c r="F19" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H19" s="3" t="s">
+      <c r="I19" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I19" s="3" t="s">
+      <c r="J19" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="J19" s="3" t="s">
+      <c r="K19" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="L19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L19" s="3" t="s">
+      <c r="M19" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="M19" s="16">
+      <c r="N19" s="16">
         <v>3</v>
       </c>
-      <c r="N19" s="19">
+      <c r="O19" s="19">
         <v>80</v>
       </c>
-      <c r="O19" s="3" t="s">
+      <c r="P19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P19" s="9">
+      <c r="Q19" s="9">
         <v>46151</v>
       </c>
-      <c r="Q19" s="3" t="s">
+      <c r="R19" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="R19" s="11">
+      <c r="S19" s="11">
         <v>25.99</v>
       </c>
-      <c r="S19" s="3" t="s">
+      <c r="T19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T19" s="9">
+      <c r="U19" s="9">
         <v>46151</v>
       </c>
-      <c r="U19" s="9" t="s">
+      <c r="V19" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V19" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y19" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="Z19" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="AA19" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB19" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD19" s="24" t="s">
+      <c r="AC19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="24" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="20" spans="1:30" ht="150">
+    <row r="20" spans="1:31" ht="150">
       <c r="A20" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Furby DJ Furby</v>
@@ -3186,76 +3249,79 @@
         <v>16</v>
       </c>
       <c r="F20" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="J20" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="L20" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L20" s="3" t="s">
+      <c r="M20" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="M20" s="16">
+      <c r="N20" s="16">
         <v>4.8</v>
       </c>
-      <c r="N20" s="19">
+      <c r="O20" s="19">
         <v>772</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="P20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P20" s="9">
+      <c r="Q20" s="9">
         <v>46150</v>
       </c>
-      <c r="Q20" s="3" t="s">
+      <c r="R20" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="R20" s="11">
+      <c r="S20" s="11">
         <v>50.11</v>
       </c>
-      <c r="S20" s="3" t="s">
+      <c r="T20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T20" s="9">
+      <c r="U20" s="9">
         <v>46150</v>
       </c>
-      <c r="U20" s="9" t="s">
+      <c r="V20" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X20" s="2" t="s">
+      <c r="X20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y20" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>27</v>
       </c>
       <c r="AB20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC20" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="AD20" s="24" t="s">
+      <c r="AE20" s="24" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="21" spans="1:30" ht="165">
+    <row r="21" spans="1:31" ht="165">
       <c r="A21" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Loona Robot Pet Dog</v>
@@ -3273,73 +3339,76 @@
         <v>16</v>
       </c>
       <c r="F21" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="H21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H21" s="3" t="s">
+      <c r="I21" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="L21" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="M21" s="16">
+      <c r="N21" s="16">
         <v>4.2</v>
       </c>
-      <c r="N21" s="19">
+      <c r="O21" s="19">
         <v>1199</v>
       </c>
-      <c r="O21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P21" s="9">
+      <c r="Q21" s="9">
         <v>46150</v>
       </c>
-      <c r="Q21" s="3" t="s">
+      <c r="R21" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="R21" s="11">
+      <c r="S21" s="11">
         <v>499</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="T21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T21" s="9">
+      <c r="U21" s="9">
         <v>46150</v>
       </c>
-      <c r="U21" s="9" t="s">
+      <c r="V21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X21" s="2" t="s">
+      <c r="X21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y21" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB21" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC21" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="AD21" s="24" t="s">
+      <c r="AE21" s="24" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:30" ht="60">
+    <row r="22" spans="1:31" ht="60">
       <c r="A22" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Perfect Petzzz Grey Tabby Cat</v>
@@ -3357,73 +3426,76 @@
         <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="3" t="s">
+      <c r="H22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="3" t="s">
+      <c r="I22" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="L22" s="3" t="s">
+      <c r="M22" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="M22" s="16">
+      <c r="N22" s="16">
         <v>4.3</v>
       </c>
-      <c r="N22" s="19">
+      <c r="O22" s="19">
         <v>848</v>
       </c>
-      <c r="O22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P22" s="9">
+      <c r="Q22" s="9">
         <v>46150</v>
       </c>
-      <c r="Q22" s="3" t="s">
+      <c r="R22" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="R22" s="11">
+      <c r="S22" s="11">
         <v>44.45</v>
       </c>
-      <c r="S22" s="3" t="s">
+      <c r="T22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T22" s="9">
+      <c r="U22" s="9">
         <v>46150</v>
       </c>
-      <c r="U22" s="9" t="s">
+      <c r="V22" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y22" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD22" s="24" t="s">
+      <c r="AB22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE22" s="24" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="23" spans="1:30" ht="60" customHeight="1">
+    <row r="23" spans="1:31" ht="60" customHeight="1">
       <c r="A23" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Border Collie</v>
@@ -3441,73 +3513,76 @@
         <v>17</v>
       </c>
       <c r="F23" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="H23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="L23" s="3" t="s">
+      <c r="M23" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="M23" s="16">
+      <c r="N23" s="16">
         <v>4.3</v>
       </c>
-      <c r="N23" s="19">
+      <c r="O23" s="19">
         <v>403</v>
       </c>
-      <c r="O23" s="3" t="s">
+      <c r="P23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P23" s="9">
+      <c r="Q23" s="9">
         <v>46150</v>
       </c>
-      <c r="Q23" s="3" t="s">
+      <c r="R23" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="R23" s="11">
+      <c r="S23" s="11">
         <v>44.45</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="T23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T23" s="9">
+      <c r="U23" s="9">
         <v>46150</v>
       </c>
-      <c r="U23" s="9" t="s">
+      <c r="V23" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y23" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD23" s="24" t="s">
+      <c r="AB23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="24" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="24" spans="1:30" ht="60" customHeight="1">
+    <row r="24" spans="1:31" ht="60" customHeight="1">
       <c r="A24" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Chocolate Lab</v>
@@ -3525,73 +3600,76 @@
         <v>17</v>
       </c>
       <c r="F24" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="H24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="I24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="I24" s="3" t="s">
+      <c r="J24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="J24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="L24" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="L24" s="3" t="s">
+      <c r="M24" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="M24" s="16">
+      <c r="N24" s="16">
         <v>4.3</v>
       </c>
-      <c r="N24" s="19">
+      <c r="O24" s="19">
         <v>553</v>
       </c>
-      <c r="O24" s="3" t="s">
+      <c r="P24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P24" s="9">
+      <c r="Q24" s="9">
         <v>46150</v>
       </c>
-      <c r="Q24" s="3" t="s">
+      <c r="R24" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="R24" s="11">
+      <c r="S24" s="11">
         <v>44.45</v>
       </c>
-      <c r="S24" s="3" t="s">
+      <c r="T24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T24" s="9">
+      <c r="U24" s="9">
         <v>46150</v>
       </c>
-      <c r="U24" s="9" t="s">
+      <c r="V24" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD24" s="24" t="s">
+      <c r="AB24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="24" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="25" spans="1:30" ht="60" customHeight="1">
+    <row r="25" spans="1:31" ht="60" customHeight="1">
       <c r="A25" s="6" t="str">
         <f>_xlfn.CONCAT(B25, " ", C25)</f>
         <v>Perfect Petzzz Original Plush White Cat</v>
@@ -3609,73 +3687,76 @@
         <v>17</v>
       </c>
       <c r="F25" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="H25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="I25" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="J25" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="L25" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="M25" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="M25" s="16">
+      <c r="N25" s="16">
         <v>4</v>
       </c>
-      <c r="N25" s="19">
+      <c r="O25" s="19">
         <v>54</v>
       </c>
-      <c r="O25" s="3" t="s">
+      <c r="P25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P25" s="9">
+      <c r="Q25" s="9">
         <v>46150</v>
       </c>
-      <c r="Q25" s="3" t="s">
+      <c r="R25" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="R25" s="11">
+      <c r="S25" s="11">
         <v>53.9</v>
       </c>
-      <c r="S25" s="3" t="s">
+      <c r="T25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T25" s="9">
+      <c r="U25" s="9">
         <v>46150</v>
       </c>
-      <c r="U25" s="9" t="s">
+      <c r="V25" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V25" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y25" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z25" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="AA25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD25" s="24" t="s">
+      <c r="AB25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE25" s="24" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="26" spans="1:30" ht="27.75" customHeight="1">
+    <row r="26" spans="1:31" ht="27.75" customHeight="1">
       <c r="A26" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Perfect Petzzz Original Siamese Cat</v>
@@ -3693,73 +3774,76 @@
         <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="L26" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L26" s="3" t="s">
+      <c r="M26" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="M26" s="16">
+      <c r="N26" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="N26" s="19">
+      <c r="O26" s="19">
         <v>16</v>
       </c>
-      <c r="O26" s="3" t="s">
+      <c r="P26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P26" s="9">
+      <c r="Q26" s="9">
         <v>46150</v>
       </c>
-      <c r="Q26" s="3" t="s">
+      <c r="R26" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="R26" s="11">
+      <c r="S26" s="11">
         <v>53.9</v>
       </c>
-      <c r="S26" s="3" t="s">
+      <c r="T26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T26" s="9">
+      <c r="U26" s="9">
         <v>46150</v>
       </c>
-      <c r="U26" s="9" t="s">
+      <c r="V26" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="X26" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>27</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AD26" s="24" t="s">
+      <c r="AB26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE26" s="24" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="27" spans="1:30" ht="150">
+    <row r="27" spans="1:31" ht="150">
       <c r="A27" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Ropet KAMOMO</v>
@@ -3777,76 +3861,79 @@
         <v>16</v>
       </c>
       <c r="F27" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="H27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H27" s="3" t="s">
+      <c r="I27" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="L27" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="L27" s="3" t="s">
+      <c r="M27" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="M27" s="16">
+      <c r="N27" s="16">
         <v>4.3</v>
       </c>
-      <c r="N27" s="19">
+      <c r="O27" s="19">
         <v>17</v>
       </c>
-      <c r="O27" s="3" t="s">
+      <c r="P27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P27" s="9">
+      <c r="Q27" s="9">
         <v>46152</v>
       </c>
-      <c r="Q27" s="3" t="s">
+      <c r="R27" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="R27" s="11">
+      <c r="S27" s="11">
         <v>349</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="T27" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="T27" s="9">
+      <c r="U27" s="9">
         <v>46163</v>
       </c>
-      <c r="U27" s="9" t="s">
+      <c r="V27" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X27" s="2" t="s">
+      <c r="X27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y27" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>26</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AD27" s="24" t="s">
+      <c r="AC27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE27" s="24" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="28" spans="1:30" ht="165">
+    <row r="28" spans="1:31" ht="165">
       <c r="A28" s="6" t="str">
         <f t="shared" si="1"/>
         <v>Ruko 18011 Smart Robot Dog</v>
@@ -3864,75 +3951,78 @@
         <v>16</v>
       </c>
       <c r="F28" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="I28" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="I28" s="3" t="s">
+      <c r="J28" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="L28" s="3" t="s">
+      <c r="M28" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="M28" s="16">
+      <c r="N28" s="16">
         <v>4.4000000000000004</v>
       </c>
-      <c r="N28" s="19">
+      <c r="O28" s="19">
         <v>283</v>
       </c>
-      <c r="O28" s="3" t="s">
+      <c r="P28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P28" s="9">
+      <c r="Q28" s="9">
         <v>46150</v>
       </c>
-      <c r="Q28" s="3" t="s">
+      <c r="R28" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="R28" s="11">
+      <c r="S28" s="11">
         <v>69.989999999999995</v>
       </c>
-      <c r="S28" s="3" t="s">
+      <c r="T28" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T28" s="9">
+      <c r="U28" s="9">
         <v>46150</v>
       </c>
-      <c r="U28" s="9" t="s">
+      <c r="V28" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="V28" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="W28" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="X28" s="2" t="s">
+      <c r="X28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Y28" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="Z28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AD28" s="24" t="s">
+      <c r="AA28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE28" s="24" t="s">
         <v>287</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AD28" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD28">
+  <autoFilter ref="A1:AE28" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AE28">
       <sortCondition ref="A1:A28"/>
     </sortState>
   </autoFilter>
@@ -3942,18 +4032,24 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{33C992CF-22D4-4E94-80E1-2C06CE97D7D6}">
           <x14:formula1>
             <xm:f>Lists!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:U1048576</xm:sqref>
+          <xm:sqref>V1:V1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37BE27F9-E75E-4C54-9192-7DED9B8091B0}">
           <x14:formula1>
             <xm:f>Lists!$A$7:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>W1:W1048576</xm:sqref>
+          <xm:sqref>X1:X1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FE3F9960-CC34-4E23-8422-16257A51BC9B}">
+          <x14:formula1>
+            <xm:f>Lists!$A$12:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>F1:F1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3984,7 +4080,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AABE60FF-1DCC-4956-9447-8879E50144AD}">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.42578125" customWidth="1"/>
@@ -4013,6 +4109,16 @@
     <row r="8" spans="1:1">
       <c r="A8" t="s">
         <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7694B779-0410-4F59-8596-8AA8E412B177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F1A7FA-56ED-4FB7-8679-F757E36005E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{61C7E0C1-FB54-4384-9680-235C84117D88}"/>
   </bookViews>
@@ -19,7 +19,7 @@
     <sheet name="Maybe Later" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AE$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Product Matrix'!$A$1:$AH$27</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="772" uniqueCount="301">
   <si>
     <t xml:space="preserve"> Enabot</t>
   </si>
@@ -921,6 +921,33 @@
   </si>
   <si>
     <t>Mobile</t>
+  </si>
+  <si>
+    <t>Suggested Age Range</t>
+  </si>
+  <si>
+    <t>Age Range Source</t>
+  </si>
+  <si>
+    <t>3+</t>
+  </si>
+  <si>
+    <t>Chongerker Web Site</t>
+  </si>
+  <si>
+    <t>5+</t>
+  </si>
+  <si>
+    <t>6+</t>
+  </si>
+  <si>
+    <t>Amazon and Hasbro</t>
+  </si>
+  <si>
+    <t>Keyi Site</t>
+  </si>
+  <si>
+    <t>Sound Level Control</t>
   </si>
 </sst>
 </file>
@@ -1049,7 +1076,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1142,6 +1169,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1165,15 +1201,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>63</xdr:row>
+      <xdr:row>62</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>27</xdr:col>
       <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>64</xdr:row>
+      <xdr:row>63</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1544,7 +1580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-  <dimension ref="A1:AE28"/>
+  <dimension ref="A1:AH27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="32.140625" style="6" customWidth="1"/>
@@ -1554,32 +1590,34 @@
     <col min="5" max="6" width="17.85546875" style="3" customWidth="1"/>
     <col min="7" max="7" width="10.28515625" style="3" customWidth="1"/>
     <col min="8" max="8" width="9.7109375" style="3" customWidth="1"/>
-    <col min="9" max="9" width="52.140625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="15" style="3" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="3" customWidth="1"/>
-    <col min="13" max="13" width="15.5703125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="10.7109375" style="16" customWidth="1"/>
-    <col min="15" max="15" width="10.7109375" style="19" customWidth="1"/>
-    <col min="16" max="16" width="10.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="13.28515625" style="9" customWidth="1"/>
-    <col min="18" max="18" width="80.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.85546875" style="11" customWidth="1"/>
-    <col min="20" max="20" width="10" style="3" customWidth="1"/>
-    <col min="21" max="22" width="13.28515625" style="9" customWidth="1"/>
-    <col min="23" max="23" width="6.140625" style="3" customWidth="1"/>
-    <col min="24" max="24" width="9.140625" style="3" customWidth="1"/>
-    <col min="25" max="25" width="54.140625" style="3" customWidth="1"/>
-    <col min="26" max="26" width="32.140625" style="6" customWidth="1"/>
-    <col min="27" max="27" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.5703125" style="3" customWidth="1"/>
-    <col min="31" max="31" width="200.7109375" style="25" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="3"/>
+    <col min="9" max="9" width="18.140625" style="33" customWidth="1"/>
+    <col min="10" max="11" width="18.140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="52.140625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="15" style="3" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" style="16" customWidth="1"/>
+    <col min="18" max="18" width="10.7109375" style="19" customWidth="1"/>
+    <col min="19" max="19" width="10.7109375" style="3" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" style="9" customWidth="1"/>
+    <col min="21" max="21" width="80.7109375" style="3" customWidth="1"/>
+    <col min="22" max="22" width="8.85546875" style="11" customWidth="1"/>
+    <col min="23" max="23" width="10" style="3" customWidth="1"/>
+    <col min="24" max="25" width="13.28515625" style="9" customWidth="1"/>
+    <col min="26" max="26" width="6.140625" style="3" customWidth="1"/>
+    <col min="27" max="27" width="9.140625" style="3" customWidth="1"/>
+    <col min="28" max="28" width="54.140625" style="3" customWidth="1"/>
+    <col min="29" max="29" width="32.140625" style="6" customWidth="1"/>
+    <col min="30" max="30" width="9.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="15.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="18.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="10.5703125" style="3" customWidth="1"/>
+    <col min="34" max="34" width="200.7109375" style="25" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" s="6" customFormat="1" ht="30">
+    <row r="1" spans="1:34" s="6" customFormat="1" ht="30">
       <c r="A1" s="6" t="s">
         <v>180</v>
       </c>
@@ -1604,85 +1642,94 @@
       <c r="H1" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="L1" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="M1" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="N1" s="15" t="s">
+      <c r="Q1" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="R1" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="U1" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="W1" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="AE1" s="23" t="s">
+      <c r="AH1" s="23" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:34">
       <c r="A2" s="6" t="str">
-        <f t="shared" ref="A2:A7" si="0">_xlfn.CONCAT(B2, " ", C2)</f>
+        <f>_xlfn.CONCAT(B2, " ", C2)</f>
         <v xml:space="preserve"> </v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="60">
+    <row r="3" spans="1:34" ht="60">
       <c r="A3" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B3, " ", C3)</f>
         <v xml:space="preserve"> Chongker Breathing Red Panda Plush </v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1706,77 +1753,86 @@
       <c r="H3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K3" s="3">
+        <v>5</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="N3" s="16">
+      <c r="Q3" s="16">
         <v>5</v>
       </c>
-      <c r="O3" s="19">
+      <c r="R3" s="19">
         <v>2</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="Q3" s="9">
+      <c r="T3" s="9">
         <v>46153</v>
       </c>
-      <c r="R3" s="21" t="s">
+      <c r="U3" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="S3" s="11">
+      <c r="V3" s="11">
         <v>119</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="U3" s="9">
+      <c r="X3" s="9">
         <v>46150</v>
       </c>
-      <c r="V3" s="9" t="s">
+      <c r="Y3" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y3" s="2" t="s">
+      <c r="Z3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="5"/>
-      <c r="AA3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AC3" s="5"/>
       <c r="AD3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE3" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH3" s="24" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="4" spans="1:31" ht="75">
+    <row r="4" spans="1:34" ht="75">
       <c r="A4" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B4, " ", C4)</f>
         <v xml:space="preserve"> Chongker MateCat 1.1 </v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1800,77 +1856,86 @@
       <c r="H4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K4" s="3">
+        <v>4</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="N4" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="O4" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="N4" s="16">
+      <c r="Q4" s="16">
         <v>4</v>
       </c>
-      <c r="O4" s="19">
+      <c r="R4" s="19">
         <v>2</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="S4" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="Q4" s="9">
+      <c r="T4" s="9">
         <v>46153</v>
       </c>
-      <c r="R4" s="21" t="s">
+      <c r="U4" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="S4" s="11">
+      <c r="V4" s="11">
         <v>149</v>
       </c>
-      <c r="T4" s="3" t="s">
+      <c r="W4" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="U4" s="9">
+      <c r="X4" s="9">
         <v>46150</v>
       </c>
-      <c r="V4" s="9" t="s">
+      <c r="Y4" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y4" s="3" t="s">
+      <c r="Z4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB4" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC4" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AC4" s="4"/>
       <c r="AD4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE4" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH4" s="25" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="5" spans="1:31" ht="165">
+    <row r="5" spans="1:34" ht="165">
       <c r="A5" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B5, " ", C5)</f>
         <v xml:space="preserve"> Chongker MateCat Pro </v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1894,76 +1959,85 @@
       <c r="H5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K5" s="3">
+        <v>5</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="M5" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="N5" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="O5" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="N5" s="16">
+      <c r="Q5" s="16">
         <v>4.5999999999999996</v>
       </c>
-      <c r="O5" s="19">
+      <c r="R5" s="19">
         <v>456</v>
       </c>
-      <c r="P5" s="3" t="s">
+      <c r="S5" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q5" s="9">
+      <c r="T5" s="9">
         <v>46153</v>
       </c>
-      <c r="R5" s="21" t="s">
+      <c r="U5" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="S5" s="11">
+      <c r="V5" s="11">
         <v>178</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="W5" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="U5" s="9">
+      <c r="X5" s="9">
         <v>46150</v>
       </c>
-      <c r="V5" s="9" t="s">
+      <c r="Y5" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y5" s="3" t="s">
+      <c r="Z5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB5" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="AA5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC5" s="3" t="s">
-        <v>26</v>
-      </c>
       <c r="AD5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE5" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH5" s="25" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="75">
+    <row r="6" spans="1:34" ht="75">
       <c r="A6" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B6, " ", C6)</f>
         <v xml:space="preserve"> Chongker Percy 1.1 Robotic Companion Dog </v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1987,74 +2061,83 @@
       <c r="H6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K6" s="3">
+        <v>5</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="N6" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="O6" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="N6" s="16">
+      <c r="Q6" s="16">
         <v>5</v>
       </c>
-      <c r="O6" s="19">
+      <c r="R6" s="19">
         <v>5</v>
       </c>
-      <c r="Q6" s="9">
+      <c r="T6" s="9">
         <v>46153</v>
       </c>
-      <c r="R6" s="21" t="s">
+      <c r="U6" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="S6" s="11">
+      <c r="V6" s="11">
         <v>89</v>
       </c>
-      <c r="T6" s="3" t="s">
+      <c r="W6" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="U6" s="9">
+      <c r="X6" s="9">
         <v>46150</v>
       </c>
-      <c r="V6" s="9" t="s">
+      <c r="Y6" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="W6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y6" s="2" t="s">
+      <c r="Z6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB6" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC6" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AC6" s="4"/>
       <c r="AD6" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE6" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH6" s="24" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:31" ht="60">
+    <row r="7" spans="1:34" ht="60">
       <c r="A7" s="6" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(B7, " ", C7)</f>
         <v xml:space="preserve"> Chongker Percy Robot Cat </v>
       </c>
       <c r="B7" s="3" t="s">
@@ -2078,75 +2161,84 @@
       <c r="H7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K7" s="3">
+        <v>5</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="N7" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="O7" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="N7" s="16">
+      <c r="Q7" s="16">
         <v>5</v>
       </c>
-      <c r="O7" s="19">
+      <c r="R7" s="19">
         <v>16</v>
       </c>
-      <c r="P7" s="3" t="s">
+      <c r="S7" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="Q7" s="9">
+      <c r="T7" s="9">
         <v>46153</v>
       </c>
-      <c r="R7" s="21" t="s">
+      <c r="U7" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="S7" s="11">
+      <c r="V7" s="11">
         <v>89</v>
       </c>
-      <c r="T7" s="3" t="s">
+      <c r="W7" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="U7" s="9">
+      <c r="X7" s="9">
         <v>46150</v>
       </c>
-      <c r="V7" s="9" t="s">
+      <c r="Y7" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="W7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y7" s="3" t="s">
+      <c r="Z7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC7" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AC7" s="4"/>
       <c r="AD7" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE7" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH7" s="25" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="45">
+    <row r="8" spans="1:34" ht="45">
       <c r="A8" s="6" t="s">
         <v>255</v>
       </c>
@@ -2171,74 +2263,83 @@
       <c r="H8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="K8" s="3">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="N8" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="O8" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="N8" s="16">
+      <c r="Q8" s="16">
         <v>5</v>
       </c>
-      <c r="O8" s="19">
+      <c r="R8" s="19">
         <v>10</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="S8" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="Q8" s="9">
+      <c r="T8" s="9">
         <v>46161</v>
       </c>
-      <c r="R8" s="30" t="s">
+      <c r="U8" s="30" t="s">
         <v>263</v>
       </c>
-      <c r="S8" s="11">
+      <c r="V8" s="11">
         <v>109</v>
       </c>
-      <c r="T8" s="3" t="s">
+      <c r="W8" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="U8" s="9">
+      <c r="X8" s="9">
         <v>46161</v>
       </c>
-      <c r="V8" s="9" t="s">
+      <c r="Y8" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y8" s="3" t="s">
+      <c r="Z8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB8" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>26</v>
-      </c>
+      <c r="AC8" s="4"/>
       <c r="AD8" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE8" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH8" s="25" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="9" spans="1:31" ht="60">
+    <row r="9" spans="1:34" ht="60">
       <c r="A9" s="6" t="str">
-        <f t="shared" ref="A9:A28" si="1">_xlfn.CONCAT(B9, " ", C9)</f>
+        <f>_xlfn.CONCAT(B9, " ", C9)</f>
         <v xml:space="preserve"> Enabot EBO Air 2 FamilyBot </v>
       </c>
       <c r="B9" s="3" t="s">
@@ -2262,73 +2363,82 @@
       <c r="H9" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K9" s="3">
+        <v>4</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="N9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="O9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N9" s="16">
+      <c r="Q9" s="16">
         <v>4.5</v>
       </c>
-      <c r="O9" s="19">
+      <c r="R9" s="19">
         <v>72</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="S9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q9" s="9">
+      <c r="T9" s="9">
         <v>46149</v>
       </c>
-      <c r="R9" s="3" t="s">
+      <c r="U9" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="S9" s="11">
+      <c r="V9" s="11">
         <v>179</v>
       </c>
-      <c r="T9" s="3" t="s">
+      <c r="W9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U9" s="9">
+      <c r="X9" s="9">
         <v>46152</v>
       </c>
-      <c r="V9" s="9" t="s">
+      <c r="Y9" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y9" s="2" t="s">
+      <c r="Z9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB9" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE9" s="25" t="s">
+      <c r="AD9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH9" s="25" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="10" spans="1:31" ht="60">
+    <row r="10" spans="1:34" ht="60">
       <c r="A10" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(B10, " ", C10)</f>
         <v xml:space="preserve"> Enabot EBO Air 2 Plus FamilyBot </v>
       </c>
       <c r="B10" s="3" t="s">
@@ -2352,73 +2462,82 @@
       <c r="H10" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="3">
+        <v>4</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="M10" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="N10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="O10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N10" s="16">
+      <c r="Q10" s="16">
         <v>5</v>
       </c>
-      <c r="O10" s="19">
+      <c r="R10" s="19">
         <v>42</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="S10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q10" s="9">
+      <c r="T10" s="9">
         <v>46149</v>
       </c>
-      <c r="R10" s="3" t="s">
+      <c r="U10" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="S10" s="11">
+      <c r="V10" s="11">
         <v>359</v>
       </c>
-      <c r="T10" s="3" t="s">
+      <c r="W10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U10" s="9">
+      <c r="X10" s="9">
         <v>46150</v>
       </c>
-      <c r="V10" s="9" t="s">
+      <c r="Y10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y10" s="2" t="s">
+      <c r="Z10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB10" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB10" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE10" s="25" t="s">
+      <c r="AD10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE10" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH10" s="25" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="11" spans="1:31" ht="60">
+    <row r="11" spans="1:34" ht="60">
       <c r="A11" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(B11, " ", C11)</f>
         <v xml:space="preserve"> Enabot EBO Air 2S FamilyBot </v>
       </c>
       <c r="B11" s="3" t="s">
@@ -2442,73 +2561,82 @@
       <c r="H11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="3">
+        <v>4</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="M11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="N11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="O11" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="N11" s="16">
+      <c r="Q11" s="16">
         <v>5</v>
       </c>
-      <c r="O11" s="19">
+      <c r="R11" s="19">
         <v>16</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="S11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q11" s="9">
+      <c r="T11" s="9">
         <v>46149</v>
       </c>
-      <c r="R11" s="3" t="s">
+      <c r="U11" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="S11" s="11">
+      <c r="V11" s="11">
         <v>279</v>
       </c>
-      <c r="T11" s="3" t="s">
+      <c r="W11" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U11" s="9">
+      <c r="X11" s="9">
         <v>46151</v>
       </c>
-      <c r="V11" s="9" t="s">
+      <c r="Y11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="W11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y11" s="2" t="s">
+      <c r="Z11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB11" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="AA11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB11" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC11" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE11" s="25" t="s">
+      <c r="AD11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE11" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH11" s="25" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="12" spans="1:31" ht="60" customHeight="1">
+    <row r="12" spans="1:34" ht="60" customHeight="1">
       <c r="A12" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(B12, " ", C12)</f>
         <v xml:space="preserve"> Enabot EBO X FamilyBot</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -2532,73 +2660,82 @@
       <c r="H12" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K12" s="3">
+        <v>4</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="M12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K12" s="3" t="s">
+      <c r="N12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="P12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="N12" s="16">
+      <c r="Q12" s="16">
         <v>4.5</v>
       </c>
-      <c r="O12" s="19">
+      <c r="R12" s="19">
         <v>20</v>
       </c>
-      <c r="P12" s="3" t="s">
+      <c r="S12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q12" s="9">
+      <c r="T12" s="9">
         <v>46149</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="U12" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="S12" s="11">
+      <c r="V12" s="11">
         <v>789</v>
       </c>
-      <c r="T12" s="3" t="s">
+      <c r="W12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U12" s="9">
+      <c r="X12" s="9">
         <v>46149</v>
       </c>
-      <c r="V12" s="9" t="s">
+      <c r="Y12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="W12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y12" s="2" t="s">
+      <c r="Z12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB12" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="AA12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB12" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC12" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE12" s="25" t="s">
+      <c r="AD12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH12" s="25" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="13" spans="1:31" ht="45.75" thickBot="1">
+    <row r="13" spans="1:34" ht="45.75" thickBot="1">
       <c r="A13" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(B13, " ", C13)</f>
         <v xml:space="preserve"> Enabot ROLA Mini Pet Monitor</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -2622,73 +2759,82 @@
       <c r="H13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="3">
+        <v>4</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="M13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="N13" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="L13" s="3" t="s">
+      <c r="O13" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="P13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="N13" s="16">
+      <c r="Q13" s="16">
         <v>5</v>
       </c>
-      <c r="O13" s="19">
+      <c r="R13" s="19">
         <v>73</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="S13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="Q13" s="9">
+      <c r="T13" s="9">
         <v>46149</v>
       </c>
-      <c r="R13" s="21" t="s">
+      <c r="U13" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="S13" s="11">
+      <c r="V13" s="11">
         <v>139</v>
       </c>
-      <c r="T13" s="3" t="s">
+      <c r="W13" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U13" s="9">
+      <c r="X13" s="9">
         <v>46153</v>
       </c>
-      <c r="V13" s="9" t="s">
+      <c r="Y13" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y13" s="2" t="s">
+      <c r="Z13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB13" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="AA13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE13" s="25" t="s">
+      <c r="AD13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE13" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH13" s="25" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="14" spans="1:31" ht="105.75" thickBot="1">
+    <row r="14" spans="1:34" ht="105.75" thickBot="1">
       <c r="A14" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(B14, " ", C14)</f>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Orange Tabby</v>
       </c>
       <c r="B14" s="3" t="s">
@@ -2712,74 +2858,83 @@
       <c r="H14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K14" s="3">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="M14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="N14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="L14" s="29" t="s">
+      <c r="O14" s="29" t="s">
         <v>111</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="N14" s="16">
+      <c r="Q14" s="16">
         <v>4.5</v>
       </c>
-      <c r="O14" s="19">
+      <c r="R14" s="19">
         <v>11640</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q14" s="9">
+      <c r="T14" s="9">
         <v>46153</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="U14" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="S14" s="11">
+      <c r="V14" s="11">
         <v>159.99</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U14" s="9">
+      <c r="X14" s="9">
         <v>46150</v>
       </c>
-      <c r="V14" s="9" t="s">
+      <c r="Y14" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y14" s="2" t="s">
+      <c r="Z14" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE14" s="24" t="s">
+      <c r="AC14" s="4"/>
+      <c r="AD14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH14" s="24" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="15" spans="1:31" ht="105">
+    <row r="15" spans="1:34" ht="105">
       <c r="A15" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(B15, " ", C15)</f>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Silver</v>
       </c>
       <c r="B15" s="3" t="s">
@@ -2803,72 +2958,81 @@
       <c r="H15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="3" t="s">
+      <c r="I15" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K15" s="3">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="M15" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="N15" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="L15" s="3" t="s">
+      <c r="O15" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="M15" s="3" t="s">
+      <c r="P15" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="N15" s="16">
+      <c r="Q15" s="16">
         <v>4.5</v>
       </c>
-      <c r="O15" s="19">
+      <c r="R15" s="19">
         <v>11640</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="S15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q15" s="9">
+      <c r="T15" s="9">
         <v>46153</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="U15" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="S15" s="11">
+      <c r="V15" s="11">
         <v>159.99</v>
       </c>
-      <c r="T15" s="3" t="s">
+      <c r="W15" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U15" s="9">
+      <c r="X15" s="9">
         <v>46150</v>
       </c>
-      <c r="V15" s="9" t="s">
+      <c r="Y15" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y15" s="2" t="s">
+      <c r="Z15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB15" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC15" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE15" s="26" t="s">
+      <c r="AC15" s="4"/>
+      <c r="AD15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH15" s="26" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="60" customHeight="1">
+    <row r="16" spans="1:34" ht="60" customHeight="1">
       <c r="A16" s="6" t="str">
         <f>_xlfn.CONCAT(B16, " ", C16)</f>
         <v xml:space="preserve"> Joy for All Companion Pet Cat Tuxedo</v>
@@ -2894,74 +3058,83 @@
       <c r="H16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="I16" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K16" s="3">
+        <v>5</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="M16" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="N16" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="L16" s="3" t="s">
+      <c r="O16" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="P16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="N16" s="16">
+      <c r="Q16" s="16">
         <v>4.5</v>
       </c>
-      <c r="O16" s="19">
+      <c r="R16" s="19">
         <v>11640</v>
       </c>
-      <c r="P16" s="3" t="s">
+      <c r="S16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q16" s="9">
+      <c r="T16" s="9">
         <v>46150</v>
       </c>
-      <c r="R16" s="3" t="s">
+      <c r="U16" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="S16" s="11">
+      <c r="V16" s="11">
         <v>159.99</v>
       </c>
-      <c r="T16" s="3" t="s">
+      <c r="W16" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U16" s="9">
+      <c r="X16" s="9">
         <v>46150</v>
       </c>
-      <c r="V16" s="9" t="s">
+      <c r="Y16" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y16" s="3" t="s">
+      <c r="Z16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB16" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE16" s="31" t="s">
+      <c r="AC16" s="4"/>
+      <c r="AD16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH16" s="31" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="17" spans="1:31" ht="60">
+    <row r="17" spans="1:34" ht="60">
       <c r="A17" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(B17, " ", C17)</f>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Freckled</v>
       </c>
       <c r="B17" s="3" t="s">
@@ -2985,74 +3158,83 @@
       <c r="H17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="I17" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K17" s="3">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="M17" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="N17" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L17" s="3" t="s">
+      <c r="O17" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="P17" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="N17" s="16">
+      <c r="Q17" s="16">
         <v>4.3</v>
       </c>
-      <c r="O17" s="19">
+      <c r="R17" s="19">
         <v>5163</v>
       </c>
-      <c r="P17" s="3" t="s">
+      <c r="S17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="T17" s="9">
         <v>46150</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="U17" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="S17" s="11">
+      <c r="V17" s="11">
         <v>179</v>
       </c>
-      <c r="T17" s="3" t="s">
+      <c r="W17" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U17" s="9">
+      <c r="X17" s="9">
         <v>46150</v>
       </c>
-      <c r="V17" s="9" t="s">
+      <c r="Y17" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y17" s="2" t="s">
+      <c r="Z17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB17" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE17" s="26" t="s">
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH17" s="26" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="18" spans="1:31" ht="60">
+    <row r="18" spans="1:34" ht="60">
       <c r="A18" s="6" t="str">
-        <f t="shared" si="1"/>
+        <f>_xlfn.CONCAT(B18, " ", C18)</f>
         <v xml:space="preserve"> Joy for All Companion Pet Pup Golden</v>
       </c>
       <c r="B18" s="3" t="s">
@@ -3076,90 +3258,99 @@
       <c r="H18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="I18" s="3" t="s">
+      <c r="I18" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K18" s="3">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="M18" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="N18" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="L18" s="3" t="s">
+      <c r="O18" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="P18" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="N18" s="16">
+      <c r="Q18" s="16">
         <v>4.3</v>
       </c>
-      <c r="O18" s="19">
+      <c r="R18" s="19">
         <v>5164</v>
       </c>
-      <c r="P18" s="3" t="s">
+      <c r="S18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q18" s="9">
+      <c r="T18" s="9">
         <v>46153</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="U18" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="S18" s="11">
+      <c r="V18" s="11">
         <v>179</v>
       </c>
-      <c r="T18" s="3" t="s">
+      <c r="W18" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U18" s="9">
+      <c r="X18" s="9">
         <v>46150</v>
       </c>
-      <c r="V18" s="9" t="s">
+      <c r="Y18" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y18" s="2" t="s">
+      <c r="Z18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA18" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB18" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE18" s="26" t="s">
+      <c r="AC18" s="4"/>
+      <c r="AD18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH18" s="26" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="19" spans="1:31" ht="74.25" customHeight="1">
+    <row r="19" spans="1:34" ht="150">
       <c r="A19" s="6" t="str">
         <f>_xlfn.CONCAT(B19, " ", C19)</f>
-        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
+        <v>Furby DJ Furby</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>63</v>
+        <v>50</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>21</v>
@@ -3167,89 +3358,98 @@
       <c r="H19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I19" s="3" t="s">
-        <v>143</v>
+      <c r="I19" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>144</v>
+        <v>298</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="N19" s="16">
-        <v>3</v>
-      </c>
-      <c r="O19" s="19">
+        <v>174</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>4.8</v>
+      </c>
+      <c r="R19" s="19">
+        <v>772</v>
+      </c>
+      <c r="S19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P19" s="3" t="s">
+      <c r="T19" s="9">
+        <v>46150</v>
+      </c>
+      <c r="U19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="V19" s="11">
+        <v>50.11</v>
+      </c>
+      <c r="W19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q19" s="9">
-        <v>46151</v>
-      </c>
-      <c r="R19" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="S19" s="11">
-        <v>25.99</v>
-      </c>
-      <c r="T19" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="U19" s="9">
-        <v>46151</v>
-      </c>
-      <c r="V19" s="9" t="s">
+      <c r="X19" s="9">
+        <v>46150</v>
+      </c>
+      <c r="Y19" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="W19" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y19" s="2" t="s">
-        <v>232</v>
+      <c r="Z19" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC19" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE19" s="24" t="s">
-        <v>279</v>
+        <v>26</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="AD19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF19" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="AH19" s="24" t="s">
+        <v>277</v>
       </c>
     </row>
-    <row r="20" spans="1:31" ht="150">
+    <row r="20" spans="1:34" ht="165">
       <c r="A20" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>Furby DJ Furby</v>
+        <f>_xlfn.CONCAT(B20, " ", C20)</f>
+        <v>Loona Robot Pet Dog</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>288</v>
+        <v>48</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G20" s="3" t="s">
         <v>21</v>
@@ -3257,170 +3457,185 @@
       <c r="H20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>175</v>
+      <c r="I20" s="33" t="s">
+        <v>297</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>173</v>
+        <v>299</v>
+      </c>
+      <c r="K20" s="3">
+        <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="N20" s="16">
-        <v>4.8</v>
-      </c>
-      <c r="O20" s="19">
-        <v>772</v>
-      </c>
-      <c r="P20" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="Q20" s="16">
+        <v>4.2</v>
+      </c>
+      <c r="R20" s="19">
+        <v>1199</v>
+      </c>
+      <c r="S20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q20" s="9">
+      <c r="T20" s="9">
         <v>46150</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="S20" s="11">
-        <v>50.11</v>
-      </c>
-      <c r="T20" s="3" t="s">
+      <c r="U20" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="V20" s="11">
+        <v>499</v>
+      </c>
+      <c r="W20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U20" s="9">
+      <c r="X20" s="9">
         <v>46150</v>
       </c>
-      <c r="V20" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y20" s="2" t="s">
-        <v>242</v>
+      <c r="Y20" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z20" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB20" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB20" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="AD20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE20" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF20" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="AE20" s="24" t="s">
-        <v>277</v>
+      <c r="AH20" s="24" t="s">
+        <v>280</v>
       </c>
     </row>
-    <row r="21" spans="1:31" ht="165">
+    <row r="21" spans="1:34" ht="60">
       <c r="A21" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>Loona Robot Pet Dog</v>
+        <f>_xlfn.CONCAT(B21, " ", C21)</f>
+        <v>Perfect Petzzz Grey Tabby Cat</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>63</v>
+        <v>39</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>60</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>168</v>
+        <v>23</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>294</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>171</v>
+        <v>80</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="N21" s="16">
-        <v>4.2</v>
-      </c>
-      <c r="O21" s="19">
-        <v>1199</v>
+        <v>272</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>153</v>
       </c>
       <c r="P21" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q21" s="16">
+        <v>4.3</v>
+      </c>
+      <c r="R21" s="19">
+        <v>848</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q21" s="9">
+      <c r="T21" s="9">
         <v>46150</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="S21" s="11">
-        <v>499</v>
-      </c>
-      <c r="T21" s="3" t="s">
+      <c r="U21" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="V21" s="11">
+        <v>44.45</v>
+      </c>
+      <c r="W21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U21" s="9">
+      <c r="X21" s="9">
         <v>46150</v>
       </c>
-      <c r="V21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="W21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y21" s="2" t="s">
-        <v>240</v>
+      <c r="Y21" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z21" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AB21" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="AE21" s="24" t="s">
-        <v>280</v>
+        <v>27</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="AD21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH21" s="24" t="s">
+        <v>281</v>
       </c>
     </row>
-    <row r="22" spans="1:31" ht="60">
+    <row r="22" spans="1:34" ht="60" customHeight="1">
       <c r="A22" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>Perfect Petzzz Grey Tabby Cat</v>
+        <f>_xlfn.CONCAT(B22, " ", C22)</f>
+        <v>Perfect Petzzz Original Border Collie</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>191</v>
+        <v>156</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>17</v>
@@ -3434,77 +3649,86 @@
       <c r="H22" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>272</v>
+      <c r="I22" s="33" t="s">
+        <v>294</v>
       </c>
       <c r="J22" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K22" s="3">
+        <v>1</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N22" s="16">
+      <c r="P22" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="Q22" s="16">
         <v>4.3</v>
       </c>
-      <c r="O22" s="19">
-        <v>848</v>
-      </c>
-      <c r="P22" s="3" t="s">
+      <c r="R22" s="19">
+        <v>403</v>
+      </c>
+      <c r="S22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q22" s="9">
+      <c r="T22" s="9">
         <v>46150</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="S22" s="11">
+      <c r="U22" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="V22" s="11">
         <v>44.45</v>
       </c>
-      <c r="T22" s="3" t="s">
+      <c r="W22" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U22" s="9">
+      <c r="X22" s="9">
         <v>46150</v>
       </c>
-      <c r="V22" s="9" t="s">
+      <c r="Y22" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y22" s="2" t="s">
-        <v>243</v>
+      <c r="Z22" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE22" s="24" t="s">
-        <v>281</v>
+      <c r="AB22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH22" s="24" t="s">
+        <v>282</v>
       </c>
     </row>
-    <row r="23" spans="1:31" ht="60" customHeight="1">
+    <row r="23" spans="1:34" ht="60" customHeight="1">
       <c r="A23" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Border Collie</v>
+        <f>_xlfn.CONCAT(B23, " ", C23)</f>
+        <v>Perfect Petzzz Original Chocolate Lab</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>63</v>
@@ -3521,80 +3745,89 @@
       <c r="H23" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>155</v>
+      <c r="I23" s="33" t="s">
+        <v>294</v>
       </c>
       <c r="J23" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K23" s="3">
+        <v>1</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="N23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="O23" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="M23" s="3" t="s">
+      <c r="P23" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="N23" s="16">
+      <c r="Q23" s="16">
         <v>4.3</v>
       </c>
-      <c r="O23" s="19">
-        <v>403</v>
-      </c>
-      <c r="P23" s="3" t="s">
+      <c r="R23" s="19">
+        <v>553</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q23" s="9">
+      <c r="T23" s="9">
         <v>46150</v>
       </c>
-      <c r="R23" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="S23" s="11">
+      <c r="U23" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="V23" s="11">
         <v>44.45</v>
       </c>
-      <c r="T23" s="3" t="s">
+      <c r="W23" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U23" s="9">
+      <c r="X23" s="9">
         <v>46150</v>
       </c>
-      <c r="V23" s="9" t="s">
+      <c r="Y23" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y23" s="2" t="s">
-        <v>43</v>
+      <c r="Z23" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA23" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE23" s="24" t="s">
-        <v>282</v>
+      <c r="AB23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="AD23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH23" s="24" t="s">
+        <v>283</v>
       </c>
     </row>
-    <row r="24" spans="1:31" ht="60" customHeight="1">
+    <row r="24" spans="1:34" ht="60" customHeight="1">
       <c r="A24" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Chocolate Lab</v>
+        <f>_xlfn.CONCAT(B24, " ", C24)</f>
+        <v>Perfect Petzzz Original Plush White Cat</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>17</v>
@@ -3608,77 +3841,86 @@
       <c r="H24" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>154</v>
+      <c r="I24" s="33" t="s">
+        <v>294</v>
       </c>
       <c r="J24" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K24" s="3">
+        <v>1</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="N24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="O24" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="N24" s="16">
-        <v>4.3</v>
-      </c>
-      <c r="O24" s="19">
-        <v>553</v>
-      </c>
       <c r="P24" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q24" s="16">
+        <v>4</v>
+      </c>
+      <c r="R24" s="19">
+        <v>54</v>
+      </c>
+      <c r="S24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q24" s="9">
+      <c r="T24" s="9">
         <v>46150</v>
       </c>
-      <c r="R24" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="S24" s="11">
-        <v>44.45</v>
-      </c>
-      <c r="T24" s="3" t="s">
+      <c r="U24" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="V24" s="11">
+        <v>53.9</v>
+      </c>
+      <c r="W24" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U24" s="9">
+      <c r="X24" s="9">
         <v>46150</v>
       </c>
-      <c r="V24" s="9" t="s">
+      <c r="Y24" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y24" s="2" t="s">
-        <v>44</v>
+      <c r="Z24" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE24" s="24" t="s">
-        <v>283</v>
+      <c r="AB24" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AD24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH24" s="24" t="s">
+        <v>284</v>
       </c>
     </row>
-    <row r="25" spans="1:31" ht="60" customHeight="1">
+    <row r="25" spans="1:34" ht="27.75" customHeight="1">
       <c r="A25" s="6" t="str">
         <f>_xlfn.CONCAT(B25, " ", C25)</f>
-        <v>Perfect Petzzz Original Plush White Cat</v>
+        <v>Perfect Petzzz Original Siamese Cat</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>60</v>
@@ -3695,335 +3937,275 @@
       <c r="H25" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>161</v>
+      <c r="I25" s="33" t="s">
+        <v>294</v>
       </c>
       <c r="J25" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K25" s="3">
+        <v>1</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="M25" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="N25" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="L25" s="3" t="s">
+      <c r="O25" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="M25" s="3" t="s">
+      <c r="P25" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="N25" s="16">
-        <v>4</v>
-      </c>
-      <c r="O25" s="19">
-        <v>54</v>
-      </c>
-      <c r="P25" s="3" t="s">
+      <c r="Q25" s="16">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R25" s="19">
+        <v>16</v>
+      </c>
+      <c r="S25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q25" s="9">
+      <c r="T25" s="9">
         <v>46150</v>
       </c>
-      <c r="R25" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="S25" s="11">
+      <c r="U25" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="V25" s="11">
         <v>53.9</v>
       </c>
-      <c r="T25" s="3" t="s">
+      <c r="W25" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="U25" s="9">
+      <c r="X25" s="9">
         <v>46150</v>
       </c>
-      <c r="V25" s="9" t="s">
+      <c r="Y25" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="W25" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y25" s="2" t="s">
-        <v>55</v>
+      <c r="Z25" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="AB25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE25" s="24" t="s">
-        <v>284</v>
+      <c r="AB25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH25" s="24" t="s">
+        <v>285</v>
       </c>
     </row>
-    <row r="26" spans="1:31" ht="27.75" customHeight="1">
+    <row r="26" spans="1:34" ht="150">
       <c r="A26" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>Perfect Petzzz Original Siamese Cat</v>
+        <f>_xlfn.CONCAT(B26, " ", C26)</f>
+        <v>Ropet KAMOMO</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>60</v>
+        <v>28</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>290</v>
       </c>
       <c r="G26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>162</v>
+      <c r="I26" s="33" t="s">
+        <v>294</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>160</v>
+        <v>80</v>
+      </c>
+      <c r="K26" s="3">
+        <v>4</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="N26" s="16">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="O26" s="19">
-        <v>16</v>
+        <v>151</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>184</v>
       </c>
       <c r="P26" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q26" s="16">
+        <v>4.3</v>
+      </c>
+      <c r="R26" s="19">
+        <v>17</v>
+      </c>
+      <c r="S26" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q26" s="9">
-        <v>46150</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="S26" s="11">
-        <v>53.9</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="U26" s="9">
-        <v>46150</v>
-      </c>
-      <c r="V26" s="9" t="s">
-        <v>85</v>
+      <c r="T26" s="9">
+        <v>46152</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="V26" s="11">
+        <v>349</v>
       </c>
       <c r="W26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y26" s="2" t="s">
-        <v>45</v>
+        <v>265</v>
+      </c>
+      <c r="X26" s="9">
+        <v>46163</v>
+      </c>
+      <c r="Y26" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AB26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AE26" s="24" t="s">
-        <v>285</v>
+        <v>26</v>
+      </c>
+      <c r="AB26" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="AD26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH26" s="24" t="s">
+        <v>286</v>
       </c>
     </row>
-    <row r="27" spans="1:31" ht="150">
+    <row r="27" spans="1:34" ht="165">
       <c r="A27" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>Ropet KAMOMO</v>
+        <f>_xlfn.CONCAT(B27, " ", C27)</f>
+        <v>Ruko 18011 Smart Robot Dog</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>61</v>
+        <v>46</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>63</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>147</v>
+      <c r="I27" s="34">
+        <v>46089</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>148</v>
+        <v>80</v>
+      </c>
+      <c r="K27" s="3">
+        <v>2</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="N27" s="16">
-        <v>4.3</v>
-      </c>
-      <c r="O27" s="19">
-        <v>17</v>
+        <v>164</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>166</v>
       </c>
       <c r="P27" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q27" s="16">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="R27" s="19">
+        <v>283</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="Q27" s="9">
-        <v>46152</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="S27" s="11">
-        <v>349</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="U27" s="9">
-        <v>46163</v>
-      </c>
-      <c r="V27" s="9" t="s">
-        <v>25</v>
+      <c r="T27" s="9">
+        <v>46150</v>
+      </c>
+      <c r="U27" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="V27" s="11">
+        <v>69.989999999999995</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y27" s="2" t="s">
-        <v>241</v>
+        <v>80</v>
+      </c>
+      <c r="X27" s="9">
+        <v>46150</v>
+      </c>
+      <c r="Y27" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z27" s="3" t="s">
+        <v>26</v>
       </c>
       <c r="AA27" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE27" s="24" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" ht="165">
-      <c r="A28" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v>Ruko 18011 Smart Robot Dog</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="N28" s="16">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="O28" s="19">
-        <v>283</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q28" s="9">
-        <v>46150</v>
-      </c>
-      <c r="R28" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="S28" s="11">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="T28" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="U28" s="9">
-        <v>46150</v>
-      </c>
-      <c r="V28" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="W28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="X28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="Y28" s="2" t="s">
+      <c r="AB27" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="AA28" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="AE28" s="24" t="s">
+      <c r="AD27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF27" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="AH27" s="24" t="s">
         <v>287</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE28" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AE28">
-      <sortCondition ref="A1:A28"/>
+  <autoFilter ref="A1:AH27" xr:uid="{FC813FA4-AD85-4CAC-9680-9CA13E0F2B1E}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AH27">
+      <sortCondition ref="A1:A27"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="10" type="noConversion"/>
@@ -4037,13 +4219,13 @@
           <x14:formula1>
             <xm:f>Lists!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>V1:V1048576</xm:sqref>
+          <xm:sqref>Y1:Y1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37BE27F9-E75E-4C54-9192-7DED9B8091B0}">
           <x14:formula1>
             <xm:f>Lists!$A$7:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>X1:X1048576</xm:sqref>
+          <xm:sqref>AA1:AA1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FE3F9960-CC34-4E23-8422-16257A51BC9B}">
           <x14:formula1>
@@ -4128,10 +4310,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3587DF7-27DE-4C49-A0D7-210E14A8420B}">
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:30" s="3" customFormat="1" ht="409.5">
+    <row r="1" spans="1:33" s="3" customFormat="1" ht="409.5">
       <c r="A1" s="3" t="str">
         <f>_xlfn.CONCAT(B1, " ", C1)</f>
         <v xml:space="preserve"> Enabot EBO Max FamilyBot </v>
@@ -4213,7 +4395,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="2" spans="1:30" s="3" customFormat="1" ht="210">
+    <row r="2" spans="1:33" s="3" customFormat="1" ht="210">
       <c r="A2" s="3" t="s">
         <v>252</v>
       </c>
@@ -4267,7 +4449,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="12" customFormat="1" ht="75">
+    <row r="3" spans="1:33" s="12" customFormat="1" ht="75">
       <c r="A3" s="3" t="str">
         <f>_xlfn.CONCAT(B3, " ", C3)</f>
         <v xml:space="preserve"> Elephant Robotics MarsCat </v>
@@ -4316,7 +4498,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="12" customFormat="1" ht="15" customHeight="1">
+    <row r="4" spans="1:33" s="12" customFormat="1" ht="15" customHeight="1">
       <c r="A4" s="3" t="str">
         <f>_xlfn.CONCAT(B4, " ", C4)</f>
         <v xml:space="preserve"> Elephant Robotics metaCat </v>
@@ -4368,7 +4550,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="12" customFormat="1" ht="405">
+    <row r="5" spans="1:33" s="12" customFormat="1" ht="405">
       <c r="A5" s="3" t="str">
         <f>_xlfn.CONCAT(B5, " ", C5)</f>
         <v xml:space="preserve"> Elephant Robotics metaDog </v>
@@ -4420,7 +4602,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="12" customFormat="1" ht="360">
+    <row r="6" spans="1:33" s="12" customFormat="1" ht="360">
       <c r="A6" s="3" t="str">
         <f>_xlfn.CONCAT(B6, " ", C6)</f>
         <v xml:space="preserve"> Elephant Robotics metaPanda </v>
@@ -4472,22 +4654,120 @@
         <v>27</v>
       </c>
     </row>
+    <row r="7" spans="1:33" s="3" customFormat="1" ht="74.25" customHeight="1">
+      <c r="A7" s="6" t="str">
+        <f>_xlfn.CONCAT(B7, " ", C7)</f>
+        <v xml:space="preserve"> Wuffy Wuffy Robot Puppy </v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="33"/>
+      <c r="K7" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="P7" s="16">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="19">
+        <v>80</v>
+      </c>
+      <c r="R7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="S7" s="9">
+        <v>46151</v>
+      </c>
+      <c r="T7" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="U7" s="11">
+        <v>25.99</v>
+      </c>
+      <c r="V7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="W7" s="9">
+        <v>46151</v>
+      </c>
+      <c r="X7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y7" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG7" s="24" t="s">
+        <v>279</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{33C992CF-22D4-4E94-80E1-2C06CE97D7D6}">
           <x14:formula1>
             <xm:f>Lists!$A$1:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>U1:U6</xm:sqref>
+          <xm:sqref>U1:U6 X7</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{37BE27F9-E75E-4C54-9192-7DED9B8091B0}">
           <x14:formula1>
             <xm:f>Lists!$A$7:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>W1:W2</xm:sqref>
+          <xm:sqref>W1:W2 Z7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FE3F9960-CC34-4E23-8422-16257A51BC9B}">
+          <x14:formula1>
+            <xm:f>Lists!$A$12:$A$13</xm:f>
+          </x14:formula1>
+          <xm:sqref>F7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504B2F51-97F8-47EF-A42D-D69EF1A6B428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E699FE1F-CE6A-40E6-B516-3869D85584D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="801" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="314">
   <si>
     <t>Manufacturer and Product</t>
   </si>
@@ -978,9 +978,6 @@
   </si>
   <si>
     <t>https://amzn.to/3TIQSV2</t>
-  </si>
-  <si>
-    <t>349,00</t>
   </si>
   <si>
     <t>4..5</t>
@@ -993,7 +990,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0.00;[Red]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00;[Red]#,##0.00"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -1213,10 +1210,10 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="3" applyNumberFormat="1" applyAlignment="1">
@@ -4102,8 +4099,8 @@
       <c r="V26" s="22" t="s">
         <v>265</v>
       </c>
-      <c r="W26" s="34" t="s">
-        <v>313</v>
+      <c r="W26" s="34">
+        <v>349</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>263</v>
@@ -4186,7 +4183,7 @@
         <v>275</v>
       </c>
       <c r="R27" s="15" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="S27" s="18">
         <v>346</v>

--- a/Documentation/Product Matrix.xlsx
+++ b/Documentation/Product Matrix.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tim Thomasson\Interactive-Pet-Marketplace\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E699FE1F-CE6A-40E6-B516-3869D85584D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F386B124-F6D7-4378-BB61-14C525D15CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Matrix" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="313">
   <si>
     <t>Manufacturer and Product</t>
   </si>
@@ -978,9 +978,6 @@
   </si>
   <si>
     <t>https://amzn.to/3TIQSV2</t>
-  </si>
-  <si>
-    <t>4..5</t>
   </si>
 </sst>
 </file>
@@ -4155,8 +4152,8 @@
       <c r="H27" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="I27" s="31">
-        <v>46089</v>
+      <c r="I27" s="31" t="s">
+        <v>205</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>76</v>
@@ -4182,8 +4179,8 @@
       <c r="Q27" s="22" t="s">
         <v>275</v>
       </c>
-      <c r="R27" s="15" t="s">
-        <v>313</v>
+      <c r="R27" s="15">
+        <v>4.5</v>
       </c>
       <c r="S27" s="18">
         <v>346</v>
